--- a/data/spain/p6_deployment/data_preparation/df_selected_nan.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_selected_nan.xlsx
@@ -1261,28 +1261,28 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>-1.783726959063851</v>
+        <v>-1.783630500779962</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>-2.221894966058168</v>
+        <v>-2.204178096812079</v>
       </c>
       <c r="AB8" t="n">
-        <v>-3.556801636502492</v>
+        <v>-3.546754554571267</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>-1.884083062261185</v>
+        <v>-1.922538783459844</v>
       </c>
       <c r="AE8" t="n">
-        <v>-0.05101724504959215</v>
+        <v>0.01642599314148536</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.1256523541628751</v>
+        <v>0.1735270731669427</v>
       </c>
     </row>
     <row r="9">

--- a/data/spain/p6_deployment/data_preparation/df_selected_nan.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_selected_nan.xlsx
@@ -661,28 +661,28 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0.8793825739938163</v>
+        <v>-0.9403909451778998</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>-1.728333427653596</v>
+        <v>-1.740677530360975</v>
       </c>
       <c r="AB2" t="n">
-        <v>-2.772792663759897</v>
+        <v>-2.816831953859889</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>-1.179967850909398</v>
+        <v>-1.187146271545754</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.3754595479068735</v>
+        <v>0.3938154345406206</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.5924742172463189</v>
+        <v>0.5260668824132689</v>
       </c>
     </row>
     <row r="3">
@@ -761,28 +761,28 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.910742552584788</v>
+        <v>1.922409289296505</v>
       </c>
       <c r="Z3" t="n">
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.122412397300717</v>
+        <v>3.120856364125876</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.823306420216245</v>
+        <v>5.826307707975066</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.336542661990114</v>
+        <v>2.33637306595699</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0.268628646594458</v>
+        <v>-0.2568938792882714</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.7360289509449764</v>
+        <v>-0.7336108628410466</v>
       </c>
     </row>
     <row r="4">
@@ -961,28 +961,28 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.3405176435346139</v>
+        <v>-0.3174162503151651</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.1905440461747585</v>
+        <v>0.2168252937890907</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.04852790190720657</v>
+        <v>-0.0445830486428026</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.154028811858041</v>
+        <v>0.1591520457510329</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.203019874194122</v>
+        <v>0.2142763982083906</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.4384178969825435</v>
+        <v>-0.3932572619854823</v>
       </c>
     </row>
     <row r="6">
@@ -1061,28 +1061,28 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>-1.90244514006844</v>
+        <v>-1.914111876780157</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>-3.118377882890405</v>
+        <v>-3.116821849715564</v>
       </c>
       <c r="AB6" t="n">
-        <v>-5.81313243484263</v>
+        <v>-5.816133722601451</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>-2.324938614718639</v>
+        <v>-2.324769018685514</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.2659117096392433</v>
+        <v>0.2541769423330567</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.7606756626308502</v>
+        <v>0.7582575745269202</v>
       </c>
     </row>
     <row r="7">
@@ -1361,7 +1361,7 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.005451210704542</v>
+        <v>0.9903002405992983</v>
       </c>
       <c r="Z9" t="n">
         <v>0</v>
@@ -1370,19 +1370,19 @@
         <v>0.08675415580748531</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.6254660620133495</v>
+        <v>0.6260498160425421</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.9190666570749939</v>
+        <v>0.9146087688417647</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0.141962606387194</v>
+        <v>-0.1888055859225821</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.1984516976288954</v>
+        <v>-0.2336115217047379</v>
       </c>
     </row>
     <row r="10">
@@ -1761,28 +1761,28 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.7946923478262913</v>
+        <v>0.7336839766422076</v>
       </c>
       <c r="Z13" t="n">
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.4200523063345913</v>
+        <v>0.4077082036272121</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.8013586140150831</v>
+        <v>0.7573193239150908</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.5477467382570875</v>
+        <v>0.5405683176207317</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0.8854826934661758</v>
+        <v>-0.8671268068324287</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.2520987607142808</v>
+        <v>0.1856914258812308</v>
       </c>
     </row>
   </sheetData>

--- a/data/spain/p6_deployment/data_preparation/df_selected_nan.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_selected_nan.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF13"/>
+  <dimension ref="A1:AF26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -661,28 +661,28 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0.8793825739938163</v>
+        <v>-0.9403909451778998</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>-1.728333427653596</v>
+        <v>-1.740677530360975</v>
       </c>
       <c r="AB2" t="n">
-        <v>-2.772792663759897</v>
+        <v>-2.816831953859889</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>-1.179967850909398</v>
+        <v>-1.187146271545754</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.3754595479068735</v>
+        <v>0.3938154345406206</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.5924742172463189</v>
+        <v>0.5260668824132689</v>
       </c>
     </row>
     <row r="3">
@@ -761,62 +761,62 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.910742552584788</v>
+        <v>1.922409289296505</v>
       </c>
       <c r="Z3" t="n">
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.122412397300717</v>
+        <v>3.120856364125876</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.823306420216245</v>
+        <v>5.826307707975066</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.336542661990114</v>
+        <v>2.33637306595699</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0.268628646594458</v>
+        <v>-0.2568938792882714</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.7360289509449764</v>
+        <v>-0.7336108628410466</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>E1Xs9lu2</t>
+          <t>8CpDVHAM</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.116923437005787</v>
+        <v>-1.177501316934839</v>
       </c>
       <c r="C4" t="n">
-        <v>1.008351687704268</v>
+        <v>-0.05263338288914304</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.2786545907204963</v>
+        <v>-1.549162570724393</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.8430651861914329</v>
+        <v>0.6542183108058229</v>
       </c>
       <c r="F4" t="n">
         <v>-0.3161939140908171</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.09113424607748329</v>
+        <v>-1.880828363188178</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.3927305149719172</v>
+        <v>0.895351072412264</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1892768712128023</v>
+        <v>-1.633725745171589</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.9950335157235638</v>
+        <v>1.134002875826239</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -861,62 +861,62 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0.4661695781472107</v>
+        <v>-1.046272644059392</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>-0.4651151130289514</v>
+        <v>-1.668671091240665</v>
       </c>
       <c r="AB4" t="n">
-        <v>-1.079639703620966</v>
+        <v>-3.564108955180584</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0.5213863423788073</v>
+        <v>-2.132167547863206</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.7171475541134533</v>
+        <v>-0.06977751774925442</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.3462593151923172</v>
+        <v>1.899962667930923</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>ITdtTrn2</t>
+          <t>4KmdZaBc</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.930401304312008</v>
+        <v>-1.427802199182907</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.2137956720932055</v>
+        <v>0.8740497800342159</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.3712081521777338</v>
+        <v>-1.321985647147537</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8157956665968937</v>
+        <v>0.6542183108058229</v>
       </c>
       <c r="F5" t="n">
         <v>-0.3161939140908171</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.7227909932930227</v>
+        <v>-1.143895491436716</v>
       </c>
       <c r="H5" t="n">
         <v>-0.8220910440999777</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3715771328512414</v>
+        <v>-1.269125221894711</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4243240786429714</v>
+        <v>-0.2853547185402961</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -961,62 +961,62 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.3405176435346139</v>
+        <v>-0.2348614860309448</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.1905440461747585</v>
+        <v>-0.9177269575195536</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.04852790190720657</v>
+        <v>-0.3977196124865265</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.154028811858041</v>
+        <v>-0.7355372783842571</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.203019874194122</v>
+        <v>-0.7010869176445007</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.4384178969825435</v>
+        <v>0.6463028341325076</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>M3h3GWnS</t>
+          <t>hpMqQeYq</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-1.427802199182907</v>
+        <v>1.116923437005787</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2428308139849714</v>
+        <v>-1.167339216550575</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.321985647147537</v>
+        <v>-0.2786545907204963</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2556608331878484</v>
+        <v>0.5572718973311804</v>
       </c>
       <c r="F6" t="n">
         <v>-0.3161939140908171</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.670276114116332</v>
+        <v>0.01414187845843995</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.680812102356098</v>
+        <v>0.895351072412264</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.269125221894711</v>
+        <v>0.006976609574363205</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.9950335157235638</v>
+        <v>1.843681673009507</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -1061,59 +1061,59 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>-1.90244514006844</v>
+        <v>0.6223631565632936</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>-3.118377882890405</v>
+        <v>0.8157515099381268</v>
       </c>
       <c r="AB6" t="n">
-        <v>-5.81313243484263</v>
+        <v>0.2596761647150918</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>-2.324938614718639</v>
+        <v>0.3977030929319241</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.2659117096392433</v>
+        <v>0.9362956489452896</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.7606756626308502</v>
+        <v>0.9305092990726417</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Eax2EqHs</t>
+          <t>ChPK4l66</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9709145890277466</v>
+        <v>1.012631402735758</v>
       </c>
       <c r="C7" t="n">
-        <v>-1.18076940731758</v>
+        <v>1.223234739976351</v>
       </c>
       <c r="D7" t="n">
         <v>-0.446933793370019</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.6384005355227432</v>
+        <v>-0.9184679522272658</v>
       </c>
       <c r="F7" t="n">
         <v>-0.3161939140908171</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2246941275302864</v>
+        <v>0.3299702520662097</v>
       </c>
       <c r="H7" t="n">
-        <v>1.324711601540324</v>
+        <v>0.895351072412264</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7361776561281197</v>
+        <v>0.006976609574363205</v>
       </c>
       <c r="J7" t="n">
         <v>1.134002875826239</v>
@@ -1161,62 +1161,62 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.2108863063377306</v>
+        <v>0.7604703125814853</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.4833357263605067</v>
+        <v>1.410876497063821</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.141700141060192</v>
+        <v>0.4179709941543021</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.067308411068589</v>
+        <v>0.1470819966804816</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.08546743624035702</v>
+        <v>0.7153822161533081</v>
       </c>
       <c r="AF7" t="n">
-        <v>-1.572492244283348</v>
+        <v>1.065489001404136</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>KbKTWiX8</t>
+          <t>MNr3HRkC</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-1.031492468956799</v>
+        <v>0.887480961611724</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.05263338288914304</v>
+        <v>1.639570653753512</v>
       </c>
       <c r="D8" t="n">
-        <v>1.858491282928442</v>
+        <v>0.3776342996126424</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6542183108058229</v>
+        <v>0.2556608331878484</v>
       </c>
       <c r="F8" t="n">
         <v>-0.3161939140908171</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.617761234939641</v>
+        <v>-0.406962619685253</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.110172631484159</v>
+        <v>-0.3927305149719172</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.180626530086907</v>
+        <v>-0.9045246986178325</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.704712312906831</v>
+        <v>-0.2853547185402961</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1261,62 +1261,62 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>-1.783630500779962</v>
+        <v>-1.193666876574569</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>-2.204178096812079</v>
+        <v>-1.829707651421767</v>
       </c>
       <c r="AB8" t="n">
-        <v>-3.546754554571267</v>
+        <v>-0.7226542144563018</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>-1.922538783459844</v>
+        <v>-0.5730812288106953</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.01642599314148536</v>
+        <v>-0.6549638222694014</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.1735270731669427</v>
+        <v>-1.597732234095453</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>ruUIA1G6</t>
+          <t>hA5zaJZp</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.9480588415407764</v>
+        <v>-0.3118774324936029</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.4018183428312783</v>
+        <v>-0.5898410135693511</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2786545907204963</v>
+        <v>-0.000993906348783775</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1048553011161823</v>
+        <v>1.203581320495464</v>
       </c>
       <c r="F9" t="n">
         <v>-0.3161939140908171</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2246941275302864</v>
+        <v>0.01414187845843995</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>-0.3927305149719172</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3715771328512414</v>
+        <v>0.1892768712128023</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>0.4243240786429714</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1361,62 +1361,62 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.005451210704542</v>
+        <v>-1.028752415741359</v>
       </c>
       <c r="Z9" t="n">
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.08675415580748531</v>
+        <v>-0.2273248469884925</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.6254660620133495</v>
+        <v>-0.3932873498220891</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.9190666570749939</v>
+        <v>-0.5788908884223708</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0.141962606387194</v>
+        <v>0.9101734299838777</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.1984516976288954</v>
+        <v>0.09582423922648542</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>hnqZAAAk</t>
+          <t>IVonL9jm</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.6038951284496825</v>
+        <v>0.2721579594185562</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8740497800342159</v>
+        <v>1.961895232161637</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3776342996126424</v>
+        <v>1.219030312860256</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6542183108058229</v>
+        <v>-0.185983939307745</v>
       </c>
       <c r="F10" t="n">
         <v>-0.3161939140908171</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.406962619685253</v>
+        <v>2.751321116392444</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.8220910440999777</v>
+        <v>0.895351072412264</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.7222244369793933</v>
+        <v>2.74148053415095</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.9950335157235638</v>
+        <v>0.4243240786429714</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -1461,62 +1461,62 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0.5532584264083256</v>
+        <v>2.967594704534655</v>
       </c>
       <c r="Z10" t="n">
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>-0.8946401627174633</v>
+        <v>2.996844693921191</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0.6110433304391785</v>
+        <v>6.377847295808143</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>-1.039414740262161</v>
+        <v>2.801960239728194</v>
       </c>
       <c r="AE10" t="n">
-        <v>-1.319775082193424</v>
+        <v>0.0006103357647526598</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.3739574572626534</v>
+        <v>-0.2356922561954734</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>nDzACNof</t>
+          <t>OQqSjnv9</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-1.156642910080833</v>
+        <v>-0.1658685845155632</v>
       </c>
       <c r="C11" t="n">
-        <v>0.9412007338692419</v>
+        <v>0.9680611154032523</v>
       </c>
       <c r="D11" t="n">
-        <v>1.858491282928442</v>
+        <v>0.3608063793476901</v>
       </c>
       <c r="E11" t="n">
-        <v>1.203581320495464</v>
+        <v>-0.8430651861914329</v>
       </c>
       <c r="F11" t="n">
         <v>-0.3161939140908171</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2246941275302864</v>
+        <v>-0.7227909932930227</v>
       </c>
       <c r="H11" t="n">
-        <v>0.4659905432842035</v>
+        <v>-0.8220910440999777</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7361776561281197</v>
+        <v>-0.1753236520640759</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4243240786429714</v>
+        <v>-0.2853547185402961</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1561,62 +1561,62 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.6701977130784036</v>
+        <v>-0.9525621358972615</v>
       </c>
       <c r="Z11" t="n">
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.3448163449288419</v>
+        <v>-1.058801097724101</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.307831181908703</v>
+        <v>-1.397731498533852</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.2077737763464778</v>
+        <v>-1.3996009544896</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0.2683044833351454</v>
+        <v>-0.3433676456281605</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.6319492544233218</v>
+        <v>0.8870534694918899</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>QyafIhIF</t>
+          <t>YcAFQVSP</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.60709599807492</v>
+        <v>0.6684676896446642</v>
       </c>
       <c r="C12" t="n">
-        <v>1.223234739976351</v>
+        <v>-1.18076940731758</v>
       </c>
       <c r="D12" t="n">
-        <v>1.219030312860256</v>
+        <v>-1.321985647147537</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.9184679522272658</v>
+        <v>-0.6384005355227432</v>
       </c>
       <c r="F12" t="n">
         <v>-0.3161939140908171</v>
       </c>
       <c r="G12" t="n">
-        <v>0.8563508747458258</v>
+        <v>-0.406962619685253</v>
       </c>
       <c r="H12" t="n">
-        <v>0.4659905432842035</v>
+        <v>-0.8220910440999777</v>
       </c>
       <c r="I12" t="n">
-        <v>0.006976609574363205</v>
+        <v>-0.7222244369793933</v>
       </c>
       <c r="J12" t="n">
-        <v>0.4243240786429714</v>
+        <v>-0.9950335157235638</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1661,128 +1661,1428 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.2037041538834944</v>
+        <v>-0.6195048652443672</v>
       </c>
       <c r="Z12" t="n">
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.618935694999978</v>
+        <v>-0.4756801283372115</v>
       </c>
       <c r="AB12" t="n">
-        <v>-0.4963478562605419</v>
+        <v>0.0001316627792189005</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>-0.3950959388945559</v>
+        <v>0.4160570059681963</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.416785489970804</v>
+        <v>1.328002822167089</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.471668708881815</v>
+        <v>-1.534940499713011</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>hO0nKEm3</t>
+          <t>WhAFMMRi</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.6768995524387025</v>
+        <v>-0.03028893996452622</v>
       </c>
       <c r="C13" t="n">
-        <v>0.6457365369951275</v>
+        <v>-0.6435617766373719</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.549162570724393</v>
+        <v>-0.9349434810536349</v>
       </c>
       <c r="E13" t="n">
-        <v>1.278984086531297</v>
+        <v>-0.6384005355227432</v>
       </c>
       <c r="F13" t="n">
         <v>-0.3161939140908171</v>
       </c>
       <c r="G13" t="n">
+        <v>4.541015233503139</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.895351072412264</v>
+      </c>
+      <c r="I13" t="n">
+        <v>4.92908367381222</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.843681673009507</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.9486883576942479</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.744712044771286</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>2.827005939233504</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.19875031881723</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>-0.3965323714958353</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>-0.5014201707273952</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>vJDNK0d4</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>-0.9480588415407764</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-1.462803413424689</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-0.2786545907204963</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1.278984086531297</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-0.3161939140908171</v>
+      </c>
+      <c r="G14" t="n">
         <v>0.4352463766021329</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H14" t="n">
+        <v>0.03663001415614314</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.829979225958754</v>
+      </c>
+      <c r="J14" t="n">
+        <v>-0.2853547185402961</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>-0.3609978217776155</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-0.1195011535840721</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.01435175558099338</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.02603839490575143</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0.1040381479899793</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>-0.4224560151910434</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>QekfJmLa</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.8249057410497068</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1.102363023073304</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.9349434810536349</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-0.2613867053435781</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-0.3161939140908171</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.9616269992817491</v>
+      </c>
+      <c r="H15" t="n">
         <v>0.4659905432842035</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I15" t="n">
+        <v>1.465378702681876</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.134002875826239</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>-0.2021573344532501</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-0.02851655913523659</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.2477684952663456</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.2012557632126838</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0.05379059037744997</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>-0.866026214947702</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>8KIT2SzJ</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>-1.156642910080833</v>
+      </c>
+      <c r="C16" t="n">
+        <v>-1.019607118113518</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.858491282928442</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.5572718973311804</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-0.3161939140908171</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-1.143895491436716</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-1.251451573228038</v>
+      </c>
+      <c r="I16" t="n">
+        <v>-0.7222244369793933</v>
+      </c>
+      <c r="J16" t="n">
+        <v>-1.704712312906831</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.5422555622631005</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0.1853645217140456</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.128932726299195</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.2251983575732518</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>-0.1626808971729748</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0.4471956022181033</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>E1Xs9lu2</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1.116923437005787</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1.008351687704268</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-0.2786545907204963</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-0.8430651861914329</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-0.3161939140908171</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-0.09113424607748329</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-0.3927305149719172</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.1892768712128023</v>
+      </c>
+      <c r="J17" t="n">
+        <v>-0.9950335157235638</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>-0.4661695781472107</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-0.4651151130289514</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>-1.079639703620966</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>-0.5213863423788073</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0.7171475541134533</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0.3462593151923172</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>ITdtTrn2</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1.930401304312008</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-0.2137956720932055</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-0.3712081521777338</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.8157956665968937</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-0.3161939140908171</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-0.7227909932930227</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-0.8220910440999777</v>
+      </c>
+      <c r="I18" t="n">
         <v>0.3715771328512414</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J18" t="n">
+        <v>0.4243240786429714</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>-0.3174162503151651</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0.2168252937890907</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>-0.0445830486428026</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.1591520457510329</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0.2142763982083906</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>-0.3932572619854823</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>M3h3GWnS</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>-1.427802199182907</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.2428308139849714</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-1.321985647147537</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.2556608331878484</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-0.3161939140908171</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-1.670276114116332</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-1.680812102356098</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-1.269125221894711</v>
+      </c>
+      <c r="J19" t="n">
+        <v>-0.9950335157235638</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>-1.914111876780157</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-3.116821849715564</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>-5.816133722601451</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>-2.324769018685514</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0.2541769423330567</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0.7582575745269202</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Eax2EqHs</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.9709145890277466</v>
+      </c>
+      <c r="C20" t="n">
+        <v>-1.18076940731758</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-0.446933793370019</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-0.6384005355227432</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-0.3161939140908171</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.2246941275302864</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.324711601540324</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.7361776561281197</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.134002875826239</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0.2108863063377306</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0.4833357263605067</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.141700141060192</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.067308411068589</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0.08546743624035702</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>-1.572492244283348</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>KbKTWiX8</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>-1.031492468956799</v>
+      </c>
+      <c r="C21" t="n">
+        <v>-0.05263338288914304</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.858491282928442</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.6542183108058229</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-0.3161939140908171</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-2.617761234939641</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-2.110172631484159</v>
+      </c>
+      <c r="I21" t="n">
+        <v>-2.180626530086907</v>
+      </c>
+      <c r="J21" t="n">
+        <v>-1.704712312906831</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>-1.783630500779962</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-2.204178096812079</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>-3.546754554571267</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>-1.922538783459844</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0.01642599314148536</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0.1735270731669427</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>ruUIA1G6</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>-0.9480588415407764</v>
+      </c>
+      <c r="C22" t="n">
+        <v>-0.4018183428312783</v>
+      </c>
+      <c r="D22" t="n">
+        <v>-0.2786545907204963</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.1048553011161823</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-0.3161939140908171</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.2246941275302864</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.3715771328512414</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0.9903002405992983</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0.08675415580748531</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.6260498160425421</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0.9146087688417647</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>-0.1888055859225821</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>-0.2336115217047379</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>hnqZAAAk</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>-0.6038951284496825</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.8740497800342159</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.3776342996126424</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.6542183108058229</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-0.3161939140908171</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-0.406962619685253</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-0.8220910440999777</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-0.7222244369793933</v>
+      </c>
+      <c r="J23" t="n">
+        <v>-0.9950335157235638</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>-0.5532584264083256</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-0.8946401627174633</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>-0.6110433304391785</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>-1.039414740262161</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>-1.319775082193424</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0.3739574572626534</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>nDzACNof</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>-1.156642910080833</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.9412007338692419</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1.858491282928442</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1.203581320495464</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-0.3161939140908171</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.2246941275302864</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.4659905432842035</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.7361776561281197</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.4243240786429714</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0.6701977130784036</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0.3448163449288419</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0.307831181908703</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.2077737763464778</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>-0.2683044833351454</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0.6319492544233218</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>QyafIhIF</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1.60709599807492</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1.223234739976351</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1.219030312860256</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-0.9184679522272658</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-0.3161939140908171</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.8563508747458258</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.4659905432842035</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.006976609574363205</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.4243240786429714</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0.2037041538834944</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.618935694999978</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>-0.4963478562605419</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>-0.3950959388945559</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.416785489970804</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.471668708881815</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>hO0nKEm3</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>-0.6768995524387025</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.6457365369951275</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-1.549162570724393</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1.278984086531297</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-0.3161939140908171</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.4352463766021329</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.4659905432842035</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.3715771328512414</v>
+      </c>
+      <c r="J26" t="n">
         <v>-0.2853547185402961</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0.7946923478262913</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>0.4200523063345913</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>0.8013586140150831</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0.5477467382570875</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>-0.8854826934661758</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>0.2520987607142808</v>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0.7336839766422076</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0.4077082036272121</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0.7573193239150908</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.5405683176207317</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>-0.8671268068324287</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0.1856914258812308</v>
       </c>
     </row>
   </sheetData>

--- a/data/spain/p6_deployment/data_preparation/df_selected_nan.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_selected_nan.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF26"/>
+  <dimension ref="A1:AF15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -788,32 +788,32 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>8CpDVHAM</t>
+          <t>QekfJmLa</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-1.177501316934839</v>
+        <v>0.8249057410497068</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.05263338288914304</v>
+        <v>1.102363023073304</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.549162570724393</v>
+        <v>-0.9349434810536349</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6542183108058229</v>
+        <v>-0.2613867053435781</v>
       </c>
       <c r="F4" t="n">
         <v>-0.3161939140908171</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.880828363188178</v>
+        <v>0.9616269992817491</v>
       </c>
       <c r="H4" t="n">
-        <v>0.895351072412264</v>
+        <v>0.4659905432842035</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.633725745171589</v>
+        <v>1.465378702681876</v>
       </c>
       <c r="J4" t="n">
         <v>1.134002875826239</v>
@@ -861,47 +861,47 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>-1.046272644059392</v>
+        <v>-0.2021573344532501</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>-1.668671091240665</v>
+        <v>-0.02851655913523659</v>
       </c>
       <c r="AB4" t="n">
-        <v>-3.564108955180584</v>
+        <v>0.2477684952663456</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>-2.132167547863206</v>
+        <v>0.2012557632126838</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0.06977751774925442</v>
+        <v>0.05379059037744997</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.899962667930923</v>
+        <v>-0.866026214947702</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>4KmdZaBc</t>
+          <t>8KIT2SzJ</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-1.427802199182907</v>
+        <v>-1.156642910080833</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8740497800342159</v>
+        <v>-1.019607118113518</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.321985647147537</v>
+        <v>1.858491282928442</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6542183108058229</v>
+        <v>0.5572718973311804</v>
       </c>
       <c r="F5" t="n">
         <v>-0.3161939140908171</v>
@@ -910,13 +910,13 @@
         <v>-1.143895491436716</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.8220910440999777</v>
+        <v>-1.251451573228038</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.269125221894711</v>
+        <v>-0.7222244369793933</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.2853547185402961</v>
+        <v>-1.704712312906831</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -961,62 +961,62 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.2348614860309448</v>
+        <v>0.5422555622631005</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.9177269575195536</v>
+        <v>0.1853645217140456</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.3977196124865265</v>
+        <v>0.128932726299195</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.7355372783842571</v>
+        <v>0.2251983575732518</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.7010869176445007</v>
+        <v>-0.1626808971729748</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.6463028341325076</v>
+        <v>0.4471956022181033</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hpMqQeYq</t>
+          <t>E1Xs9lu2</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1.116923437005787</v>
       </c>
       <c r="C6" t="n">
-        <v>-1.167339216550575</v>
+        <v>1.008351687704268</v>
       </c>
       <c r="D6" t="n">
         <v>-0.2786545907204963</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5572718973311804</v>
+        <v>-0.8430651861914329</v>
       </c>
       <c r="F6" t="n">
         <v>-0.3161939140908171</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01414187845843995</v>
+        <v>-0.09113424607748329</v>
       </c>
       <c r="H6" t="n">
-        <v>0.895351072412264</v>
+        <v>-0.3927305149719172</v>
       </c>
       <c r="I6" t="n">
-        <v>0.006976609574363205</v>
+        <v>0.1892768712128023</v>
       </c>
       <c r="J6" t="n">
-        <v>1.843681673009507</v>
+        <v>-0.9950335157235638</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -1061,62 +1061,62 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.6223631565632936</v>
+        <v>-0.4661695781472107</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.8157515099381268</v>
+        <v>-0.4651151130289514</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.2596761647150918</v>
+        <v>-1.079639703620966</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.3977030929319241</v>
+        <v>-0.5213863423788073</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.9362956489452896</v>
+        <v>0.7171475541134533</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.9305092990726417</v>
+        <v>0.3462593151923172</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>ChPK4l66</t>
+          <t>ITdtTrn2</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.012631402735758</v>
+        <v>1.930401304312008</v>
       </c>
       <c r="C7" t="n">
-        <v>1.223234739976351</v>
+        <v>-0.2137956720932055</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.446933793370019</v>
+        <v>-0.3712081521777338</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9184679522272658</v>
+        <v>0.8157956665968937</v>
       </c>
       <c r="F7" t="n">
         <v>-0.3161939140908171</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3299702520662097</v>
+        <v>-0.7227909932930227</v>
       </c>
       <c r="H7" t="n">
-        <v>0.895351072412264</v>
+        <v>-0.8220910440999777</v>
       </c>
       <c r="I7" t="n">
-        <v>0.006976609574363205</v>
+        <v>0.3715771328512414</v>
       </c>
       <c r="J7" t="n">
-        <v>1.134002875826239</v>
+        <v>0.4243240786429714</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1161,44 +1161,44 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.7604703125814853</v>
+        <v>-0.3174162503151651</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.410876497063821</v>
+        <v>0.2168252937890907</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.4179709941543021</v>
+        <v>-0.0445830486428026</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.1470819966804816</v>
+        <v>0.1591520457510329</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.7153822161533081</v>
+        <v>0.2142763982083906</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.065489001404136</v>
+        <v>-0.3932572619854823</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>MNr3HRkC</t>
+          <t>M3h3GWnS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.887480961611724</v>
+        <v>-1.427802199182907</v>
       </c>
       <c r="C8" t="n">
-        <v>1.639570653753512</v>
+        <v>0.2428308139849714</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3776342996126424</v>
+        <v>-1.321985647147537</v>
       </c>
       <c r="E8" t="n">
         <v>0.2556608331878484</v>
@@ -1207,16 +1207,16 @@
         <v>-0.3161939140908171</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.406962619685253</v>
+        <v>-1.670276114116332</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3927305149719172</v>
+        <v>-1.680812102356098</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.9045246986178325</v>
+        <v>-1.269125221894711</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.2853547185402961</v>
+        <v>-0.9950335157235638</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1261,62 +1261,62 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>-1.193666876574569</v>
+        <v>-1.914111876780157</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>-1.829707651421767</v>
+        <v>-3.116821849715564</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0.7226542144563018</v>
+        <v>-5.816133722601451</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>-0.5730812288106953</v>
+        <v>-2.324769018685514</v>
       </c>
       <c r="AE8" t="n">
-        <v>-0.6549638222694014</v>
+        <v>0.2541769423330567</v>
       </c>
       <c r="AF8" t="n">
-        <v>-1.597732234095453</v>
+        <v>0.7582575745269202</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>hA5zaJZp</t>
+          <t>Eax2EqHs</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.3118774324936029</v>
+        <v>0.9709145890277466</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.5898410135693511</v>
+        <v>-1.18076940731758</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.000993906348783775</v>
+        <v>-0.446933793370019</v>
       </c>
       <c r="E9" t="n">
-        <v>1.203581320495464</v>
+        <v>-0.6384005355227432</v>
       </c>
       <c r="F9" t="n">
         <v>-0.3161939140908171</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01414187845843995</v>
+        <v>0.2246941275302864</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.3927305149719172</v>
+        <v>1.324711601540324</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1892768712128023</v>
+        <v>0.7361776561281197</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4243240786429714</v>
+        <v>1.134002875826239</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1361,62 +1361,62 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>-1.028752415741359</v>
+        <v>0.2108863063377306</v>
       </c>
       <c r="Z9" t="n">
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>-0.2273248469884925</v>
+        <v>0.4833357263605067</v>
       </c>
       <c r="AB9" t="n">
-        <v>-0.3932873498220891</v>
+        <v>1.141700141060192</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>-0.5788908884223708</v>
+        <v>1.067308411068589</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.9101734299838777</v>
+        <v>0.08546743624035702</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.09582423922648542</v>
+        <v>-1.572492244283348</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>IVonL9jm</t>
+          <t>KbKTWiX8</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2721579594185562</v>
+        <v>-1.031492468956799</v>
       </c>
       <c r="C10" t="n">
-        <v>1.961895232161637</v>
+        <v>-0.05263338288914304</v>
       </c>
       <c r="D10" t="n">
-        <v>1.219030312860256</v>
+        <v>1.858491282928442</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.185983939307745</v>
+        <v>0.6542183108058229</v>
       </c>
       <c r="F10" t="n">
         <v>-0.3161939140908171</v>
       </c>
       <c r="G10" t="n">
-        <v>2.751321116392444</v>
+        <v>-2.617761234939641</v>
       </c>
       <c r="H10" t="n">
-        <v>0.895351072412264</v>
+        <v>-2.110172631484159</v>
       </c>
       <c r="I10" t="n">
-        <v>2.74148053415095</v>
+        <v>-2.180626530086907</v>
       </c>
       <c r="J10" t="n">
-        <v>0.4243240786429714</v>
+        <v>-1.704712312906831</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -1461,62 +1461,62 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.967594704534655</v>
+        <v>-1.783630500779962</v>
       </c>
       <c r="Z10" t="n">
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.996844693921191</v>
+        <v>-2.204178096812079</v>
       </c>
       <c r="AB10" t="n">
-        <v>6.377847295808143</v>
+        <v>-3.546754554571267</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.801960239728194</v>
+        <v>-1.922538783459844</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.0006103357647526598</v>
+        <v>0.01642599314148536</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.2356922561954734</v>
+        <v>0.1735270731669427</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>OQqSjnv9</t>
+          <t>ruUIA1G6</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.1658685845155632</v>
+        <v>-0.9480588415407764</v>
       </c>
       <c r="C11" t="n">
-        <v>0.9680611154032523</v>
+        <v>-0.4018183428312783</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3608063793476901</v>
+        <v>-0.2786545907204963</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.8430651861914329</v>
+        <v>0.1048553011161823</v>
       </c>
       <c r="F11" t="n">
         <v>-0.3161939140908171</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.7227909932930227</v>
+        <v>0.2246941275302864</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.8220910440999777</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1753236520640759</v>
+        <v>0.3715771328512414</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.2853547185402961</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1561,47 +1561,47 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>-0.9525621358972615</v>
+        <v>0.9903002405992983</v>
       </c>
       <c r="Z11" t="n">
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>-1.058801097724101</v>
+        <v>0.08675415580748531</v>
       </c>
       <c r="AB11" t="n">
-        <v>-1.397731498533852</v>
+        <v>0.6260498160425421</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>-1.3996009544896</v>
+        <v>0.9146087688417647</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0.3433676456281605</v>
+        <v>-0.1888055859225821</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.8870534694918899</v>
+        <v>-0.2336115217047379</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>YcAFQVSP</t>
+          <t>hnqZAAAk</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6684676896446642</v>
+        <v>-0.6038951284496825</v>
       </c>
       <c r="C12" t="n">
-        <v>-1.18076940731758</v>
+        <v>0.8740497800342159</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.321985647147537</v>
+        <v>0.3776342996126424</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.6384005355227432</v>
+        <v>0.6542183108058229</v>
       </c>
       <c r="F12" t="n">
         <v>-0.3161939140908171</v>
@@ -1661,62 +1661,62 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>-0.6195048652443672</v>
+        <v>-0.5532584264083256</v>
       </c>
       <c r="Z12" t="n">
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>-0.4756801283372115</v>
+        <v>-0.8946401627174633</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.0001316627792189005</v>
+        <v>-0.6110433304391785</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.4160570059681963</v>
+        <v>-1.039414740262161</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.328002822167089</v>
+        <v>-1.319775082193424</v>
       </c>
       <c r="AF12" t="n">
-        <v>-1.534940499713011</v>
+        <v>0.3739574572626534</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>WhAFMMRi</t>
+          <t>nDzACNof</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.03028893996452622</v>
+        <v>-1.156642910080833</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.6435617766373719</v>
+        <v>0.9412007338692419</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.9349434810536349</v>
+        <v>1.858491282928442</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.6384005355227432</v>
+        <v>1.203581320495464</v>
       </c>
       <c r="F13" t="n">
         <v>-0.3161939140908171</v>
       </c>
       <c r="G13" t="n">
-        <v>4.541015233503139</v>
+        <v>0.2246941275302864</v>
       </c>
       <c r="H13" t="n">
-        <v>0.895351072412264</v>
+        <v>0.4659905432842035</v>
       </c>
       <c r="I13" t="n">
-        <v>4.92908367381222</v>
+        <v>0.7361776561281197</v>
       </c>
       <c r="J13" t="n">
-        <v>1.843681673009507</v>
+        <v>0.4243240786429714</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1761,62 +1761,62 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.9486883576942479</v>
+        <v>0.6701977130784036</v>
       </c>
       <c r="Z13" t="n">
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.744712044771286</v>
+        <v>0.3448163449288419</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.827005939233504</v>
+        <v>0.307831181908703</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.19875031881723</v>
+        <v>0.2077737763464778</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0.3965323714958353</v>
+        <v>-0.2683044833351454</v>
       </c>
       <c r="AF13" t="n">
-        <v>-0.5014201707273952</v>
+        <v>0.6319492544233218</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>vJDNK0d4</t>
+          <t>QyafIhIF</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.9480588415407764</v>
+        <v>1.60709599807492</v>
       </c>
       <c r="C14" t="n">
-        <v>-1.462803413424689</v>
+        <v>1.223234739976351</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.2786545907204963</v>
+        <v>1.219030312860256</v>
       </c>
       <c r="E14" t="n">
-        <v>1.278984086531297</v>
+        <v>-0.9184679522272658</v>
       </c>
       <c r="F14" t="n">
         <v>-0.3161939140908171</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4352463766021329</v>
+        <v>0.8563508747458258</v>
       </c>
       <c r="H14" t="n">
-        <v>0.03663001415614314</v>
+        <v>0.4659905432842035</v>
       </c>
       <c r="I14" t="n">
-        <v>1.829979225958754</v>
+        <v>0.006976609574363205</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.2853547185402961</v>
+        <v>0.4243240786429714</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1861,62 +1861,62 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>-0.3609978217776155</v>
+        <v>0.2037041538834944</v>
       </c>
       <c r="Z14" t="n">
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>-0.1195011535840721</v>
+        <v>1.618935694999978</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.01435175558099338</v>
+        <v>-0.4963478562605419</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.02603839490575143</v>
+        <v>-0.3950959388945559</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.1040381479899793</v>
+        <v>1.416785489970804</v>
       </c>
       <c r="AF14" t="n">
-        <v>-0.4224560151910434</v>
+        <v>1.471668708881815</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>QekfJmLa</t>
+          <t>hO0nKEm3</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.8249057410497068</v>
+        <v>-0.6768995524387025</v>
       </c>
       <c r="C15" t="n">
-        <v>1.102363023073304</v>
+        <v>0.6457365369951275</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.9349434810536349</v>
+        <v>-1.549162570724393</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.2613867053435781</v>
+        <v>1.278984086531297</v>
       </c>
       <c r="F15" t="n">
         <v>-0.3161939140908171</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9616269992817491</v>
+        <v>0.4352463766021329</v>
       </c>
       <c r="H15" t="n">
         <v>0.4659905432842035</v>
       </c>
       <c r="I15" t="n">
-        <v>1.465378702681876</v>
+        <v>0.3715771328512414</v>
       </c>
       <c r="J15" t="n">
-        <v>1.134002875826239</v>
+        <v>-0.2853547185402961</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1961,1127 +1961,27 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>-0.2021573344532501</v>
+        <v>0.7336839766422076</v>
       </c>
       <c r="Z15" t="n">
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>-0.02851655913523659</v>
+        <v>0.4077082036272121</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.2477684952663456</v>
+        <v>0.7573193239150908</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.2012557632126838</v>
+        <v>0.5405683176207317</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.05379059037744997</v>
+        <v>-0.8671268068324287</v>
       </c>
       <c r="AF15" t="n">
-        <v>-0.866026214947702</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>8KIT2SzJ</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>-1.156642910080833</v>
-      </c>
-      <c r="C16" t="n">
-        <v>-1.019607118113518</v>
-      </c>
-      <c r="D16" t="n">
-        <v>1.858491282928442</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0.5572718973311804</v>
-      </c>
-      <c r="F16" t="n">
-        <v>-0.3161939140908171</v>
-      </c>
-      <c r="G16" t="n">
-        <v>-1.143895491436716</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-1.251451573228038</v>
-      </c>
-      <c r="I16" t="n">
-        <v>-0.7222244369793933</v>
-      </c>
-      <c r="J16" t="n">
-        <v>-1.704712312906831</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0.5422555622631005</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>0.1853645217140456</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>0.128932726299195</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>0.2251983575732518</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>-0.1626808971729748</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>0.4471956022181033</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>E1Xs9lu2</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1.116923437005787</v>
-      </c>
-      <c r="C17" t="n">
-        <v>1.008351687704268</v>
-      </c>
-      <c r="D17" t="n">
-        <v>-0.2786545907204963</v>
-      </c>
-      <c r="E17" t="n">
-        <v>-0.8430651861914329</v>
-      </c>
-      <c r="F17" t="n">
-        <v>-0.3161939140908171</v>
-      </c>
-      <c r="G17" t="n">
-        <v>-0.09113424607748329</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-0.3927305149719172</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0.1892768712128023</v>
-      </c>
-      <c r="J17" t="n">
-        <v>-0.9950335157235638</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>-0.4661695781472107</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>-0.4651151130289514</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>-1.079639703620966</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>-0.5213863423788073</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>0.7171475541134533</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>0.3462593151923172</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>ITdtTrn2</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1.930401304312008</v>
-      </c>
-      <c r="C18" t="n">
-        <v>-0.2137956720932055</v>
-      </c>
-      <c r="D18" t="n">
-        <v>-0.3712081521777338</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0.8157956665968937</v>
-      </c>
-      <c r="F18" t="n">
-        <v>-0.3161939140908171</v>
-      </c>
-      <c r="G18" t="n">
-        <v>-0.7227909932930227</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-0.8220910440999777</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0.3715771328512414</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0.4243240786429714</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>-0.3174162503151651</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>0.2168252937890907</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>-0.0445830486428026</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>0.1591520457510329</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>0.2142763982083906</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>-0.3932572619854823</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>M3h3GWnS</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>-1.427802199182907</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0.2428308139849714</v>
-      </c>
-      <c r="D19" t="n">
-        <v>-1.321985647147537</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0.2556608331878484</v>
-      </c>
-      <c r="F19" t="n">
-        <v>-0.3161939140908171</v>
-      </c>
-      <c r="G19" t="n">
-        <v>-1.670276114116332</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-1.680812102356098</v>
-      </c>
-      <c r="I19" t="n">
-        <v>-1.269125221894711</v>
-      </c>
-      <c r="J19" t="n">
-        <v>-0.9950335157235638</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>-1.914111876780157</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>-3.116821849715564</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>-5.816133722601451</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>-2.324769018685514</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>0.2541769423330567</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>0.7582575745269202</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>Eax2EqHs</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>0.9709145890277466</v>
-      </c>
-      <c r="C20" t="n">
-        <v>-1.18076940731758</v>
-      </c>
-      <c r="D20" t="n">
-        <v>-0.446933793370019</v>
-      </c>
-      <c r="E20" t="n">
-        <v>-0.6384005355227432</v>
-      </c>
-      <c r="F20" t="n">
-        <v>-0.3161939140908171</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0.2246941275302864</v>
-      </c>
-      <c r="H20" t="n">
-        <v>1.324711601540324</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0.7361776561281197</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1.134002875826239</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>0.2108863063377306</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>0.4833357263605067</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.141700141060192</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.067308411068589</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>0.08546743624035702</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>-1.572492244283348</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>KbKTWiX8</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>-1.031492468956799</v>
-      </c>
-      <c r="C21" t="n">
-        <v>-0.05263338288914304</v>
-      </c>
-      <c r="D21" t="n">
-        <v>1.858491282928442</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0.6542183108058229</v>
-      </c>
-      <c r="F21" t="n">
-        <v>-0.3161939140908171</v>
-      </c>
-      <c r="G21" t="n">
-        <v>-2.617761234939641</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-2.110172631484159</v>
-      </c>
-      <c r="I21" t="n">
-        <v>-2.180626530086907</v>
-      </c>
-      <c r="J21" t="n">
-        <v>-1.704712312906831</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>-1.783630500779962</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>-2.204178096812079</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>-3.546754554571267</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>-1.922538783459844</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>0.01642599314148536</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>0.1735270731669427</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>ruUIA1G6</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>-0.9480588415407764</v>
-      </c>
-      <c r="C22" t="n">
-        <v>-0.4018183428312783</v>
-      </c>
-      <c r="D22" t="n">
-        <v>-0.2786545907204963</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0.1048553011161823</v>
-      </c>
-      <c r="F22" t="n">
-        <v>-0.3161939140908171</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.2246941275302864</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0.3715771328512414</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>0.9903002405992983</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>0.08675415580748531</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>0.6260498160425421</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>0.9146087688417647</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>-0.1888055859225821</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>-0.2336115217047379</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>hnqZAAAk</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>-0.6038951284496825</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0.8740497800342159</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0.3776342996126424</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0.6542183108058229</v>
-      </c>
-      <c r="F23" t="n">
-        <v>-0.3161939140908171</v>
-      </c>
-      <c r="G23" t="n">
-        <v>-0.406962619685253</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-0.8220910440999777</v>
-      </c>
-      <c r="I23" t="n">
-        <v>-0.7222244369793933</v>
-      </c>
-      <c r="J23" t="n">
-        <v>-0.9950335157235638</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" t="n">
-        <v>0</v>
-      </c>
-      <c r="W23" t="n">
-        <v>0</v>
-      </c>
-      <c r="X23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>-0.5532584264083256</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>-0.8946401627174633</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>-0.6110433304391785</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>-1.039414740262161</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>-1.319775082193424</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>0.3739574572626534</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>nDzACNof</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>-1.156642910080833</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0.9412007338692419</v>
-      </c>
-      <c r="D24" t="n">
-        <v>1.858491282928442</v>
-      </c>
-      <c r="E24" t="n">
-        <v>1.203581320495464</v>
-      </c>
-      <c r="F24" t="n">
-        <v>-0.3161939140908171</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0.2246941275302864</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.4659905432842035</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0.7361776561281197</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0.4243240786429714</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" t="n">
-        <v>0</v>
-      </c>
-      <c r="W24" t="n">
-        <v>0</v>
-      </c>
-      <c r="X24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>0.6701977130784036</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>0.3448163449288419</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>0.307831181908703</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>0.2077737763464778</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>-0.2683044833351454</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>0.6319492544233218</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>QyafIhIF</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>1.60709599807492</v>
-      </c>
-      <c r="C25" t="n">
-        <v>1.223234739976351</v>
-      </c>
-      <c r="D25" t="n">
-        <v>1.219030312860256</v>
-      </c>
-      <c r="E25" t="n">
-        <v>-0.9184679522272658</v>
-      </c>
-      <c r="F25" t="n">
-        <v>-0.3161939140908171</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0.8563508747458258</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.4659905432842035</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0.006976609574363205</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0.4243240786429714</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" t="n">
-        <v>0</v>
-      </c>
-      <c r="W25" t="n">
-        <v>0</v>
-      </c>
-      <c r="X25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>0.2037041538834944</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.618935694999978</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>-0.4963478562605419</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>-0.3950959388945559</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.416785489970804</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.471668708881815</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>hO0nKEm3</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>-0.6768995524387025</v>
-      </c>
-      <c r="C26" t="n">
-        <v>0.6457365369951275</v>
-      </c>
-      <c r="D26" t="n">
-        <v>-1.549162570724393</v>
-      </c>
-      <c r="E26" t="n">
-        <v>1.278984086531297</v>
-      </c>
-      <c r="F26" t="n">
-        <v>-0.3161939140908171</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0.4352463766021329</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0.4659905432842035</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0.3715771328512414</v>
-      </c>
-      <c r="J26" t="n">
-        <v>-0.2853547185402961</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" t="n">
-        <v>0</v>
-      </c>
-      <c r="W26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>0.7336839766422076</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>0.4077082036272121</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>0.7573193239150908</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>0.5405683176207317</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>-0.8671268068324287</v>
-      </c>
-      <c r="AF26" t="n">
         <v>0.1856914258812308</v>
       </c>
     </row>

--- a/data/spain/p6_deployment/data_preparation/df_selected_nan.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_selected_nan.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF15"/>
+  <dimension ref="A1:AF20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -588,35 +588,35 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>ng6idLW1</t>
+          <t>MNr3HRkC</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.6768995524387025</v>
+        <v>0.887480961611724</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.05263338288914304</v>
+        <v>1.639570653753512</v>
       </c>
       <c r="D2" t="n">
-        <v>-1.549162570724393</v>
+        <v>0.3776342996126424</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6542183108058229</v>
+        <v>0.2556608331878484</v>
       </c>
       <c r="F2" t="n">
-        <v>3.162616215670679</v>
+        <v>-0.3161939140908171</v>
       </c>
       <c r="G2" t="n">
-        <v>-4.407455352050336</v>
+        <v>-0.406962619685253</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.8220910440999777</v>
+        <v>-0.3927305149719172</v>
       </c>
       <c r="I2" t="n">
-        <v>-2.727527315002224</v>
+        <v>-0.9045246986178325</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4243240786429714</v>
+        <v>-0.2853547185402961</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -661,62 +661,62 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0.9403909451778998</v>
+        <v>-1.176549014244474</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>-1.740677530360975</v>
+        <v>-1.834193508340854</v>
       </c>
       <c r="AB2" t="n">
-        <v>-2.816831953859889</v>
+        <v>-0.6802337814803333</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>-1.187146271545754</v>
+        <v>-0.6153565546655116</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.3938154345406206</v>
+        <v>-0.8501718887317512</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.5260668824132689</v>
+        <v>-1.624646159320207</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>CWcwKOO8</t>
+          <t>hA5zaJZp</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2721579594185562</v>
+        <v>-0.3118774324936029</v>
       </c>
       <c r="C3" t="n">
-        <v>-1.462803413424689</v>
+        <v>-0.5898410135693511</v>
       </c>
       <c r="D3" t="n">
-        <v>1.219030312860256</v>
+        <v>-0.000993906348783775</v>
       </c>
       <c r="E3" t="n">
-        <v>1.278984086531297</v>
+        <v>1.203581320495464</v>
       </c>
       <c r="F3" t="n">
-        <v>3.162616215670679</v>
+        <v>-0.3161939140908171</v>
       </c>
       <c r="G3" t="n">
-        <v>1.698559871033212</v>
+        <v>0.01414187845843995</v>
       </c>
       <c r="H3" t="n">
-        <v>1.324711601540324</v>
+        <v>-0.3927305149719172</v>
       </c>
       <c r="I3" t="n">
-        <v>1.647678964320315</v>
+        <v>0.1892768712128023</v>
       </c>
       <c r="J3" t="n">
-        <v>1.134002875826239</v>
+        <v>0.4243240786429714</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -761,62 +761,62 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.922409289296505</v>
+        <v>-1.109160730370822</v>
       </c>
       <c r="Z3" t="n">
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.120856364125876</v>
+        <v>-0.2352867091787993</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.826307707975066</v>
+        <v>-0.4108480807015764</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.33637306595699</v>
+        <v>-0.6111610675644065</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0.2568938792882714</v>
+        <v>0.8150478963411982</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.7336108628410466</v>
+        <v>-0.07444269734402216</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>QekfJmLa</t>
+          <t>IVonL9jm</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8249057410497068</v>
+        <v>0.2721579594185562</v>
       </c>
       <c r="C4" t="n">
-        <v>1.102363023073304</v>
+        <v>1.961895232161637</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.9349434810536349</v>
+        <v>1.219030312860256</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.2613867053435781</v>
+        <v>-0.185983939307745</v>
       </c>
       <c r="F4" t="n">
         <v>-0.3161939140908171</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9616269992817491</v>
+        <v>2.751321116392444</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4659905432842035</v>
+        <v>0.895351072412264</v>
       </c>
       <c r="I4" t="n">
-        <v>1.465378702681876</v>
+        <v>2.74148053415095</v>
       </c>
       <c r="J4" t="n">
-        <v>1.134002875826239</v>
+        <v>0.4243240786429714</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -861,62 +861,62 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0.2021573344532501</v>
+        <v>2.851519830913291</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>-0.02851655913523659</v>
+        <v>2.96772352855776</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.2477684952663456</v>
+        <v>6.186017148108498</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.2012557632126838</v>
+        <v>2.764847738754058</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.05379059037744997</v>
+        <v>-0.1945225964520229</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.866026214947702</v>
+        <v>-0.261277791646914</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>8KIT2SzJ</t>
+          <t>OQqSjnv9</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-1.156642910080833</v>
+        <v>-0.1658685845155632</v>
       </c>
       <c r="C5" t="n">
-        <v>-1.019607118113518</v>
+        <v>0.9680611154032523</v>
       </c>
       <c r="D5" t="n">
-        <v>1.858491282928442</v>
+        <v>0.3608063793476901</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5572718973311804</v>
+        <v>-0.8430651861914329</v>
       </c>
       <c r="F5" t="n">
         <v>-0.3161939140908171</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.143895491436716</v>
+        <v>-0.7227909932930227</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.251451573228038</v>
+        <v>-0.8220910440999777</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.7222244369793933</v>
+        <v>-0.1753236520640759</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.704712312906831</v>
+        <v>-0.2853547185402961</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -961,59 +961,59 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.5422555622631005</v>
+        <v>-0.8269791228363323</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.1853645217140456</v>
+        <v>-0.99526791243123</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.128932726299195</v>
+        <v>-1.308091264757385</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.2251983575732518</v>
+        <v>-1.372596817464782</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.1626808971729748</v>
+        <v>-0.324792896010433</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.4471956022181033</v>
+        <v>1.010919377807262</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>E1Xs9lu2</t>
+          <t>YcAFQVSP</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.116923437005787</v>
+        <v>0.6684676896446642</v>
       </c>
       <c r="C6" t="n">
-        <v>1.008351687704268</v>
+        <v>-1.18076940731758</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2786545907204963</v>
+        <v>-1.321985647147537</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.8430651861914329</v>
+        <v>-0.6384005355227432</v>
       </c>
       <c r="F6" t="n">
         <v>-0.3161939140908171</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.09113424607748329</v>
+        <v>-0.406962619685253</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.3927305149719172</v>
+        <v>-0.8220910440999777</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1892768712128023</v>
+        <v>-0.7222244369793933</v>
       </c>
       <c r="J6" t="n">
         <v>-0.9950335157235638</v>
@@ -1061,62 +1061,62 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.4661695781472107</v>
+        <v>-0.5642056869979519</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.4651151130289514</v>
+        <v>-0.5305236641352513</v>
       </c>
       <c r="AB6" t="n">
-        <v>-1.079639703620966</v>
+        <v>0.01926224934003505</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0.5213863423788073</v>
+        <v>0.4127120164855981</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.7171475541134533</v>
+        <v>1.250893659554744</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.3462593151923172</v>
+        <v>-1.55008095527556</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>ITdtTrn2</t>
+          <t>WhAFMMRi</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.930401304312008</v>
+        <v>-0.03028893996452622</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.2137956720932055</v>
+        <v>-0.6435617766373719</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3712081521777338</v>
+        <v>-0.9349434810536349</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8157956665968937</v>
+        <v>-0.6384005355227432</v>
       </c>
       <c r="F7" t="n">
         <v>-0.3161939140908171</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.7227909932930227</v>
+        <v>4.541015233503139</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.8220910440999777</v>
+        <v>0.895351072412264</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3715771328512414</v>
+        <v>4.92908367381222</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4243240786429714</v>
+        <v>1.843681673009507</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1161,62 +1161,62 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.3174162503151651</v>
+        <v>0.636710425956089</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.2168252937890907</v>
+        <v>1.514135274997804</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0.0445830486428026</v>
+        <v>2.310345541214724</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.1591520457510329</v>
+        <v>1.060786637639232</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.2142763982083906</v>
+        <v>-0.2967117883698193</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.3932572619854823</v>
+        <v>-0.6427585751231412</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>M3h3GWnS</t>
+          <t>vJDNK0d4</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-1.427802199182907</v>
+        <v>-0.9480588415407764</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2428308139849714</v>
+        <v>-1.462803413424689</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.321985647147537</v>
+        <v>-0.2786545907204963</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2556608331878484</v>
+        <v>1.278984086531297</v>
       </c>
       <c r="F8" t="n">
         <v>-0.3161939140908171</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.670276114116332</v>
+        <v>0.4352463766021329</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.680812102356098</v>
+        <v>0.03663001415614314</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.269125221894711</v>
+        <v>1.829979225958754</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.9950335157235638</v>
+        <v>-0.2853547185402961</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1261,59 +1261,59 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>-1.914111876780157</v>
+        <v>-0.2837709551007949</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>-3.116821849715564</v>
+        <v>-0.08276385474384988</v>
       </c>
       <c r="AB8" t="n">
-        <v>-5.816133722601451</v>
+        <v>0.05329763002034062</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>-2.324769018685514</v>
+        <v>0.07712301797458589</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.2541769423330567</v>
+        <v>0.05927344714980161</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.7582575745269202</v>
+        <v>-0.395486291866894</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Eax2EqHs</t>
+          <t>QekfJmLa</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9709145890277466</v>
+        <v>0.8249057410497068</v>
       </c>
       <c r="C9" t="n">
-        <v>-1.18076940731758</v>
+        <v>1.102363023073304</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.446933793370019</v>
+        <v>-0.9349434810536349</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.6384005355227432</v>
+        <v>-0.2613867053435781</v>
       </c>
       <c r="F9" t="n">
         <v>-0.3161939140908171</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2246941275302864</v>
+        <v>0.9616269992817491</v>
       </c>
       <c r="H9" t="n">
-        <v>1.324711601540324</v>
+        <v>0.4659905432842035</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7361776561281197</v>
+        <v>1.465378702681876</v>
       </c>
       <c r="J9" t="n">
         <v>1.134002875826239</v>
@@ -1361,59 +1361,59 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.2108863063377306</v>
+        <v>-0.1303832042632055</v>
       </c>
       <c r="Z9" t="n">
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.4833357263605067</v>
+        <v>-0.02533535472743207</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.141700141060192</v>
+        <v>0.2533227205008814</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.067308411068589</v>
+        <v>0.2367012059207824</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.08546743624035702</v>
+        <v>0.08647480884779891</v>
       </c>
       <c r="AF9" t="n">
-        <v>-1.572492244283348</v>
+        <v>-0.8033507408814324</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>KbKTWiX8</t>
+          <t>8KIT2SzJ</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-1.031492468956799</v>
+        <v>-1.156642910080833</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.05263338288914304</v>
+        <v>-1.019607118113518</v>
       </c>
       <c r="D10" t="n">
         <v>1.858491282928442</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6542183108058229</v>
+        <v>0.5572718973311804</v>
       </c>
       <c r="F10" t="n">
         <v>-0.3161939140908171</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.617761234939641</v>
+        <v>-1.143895491436716</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.110172631484159</v>
+        <v>-1.251451573228038</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.180626530086907</v>
+        <v>-0.7222244369793933</v>
       </c>
       <c r="J10" t="n">
         <v>-1.704712312906831</v>
@@ -1461,62 +1461,62 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>-1.783630500779962</v>
+        <v>0.5809051748532111</v>
       </c>
       <c r="Z10" t="n">
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>-2.204178096812079</v>
+        <v>0.1782349927224163</v>
       </c>
       <c r="AB10" t="n">
-        <v>-3.546754554571267</v>
+        <v>0.14742917306234</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>-1.922538783459844</v>
+        <v>0.1188064739952693</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.01642599314148536</v>
+        <v>-0.08275601019472806</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.1735270731669427</v>
+        <v>0.6134182093954561</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>ruUIA1G6</t>
+          <t>E1Xs9lu2</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.9480588415407764</v>
+        <v>1.116923437005787</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.4018183428312783</v>
+        <v>1.008351687704268</v>
       </c>
       <c r="D11" t="n">
         <v>-0.2786545907204963</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1048553011161823</v>
+        <v>-0.8430651861914329</v>
       </c>
       <c r="F11" t="n">
         <v>-0.3161939140908171</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2246941275302864</v>
+        <v>-0.09113424607748329</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>-0.3927305149719172</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3715771328512414</v>
+        <v>0.1892768712128023</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>-0.9950335157235638</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1561,62 +1561,62 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.9903002405992983</v>
+        <v>-0.5257635316976885</v>
       </c>
       <c r="Z11" t="n">
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.08675415580748531</v>
+        <v>-0.6503101965120481</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.6260498160425421</v>
+        <v>-1.0894391780166</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.9146087688417647</v>
+        <v>-0.5412146705835658</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0.1888055859225821</v>
+        <v>0.7289616688824532</v>
       </c>
       <c r="AF11" t="n">
-        <v>-0.2336115217047379</v>
+        <v>0.2012448768339101</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>hnqZAAAk</t>
+          <t>ITdtTrn2</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.6038951284496825</v>
+        <v>1.930401304312008</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8740497800342159</v>
+        <v>-0.2137956720932055</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3776342996126424</v>
+        <v>-0.3712081521777338</v>
       </c>
       <c r="E12" t="n">
-        <v>0.6542183108058229</v>
+        <v>0.8157956665968937</v>
       </c>
       <c r="F12" t="n">
         <v>-0.3161939140908171</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.406962619685253</v>
+        <v>-0.7227909932930227</v>
       </c>
       <c r="H12" t="n">
         <v>-0.8220910440999777</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.7222244369793933</v>
+        <v>0.3715771328512414</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.9950335157235638</v>
+        <v>0.4243240786429714</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1661,62 +1661,62 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>-0.5532584264083256</v>
+        <v>-0.3103209566115768</v>
       </c>
       <c r="Z12" t="n">
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>-0.8946401627174633</v>
+        <v>0.1620971692446173</v>
       </c>
       <c r="AB12" t="n">
-        <v>-0.6110433304391785</v>
+        <v>-0.04659575832850694</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>-1.039414740262161</v>
+        <v>0.1741614340996327</v>
       </c>
       <c r="AE12" t="n">
-        <v>-1.319775082193424</v>
+        <v>0.2509099200156272</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.3739574572626534</v>
+        <v>-0.4537266872241248</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>nDzACNof</t>
+          <t>M3h3GWnS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-1.156642910080833</v>
+        <v>-1.427802199182907</v>
       </c>
       <c r="C13" t="n">
-        <v>0.9412007338692419</v>
+        <v>0.2428308139849714</v>
       </c>
       <c r="D13" t="n">
-        <v>1.858491282928442</v>
+        <v>-1.321985647147537</v>
       </c>
       <c r="E13" t="n">
-        <v>1.203581320495464</v>
+        <v>0.2556608331878484</v>
       </c>
       <c r="F13" t="n">
         <v>-0.3161939140908171</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2246941275302864</v>
+        <v>-1.670276114116332</v>
       </c>
       <c r="H13" t="n">
-        <v>0.4659905432842035</v>
+        <v>-1.680812102356098</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7361776561281197</v>
+        <v>-1.269125221894711</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4243240786429714</v>
+        <v>-0.9950335157235638</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1761,62 +1761,62 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.6701977130784036</v>
+        <v>-1.858685770101388</v>
       </c>
       <c r="Z13" t="n">
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.3448163449288419</v>
+        <v>-3.097323490843598</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.307831181908703</v>
+        <v>-5.646402083515123</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.2077737763464778</v>
+        <v>-2.297905675938274</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0.2683044833351454</v>
+        <v>0.2688330649808613</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.6319492544233218</v>
+        <v>0.7707679551628334</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>QyafIhIF</t>
+          <t>Eax2EqHs</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.60709599807492</v>
+        <v>0.9709145890277466</v>
       </c>
       <c r="C14" t="n">
-        <v>1.223234739976351</v>
+        <v>-1.18076940731758</v>
       </c>
       <c r="D14" t="n">
-        <v>1.219030312860256</v>
+        <v>-0.446933793370019</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.9184679522272658</v>
+        <v>-0.6384005355227432</v>
       </c>
       <c r="F14" t="n">
         <v>-0.3161939140908171</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8563508747458258</v>
+        <v>0.2246941275302864</v>
       </c>
       <c r="H14" t="n">
-        <v>0.4659905432842035</v>
+        <v>1.324711601540324</v>
       </c>
       <c r="I14" t="n">
-        <v>0.006976609574363205</v>
+        <v>0.7361776561281197</v>
       </c>
       <c r="J14" t="n">
-        <v>0.4243240786429714</v>
+        <v>1.134002875826239</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1861,128 +1861,628 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.2037041538834944</v>
+        <v>0.1284653216468656</v>
       </c>
       <c r="Z14" t="n">
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.618935694999978</v>
+        <v>0.4550913463905611</v>
       </c>
       <c r="AB14" t="n">
-        <v>-0.4963478562605419</v>
+        <v>1.073664567078601</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>-0.3950959388945559</v>
+        <v>1.005357709036498</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.416785489970804</v>
+        <v>0.08153952606774897</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.471668708881815</v>
+        <v>-1.648848705001845</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>hO0nKEm3</t>
+          <t>KbKTWiX8</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.6768995524387025</v>
+        <v>-1.031492468956799</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6457365369951275</v>
+        <v>-0.05263338288914304</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.549162570724393</v>
+        <v>1.858491282928442</v>
       </c>
       <c r="E15" t="n">
-        <v>1.278984086531297</v>
+        <v>0.6542183108058229</v>
       </c>
       <c r="F15" t="n">
         <v>-0.3161939140908171</v>
       </c>
       <c r="G15" t="n">
+        <v>-2.617761234939641</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-2.110172631484159</v>
+      </c>
+      <c r="I15" t="n">
+        <v>-2.180626530086907</v>
+      </c>
+      <c r="J15" t="n">
+        <v>-1.704712312906831</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>-1.648959751912772</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-2.005236735224019</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>-3.158601791938133</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>-1.793322966209051</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>-0.08422467868644465</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0.1165347973347795</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>ruUIA1G6</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>-0.9480588415407764</v>
+      </c>
+      <c r="C16" t="n">
+        <v>-0.4018183428312783</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-0.2786545907204963</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.1048553011161823</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-0.3161939140908171</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.2246941275302864</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.3715771328512414</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.136307996601569</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0.105820576083965</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.6496783713259646</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.9772565782250728</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>-0.1867211936922793</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>-0.005684086171706431</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>hnqZAAAk</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>-0.6038951284496825</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.8740497800342159</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.3776342996126424</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.6542183108058229</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-0.3161939140908171</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-0.406962619685253</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-0.8220910440999777</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-0.7222244369793933</v>
+      </c>
+      <c r="J17" t="n">
+        <v>-0.9950335157235638</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>-0.5696580224274288</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-0.8903221109964237</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>-0.6074621512786482</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>-1.035882512175636</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>-1.363527292776956</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0.3813919174581616</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>nDzACNof</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>-1.156642910080833</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.9412007338692419</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.858491282928442</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1.203581320495464</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-0.3161939140908171</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.2246941275302864</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.4659905432842035</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.7361776561281197</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.4243240786429714</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.6694948643754925</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0.29419995506045</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.3013695788089274</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.1553824725741556</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>-0.1865945751512605</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0.6954890850639265</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>QyafIhIF</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1.60709599807492</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1.223234739976351</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.219030312860256</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-0.9184679522272658</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-0.3161939140908171</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.8563508747458258</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.4659905432842035</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.006976609574363205</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.4243240786429714</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0.2624753674757944</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.606571420497667</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>-0.4512294150507359</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>-0.3594202665678702</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.188833999592257</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.530828808151101</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>hO0nKEm3</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>-0.6768995524387025</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.6457365369951275</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-1.549162570724393</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1.278984086531297</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-0.3161939140908171</v>
+      </c>
+      <c r="G20" t="n">
         <v>0.4352463766021329</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H20" t="n">
         <v>0.4659905432842035</v>
       </c>
-      <c r="I15" t="n">
+      <c r="I20" t="n">
         <v>0.3715771328512414</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J20" t="n">
         <v>-0.2853547185402961</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0.7336839766422076</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>0.4077082036272121</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>0.7573193239150908</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>0.5405683176207317</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>-0.8671268068324287</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>0.1856914258812308</v>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0.7873569375092309</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0.4393090395846398</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.84253873956543</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.5589628259938779</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>-0.9349533108397521</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0.2424535890876401</v>
       </c>
     </row>
   </sheetData>

--- a/data/spain/p6_deployment/data_preparation/df_selected_nan.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_selected_nan.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF20"/>
+  <dimension ref="A1:AF32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -588,541 +588,541 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MNr3HRkC</t>
+          <t>YN50iYWr</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.887480961611724</v>
+        <v>0.2721579594185562</v>
       </c>
       <c r="C2" t="n">
         <v>1.639570653753512</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3776342996126424</v>
+        <v>-0.2786545907204963</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2556608331878484</v>
+        <v>-1.543233727952739</v>
       </c>
       <c r="F2" t="n">
         <v>-0.3161939140908171</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.406962619685253</v>
+        <v>2.119664369176905</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.3927305149719172</v>
+        <v>0.4659905432842035</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.9045246986178325</v>
+        <v>1.647678964320315</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.2853547185402961</v>
+        <v>0.4243240786429714</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>0.5987362797997117</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>0.9675559952517809</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>-1.293986329542964</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>-0.346462816345706</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>0.05867079225544721</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>0.04384578161981739</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-0.05809667966731939</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>-1.362087994347697</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.145295406980734</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>-2.515010047009671</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>0.07348778384082316</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.474574310648922</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>-0.8890537965590347</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-0.8811837012552609</v>
       </c>
       <c r="Y2" t="n">
-        <v>-1.176549014244474</v>
+        <v>1.474949198964272</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>-1.834193508340854</v>
+        <v>1.438041068781858</v>
       </c>
       <c r="AB2" t="n">
-        <v>-0.6802337814803333</v>
+        <v>5.089434551698367</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0.6153565546655116</v>
+        <v>1.662621156047688</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0.8501718887317512</v>
+        <v>-1.131487722966436</v>
       </c>
       <c r="AF2" t="n">
-        <v>-1.624646159320207</v>
+        <v>-0.8949306483828875</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hA5zaJZp</t>
+          <t>h4pRxZHk</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.3118774324936029</v>
+        <v>0.6684676896446642</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.5898410135693511</v>
+        <v>0.9680611154032523</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.000993906348783775</v>
+        <v>-0.6572827966819225</v>
       </c>
       <c r="E3" t="n">
-        <v>1.203581320495464</v>
+        <v>-1.52169008051393</v>
       </c>
       <c r="F3" t="n">
         <v>-0.3161939140908171</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01414187845843995</v>
+        <v>0.4352463766021329</v>
       </c>
       <c r="H3" t="n">
         <v>-0.3927305149719172</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1892768712128023</v>
+        <v>0.5538773944896805</v>
       </c>
       <c r="J3" t="n">
         <v>0.4243240786429714</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>-0.6004321192265963</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>-1.026461807438338</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>-0.3589512550077246</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>-1.333351558825785</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>0.3753673079261018</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>0.04384578161981739</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.131843825980273</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>-0.5548252321793197</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>-1.720196558039189</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.019071081209555</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>-1.2924631077809</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>-0.5883957168992872</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>-0.1746402550614765</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-1.374583770492558</v>
       </c>
       <c r="Y3" t="n">
-        <v>-1.109160730370822</v>
+        <v>-0.7395983748862066</v>
       </c>
       <c r="Z3" t="n">
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0.2352867091787993</v>
+        <v>-0.971137039656529</v>
       </c>
       <c r="AB3" t="n">
-        <v>-0.4108480807015764</v>
+        <v>-1.115281360112996</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0.6111610675644065</v>
+        <v>-0.6153153609049162</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.8150478963411982</v>
+        <v>1.090847567656925</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.07444269734402216</v>
+        <v>0.07027992109869055</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>IVonL9jm</t>
+          <t>n1v9mjW7</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2721579594185562</v>
+        <v>0.8249057410497068</v>
       </c>
       <c r="C4" t="n">
-        <v>1.961895232161637</v>
+        <v>1.223234739976351</v>
       </c>
       <c r="D4" t="n">
-        <v>1.219030312860256</v>
+        <v>0.8319881467663537</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.185983939307745</v>
+        <v>-1.543233727952739</v>
       </c>
       <c r="F4" t="n">
         <v>-0.3161939140908171</v>
       </c>
       <c r="G4" t="n">
-        <v>2.751321116392444</v>
+        <v>-0.1964103706134065</v>
       </c>
       <c r="H4" t="n">
-        <v>0.895351072412264</v>
+        <v>-1.680812102356098</v>
       </c>
       <c r="I4" t="n">
-        <v>2.74148053415095</v>
+        <v>-0.5399241753409542</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4243240786429714</v>
+        <v>-1.704712312906831</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>-0.0008479197134423351</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>-0.02945290609327835</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.277360125428944</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>-1.086629373205765</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>0.05867079225544721</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>0.9634607773628866</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1.015650466645634</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.136050641715271</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>0.8587462104787417</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>0.7351645838492393</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.439438675462547</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.4430892968748174</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>-0.26907250576961</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>0.4601881437647747</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.851519830913291</v>
+        <v>0.1945557599077535</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.96772352855776</v>
+        <v>0.907124397345265</v>
       </c>
       <c r="AB4" t="n">
-        <v>6.186017148108498</v>
+        <v>-0.2953122322423959</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.764847738754058</v>
+        <v>-0.1208519062213011</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0.1945225964520229</v>
+        <v>1.189753943656909</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.261277791646914</v>
+        <v>0.5367736080749596</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>OQqSjnv9</t>
+          <t>tQQLbGv9</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.1658685845155632</v>
+        <v>0.887480961611724</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9680611154032523</v>
+        <v>-0.5898410135693511</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3608063793476901</v>
+        <v>1.858491282928442</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.8430651861914329</v>
+        <v>0.3741508941013003</v>
       </c>
       <c r="F5" t="n">
         <v>-0.3161939140908171</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.7227909932930227</v>
+        <v>0.2246941275302864</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.8220910440999777</v>
+        <v>-0.3927305149719172</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1753236520640759</v>
+        <v>0.1892768712128023</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.2853547185402961</v>
+        <v>-0.9950335157235638</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>-0.0008479197134423351</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-0.02945290609327835</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>-1.060227560909154</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>-3.060406858165924</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>-0.2580257234152074</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>-0.8757692141232519</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.05809667966731939</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.405138229104729</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-2.006745754541182</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>0.9986922566215833</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>-1.2924631077809</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.5883957168992872</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.07945874966631063</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>0.8288408972370866</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.8269791228363323</v>
+        <v>-0.5418041990823114</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.99526791243123</v>
+        <v>-0.2336554884809496</v>
       </c>
       <c r="AB5" t="n">
-        <v>-1.308091264757385</v>
+        <v>-0.2205392685845242</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>-1.372596817464782</v>
+        <v>0.1952152235592716</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.324792896010433</v>
+        <v>0.6354538630409108</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.010919377807262</v>
+        <v>-0.9205206084565062</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>YcAFQVSP</t>
+          <t>vyy1kC1e</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6684676896446642</v>
+        <v>-0.9480588415407764</v>
       </c>
       <c r="C6" t="n">
-        <v>-1.18076940731758</v>
+        <v>-1.167339216550575</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.321985647147537</v>
+        <v>-1.448195049134679</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.6384005355227432</v>
+        <v>1.203581320495464</v>
       </c>
       <c r="F6" t="n">
         <v>-0.3161939140908171</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.406962619685253</v>
+        <v>-0.5122387442211762</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.8220910440999777</v>
+        <v>0.03663001415614314</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7222244369793933</v>
+        <v>-0.5399241753409542</v>
       </c>
       <c r="J6" t="n">
         <v>-0.9950335157235638</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>-0.0008479197134423351</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-0.02945290609327835</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2.446153968597993</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>-0.09974063072568611</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>-0.5747222390858621</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-0.8757692141232519</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.05809667966731939</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.597875466936352</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-3.152942540549151</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>0.2081092383045511</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>0.528804747714731</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.9588318037618696</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.106465257510448</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.033666062255833</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.5642056869979519</v>
+        <v>-0.1342134832552984</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.5305236641352513</v>
+        <v>-0.2465853083157257</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.01926224934003505</v>
+        <v>0.08742366575769804</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.4127120164855981</v>
+        <v>-0.02990349448117196</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.250893659554744</v>
+        <v>0.1735500695152346</v>
       </c>
       <c r="AF6" t="n">
-        <v>-1.55008095527556</v>
+        <v>0.2162267338875962</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>WhAFMMRi</t>
+          <t>EJYZzDn2</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.03028893996452622</v>
+        <v>-1.031492468956799</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.6435617766373719</v>
+        <v>1.102363023073304</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9349434810536349</v>
+        <v>0.6048112231894981</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.6384005355227432</v>
+        <v>-0.2613867053435781</v>
       </c>
       <c r="F7" t="n">
         <v>-0.3161939140908171</v>
       </c>
       <c r="G7" t="n">
-        <v>4.541015233503139</v>
+        <v>-0.1964103706134065</v>
       </c>
       <c r="H7" t="n">
-        <v>0.895351072412264</v>
+        <v>-0.3927305149719172</v>
       </c>
       <c r="I7" t="n">
-        <v>4.92908367381222</v>
+        <v>1.100778179404998</v>
       </c>
       <c r="J7" t="n">
-        <v>1.843681673009507</v>
+        <v>1.134002875826239</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>-0.0008479197134423351</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-0.02945290609327835</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1131,7 +1131,7 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>-0.2580257234152074</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -1155,174 +1155,174 @@
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.04097587739552059</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>0.4624883890416147</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.636710425956089</v>
+        <v>-1.258211030762132</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.514135274997804</v>
+        <v>-1.024459423698013</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.310345541214724</v>
+        <v>-0.41877770202744</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.060786637639232</v>
+        <v>-0.5895093016633258</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.2967117883698193</v>
+        <v>-0.8803629611907847</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.6427585751231412</v>
+        <v>-1.427068559459945</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>vJDNK0d4</t>
+          <t>xhKUdf9L</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.9480588415407764</v>
+        <v>-0.3118774324936029</v>
       </c>
       <c r="C8" t="n">
         <v>-1.462803413424689</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2786545907204963</v>
+        <v>-1.448195049134679</v>
       </c>
       <c r="E8" t="n">
-        <v>1.278984086531297</v>
+        <v>1.235896791653678</v>
       </c>
       <c r="F8" t="n">
         <v>-0.3161939140908171</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4352463766021329</v>
+        <v>-0.3016864951493298</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03663001415614314</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>1.829979225958754</v>
+        <v>-0.5399241753409542</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.2853547185402961</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>-0.0008479197134423351</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-0.02945290609327835</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>-0.3589512550077246</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>0.6404259261343733</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>0.05867079225544721</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.04384578161981739</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.05809667966731939</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>0.2524375299890573</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.291492192988703</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>-0.5824737800124812</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>-0.3818291800330847</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.4430892968748174</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>0.8147801914622566</v>
       </c>
       <c r="Y8" t="n">
-        <v>-0.2837709551007949</v>
+        <v>-1.320935541689849</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>-0.08276385474384988</v>
+        <v>-0.1724533422257953</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.05329763002034062</v>
+        <v>-0.5538270259764786</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.07712301797458589</v>
+        <v>-0.8362329100145018</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.05927344714980161</v>
+        <v>0.2134513761857451</v>
       </c>
       <c r="AF8" t="n">
-        <v>-0.395486291866894</v>
+        <v>-0.312634537913667</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>QekfJmLa</t>
+          <t>GOO6q4Wr</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8249057410497068</v>
+        <v>-0.1658685845155632</v>
       </c>
       <c r="C9" t="n">
-        <v>1.102363023073304</v>
+        <v>-1.18076940731758</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.9349434810536349</v>
+        <v>0.3608063793476901</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2613867053435781</v>
+        <v>-1.52169008051393</v>
       </c>
       <c r="F9" t="n">
         <v>-0.3161939140908171</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9616269992817491</v>
+        <v>0.3299702520662097</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4659905432842035</v>
+        <v>-0.8220910440999777</v>
       </c>
       <c r="I9" t="n">
-        <v>1.465378702681876</v>
+        <v>0.1892768712128023</v>
       </c>
       <c r="J9" t="n">
-        <v>1.134002875826239</v>
+        <v>-1.704712312906831</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>-0.0008479197134423351</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-0.02945290609327835</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -1331,7 +1331,7 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>-0.5747222390858621</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -1355,74 +1355,74 @@
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.1475442427870024</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>0.4566708195573823</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0.1303832042632055</v>
+        <v>-0.668536420371175</v>
       </c>
       <c r="Z9" t="n">
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>-0.02533535472743207</v>
+        <v>-0.4727123965416657</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.2533227205008814</v>
+        <v>-0.2412110435397512</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.2367012059207824</v>
+        <v>-0.3673781366639252</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.08647480884779891</v>
+        <v>-0.1629240420143491</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.8033507408814324</v>
+        <v>-0.5438441397254858</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>8KIT2SzJ</t>
+          <t>SM0npHPF</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-1.156642910080833</v>
+        <v>-0.6768995524387025</v>
       </c>
       <c r="C10" t="n">
-        <v>-1.019607118113518</v>
+        <v>1.008351687704268</v>
       </c>
       <c r="D10" t="n">
-        <v>1.858491282928442</v>
+        <v>-0.6572827966819225</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5572718973311804</v>
+        <v>-0.8430651861914329</v>
       </c>
       <c r="F10" t="n">
         <v>-0.3161939140908171</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.143895491436716</v>
+        <v>-1.775552238652255</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.251451573228038</v>
+        <v>0.4659905432842035</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.7222244369793933</v>
+        <v>-0.1753236520640759</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.704712312906831</v>
+        <v>1.134002875826239</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>-0.0008479197134423351</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>-0.02945290609327835</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1431,7 +1431,7 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>0.05867079225544721</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -1455,74 +1455,74 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-0.2945998259591579</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.4929677292310901</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.5809051748532111</v>
+        <v>-0.6772624973238178</v>
       </c>
       <c r="Z10" t="n">
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.1782349927224163</v>
+        <v>-1.052382111277284</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.14742917306234</v>
+        <v>-0.607270681512437</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.1188064739952693</v>
+        <v>-0.3282624831437208</v>
       </c>
       <c r="AE10" t="n">
-        <v>-0.08275601019472806</v>
+        <v>0.2637299423156031</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.6134182093954561</v>
+        <v>-0.6637816798584217</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>E1Xs9lu2</t>
+          <t>OlferefS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.116923437005787</v>
+        <v>-0.03028893996452622</v>
       </c>
       <c r="C11" t="n">
-        <v>1.008351687704268</v>
+        <v>1.961895232161637</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.2786545907204963</v>
+        <v>0.6048112231894981</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.8430651861914329</v>
+        <v>-0.185983939307745</v>
       </c>
       <c r="F11" t="n">
         <v>-0.3161939140908171</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.09113424607748329</v>
+        <v>2.961873365464291</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3927305149719172</v>
+        <v>0.03663001415614314</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1892768712128023</v>
+        <v>2.376880010874072</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.9950335157235638</v>
+        <v>0.4243240786429714</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>-0.0008479197134423351</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>-0.02945290609327835</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1531,7 +1531,7 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>0.6920638235967563</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -1555,274 +1555,274 @@
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>-0.4562905690798093</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>0.2973647340197388</v>
       </c>
       <c r="Y11" t="n">
-        <v>-0.5257635316976885</v>
+        <v>1.897316535415044</v>
       </c>
       <c r="Z11" t="n">
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>-0.6503101965120481</v>
+        <v>1.892425111201265</v>
       </c>
       <c r="AB11" t="n">
-        <v>-1.0894391780166</v>
+        <v>3.664697070260524</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>-0.5412146705835658</v>
+        <v>2.265898417916833</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.7289616688824532</v>
+        <v>0.0838308543246023</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.2012448768339101</v>
+        <v>-0.9010470733100063</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>ITdtTrn2</t>
+          <t>0ns5XwtA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.930401304312008</v>
+        <v>-0.6038951284496825</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.2137956720932055</v>
+        <v>0.2428308139849714</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.3712081521777338</v>
+        <v>0.8319881467663537</v>
       </c>
       <c r="E12" t="n">
-        <v>0.8157956665968937</v>
+        <v>1.235896791653678</v>
       </c>
       <c r="F12" t="n">
         <v>-0.3161939140908171</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.7227909932930227</v>
+        <v>-0.8280671178289459</v>
       </c>
       <c r="H12" t="n">
         <v>-0.8220910440999777</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3715771328512414</v>
+        <v>-1.086824960256272</v>
       </c>
       <c r="J12" t="n">
-        <v>0.4243240786429714</v>
+        <v>-0.9950335157235638</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>-0.0008479197134423351</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>-0.02945290609327835</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>0.5760838195275146</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.380592482994433</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>0.05867079225544721</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>0.9634607773628866</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1.015650466645634</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2.136050641715271</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1.145295406980734</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1.613590159757053</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>0.528804747714731</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-0.07265321001223485</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>-0.5256451789121339</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-1.137863613594894</v>
       </c>
       <c r="Y12" t="n">
-        <v>-0.3103209566115768</v>
+        <v>-2.031009384004508</v>
       </c>
       <c r="Z12" t="n">
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.1620971692446173</v>
+        <v>-2.910320844164445</v>
       </c>
       <c r="AB12" t="n">
-        <v>-0.04659575832850694</v>
+        <v>-5.519382384445691</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.1741614340996327</v>
+        <v>-2.458316212808772</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.2509099200156272</v>
+        <v>-0.2966774314496025</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0.4537266872241248</v>
+        <v>0.4283519452472794</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>M3h3GWnS</t>
+          <t>CQ0ABdJj</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-1.427802199182907</v>
+        <v>1.221215471275815</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2428308139849714</v>
+        <v>-0.8987354012104708</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.321985647147537</v>
+        <v>0.2850807381554049</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2556608331878484</v>
+        <v>-0.035178407236079</v>
       </c>
       <c r="F13" t="n">
         <v>-0.3161939140908171</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.670276114116332</v>
+        <v>0.1194180029943632</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.680812102356098</v>
+        <v>0.895351072412264</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.269125221894711</v>
+        <v>-0.3576239137025151</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.9950335157235638</v>
+        <v>1.134002875826239</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>-0.0008479197134423351</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>-0.02945290609327835</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>-0.5927100236415342</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.120759039854493</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>0.05867079225544721</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>0.04384578161981739</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-0.05809667966731939</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>-1.900263169126615</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>-0.2874505755292275</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>-0.05541843446779299</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>-1.2924631077809</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>-0.07265321001223485</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.729081610373652</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-0.3657031853940205</v>
       </c>
       <c r="Y13" t="n">
-        <v>-1.858685770101388</v>
+        <v>0.3846154768477741</v>
       </c>
       <c r="Z13" t="n">
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>-3.097323490843598</v>
+        <v>0.1530676065222563</v>
       </c>
       <c r="AB13" t="n">
-        <v>-5.646402083515123</v>
+        <v>0.678937486783986</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>-2.297905675938274</v>
+        <v>0.8185573277449283</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.2688330649808613</v>
+        <v>-0.5248659253589179</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.7707679551628334</v>
+        <v>-0.6659309966070026</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Eax2EqHs</t>
+          <t>KhwykQ8L</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9709145890277466</v>
+        <v>1.012631402735758</v>
       </c>
       <c r="C14" t="n">
-        <v>-1.18076940731758</v>
+        <v>-0.2137956720932055</v>
       </c>
       <c r="D14" t="n">
         <v>-0.446933793370019</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.6384005355227432</v>
+        <v>0.8157956665968937</v>
       </c>
       <c r="F14" t="n">
         <v>-0.3161939140908171</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2246941275302864</v>
+        <v>1.172179248353596</v>
       </c>
       <c r="H14" t="n">
-        <v>1.324711601540324</v>
+        <v>0.895351072412264</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7361776561281197</v>
+        <v>1.647678964320315</v>
       </c>
       <c r="J14" t="n">
-        <v>1.134002875826239</v>
+        <v>0.4243240786429714</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>-0.0008479197134423351</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>-0.02945290609327835</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1831,7 +1831,7 @@
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>0.05867079225544721</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -1855,174 +1855,174 @@
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>0.1389035524662068</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-0.7201469612228875</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.1284653216468656</v>
+        <v>1.599733812403837</v>
       </c>
       <c r="Z14" t="n">
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.4550913463905611</v>
+        <v>1.571384532797011</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.073664567078601</v>
+        <v>1.735574084224872</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.005357709036498</v>
+        <v>1.699005155245699</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.08153952606774897</v>
+        <v>0.3461594197461879</v>
       </c>
       <c r="AF14" t="n">
-        <v>-1.648848705001845</v>
+        <v>-0.02995493811942317</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>KbKTWiX8</t>
+          <t>v1KiOZ2d</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-1.031492468956799</v>
+        <v>0.9709145890277466</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.05263338288914304</v>
+        <v>0.9412007338692419</v>
       </c>
       <c r="D15" t="n">
-        <v>1.858491282928442</v>
+        <v>-0.446933793370019</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6542183108058229</v>
+        <v>1.203581320495464</v>
       </c>
       <c r="F15" t="n">
         <v>-0.3161939140908171</v>
       </c>
       <c r="G15" t="n">
-        <v>-2.617761234939641</v>
+        <v>0.2246941275302864</v>
       </c>
       <c r="H15" t="n">
-        <v>-2.110172631484159</v>
+        <v>0.895351072412264</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.180626530086907</v>
+        <v>0.7361776561281197</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.704712312906831</v>
+        <v>0.4243240786429714</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>-0.0008479197134423351</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>-0.02945290609327835</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>0.3423250508937048</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.380592482994433</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>0.05867079225544721</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>0.04384578161981739</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-0.05809667966731939</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>-2.438438343905533</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>3.724238175498664</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>-2.690695162191234</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.439438675462547</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.4430892968748174</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>-1.035826754276455</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.3124260203095288</v>
       </c>
       <c r="Y15" t="n">
-        <v>-1.648959751912772</v>
+        <v>1.032527387056111</v>
       </c>
       <c r="Z15" t="n">
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>-2.005236735224019</v>
+        <v>1.148980708661915</v>
       </c>
       <c r="AB15" t="n">
-        <v>-3.158601791938133</v>
+        <v>1.296228158906324</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>-1.793322966209051</v>
+        <v>0.8624471533992253</v>
       </c>
       <c r="AE15" t="n">
-        <v>-0.08422467868644465</v>
+        <v>-0.09831067429528116</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.1165347973347795</v>
+        <v>0.2685679049992022</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>ruUIA1G6</t>
+          <t>f92vnwe3</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.9480588415407764</v>
+        <v>1.930401304312008</v>
       </c>
       <c r="C16" t="n">
         <v>-0.4018183428312783</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2786545907204963</v>
+        <v>-0.3712081521777338</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1048553011161823</v>
+        <v>-0.035178407236079</v>
       </c>
       <c r="F16" t="n">
         <v>-0.3161939140908171</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2246941275302864</v>
+        <v>-0.1964103706134065</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>0.895351072412264</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3715771328512414</v>
+        <v>-0.5399241753409542</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>0.4243240786429714</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>-0.0008479197134423351</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>-0.02945290609327835</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2031,7 +2031,7 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>0.05867079225544721</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
@@ -2055,434 +2055,1634 @@
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.3377424968294769</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.136307996601569</v>
+        <v>0.3293581491332161</v>
       </c>
       <c r="Z16" t="n">
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.105820576083965</v>
+        <v>0.2990525626135488</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.6496783713259646</v>
+        <v>0.03946434900179228</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.9772565782250728</v>
+        <v>0.3759750074585397</v>
       </c>
       <c r="AE16" t="n">
-        <v>-0.1867211936922793</v>
+        <v>-0.4109444071146311</v>
       </c>
       <c r="AF16" t="n">
-        <v>-0.005684086171706431</v>
+        <v>-0.1273112437849857</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>hnqZAAAk</t>
+          <t>0Y1WIvRG</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.6038951284496825</v>
+        <v>-0.6768995524387025</v>
       </c>
       <c r="C17" t="n">
-        <v>0.8740497800342159</v>
+        <v>-1.019607118113518</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3776342996126424</v>
+        <v>-0.6572827966819225</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6542183108058229</v>
+        <v>1.849890743659747</v>
       </c>
       <c r="F17" t="n">
         <v>-0.3161939140908171</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.406962619685253</v>
+        <v>-1.354447740508562</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.8220910440999777</v>
+        <v>0.4659905432842035</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.7222244369793933</v>
+        <v>-0.1753236520640759</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.9950335157235638</v>
+        <v>0.4243240786429714</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>-0.0008479197134423351</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>-0.02945290609327835</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>0.3423250508937048</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>-2.320240301305864</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>0.533715565761429</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>0.04384578161981739</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.131843825980273</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.059700292157434</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>-0.2874505755292275</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>-2.954222834963578</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.439438675462547</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-3.167108251334549</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.3852664050176349</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.5946277218528135</v>
       </c>
       <c r="Y17" t="n">
-        <v>-0.5696580224274288</v>
+        <v>1.072684893651564</v>
       </c>
       <c r="Z17" t="n">
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>-0.8903221109964237</v>
+        <v>0.5438361926025077</v>
       </c>
       <c r="AB17" t="n">
-        <v>-0.6074621512786482</v>
+        <v>0.894371144681178</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>-1.035882512175636</v>
+        <v>0.8200928324252474</v>
       </c>
       <c r="AE17" t="n">
-        <v>-1.363527292776956</v>
+        <v>0.443579632273531</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.3813919174581616</v>
+        <v>0.5114746253820348</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>nDzACNof</t>
+          <t>8CpDVHAM</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-1.156642910080833</v>
+        <v>-1.177501316934839</v>
       </c>
       <c r="C18" t="n">
-        <v>0.9412007338692419</v>
+        <v>-0.05263338288914304</v>
       </c>
       <c r="D18" t="n">
-        <v>1.858491282928442</v>
+        <v>-0.446933793370019</v>
       </c>
       <c r="E18" t="n">
-        <v>1.203581320495464</v>
+        <v>1.849890743659747</v>
       </c>
       <c r="F18" t="n">
         <v>-0.3161939140908171</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2246941275302864</v>
+        <v>-1.880828363188178</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4659905432842035</v>
+        <v>0.895351072412264</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7361776561281197</v>
+        <v>-1.633725745171589</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4243240786429714</v>
+        <v>1.134002875826239</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>-0.0008479197134423351</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-0.02945290609327835</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>-1.293986329542964</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.133870297374413</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>0.05867079225544721</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>0.04384578161981739</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.05809667966731939</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.136050641715271</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>0.8587462104787417</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.579858293255648</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>-1.2924631077809</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.990316817535974</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.01830336918801166</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.5248344554006344</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.6694948643754925</v>
+        <v>-0.8656993792002827</v>
       </c>
       <c r="Z18" t="n">
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.29419995506045</v>
+        <v>-1.565555052884447</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.3013695788089274</v>
+        <v>-3.350160857743008</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.1553824725741556</v>
+        <v>-2.031531100248878</v>
       </c>
       <c r="AE18" t="n">
-        <v>-0.1865945751512605</v>
+        <v>-0.1724487404143693</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.6954890850639265</v>
+        <v>1.996061154101972</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>QyafIhIF</t>
+          <t>4KmdZaBc</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.60709599807492</v>
+        <v>-1.427802199182907</v>
       </c>
       <c r="C19" t="n">
-        <v>1.223234739976351</v>
+        <v>0.8740497800342159</v>
       </c>
       <c r="D19" t="n">
-        <v>1.219030312860256</v>
+        <v>-0.2786545907204963</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.9184679522272658</v>
+        <v>0.3741508941013003</v>
       </c>
       <c r="F19" t="n">
         <v>-0.3161939140908171</v>
       </c>
       <c r="G19" t="n">
-        <v>0.8563508747458258</v>
+        <v>-1.143895491436716</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4659905432842035</v>
+        <v>-0.8220910440999777</v>
       </c>
       <c r="I19" t="n">
-        <v>0.006976609574363205</v>
+        <v>-1.269125221894711</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4243240786429714</v>
+        <v>-0.2853547185402961</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>-0.0008479197134423351</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>-0.02945290609327835</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>-1.293986329542964</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>-0.5931850019657258</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>0.05867079225544721</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>-0.8757692141232519</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.131843825980273</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>-1.093000406958238</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>-2.293294951043173</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1.613590159757053</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>0.07348778384082316</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.5883957168992872</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.112892576863358</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.2984096952300594</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.2624753674757944</v>
+        <v>-0.2656892840308702</v>
       </c>
       <c r="Z19" t="n">
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.606571420497667</v>
+        <v>-0.9652226953925841</v>
       </c>
       <c r="AB19" t="n">
-        <v>-0.4512294150507359</v>
+        <v>-0.4211069802241545</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>-0.3594202665678702</v>
+        <v>-0.7728486396565969</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.188833999592257</v>
+        <v>-0.5654053358389591</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.530828808151101</v>
+        <v>0.5630393566933021</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>hO0nKEm3</t>
+          <t>hpMqQeYq</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.6768995524387025</v>
+        <v>1.116923437005787</v>
       </c>
       <c r="C20" t="n">
-        <v>0.6457365369951275</v>
+        <v>-1.167339216550575</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.549162570724393</v>
+        <v>-0.2786545907204963</v>
       </c>
       <c r="E20" t="n">
-        <v>1.278984086531297</v>
+        <v>1.203581320495464</v>
       </c>
       <c r="F20" t="n">
         <v>-0.3161939140908171</v>
       </c>
       <c r="G20" t="n">
+        <v>0.01414187845843995</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.895351072412264</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.006976609574363205</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.843681673009507</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-0.0008479197134423351</v>
+      </c>
+      <c r="L20" t="n">
+        <v>-0.02945290609327835</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>-0.8914187547565166</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.006510066316039</v>
+      </c>
+      <c r="X20" t="n">
+        <v>-1.768922429281603</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0.6255796148815073</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0.8126284772961069</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.2209184506424494</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.3954275180880775</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0.8815382317411677</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0.8846033307732526</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>ChPK4l66</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1.012631402735758</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1.223234739976351</v>
+      </c>
+      <c r="D21" t="n">
+        <v>-0.446933793370019</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-1.543233727952739</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-0.3161939140908171</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.3299702520662097</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.895351072412264</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.006976609574363205</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.134002875826239</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.05867079225544721</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>-0.2366342108138557</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0.8710626877604557</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.479922316476511</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.5425084149537478</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0.1714217223657018</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0.5309823478743868</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.094818695116107</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>MNr3HRkC</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0.887480961611724</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1.639570653753512</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1.858491282928442</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-1.543233727952739</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-0.3161939140908171</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-0.406962619685253</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-0.3927305149719172</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-0.9045246986178325</v>
+      </c>
+      <c r="J22" t="n">
+        <v>-0.2853547185402961</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-1.995262635444393</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-1.826795930065825</v>
+      </c>
+      <c r="O22" t="n">
+        <v>-0.8914187547565166</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0.04384578161981739</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.015650466645634</v>
+      </c>
+      <c r="R22" t="n">
+        <v>3.212400991273106</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.285647817474757</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0.2081092383045511</v>
+      </c>
+      <c r="U22" t="n">
+        <v>-0.8371461439069926</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0.9588318037618696</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>-1.106161796638896</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>-1.709969778273847</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>-0.6606610867054626</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>-0.6120838804732882</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>-0.7899943544199132</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>-1.411746023277988</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>hA5zaJZp</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>-0.3118774324936029</v>
+      </c>
+      <c r="C23" t="n">
+        <v>-0.5898410135693511</v>
+      </c>
+      <c r="D23" t="n">
+        <v>-1.448195049134679</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.3741508941013003</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-0.3161939140908171</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.01414187845843995</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-0.3927305149719172</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.1892768712128023</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.4243240786429714</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-1.060227560909154</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-0.5931850019657258</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.05867079225544721</v>
+      </c>
+      <c r="P23" t="n">
+        <v>-0.8757692141232519</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>-1.131843825980273</v>
+      </c>
+      <c r="R23" t="n">
+        <v>-0.5548252321793197</v>
+      </c>
+      <c r="S23" t="n">
+        <v>-0.2874505755292275</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0.7351645838492393</v>
+      </c>
+      <c r="U23" t="n">
+        <v>-0.3818291800330847</v>
+      </c>
+      <c r="V23" t="n">
+        <v>-0.07265321001223485</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>-1.042448060312279</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-0.2257855640615001</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>-0.4005910651114789</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>-0.585895266688051</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0.9330285687741228</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>-0.003928269243288692</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>IVonL9jm</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0.2721579594185562</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1.961895232161637</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-0.2786545907204963</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-0.185983939307745</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-0.3161939140908171</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2.751321116392444</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.895351072412264</v>
+      </c>
+      <c r="I24" t="n">
+        <v>2.74148053415095</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.4243240786429714</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.05867079225544721</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>-0.06675753490876454</v>
+      </c>
+      <c r="X24" t="n">
+        <v>-1.661139749895</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>2.760694120216267</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>2.845122874433018</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>5.900857071302608</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>2.691444566581236</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>-0.2308406041203185</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>-0.2478190088472578</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>YcAFQVSP</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0.6684676896446642</v>
+      </c>
+      <c r="C25" t="n">
+        <v>-1.18076940731758</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-0.6572827966819225</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-1.52169008051393</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-0.3161939140908171</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-0.406962619685253</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-0.8220910440999777</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-0.7222244369793933</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-0.9950335157235638</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-0.5927100236415342</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-1.086629373205765</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-1.84150830176848</v>
+      </c>
+      <c r="P25" t="n">
+        <v>-0.8757692141232519</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-0.05809667966731939</v>
+      </c>
+      <c r="R25" t="n">
+        <v>-2.438438343905533</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.285647817474757</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.2081092383045511</v>
+      </c>
+      <c r="U25" t="n">
+        <v>-1.2924631077809</v>
+      </c>
+      <c r="V25" t="n">
+        <v>-0.5883957168992872</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0.1097377127848397</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0.2439362711101416</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>-0.5591050194317576</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-0.4519143619341202</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0.01717201917458904</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.4295040048866132</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.191807543877616</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>-1.520800638436431</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>OQqSjnv9</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>-0.1658685845155632</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.9680611154032523</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.3608063793476901</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-1.52169008051393</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-0.3161939140908171</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-0.7227909932930227</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-0.8220910440999777</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-0.1753236520640759</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-0.2853547185402961</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.008760339267411</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>-2.02511938744238</v>
+      </c>
+      <c r="X26" t="n">
+        <v>-0.5936106642506791</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>-0.849029775825624</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-0.9919350742640745</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>-1.373664422827336</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>-1.412197502455455</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>-0.2638840182350394</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1.047236419809635</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>WhAFMMRi</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>-0.03028893996452622</v>
+      </c>
+      <c r="C27" t="n">
+        <v>-0.6435617766373719</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.6048112231894981</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-1.33856907728405</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-0.3161939140908171</v>
+      </c>
+      <c r="G27" t="n">
+        <v>4.541015233503139</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.895351072412264</v>
+      </c>
+      <c r="I27" t="n">
+        <v>4.92908367381222</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.843681673009507</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>2.679912737231803</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-0.8399071875857457</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.958849886279375</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0.9634607773628866</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>-0.05809667966731939</v>
+      </c>
+      <c r="R27" t="n">
+        <v>-0.5548252321793197</v>
+      </c>
+      <c r="S27" t="n">
+        <v>-0.2874505755292275</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0.3837943534861138</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.894755639336455</v>
+      </c>
+      <c r="V27" t="n">
+        <v>-0.5883957168992872</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>-0.7446437181682024</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0.6325080157823088</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.529351313932162</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>2.488503462004362</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.057176682989516</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>-0.2813089220211093</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>-0.6968636171839567</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>vJDNK0d4</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>-0.9480588415407764</v>
+      </c>
+      <c r="C28" t="n">
+        <v>-1.462803413424689</v>
+      </c>
+      <c r="D28" t="n">
+        <v>-1.448195049134679</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1.235896791653678</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-0.3161939140908171</v>
+      </c>
+      <c r="G28" t="n">
         <v>0.4352463766021329</v>
       </c>
-      <c r="H20" t="n">
+      <c r="H28" t="n">
+        <v>0.03663001415614314</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.829979225958754</v>
+      </c>
+      <c r="J28" t="n">
+        <v>-0.2853547185402961</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.043601356795134</v>
+      </c>
+      <c r="N28" t="n">
+        <v>-0.8399071875857457</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.05867079225544721</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0.04384578161981739</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>-0.05809667966731939</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0.7906127047679753</v>
+      </c>
+      <c r="S28" t="n">
+        <v>1.718393799984718</v>
+      </c>
+      <c r="T28" t="n">
+        <v>-2.515010047009671</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0.07348778384082316</v>
+      </c>
+      <c r="V28" t="n">
+        <v>-0.07265321001223485</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>3.022944463192594</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>-0.2968871276919609</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-0.08690027965431606</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0.05782969642979482</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.09835131267592243</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>-0.1049165563694611</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>-0.3845885447895117</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>QekfJmLa</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>0.8249057410497068</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1.102363023073304</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.8319881467663537</v>
+      </c>
+      <c r="E29" t="n">
+        <v>-0.2613867053435781</v>
+      </c>
+      <c r="F29" t="n">
+        <v>-0.3161939140908171</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.9616269992817491</v>
+      </c>
+      <c r="H29" t="n">
         <v>0.4659905432842035</v>
       </c>
-      <c r="I20" t="n">
+      <c r="I29" t="n">
+        <v>1.465378702681876</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.134002875826239</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0.05867079225544721</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1.74053653265652</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>-0.1847705676394522</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>-0.001039038949466637</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0.2450434769700311</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.2665723853186396</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>-0.04174167545033492</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>-0.8098573412606362</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>8KIT2SzJ</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>-1.156642910080833</v>
+      </c>
+      <c r="C30" t="n">
+        <v>-1.019607118113518</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1.858491282928442</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1.849890743659747</v>
+      </c>
+      <c r="F30" t="n">
+        <v>-0.3161939140908171</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-1.143895491436716</v>
+      </c>
+      <c r="H30" t="n">
+        <v>-1.251451573228038</v>
+      </c>
+      <c r="I30" t="n">
+        <v>-0.7222244369793933</v>
+      </c>
+      <c r="J30" t="n">
+        <v>-1.704712312906831</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.108566282259895</v>
+      </c>
+      <c r="N30" t="n">
+        <v>-2.073518115685845</v>
+      </c>
+      <c r="O30" t="n">
+        <v>2.908939433291338</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0.9634607773628866</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>-1.131843825980273</v>
+      </c>
+      <c r="R30" t="n">
+        <v>-0.8239128195687787</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.864590585992687</v>
+      </c>
+      <c r="T30" t="n">
+        <v>-2.515010047009671</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.439438675462547</v>
+      </c>
+      <c r="V30" t="n">
+        <v>-3.167108251334549</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0.6450775346551467</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0.2178827180173717</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0.2131202294454134</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.2114878544824629</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>-0.005250675983204982</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0.5794352962155028</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>E1Xs9lu2</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1.116923437005787</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1.008351687704268</v>
+      </c>
+      <c r="D31" t="n">
+        <v>-0.2786545907204963</v>
+      </c>
+      <c r="E31" t="n">
+        <v>-0.8430651861914329</v>
+      </c>
+      <c r="F31" t="n">
+        <v>-0.3161939140908171</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-0.09113424607748329</v>
+      </c>
+      <c r="H31" t="n">
+        <v>-0.3927305149719172</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.1892768712128023</v>
+      </c>
+      <c r="J31" t="n">
+        <v>-0.9950335157235638</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>-0.4834389476969019</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0.618087296929863</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>-0.5677243657714689</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>-1.07269013879256</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.362718942735733</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>-0.5472419666341661</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0.6977963342776422</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>0.2764589659053621</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>ITdtTrn2</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>1.930401304312008</v>
+      </c>
+      <c r="C32" t="n">
+        <v>-0.2137956720932055</v>
+      </c>
+      <c r="D32" t="n">
+        <v>-0.3712081521777338</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.8157956665968937</v>
+      </c>
+      <c r="F32" t="n">
+        <v>-0.3161939140908171</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-0.7227909932930227</v>
+      </c>
+      <c r="H32" t="n">
+        <v>-0.8220910440999777</v>
+      </c>
+      <c r="I32" t="n">
         <v>0.3715771328512414</v>
       </c>
-      <c r="J20" t="n">
-        <v>-0.2853547185402961</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>0.7873569375092309</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>0.4393090395846398</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>0.84253873956543</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>0.5589628259938779</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>-0.9349533108397521</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>0.2424535890876401</v>
+      <c r="J32" t="n">
+        <v>0.4243240786429714</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>-0.3464859108108901</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-0.007917159427234718</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0.1539113670454686</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>-0.0529771982305355</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>0.03347523177498831</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.1562189135389227</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0.2461080541936868</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>-0.5018765176947321</v>
       </c>
     </row>
   </sheetData>

--- a/data/spain/p6_deployment/data_preparation/df_selected_nan.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_selected_nan.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF20"/>
+  <dimension ref="A1:AF30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -588,1220 +588,1220 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MNr3HRkC</t>
+          <t>YN50iYWr</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.887480961611724</v>
+        <v>0.2721579594185562</v>
       </c>
       <c r="C2" t="n">
         <v>1.639570653753512</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3776342996126424</v>
+        <v>-0.2786545907204963</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2556608331878484</v>
+        <v>-1.543233727952739</v>
       </c>
       <c r="F2" t="n">
         <v>-0.3161939140908171</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.406962619685253</v>
+        <v>2.119664369176905</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.3927305149719172</v>
+        <v>0.4659905432842035</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.9045246986178325</v>
+        <v>1.647678964320315</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.2853547185402961</v>
+        <v>0.4243240786429714</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>0.5987362797997117</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>0.9675559952517809</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>-1.293986329542964</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>-0.346462816345706</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>0.05867079225544721</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>0.04384578161981739</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-0.05809667966731939</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>-1.093000406958238</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.145295406980734</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>-2.339324931828108</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>0.07348778384082316</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.474574310648922</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>-0.8731201978089164</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-0.8811837012552609</v>
       </c>
       <c r="Y2" t="n">
-        <v>-1.176549014244474</v>
+        <v>1.474949198964272</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>-1.834193508340854</v>
+        <v>1.438041068781859</v>
       </c>
       <c r="AB2" t="n">
-        <v>-0.6802337814803333</v>
+        <v>5.089434551698367</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0.6153565546655116</v>
+        <v>1.662621156047688</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0.8501718887317512</v>
+        <v>-1.131487722966445</v>
       </c>
       <c r="AF2" t="n">
-        <v>-1.624646159320207</v>
+        <v>-0.8949306483828875</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hA5zaJZp</t>
+          <t>h4pRxZHk</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.3118774324936029</v>
+        <v>0.6684676896446642</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.5898410135693511</v>
+        <v>0.9680611154032523</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.000993906348783775</v>
+        <v>-0.6572827966819225</v>
       </c>
       <c r="E3" t="n">
-        <v>1.203581320495464</v>
+        <v>-1.52169008051393</v>
       </c>
       <c r="F3" t="n">
         <v>-0.3161939140908171</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01414187845843995</v>
+        <v>0.4352463766021329</v>
       </c>
       <c r="H3" t="n">
         <v>-0.3927305149719172</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1892768712128023</v>
+        <v>0.5538773944896805</v>
       </c>
       <c r="J3" t="n">
         <v>0.4243240786429714</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>-0.6004321192265963</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>-1.026461807438338</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>-0.3589512550077246</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>-1.333351558825785</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>0.3753673079261018</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>0.04384578161981739</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.131843825980273</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>-0.5548252321793197</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>-1.720196558039189</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.019071081209555</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>-1.2924631077809</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>-0.5883957168992872</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>-0.1746402550614765</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-1.369625614682141</v>
       </c>
       <c r="Y3" t="n">
-        <v>-1.109160730370822</v>
+        <v>-0.7395983748862066</v>
       </c>
       <c r="Z3" t="n">
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0.2352867091787993</v>
+        <v>-0.971137039656529</v>
       </c>
       <c r="AB3" t="n">
-        <v>-0.4108480807015764</v>
+        <v>-1.115281360112996</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0.6111610675644065</v>
+        <v>-0.6153153609049162</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.8150478963411982</v>
+        <v>1.090847567656925</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.07444269734402216</v>
+        <v>0.07027992109869055</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>IVonL9jm</t>
+          <t>n1v9mjW7</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2721579594185562</v>
+        <v>0.8249057410497068</v>
       </c>
       <c r="C4" t="n">
-        <v>1.961895232161637</v>
+        <v>1.223234739976351</v>
       </c>
       <c r="D4" t="n">
-        <v>1.219030312860256</v>
+        <v>0.8319881467663537</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.185983939307745</v>
+        <v>-1.543233727952739</v>
       </c>
       <c r="F4" t="n">
         <v>-0.3161939140908171</v>
       </c>
       <c r="G4" t="n">
-        <v>2.751321116392444</v>
+        <v>-0.1964103706134065</v>
       </c>
       <c r="H4" t="n">
-        <v>0.895351072412264</v>
+        <v>-1.680812102356098</v>
       </c>
       <c r="I4" t="n">
-        <v>2.74148053415095</v>
+        <v>-0.5399241753409542</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4243240786429714</v>
+        <v>-1.704712312906831</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>-0.0008479197134423351</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>-0.02945290609327835</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.277360125428944</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>-1.086629373205765</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>0.05867079225544721</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>0.9634607773628866</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1.015650466645634</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.136050641715271</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>0.8587462104787417</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>0.7351645838492393</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.439438675462547</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.4430892968748174</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>-0.26907250576961</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>0.4457713522544692</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.851519830913291</v>
+        <v>0.1945557599077535</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.96772352855776</v>
+        <v>0.907124397345265</v>
       </c>
       <c r="AB4" t="n">
-        <v>6.186017148108498</v>
+        <v>-0.2953122322423963</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.764847738754058</v>
+        <v>-0.1208519062213011</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0.1945225964520229</v>
+        <v>1.189753943656909</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.261277791646914</v>
+        <v>0.5367736080749596</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>OQqSjnv9</t>
+          <t>tQQLbGv9</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.1658685845155632</v>
+        <v>0.887480961611724</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9680611154032523</v>
+        <v>-0.5898410135693511</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3608063793476901</v>
+        <v>1.858491282928442</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.8430651861914329</v>
+        <v>0.3741508941013003</v>
       </c>
       <c r="F5" t="n">
         <v>-0.3161939140908171</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.7227909932930227</v>
+        <v>0.2246941275302864</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.8220910440999777</v>
+        <v>-0.3927305149719172</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1753236520640759</v>
+        <v>0.1892768712128023</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.2853547185402961</v>
+        <v>-0.9950335157235638</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>-0.0008479197134423351</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-0.02945290609327835</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>-1.060227560909154</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>-3.060406858165924</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>-0.2580257234152074</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>-0.8757692141232519</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.05809667966731939</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.405138229104729</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-2.006745754541182</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>0.9986922566215833</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>-1.2924631077809</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.5883957168992872</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.07945874966631063</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>0.8288408972370866</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.8269791228363323</v>
+        <v>-0.5418041990823114</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.99526791243123</v>
+        <v>-0.2336554884809496</v>
       </c>
       <c r="AB5" t="n">
-        <v>-1.308091264757385</v>
+        <v>-0.2205392685845242</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>-1.372596817464782</v>
+        <v>0.1952152235592716</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.324792896010433</v>
+        <v>0.6354538630409192</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.010919377807262</v>
+        <v>-0.9205206084565062</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>YcAFQVSP</t>
+          <t>vyy1kC1e</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6684676896446642</v>
+        <v>-0.9480588415407764</v>
       </c>
       <c r="C6" t="n">
-        <v>-1.18076940731758</v>
+        <v>-1.167339216550575</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.321985647147537</v>
+        <v>-1.448195049134679</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.6384005355227432</v>
+        <v>1.203581320495464</v>
       </c>
       <c r="F6" t="n">
         <v>-0.3161939140908171</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.406962619685253</v>
+        <v>-0.5122387442211762</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.8220910440999777</v>
+        <v>0.03663001415614314</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7222244369793933</v>
+        <v>-0.5399241753409542</v>
       </c>
       <c r="J6" t="n">
         <v>-0.9950335157235638</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>-0.0008479197134423351</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-0.02945290609327835</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2.446153968597993</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>-0.09974063072568611</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>-0.5747222390858621</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-0.8757692141232519</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.05809667966731939</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.597875466936352</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-3.152942540549151</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>0.2081092383045511</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>0.528804747714731</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.9588318037618696</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.106465257510448</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.033666062255833</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.5642056869979519</v>
+        <v>-0.1342134832552984</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.5305236641352513</v>
+        <v>-0.2465853083157257</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.01926224934003505</v>
+        <v>0.08742366575769804</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.4127120164855981</v>
+        <v>-0.02990349448117196</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.250893659554744</v>
+        <v>0.1735500695152346</v>
       </c>
       <c r="AF6" t="n">
-        <v>-1.55008095527556</v>
+        <v>0.2162267338875962</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>WhAFMMRi</t>
+          <t>EJYZzDn2</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.03028893996452622</v>
+        <v>-1.031492468956799</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.6435617766373719</v>
+        <v>1.102363023073304</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9349434810536349</v>
+        <v>0.6048112231894981</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.6384005355227432</v>
+        <v>-0.8430651861914329</v>
       </c>
       <c r="F7" t="n">
         <v>-0.3161939140908171</v>
       </c>
       <c r="G7" t="n">
-        <v>4.541015233503139</v>
+        <v>-0.1964103706134065</v>
       </c>
       <c r="H7" t="n">
-        <v>0.895351072412264</v>
+        <v>-0.3927305149719172</v>
       </c>
       <c r="I7" t="n">
-        <v>4.92908367381222</v>
+        <v>1.100778179404998</v>
       </c>
       <c r="J7" t="n">
-        <v>1.843681673009507</v>
+        <v>1.134002875826239</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>-0.0008479197134423351</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-0.02945290609327835</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>-0.3589512550077246</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.874036854234473</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>-0.2580257234152074</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-0.8757692141232519</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.05809667966731939</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.328787879546893</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>0.8587462104787417</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>0.6473220262584579</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>-0.8371461439069926</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.474574310648922</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.04097587739552059</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>0.3663764456395519</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.636710425956089</v>
+        <v>-1.219004225618601</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.514135274997804</v>
+        <v>-0.983960028422509</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.310345541214724</v>
+        <v>-0.4417994939409507</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.060786637639232</v>
+        <v>-0.6217842421819845</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.2967117883698193</v>
+        <v>-0.7645744459353041</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.6427585751231412</v>
+        <v>-1.272208353762502</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>vJDNK0d4</t>
+          <t>xhKUdf9L</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.9480588415407764</v>
+        <v>-0.3118774324936029</v>
       </c>
       <c r="C8" t="n">
         <v>-1.462803413424689</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2786545907204963</v>
+        <v>-1.448195049134679</v>
       </c>
       <c r="E8" t="n">
-        <v>1.278984086531297</v>
+        <v>1.235896791653678</v>
       </c>
       <c r="F8" t="n">
         <v>-0.3161939140908171</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4352463766021329</v>
+        <v>-0.3016864951493298</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03663001415614314</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>1.829979225958754</v>
+        <v>-0.5399241753409542</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.2853547185402961</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>-0.0008479197134423351</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-0.02945290609327835</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>-0.3589512550077246</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>0.6404259261343733</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>0.05867079225544721</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.04384578161981739</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.05809667966731939</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>0.2524375299890573</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.004942996486711</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>-0.4067886648309185</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>-0.3818291800330847</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.4430892968748174</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>0.8147801914622566</v>
       </c>
       <c r="Y8" t="n">
-        <v>-0.2837709551007949</v>
+        <v>-1.320935541689849</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>-0.08276385474384988</v>
+        <v>-0.1724533422257953</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.05329763002034062</v>
+        <v>-0.5538270259764786</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.07712301797458589</v>
+        <v>-0.8362329100145018</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.05927344714980161</v>
+        <v>0.2134513761857451</v>
       </c>
       <c r="AF8" t="n">
-        <v>-0.395486291866894</v>
+        <v>-0.312634537913667</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>QekfJmLa</t>
+          <t>GOO6q4Wr</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8249057410497068</v>
+        <v>-0.1658685845155632</v>
       </c>
       <c r="C9" t="n">
-        <v>1.102363023073304</v>
+        <v>-1.18076940731758</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.9349434810536349</v>
+        <v>-0.1692731089983065</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2613867053435781</v>
+        <v>-1.52169008051393</v>
       </c>
       <c r="F9" t="n">
         <v>-0.3161939140908171</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9616269992817491</v>
+        <v>0.3299702520662097</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4659905432842035</v>
+        <v>-0.8220910440999777</v>
       </c>
       <c r="I9" t="n">
-        <v>1.465378702681876</v>
+        <v>0.1892768712128023</v>
       </c>
       <c r="J9" t="n">
-        <v>1.134002875826239</v>
+        <v>-1.704712312906831</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>-0.0008479197134423351</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-0.02945290609327835</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>-0.3589512550077246</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>0.1469815548943337</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>-0.8914187547565166</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-1.795384209866321</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0.05809667966731939</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>-3.514788693463369</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>0.285647817474757</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>-1.900112143874201</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>-1.2924631077809</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-1.104138223786339</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.2498134335339074</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>0.4566708195573823</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0.1303832042632055</v>
+        <v>-0.6961399933103511</v>
       </c>
       <c r="Z9" t="n">
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>-0.02533535472743207</v>
+        <v>-0.4822755915408862</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.2533227205008814</v>
+        <v>-0.2393580337578897</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.2367012059207824</v>
+        <v>-0.3367915558762485</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.08647480884779891</v>
+        <v>-0.1779247553563874</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.8033507408814324</v>
+        <v>-0.6177819524544923</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>8KIT2SzJ</t>
+          <t>SM0npHPF</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-1.156642910080833</v>
+        <v>-0.6768995524387025</v>
       </c>
       <c r="C10" t="n">
-        <v>-1.019607118113518</v>
+        <v>1.008351687704268</v>
       </c>
       <c r="D10" t="n">
-        <v>1.858491282928442</v>
+        <v>-0.6572827966819225</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5572718973311804</v>
+        <v>-0.8430651861914329</v>
       </c>
       <c r="F10" t="n">
         <v>-0.3161939140908171</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.143895491436716</v>
+        <v>-1.775552238652255</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.251451573228038</v>
+        <v>0.4659905432842035</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.7222244369793933</v>
+        <v>-0.1753236520640759</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.704712312906831</v>
+        <v>1.134002875826239</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>-0.0008479197134423351</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>-0.02945290609327835</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>-0.5927100236415342</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>0.1469815548943337</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>0.05867079225544721</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-0.8757692141232519</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.131843825980273</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.328787879546893</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.718393799984718</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>-1.197371683147951</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>-0.3818291800330847</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-0.5883957168992872</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-0.2945998259591579</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.5828095125159749</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.5809051748532111</v>
+        <v>-0.6856535227250711</v>
       </c>
       <c r="Z10" t="n">
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.1782349927224163</v>
+        <v>-1.002915092662761</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.14742917306234</v>
+        <v>-0.6592181814145193</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.1188064739952693</v>
+        <v>-0.3490700366541794</v>
       </c>
       <c r="AE10" t="n">
-        <v>-0.08275601019472806</v>
+        <v>0.2840929355764061</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.6134182093954561</v>
+        <v>-0.6268745520221745</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>E1Xs9lu2</t>
+          <t>OlferefS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.116923437005787</v>
+        <v>-0.03028893996452622</v>
       </c>
       <c r="C11" t="n">
-        <v>1.008351687704268</v>
+        <v>1.961895232161637</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.2786545907204963</v>
+        <v>0.6048112231894981</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.8430651861914329</v>
+        <v>0.3526072466624908</v>
       </c>
       <c r="F11" t="n">
         <v>-0.3161939140908171</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.09113424607748329</v>
+        <v>2.961873365464291</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3927305149719172</v>
+        <v>0.03663001415614314</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1892768712128023</v>
+        <v>2.376880010874072</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.9950335157235638</v>
+        <v>0.4243240786429714</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>-0.0008479197134423351</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>-0.02945290609327835</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1.511118894062754</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>-1.086629373205765</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>0.05867079225544721</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>0.9634607773628866</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1.015650466645634</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>-0.5548252321793197</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>0.8587462104787417</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>-1.724427028692639</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2.350072603210362</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-0.5883957168992872</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>-0.4562905690798093</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>0.3345509025979147</v>
       </c>
       <c r="Y11" t="n">
-        <v>-0.5257635316976885</v>
+        <v>1.897242466257742</v>
       </c>
       <c r="Z11" t="n">
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>-0.6503101965120481</v>
+        <v>1.908488345105489</v>
       </c>
       <c r="AB11" t="n">
-        <v>-1.0894391780166</v>
+        <v>3.655991313976797</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>-0.5412146705835658</v>
+        <v>2.235397524974445</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.7289616688824532</v>
+        <v>0.07488336642020067</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.2012448768339101</v>
+        <v>-0.8607852980686309</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>ITdtTrn2</t>
+          <t>0ns5XwtA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.930401304312008</v>
+        <v>-0.6038951284496825</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.2137956720932055</v>
+        <v>0.2428308139849714</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.3712081521777338</v>
+        <v>0.8319881467663537</v>
       </c>
       <c r="E12" t="n">
-        <v>0.8157956665968937</v>
+        <v>1.235896791653678</v>
       </c>
       <c r="F12" t="n">
         <v>-0.3161939140908171</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.7227909932930227</v>
+        <v>-0.8280671178289459</v>
       </c>
       <c r="H12" t="n">
         <v>-0.8220910440999777</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3715771328512414</v>
+        <v>-1.086824960256272</v>
       </c>
       <c r="J12" t="n">
-        <v>0.4243240786429714</v>
+        <v>-0.9950335157235638</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>-0.0008479197134423351</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>-0.02945290609327835</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>0.5760838195275146</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.380592482994433</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>0.05867079225544721</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>0.9634607773628866</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1.015650466645634</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.866963054325812</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1.145295406980734</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1.43790504457549</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>0.528804747714731</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-0.07265321001223485</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>-0.5256451789121339</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-1.113072834542771</v>
       </c>
       <c r="Y12" t="n">
-        <v>-0.3103209566115768</v>
+        <v>-2.031009384004508</v>
       </c>
       <c r="Z12" t="n">
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.1620971692446173</v>
+        <v>-2.910320844164445</v>
       </c>
       <c r="AB12" t="n">
-        <v>-0.04659575832850694</v>
+        <v>-5.519382384445691</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.1741614340996327</v>
+        <v>-2.458316212808772</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.2509099200156272</v>
+        <v>-0.296677431449594</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0.4537266872241248</v>
+        <v>0.4283519452472794</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>M3h3GWnS</t>
+          <t>CQ0ABdJj</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-1.427802199182907</v>
+        <v>1.221215471275815</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2428308139849714</v>
+        <v>-0.8987354012104708</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.321985647147537</v>
+        <v>0.2850807381554049</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2556608331878484</v>
+        <v>-0.035178407236079</v>
       </c>
       <c r="F13" t="n">
         <v>-0.3161939140908171</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.670276114116332</v>
+        <v>0.1194180029943632</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.680812102356098</v>
+        <v>0.895351072412264</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.269125221894711</v>
+        <v>-0.3576239137025151</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.9950335157235638</v>
+        <v>1.134002875826239</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>-0.0008479197134423351</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>-0.02945290609327835</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>-0.5927100236415342</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.120759039854493</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>0.05867079225544721</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>0.04384578161981739</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-0.05809667966731939</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>-1.900263169126615</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>-0.2874505755292275</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>-0.05541843446779299</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>-1.2924631077809</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>-0.07265321001223485</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.701283608861908</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-0.3657031853940205</v>
       </c>
       <c r="Y13" t="n">
-        <v>-1.858685770101388</v>
+        <v>0.3846154768477741</v>
       </c>
       <c r="Z13" t="n">
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>-3.097323490843598</v>
+        <v>0.1530676065222563</v>
       </c>
       <c r="AB13" t="n">
-        <v>-5.646402083515123</v>
+        <v>0.678937486783986</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>-2.297905675938274</v>
+        <v>0.8185573277449283</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.2688330649808613</v>
+        <v>-0.5248659253589179</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.7707679551628334</v>
+        <v>-0.6659309966070026</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Eax2EqHs</t>
+          <t>v1KiOZ2d</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>0.9709145890277466</v>
       </c>
       <c r="C14" t="n">
-        <v>-1.18076940731758</v>
+        <v>0.9412007338692419</v>
       </c>
       <c r="D14" t="n">
         <v>-0.446933793370019</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.6384005355227432</v>
+        <v>1.203581320495464</v>
       </c>
       <c r="F14" t="n">
         <v>-0.3161939140908171</v>
@@ -1810,679 +1810,1679 @@
         <v>0.2246941275302864</v>
       </c>
       <c r="H14" t="n">
-        <v>1.324711601540324</v>
+        <v>0.895351072412264</v>
       </c>
       <c r="I14" t="n">
         <v>0.7361776561281197</v>
       </c>
       <c r="J14" t="n">
-        <v>1.134002875826239</v>
+        <v>0.4243240786429714</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>-0.0008479197134423351</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>-0.02945290609327835</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>0.3423250508937048</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.380592482994433</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>0.05867079225544721</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>0.04384578161981739</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-0.05809667966731939</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>-2.438438343905533</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>3.724238175498664</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>-2.690695162191234</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.439438675462547</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.4430892968748174</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>-1.028656634838908</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-0.3124260203095288</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.1284653216468656</v>
+        <v>1.032527387056111</v>
       </c>
       <c r="Z14" t="n">
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.4550913463905611</v>
+        <v>1.148980708661915</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.073664567078601</v>
+        <v>1.296228158906324</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.005357709036498</v>
+        <v>0.8624471533992253</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.08153952606774897</v>
+        <v>-0.09831067429528964</v>
       </c>
       <c r="AF14" t="n">
-        <v>-1.648848705001845</v>
+        <v>0.2685679049992022</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>KbKTWiX8</t>
+          <t>KhwykQ8L</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-1.031492468956799</v>
+        <v>1.012631402735758</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.05263338288914304</v>
+        <v>-0.2137956720932055</v>
       </c>
       <c r="D15" t="n">
-        <v>1.858491282928442</v>
+        <v>1.875319203193395</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6542183108058229</v>
+        <v>0.3526072466624908</v>
       </c>
       <c r="F15" t="n">
         <v>-0.3161939140908171</v>
       </c>
       <c r="G15" t="n">
-        <v>-2.617761234939641</v>
+        <v>1.172179248353596</v>
       </c>
       <c r="H15" t="n">
-        <v>-2.110172631484159</v>
+        <v>0.895351072412264</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.180626530086907</v>
+        <v>1.647678964320315</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.704712312906831</v>
+        <v>0.4243240786429714</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>-0.0008479197134423351</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>-0.02945290609327835</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>0.108566282259895</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>-1.086629373205765</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>0.533715565761429</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.883075773105956</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1.015650466645634</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>0.5215251173785164</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>-2.579844147545166</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>-0.1432609920585743</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.439438675462547</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-0.07265321001223485</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>0.5144413157462693</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.5466115078580512</v>
       </c>
       <c r="Y15" t="n">
-        <v>-1.648959751912772</v>
+        <v>1.635728410744267</v>
       </c>
       <c r="Z15" t="n">
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>-2.005236735224019</v>
+        <v>1.531480709181709</v>
       </c>
       <c r="AB15" t="n">
-        <v>-3.158601791938133</v>
+        <v>1.785668574345093</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>-1.793322966209051</v>
+        <v>1.689226127968481</v>
       </c>
       <c r="AE15" t="n">
-        <v>-0.08422467868644465</v>
+        <v>0.3407971398274146</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.1165347973347795</v>
+        <v>0.007075746773336074</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>ruUIA1G6</t>
+          <t>f92vnwe3</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.9480588415407764</v>
+        <v>1.930401304312008</v>
       </c>
       <c r="C16" t="n">
         <v>-0.4018183428312783</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2786545907204963</v>
+        <v>-0.1692731089983065</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1048553011161823</v>
+        <v>-0.035178407236079</v>
       </c>
       <c r="F16" t="n">
         <v>-0.3161939140908171</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2246941275302864</v>
+        <v>-0.1964103706134065</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>0.895351072412264</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3715771328512414</v>
+        <v>-0.5399241753409542</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>0.4243240786429714</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>-0.0008479197134423351</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>-0.02945290609327835</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>0.5760838195275146</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>-1.580073744445805</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1.008760339267411</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>0.04384578161981739</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.131843825980273</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>0.7906127047679753</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-1.720196558039189</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>-0.5824737800124812</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>-0.3818291800330847</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-1.619880730673392</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.3735930940172377</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.136307996601569</v>
+        <v>0.3294322182905179</v>
       </c>
       <c r="Z16" t="n">
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.105820576083965</v>
+        <v>0.2829893287093249</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.6496783713259646</v>
+        <v>0.04817010528552004</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.9772565782250728</v>
+        <v>0.4064759004009277</v>
       </c>
       <c r="AE16" t="n">
-        <v>-0.1867211936922793</v>
+        <v>-0.4019969192102295</v>
       </c>
       <c r="AF16" t="n">
-        <v>-0.005684086171706431</v>
+        <v>-0.1675730190263611</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>hnqZAAAk</t>
+          <t>0Y1WIvRG</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.6038951284496825</v>
+        <v>-0.6768995524387025</v>
       </c>
       <c r="C17" t="n">
-        <v>0.8740497800342159</v>
+        <v>-1.019607118113518</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3776342996126424</v>
+        <v>-0.6572827966819225</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6542183108058229</v>
+        <v>1.849890743659747</v>
       </c>
       <c r="F17" t="n">
         <v>-0.3161939140908171</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.406962619685253</v>
+        <v>-1.354447740508562</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.8220910440999777</v>
+        <v>0.4659905432842035</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.7222244369793933</v>
+        <v>-0.1753236520640759</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.9950335157235638</v>
+        <v>0.4243240786429714</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>-0.0008479197134423351</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>-0.02945290609327835</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>0.3423250508937048</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>-2.320240301305864</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>0.533715565761429</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>0.04384578161981739</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.131843825980273</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.059700292157434</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>-0.2874505755292275</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>-2.954222834963578</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.439438675462547</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-3.167108251334549</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.3852664050176349</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.5946277218528135</v>
       </c>
       <c r="Y17" t="n">
-        <v>-0.5696580224274288</v>
+        <v>1.072684893651564</v>
       </c>
       <c r="Z17" t="n">
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>-0.8903221109964237</v>
+        <v>0.5438361926025077</v>
       </c>
       <c r="AB17" t="n">
-        <v>-0.6074621512786482</v>
+        <v>0.894371144681178</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>-1.035882512175636</v>
+        <v>0.8200928324252474</v>
       </c>
       <c r="AE17" t="n">
-        <v>-1.363527292776956</v>
+        <v>0.443579632273531</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.3813919174581616</v>
+        <v>0.5114746253820348</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>nDzACNof</t>
+          <t>8CpDVHAM</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-1.156642910080833</v>
+        <v>-1.177501316934839</v>
       </c>
       <c r="C18" t="n">
-        <v>0.9412007338692419</v>
+        <v>-0.05263338288914304</v>
       </c>
       <c r="D18" t="n">
-        <v>1.858491282928442</v>
+        <v>-0.446933793370019</v>
       </c>
       <c r="E18" t="n">
-        <v>1.203581320495464</v>
+        <v>1.849890743659747</v>
       </c>
       <c r="F18" t="n">
         <v>-0.3161939140908171</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2246941275302864</v>
+        <v>-1.880828363188178</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4659905432842035</v>
+        <v>0.895351072412264</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7361776561281197</v>
+        <v>-1.633725745171589</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4243240786429714</v>
+        <v>1.134002875826239</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>-0.0008479197134423351</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-0.02945290609327835</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>-1.293986329542964</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.133870297374413</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>0.05867079225544721</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>0.04384578161981739</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.05809667966731939</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.136050641715271</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>0.8587462104787417</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.579858293255648</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>-1.2924631077809</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.990316817535974</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.01830336918801166</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.5248344554006344</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.6694948643754925</v>
+        <v>-0.8656993792002827</v>
       </c>
       <c r="Z18" t="n">
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.29419995506045</v>
+        <v>-1.565555052884447</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.3013695788089274</v>
+        <v>-3.350160857743008</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.1553824725741556</v>
+        <v>-2.031531100248878</v>
       </c>
       <c r="AE18" t="n">
-        <v>-0.1865945751512605</v>
+        <v>-0.1724487404143608</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.6954890850639265</v>
+        <v>1.996061154101972</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>QyafIhIF</t>
+          <t>4KmdZaBc</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.60709599807492</v>
+        <v>-1.427802199182907</v>
       </c>
       <c r="C19" t="n">
-        <v>1.223234739976351</v>
+        <v>0.8740497800342159</v>
       </c>
       <c r="D19" t="n">
-        <v>1.219030312860256</v>
+        <v>-0.2786545907204963</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.9184679522272658</v>
+        <v>0.3741508941013003</v>
       </c>
       <c r="F19" t="n">
         <v>-0.3161939140908171</v>
       </c>
       <c r="G19" t="n">
-        <v>0.8563508747458258</v>
+        <v>-1.143895491436716</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4659905432842035</v>
+        <v>-0.8220910440999777</v>
       </c>
       <c r="I19" t="n">
-        <v>0.006976609574363205</v>
+        <v>-1.269125221894711</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4243240786429714</v>
+        <v>-0.2853547185402961</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>-0.0008479197134423351</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>-0.02945290609327835</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>-1.293986329542964</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>-0.5931850019657258</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>0.05867079225544721</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>-0.8757692141232519</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.131843825980273</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>-1.093000406958238</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>-2.006745754541182</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1.43790504457549</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>0.07348778384082316</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.5883957168992872</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.112892576863358</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.2984096952300594</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.2624753674757944</v>
+        <v>-0.2656892840308702</v>
       </c>
       <c r="Z19" t="n">
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.606571420497667</v>
+        <v>-0.9652226953925841</v>
       </c>
       <c r="AB19" t="n">
-        <v>-0.4512294150507359</v>
+        <v>-0.4211069802241542</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>-0.3594202665678702</v>
+        <v>-0.7728486396565969</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.188833999592257</v>
+        <v>-0.5654053358389591</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.530828808151101</v>
+        <v>0.5630393566933021</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>hO0nKEm3</t>
+          <t>hpMqQeYq</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.6768995524387025</v>
+        <v>1.116923437005787</v>
       </c>
       <c r="C20" t="n">
-        <v>0.6457365369951275</v>
+        <v>-1.167339216550575</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.549162570724393</v>
+        <v>1.875319203193395</v>
       </c>
       <c r="E20" t="n">
-        <v>1.278984086531297</v>
+        <v>1.203581320495464</v>
       </c>
       <c r="F20" t="n">
         <v>-0.3161939140908171</v>
       </c>
       <c r="G20" t="n">
+        <v>0.01414187845843995</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.895351072412264</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.006976609574363205</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.843681673009507</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-0.0008479197134423351</v>
+      </c>
+      <c r="L20" t="n">
+        <v>-0.02945290609327835</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.5760838195275146</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-0.09974063072568611</v>
+      </c>
+      <c r="O20" t="n">
+        <v>-0.8914187547565166</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.04384578161981739</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.015650466645634</v>
+      </c>
+      <c r="R20" t="n">
+        <v>-0.5548252321793197</v>
+      </c>
+      <c r="S20" t="n">
+        <v>-3.726040933553135</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.701432717347835</v>
+      </c>
+      <c r="U20" t="n">
+        <v>-0.3818291800330847</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.474574310648922</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0.8675200587573262</v>
+      </c>
+      <c r="X20" t="n">
+        <v>-1.768922429281603</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0.5863728097379768</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0.7721290820206032</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.2439402425559602</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.4277024586067361</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0.7657497164856871</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0.7297431250758097</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>ChPK4l66</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1.012631402735758</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1.223234739976351</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.875319203193395</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-1.543233727952739</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-0.3161939140908171</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.3299702520662097</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.895351072412264</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.006976609574363205</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.134002875826239</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>-0.5927100236415342</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-2.813684672545904</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.05867079225544721</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.9634607773628866</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.015650466645634</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.7906127047679753</v>
+      </c>
+      <c r="S21" t="n">
+        <v>-1.433647361537197</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0.3837943534861138</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.439438675462547</v>
+      </c>
+      <c r="V21" t="n">
+        <v>-0.5883957168992872</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0.8794537131617089</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.430455297861988</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.5944559148558302</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0.1922292758761603</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0.5106193546135837</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.05791156727986</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>MNr3HRkC</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0.887480961611724</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1.639570653753512</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1.858491282928442</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-1.543233727952739</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-0.3161939140908171</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-0.406962619685253</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-0.3927305149719172</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-0.9045246986178325</v>
+      </c>
+      <c r="J22" t="n">
+        <v>-0.2853547185402961</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-1.995262635444393</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-1.826795930065825</v>
+      </c>
+      <c r="O22" t="n">
+        <v>-0.8914187547565166</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0.04384578161981739</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.015650466645634</v>
+      </c>
+      <c r="R22" t="n">
+        <v>3.212400991273106</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.285647817474757</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0.2081092383045511</v>
+      </c>
+      <c r="U22" t="n">
+        <v>-0.8371461439069926</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0.9588318037618696</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>-1.106161796638896</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>-1.709969778273847</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>-0.6606610867054626</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>-0.6120838804732882</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>-0.7899943544199047</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>-1.411746023277988</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>hA5zaJZp</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>-0.3118774324936029</v>
+      </c>
+      <c r="C23" t="n">
+        <v>-0.5898410135693511</v>
+      </c>
+      <c r="D23" t="n">
+        <v>-1.448195049134679</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.3741508941013003</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-0.3161939140908171</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.01414187845843995</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-0.3927305149719172</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.1892768712128023</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.4243240786429714</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-1.060227560909154</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-0.5931850019657258</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.05867079225544721</v>
+      </c>
+      <c r="P23" t="n">
+        <v>-0.8757692141232519</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>-1.131843825980273</v>
+      </c>
+      <c r="R23" t="n">
+        <v>-0.5548252321793197</v>
+      </c>
+      <c r="S23" t="n">
+        <v>-0.2874505755292275</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0.7351645838492393</v>
+      </c>
+      <c r="U23" t="n">
+        <v>-0.3818291800330847</v>
+      </c>
+      <c r="V23" t="n">
+        <v>-0.07265321001223485</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>-1.042448060312279</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-0.2257855640615001</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>-0.4005910651114789</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>-0.585895266688051</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0.9330285687741228</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>-0.003928269243288692</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>IVonL9jm</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0.2721579594185562</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1.961895232161637</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-0.2786545907204963</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.3526072466624908</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-0.3161939140908171</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2.751321116392444</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.895351072412264</v>
+      </c>
+      <c r="I24" t="n">
+        <v>2.74148053415095</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.4243240786429714</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.3423250508937048</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.3937037405143535</v>
+      </c>
+      <c r="O24" t="n">
+        <v>-1.84150830176848</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.04384578161981739</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.015650466645634</v>
+      </c>
+      <c r="R24" t="n">
+        <v>-2.169350756516073</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.8587462104787417</v>
+      </c>
+      <c r="T24" t="n">
+        <v>-1.81226958628342</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.528804747714731</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.474574310648922</v>
+      </c>
+      <c r="W24" t="n">
+        <v>-0.06675753490876454</v>
+      </c>
+      <c r="X24" t="n">
+        <v>-1.586767412738644</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>2.760620051058965</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>2.861186108337242</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>5.89215131501888</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>2.660943673638848</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>-0.2397880920247286</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>-0.2075572336058824</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>YcAFQVSP</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0.6684676896446642</v>
+      </c>
+      <c r="C25" t="n">
+        <v>-1.18076940731758</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-0.6572827966819225</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-1.52169008051393</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-0.3161939140908171</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-0.406962619685253</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-0.8220910440999777</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-0.7222244369793933</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-0.9950335157235638</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-0.5927100236415342</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-1.086629373205765</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-1.84150830176848</v>
+      </c>
+      <c r="P25" t="n">
+        <v>-0.8757692141232519</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-0.05809667966731939</v>
+      </c>
+      <c r="R25" t="n">
+        <v>-2.438438343905533</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.285647817474757</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.2081092383045511</v>
+      </c>
+      <c r="U25" t="n">
+        <v>-1.2924631077809</v>
+      </c>
+      <c r="V25" t="n">
+        <v>-0.5883957168992872</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0.1097377127848397</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0.2439362711101416</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>-0.5591050194317576</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-0.4519143619341202</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0.01717201917458904</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.4295040048866132</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.191807543877607</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>-1.520800638436431</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>OQqSjnv9</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>-0.1658685845155632</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.9680611154032523</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-0.1692731089983065</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-1.52169008051393</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-0.3161939140908171</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-0.7227909932930227</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-0.8220910440999777</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-0.1753236520640759</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-0.2853547185402961</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-0.1251924863739148</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-0.09974063072568611</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.05867079225544721</v>
+      </c>
+      <c r="P26" t="n">
+        <v>-0.8757692141232519</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-1.131843825980273</v>
+      </c>
+      <c r="R26" t="n">
+        <v>-1.631175581737156</v>
+      </c>
+      <c r="S26" t="n">
+        <v>-1.720196558039189</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0.910849699030802</v>
+      </c>
+      <c r="U26" t="n">
+        <v>-1.2924631077809</v>
+      </c>
+      <c r="V26" t="n">
+        <v>-1.104138223786339</v>
+      </c>
+      <c r="W26" t="n">
+        <v>-1.69051381368992</v>
+      </c>
+      <c r="X26" t="n">
+        <v>-0.5936106642506791</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>-0.8766333487648001</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-1.001498269263295</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>-1.371811413045475</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>-1.381610921667778</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>-0.2788847315770691</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0.9732986070806289</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>WhAFMMRi</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>-0.03028893996452622</v>
+      </c>
+      <c r="C27" t="n">
+        <v>-0.6435617766373719</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.6048112231894981</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-1.33856907728405</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-0.3161939140908171</v>
+      </c>
+      <c r="G27" t="n">
+        <v>4.541015233503139</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.895351072412264</v>
+      </c>
+      <c r="I27" t="n">
+        <v>4.92908367381222</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.843681673009507</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>2.679912737231803</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-0.8399071875857457</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.958849886279375</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0.9634607773628866</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>-0.05809667966731939</v>
+      </c>
+      <c r="R27" t="n">
+        <v>-0.5548252321793197</v>
+      </c>
+      <c r="S27" t="n">
+        <v>-0.2874505755292275</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0.3837943534861138</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.894755639336455</v>
+      </c>
+      <c r="V27" t="n">
+        <v>-0.5883957168992872</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>-0.7446437181682024</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0.6325080157823088</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.529351313932162</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>2.488503462004362</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.057176682989516</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>-0.2813089220211093</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>-0.6968636171839567</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>vJDNK0d4</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>-0.9480588415407764</v>
+      </c>
+      <c r="C28" t="n">
+        <v>-1.462803413424689</v>
+      </c>
+      <c r="D28" t="n">
+        <v>-1.448195049134679</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1.235896791653678</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-0.3161939140908171</v>
+      </c>
+      <c r="G28" t="n">
         <v>0.4352463766021329</v>
       </c>
-      <c r="H20" t="n">
+      <c r="H28" t="n">
+        <v>0.03663001415614314</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.829979225958754</v>
+      </c>
+      <c r="J28" t="n">
+        <v>-0.2853547185402961</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.043601356795134</v>
+      </c>
+      <c r="N28" t="n">
+        <v>-0.8399071875857457</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.05867079225544721</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0.04384578161981739</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>-0.05809667966731939</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0.7906127047679753</v>
+      </c>
+      <c r="S28" t="n">
+        <v>1.431844603482726</v>
+      </c>
+      <c r="T28" t="n">
+        <v>-2.339324931828108</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0.07348778384082316</v>
+      </c>
+      <c r="V28" t="n">
+        <v>-0.07265321001223485</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>3.022944463192594</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>-0.2968871276919609</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-0.08690027965431606</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0.05782969642979482</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.09835131267592243</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>-0.1049165563694611</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>-0.3845885447895117</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>QekfJmLa</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>0.8249057410497068</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1.102363023073304</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.8319881467663537</v>
+      </c>
+      <c r="E29" t="n">
+        <v>-0.8430651861914329</v>
+      </c>
+      <c r="F29" t="n">
+        <v>-0.3161939140908171</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.9616269992817491</v>
+      </c>
+      <c r="H29" t="n">
         <v>0.4659905432842035</v>
       </c>
-      <c r="I20" t="n">
-        <v>0.3715771328512414</v>
-      </c>
-      <c r="J20" t="n">
-        <v>-0.2853547185402961</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>0.7873569375092309</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>0.4393090395846398</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>0.84253873956543</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>0.5589628259938779</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>-0.9349533108397521</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>0.2424535890876401</v>
+      <c r="I29" t="n">
+        <v>1.465378702681876</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.134002875826239</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>2.446153968597993</v>
+      </c>
+      <c r="N29" t="n">
+        <v>1.133870297374413</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0.05867079225544721</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0.04384578161981739</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>-0.05809667966731939</v>
+      </c>
+      <c r="R29" t="n">
+        <v>2.405138229104729</v>
+      </c>
+      <c r="S29" t="n">
+        <v>1.145295406980734</v>
+      </c>
+      <c r="T29" t="n">
+        <v>-0.7581588951940439</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0.9841217115886389</v>
+      </c>
+      <c r="V29" t="n">
+        <v>-0.07265321001223485</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>-0.1455637624959217</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0.03946035632603709</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0.22202168505652</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.2342974447999809</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0.07404683980514574</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>-0.6549971355631934</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>8KIT2SzJ</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>-1.156642910080833</v>
+      </c>
+      <c r="C30" t="n">
+        <v>-1.019607118113518</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1.858491282928442</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1.849890743659747</v>
+      </c>
+      <c r="F30" t="n">
+        <v>-0.3161939140908171</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-1.143895491436716</v>
+      </c>
+      <c r="H30" t="n">
+        <v>-1.251451573228038</v>
+      </c>
+      <c r="I30" t="n">
+        <v>-0.7222244369793933</v>
+      </c>
+      <c r="J30" t="n">
+        <v>-1.704712312906831</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.108566282259895</v>
+      </c>
+      <c r="N30" t="n">
+        <v>-2.073518115685845</v>
+      </c>
+      <c r="O30" t="n">
+        <v>2.908939433291338</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0.9634607773628866</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>-1.131843825980273</v>
+      </c>
+      <c r="R30" t="n">
+        <v>-0.8239128195687787</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.864590585992687</v>
+      </c>
+      <c r="T30" t="n">
+        <v>-2.515010047009671</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.439438675462547</v>
+      </c>
+      <c r="V30" t="n">
+        <v>-3.167108251334549</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0.6450775346551467</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0.2178827180173717</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0.2131202294454134</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.2114878544824629</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>-0.005250675983204982</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0.5794352962155028</v>
       </c>
     </row>
   </sheetData>

--- a/data/spain/p6_deployment/data_preparation/df_selected_nan.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_selected_nan.xlsx
@@ -1261,28 +1261,28 @@
         <v>0.8147801914622566</v>
       </c>
       <c r="Y8" t="n">
-        <v>-1.320935541689849</v>
+        <v>-1.310007347209919</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>-0.1724533422257953</v>
+        <v>-0.1717378945512999</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0.5538270259764786</v>
+        <v>-0.5507286704751255</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>-0.8362329100145018</v>
+        <v>-0.81547605087001</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.2134513761857451</v>
+        <v>0.2373478169568813</v>
       </c>
       <c r="AF8" t="n">
-        <v>-0.312634537913667</v>
+        <v>-0.288182531181697</v>
       </c>
     </row>
     <row r="9">
@@ -1361,28 +1361,28 @@
         <v>0.4566708195573823</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0.6961399933103511</v>
+        <v>-0.703550279359885</v>
       </c>
       <c r="Z9" t="n">
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>-0.4822755915408862</v>
+        <v>-0.4898013752810422</v>
       </c>
       <c r="AB9" t="n">
-        <v>-0.2393580337578897</v>
+        <v>-0.2364781149664771</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>-0.3367915558762485</v>
+        <v>-0.3220500698145608</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0.1779247553563874</v>
+        <v>-0.2347157385101698</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.6177819524544923</v>
+        <v>-0.6497095969724043</v>
       </c>
     </row>
     <row r="10">
@@ -1961,59 +1961,59 @@
         <v>-0.5466115078580512</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.635728410744267</v>
+        <v>1.6431386967938</v>
       </c>
       <c r="Z15" t="n">
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.531480709181709</v>
+        <v>1.539006492921865</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.785668574345093</v>
+        <v>1.78278865555368</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.689226127968481</v>
+        <v>1.674484641906793</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.3407971398274146</v>
+        <v>0.3975881229811971</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.007075746773336074</v>
+        <v>0.03900339129124807</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>f92vnwe3</t>
+          <t>0Y1WIvRG</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.930401304312008</v>
+        <v>-0.6768995524387025</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.4018183428312783</v>
+        <v>-1.019607118113518</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1692731089983065</v>
+        <v>-0.6572827966819225</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.035178407236079</v>
+        <v>1.849890743659747</v>
       </c>
       <c r="F16" t="n">
         <v>-0.3161939140908171</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.1964103706134065</v>
+        <v>-1.354447740508562</v>
       </c>
       <c r="H16" t="n">
-        <v>0.895351072412264</v>
+        <v>0.4659905432842035</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5399241753409542</v>
+        <v>-0.1753236520640759</v>
       </c>
       <c r="J16" t="n">
         <v>0.4243240786429714</v>
@@ -2025,13 +2025,13 @@
         <v>-0.02945290609327835</v>
       </c>
       <c r="M16" t="n">
-        <v>0.5760838195275146</v>
+        <v>0.3423250508937048</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.580073744445805</v>
+        <v>-2.320240301305864</v>
       </c>
       <c r="O16" t="n">
-        <v>1.008760339267411</v>
+        <v>0.533715565761429</v>
       </c>
       <c r="P16" t="n">
         <v>0.04384578161981739</v>
@@ -2040,80 +2040,80 @@
         <v>-1.131843825980273</v>
       </c>
       <c r="R16" t="n">
-        <v>0.7906127047679753</v>
+        <v>1.059700292157434</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.720196558039189</v>
+        <v>-0.2874505755292275</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5824737800124812</v>
+        <v>-2.954222834963578</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3818291800330847</v>
+        <v>1.439438675462547</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.619880730673392</v>
+        <v>-3.167108251334549</v>
       </c>
       <c r="W16" t="n">
-        <v>0.3735930940172377</v>
+        <v>0.3852664050176349</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.5946277218528135</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.3294322182905179</v>
+        <v>1.072684893651564</v>
       </c>
       <c r="Z16" t="n">
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.2829893287093249</v>
+        <v>0.5438361926025077</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.04817010528552004</v>
+        <v>0.894371144681178</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.4064759004009277</v>
+        <v>0.8200928324252474</v>
       </c>
       <c r="AE16" t="n">
-        <v>-0.4019969192102295</v>
+        <v>0.443579632273531</v>
       </c>
       <c r="AF16" t="n">
-        <v>-0.1675730190263611</v>
+        <v>0.5114746253820348</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>0Y1WIvRG</t>
+          <t>f92vnwe3</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.6768995524387025</v>
+        <v>1.930401304312008</v>
       </c>
       <c r="C17" t="n">
-        <v>-1.019607118113518</v>
+        <v>-0.4018183428312783</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.6572827966819225</v>
+        <v>-0.1692731089983065</v>
       </c>
       <c r="E17" t="n">
-        <v>1.849890743659747</v>
+        <v>-0.035178407236079</v>
       </c>
       <c r="F17" t="n">
         <v>-0.3161939140908171</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.354447740508562</v>
+        <v>-0.1964103706134065</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4659905432842035</v>
+        <v>0.895351072412264</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1753236520640759</v>
+        <v>-0.5399241753409542</v>
       </c>
       <c r="J17" t="n">
         <v>0.4243240786429714</v>
@@ -2125,13 +2125,13 @@
         <v>-0.02945290609327835</v>
       </c>
       <c r="M17" t="n">
-        <v>0.3423250508937048</v>
+        <v>0.5760838195275146</v>
       </c>
       <c r="N17" t="n">
-        <v>-2.320240301305864</v>
+        <v>-1.580073744445805</v>
       </c>
       <c r="O17" t="n">
-        <v>0.533715565761429</v>
+        <v>1.008760339267411</v>
       </c>
       <c r="P17" t="n">
         <v>0.04384578161981739</v>
@@ -2140,49 +2140,49 @@
         <v>-1.131843825980273</v>
       </c>
       <c r="R17" t="n">
-        <v>1.059700292157434</v>
+        <v>0.7906127047679753</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2874505755292275</v>
+        <v>-1.720196558039189</v>
       </c>
       <c r="T17" t="n">
-        <v>-2.954222834963578</v>
+        <v>-0.5824737800124812</v>
       </c>
       <c r="U17" t="n">
-        <v>1.439438675462547</v>
+        <v>-0.3818291800330847</v>
       </c>
       <c r="V17" t="n">
-        <v>-3.167108251334549</v>
+        <v>-1.619880730673392</v>
       </c>
       <c r="W17" t="n">
-        <v>0.3852664050176349</v>
+        <v>0.3735930940172377</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.5946277218528135</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.072684893651564</v>
+        <v>0.3185040238105876</v>
       </c>
       <c r="Z17" t="n">
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.5438361926025077</v>
+        <v>0.2822738810348295</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.894371144681178</v>
+        <v>0.04507174978416707</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.8200928324252474</v>
+        <v>0.3857190412564359</v>
       </c>
       <c r="AE17" t="n">
-        <v>0.443579632273531</v>
+        <v>-0.4258933599813656</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.5114746253820348</v>
+        <v>-0.1920250257583312</v>
       </c>
     </row>
     <row r="18">
@@ -2761,28 +2761,28 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>-1.042448060312279</v>
+        <v>-1.031519865832348</v>
       </c>
       <c r="Z23" t="n">
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>-0.2257855640615001</v>
+        <v>-0.2250701163870046</v>
       </c>
       <c r="AB23" t="n">
-        <v>-0.4005910651114789</v>
+        <v>-0.3974927096101259</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>-0.585895266688051</v>
+        <v>-0.5651384075435592</v>
       </c>
       <c r="AE23" t="n">
-        <v>0.9330285687741228</v>
+        <v>0.9569250095452588</v>
       </c>
       <c r="AF23" t="n">
-        <v>-0.003928269243288692</v>
+        <v>0.02052373748868136</v>
       </c>
     </row>
     <row r="24">
@@ -3061,28 +3061,28 @@
         <v>-0.5936106642506791</v>
       </c>
       <c r="Y26" t="n">
-        <v>-0.8766333487648001</v>
+        <v>-0.884043634814334</v>
       </c>
       <c r="Z26" t="n">
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>-1.001498269263295</v>
+        <v>-1.009024053003451</v>
       </c>
       <c r="AB26" t="n">
-        <v>-1.371811413045475</v>
+        <v>-1.368931494254062</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>-1.381610921667778</v>
+        <v>-1.36686943560609</v>
       </c>
       <c r="AE26" t="n">
-        <v>-0.2788847315770691</v>
+        <v>-0.3356757147308516</v>
       </c>
       <c r="AF26" t="n">
-        <v>0.9732986070806289</v>
+        <v>0.9413709625627168</v>
       </c>
     </row>
     <row r="27">
@@ -3364,7 +3364,7 @@
         <v>-0.1455637624959217</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>-0.5426292992322556</v>
       </c>
       <c r="AA29" t="n">
         <v>0.03946035632603709</v>
@@ -3373,7 +3373,7 @@
         <v>0.22202168505652</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>-1.239917903094969</v>
       </c>
       <c r="AD29" t="n">
         <v>0.2342974447999809</v>
@@ -3464,7 +3464,7 @@
         <v>0.6450775346551467</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>-0.502199844759193</v>
       </c>
       <c r="AA30" t="n">
         <v>0.2178827180173717</v>
@@ -3473,7 +3473,7 @@
         <v>0.2131202294454134</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>-1.195237442222339</v>
       </c>
       <c r="AD30" t="n">
         <v>0.2114878544824629</v>

--- a/data/spain/p6_deployment/data_preparation/df_selected_nan.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_selected_nan.xlsx
@@ -425,55 +425,55 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF5"/>
+  <dimension ref="A1:AA24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>id_team_home</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>id_team_away</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>id_coach_home</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>id_competition</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>is_cup</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>h2h_35</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>h2h_3</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>h2h_35_segun_loc</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>h2h_3_segun_loc</t>
-        </is>
-      </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_n_matches_last_days</t>
@@ -486,237 +486,197 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_goal_attempts</t>
+          <t>dif_mean_last_match_goal_attempts_against</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_goal_attempts_against</t>
+          <t>dif_mean_last_match_points</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_points</t>
+          <t>dif_mean_last_match_goals</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_goals</t>
+          <t>dif_mean_last_match_goals_against</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_goals_against</t>
+          <t>dif_mean_last_match_fouls</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_fouls</t>
+          <t>dif_mean_last_match_fouls_against</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_fouls_against</t>
+          <t>dif_mean_last_match_ball_possession_against</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_ball_possession_against</t>
+          <t>dif_mean_last_match_shots_on_goal</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_shots_on_goal</t>
+          <t>dif_mean_last_match_shots_on_goal_against</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_shots_on_goal_against</t>
+          <t>mean_last_match_mean_rat_player_start_away_against</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>mean_last_match_mean_rat_player_start_home_against</t>
+          <t>dif_mean_rat_player_sub</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>mean_last_match_mean_rat_player_start_away_against</t>
+          <t>dif_mean_int_rep_player_sub</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_rat_player_sub</t>
+          <t>dif_mean_hei_player_sub</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>dif_sum_val_player_miss</t>
+          <t>dif_mean_age_player_sub</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
+          <t>is_rival_match</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>OQqSjnv9</t>
+          <t>YN50iYWr</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.1658685845155632</v>
+        <v>1.820007714807149</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9680611154032523</v>
+        <v>0.3413892579673929</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.1692731089983065</v>
+        <v>1.627330338396051</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.52169008051393</v>
+        <v>-0.3606918734195383</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.3161939140908171</v>
+        <v>-1.625177222108633</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.7227909932930227</v>
+        <v>-0.9805787268653793</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.8220910440999777</v>
+        <v>-0.2234871899330499</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1753236520640759</v>
+        <v>2.756072838946071</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.2853547185402961</v>
+        <v>0.5530804851791808</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>0.7344124969974213</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.149962181909723</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.1251924863739148</v>
+        <v>-0.3553418057503047</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.09974063072568611</v>
+        <v>0.05907866795818074</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05867079225544721</v>
+        <v>0.04235341900418825</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.8757692141232519</v>
+        <v>-0.05113602590509021</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.131843825980273</v>
+        <v>-1.125979158926688</v>
       </c>
       <c r="R2" t="n">
-        <v>-1.631175581737156</v>
+        <v>1.168122082858264</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.720196558039189</v>
+        <v>-2.694691427405241</v>
       </c>
       <c r="T2" t="n">
-        <v>0.910849699030802</v>
+        <v>0.06598445314415635</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.2924631077809</v>
+        <v>1.582561869134317</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.104138223786339</v>
+        <v>0.1648571606990701</v>
       </c>
       <c r="W2" t="n">
-        <v>-1.69051381368992</v>
+        <v>1.721292351429077</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.5936106642506791</v>
+        <v>1.881986879366817</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0.884043634814334</v>
+        <v>-1.149487400761321</v>
       </c>
       <c r="Z2" t="n">
-        <v>-0.0222630948854182</v>
+        <v>-0.8523518863594111</v>
       </c>
       <c r="AA2" t="n">
-        <v>-1.009024053003451</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>-1.368931494254062</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0.06140051982038211</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>-1.36686943560609</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>-0.3356757147308516</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0.9413709625627168</v>
+        <v>-0.1662386772451152</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>YcAFQVSP</t>
+          <t>h4pRxZHk</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6684676896446642</v>
+        <v>1.879628070527517</v>
       </c>
       <c r="C3" t="n">
-        <v>-1.18076940731758</v>
+        <v>0.7168606750380806</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.6572827966819225</v>
+        <v>0.9952379932178427</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.52169008051393</v>
+        <v>-0.7402451889401905</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.3161939140908171</v>
+        <v>-1.603540170994544</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.406962619685253</v>
+        <v>-0.9805787268653793</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.8220910440999777</v>
+        <v>-0.2234871899330499</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.7222244369793933</v>
+        <v>0.5643339658922398</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.9950335157235638</v>
+        <v>-0.449883478646584</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -725,264 +685,1834 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.5927100236415342</v>
+        <v>-1.427573802679572</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.086629373205765</v>
+        <v>0.5596578178690105</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.84150830176848</v>
+        <v>0.04235341900418825</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.8757692141232519</v>
+        <v>-1.201584797557106</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.05809667966731939</v>
+        <v>-0.566808031151543</v>
       </c>
       <c r="R3" t="n">
-        <v>-2.438438343905533</v>
+        <v>-1.74579695739666</v>
       </c>
       <c r="S3" t="n">
-        <v>0.285647817474757</v>
+        <v>3.517074952582656</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2081092383045511</v>
+        <v>-1.46911340857164</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.2924631077809</v>
+        <v>-0.6197160709869246</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.5883957168992872</v>
+        <v>-0.05699808537978705</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1097377127848397</v>
+        <v>-0.8597593171068049</v>
       </c>
       <c r="X3" t="n">
-        <v>0.2439362711101416</v>
+        <v>-1.273048769746285</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.5591050194317576</v>
+        <v>1.114454694362431</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.03055603111971191</v>
+        <v>0.07458340839659147</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0.4519143619341202</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0.01717201917458904</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>-0.2737029367243435</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0.4295040048866132</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.191807543877607</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>-1.520800638436431</v>
+        <v>-0.1662386772451152</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>WhAFMMRi</t>
+          <t>n1v9mjW7</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.03028893996452622</v>
+        <v>1.820007714807149</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.6435617766373719</v>
+        <v>0.8650730765133521</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6048112231894981</v>
+        <v>1.235433084385562</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.33856907728405</v>
+        <v>0.297200540149592</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3161939140908171</v>
+        <v>-1.625177222108633</v>
       </c>
       <c r="G4" t="n">
-        <v>4.541015233503139</v>
+        <v>-0.9805787268653793</v>
       </c>
       <c r="H4" t="n">
-        <v>0.895351072412264</v>
+        <v>-0.2234871899330499</v>
       </c>
       <c r="I4" t="n">
-        <v>4.92908367381222</v>
+        <v>-0.2575681115029471</v>
       </c>
       <c r="J4" t="n">
-        <v>1.843681673009507</v>
+        <v>-1.954329424385231</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>-0.001826621254097982</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>-0.0212614987234063</v>
       </c>
       <c r="M4" t="n">
-        <v>2.679912737231803</v>
+        <v>-2.097718800760363</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.8399071875857457</v>
+        <v>-0.2746407653157058</v>
       </c>
       <c r="O4" t="n">
-        <v>1.958849886279375</v>
+        <v>0.5664439188701677</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9634607773628866</v>
+        <v>1.099312745746926</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.05809667966731939</v>
+        <v>2.36884038966797</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.5548252321793197</v>
+        <v>0.002554466756294189</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2874505755292275</v>
+        <v>0.4621078804574613</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3837943534861138</v>
+        <v>2.62448088933715</v>
       </c>
       <c r="U4" t="n">
-        <v>1.894755639336455</v>
+        <v>0.481422899073696</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.5883957168992872</v>
+        <v>1.005683709890313</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.2611291216986705</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.7446437181682024</v>
+        <v>1.220740385822067</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.6325080157823088</v>
+        <v>1.161901921165196</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.172362075996043</v>
+        <v>0.5910634540484747</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.529351313932162</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>2.488503462004362</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>-0.7316776606688018</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.057176682989516</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>-0.2813089220211093</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>-0.6968636171839567</v>
+        <v>-0.1662386772451152</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>vJDNK0d4</t>
+          <t>tQQLbGv9</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.9480588415407764</v>
+        <v>1.760387359086781</v>
       </c>
       <c r="C5" t="n">
-        <v>-1.462803413424689</v>
+        <v>0.9243580371034607</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.448195049134679</v>
+        <v>-0.4712162475956001</v>
       </c>
       <c r="E5" t="n">
-        <v>1.235896791653678</v>
+        <v>1.781675729741476</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3161939140908171</v>
+        <v>0.3005203270452851</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4352463766021329</v>
+        <v>-0.9805787268653793</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03663001415614314</v>
+        <v>-0.2234871899330499</v>
       </c>
       <c r="I5" t="n">
-        <v>1.829979225958754</v>
+        <v>0.2903666067605108</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.2853547185402961</v>
+        <v>-0.449883478646584</v>
       </c>
       <c r="K5" t="n">
+        <v>-0.001826621254097982</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-1.192485179356536</v>
+      </c>
+      <c r="M5" t="n">
+        <v>-3.303979797305789</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-0.2746407653157058</v>
+      </c>
+      <c r="O5" t="n">
+        <v>-1.00582758072777</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-0.05113602590509021</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.508633171611756</v>
+      </c>
+      <c r="R5" t="n">
+        <v>-2.037188861422153</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.174933530620007</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-1.46911340857164</v>
+      </c>
+      <c r="U5" t="n">
+        <v>-0.6197160709869246</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.248416154185294</v>
+      </c>
+      <c r="W5" t="n">
+        <v>-0.6292305203839251</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-0.3072502775665666</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.650535058975039</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>-0.876927080553953</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>-0.1662386772451152</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>vyy1kC1e</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1.760387359086781</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.8146674735397244</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-1.014815664448859</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-1.533089892472219</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.4844352615150414</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-0.9805787268653793</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-0.2234871899330499</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-0.6685191502005404</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.05159850326629842</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-0.001826621254097982</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-0.0212614987234063</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-0.3553418057503047</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-0.6083601985895924</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-1.52991808059375</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-0.6263604117310982</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.9709125702301064</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-2.037188861422153</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.2584434089824482</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.3218340967634558</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-0.3444313284717694</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.114347632997023</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-0.2229059975078889</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-0.3880460794205367</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.1523903976729984</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.1175682589352894</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-0.1662386772451152</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>EJYZzDn2</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1.760387359086781</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.893714087659869</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.121656462253484</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1.781675729741476</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-0.3377726808203395</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-0.9805787268653793</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-0.2234871899330499</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-0.2575681115029471</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-0.449883478646584</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-0.001826621254097982</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-0.0212614987234063</v>
+      </c>
+      <c r="M7" t="n">
+        <v>-0.2213128061341464</v>
+      </c>
+      <c r="N7" t="n">
+        <v>-1.275799065137365</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-1.00582758072777</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.099312745746926</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.110705352173893</v>
+      </c>
+      <c r="R7" t="n">
+        <v>-0.5802293412946906</v>
+      </c>
+      <c r="S7" t="n">
+        <v>-0.1998016518363311</v>
+      </c>
+      <c r="T7" t="n">
+        <v>-0.4457148340944425</v>
+      </c>
+      <c r="U7" t="n">
+        <v>-0.3444313284717694</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.7702733284664288</v>
+      </c>
+      <c r="W7" t="n">
+        <v>-1.436498406119787</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-1.373309940190961</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>-0.8049339449070689</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>-1.223904984434127</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>-0.1662386772451152</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>xhKUdf9L</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1.790197536946965</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-0.2119370408736204</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-1.292936296327271</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-1.533089892472219</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-0.3594097319344284</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-0.9805787268653793</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-0.2234871899330499</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-0.3945517910688116</v>
+      </c>
+      <c r="J8" t="n">
         <v>0</v>
       </c>
-      <c r="L5" t="n">
+      <c r="K8" t="n">
+        <v>-0.001826621254097982</v>
+      </c>
+      <c r="L8" t="n">
+        <v>-0.0212614987234063</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.4488321919466454</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.3927981012320673</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.5664439188701677</v>
+      </c>
+      <c r="P8" t="n">
+        <v>-0.05113602590509021</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.6913270063425337</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.605209938896502</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.5130239983262145</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.3218340967634558</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.2061381565585409</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.732256345266096</v>
+      </c>
+      <c r="W8" t="n">
+        <v>-1.505066595391495</v>
+      </c>
+      <c r="X8" t="n">
+        <v>-0.216570710244497</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.2289903123830555</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>-0.2688337014755864</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>-0.1662386772451152</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>GOO6q4Wr</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.879628070527517</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-0.07360546616336709</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-1.027457511352423</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-0.2510431378246833</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-1.603540170994544</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-0.9805787268653793</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-0.2234871899330499</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.4273502863263753</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-0.9513654605594664</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-0.001826621254097982</v>
+      </c>
+      <c r="L9" t="n">
+        <v>-0.0212614987234063</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.1807741927143287</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-1.442658781774309</v>
+      </c>
+      <c r="O9" t="n">
+        <v>-2.054008580459729</v>
+      </c>
+      <c r="P9" t="n">
+        <v>-0.05113602590509021</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>-3.642249233914841</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.2939463707817866</v>
+      </c>
+      <c r="S9" t="n">
+        <v>-2.185530248717708</v>
+      </c>
+      <c r="T9" t="n">
+        <v>-1.46911340857164</v>
+      </c>
+      <c r="U9" t="n">
+        <v>-1.170285556017235</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.256088519952595</v>
+      </c>
+      <c r="W9" t="n">
+        <v>-0.8177453192119756</v>
+      </c>
+      <c r="X9" t="n">
+        <v>-0.6426963790388309</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>-0.235925953078628</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>-0.6168550375302072</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>-0.1662386772451152</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>SM0npHPF</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1.849817892667333</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-0.5577659776492538</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.033163533928535</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.80697928410952</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-0.9219730609007416</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-0.9805787268653793</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0.2234871899330499</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-2.312323304990914</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.5530804851791808</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-0.001826621254097982</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.149962181909723</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.1807741927143287</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-0.2746407653157058</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-1.00582758072777</v>
+      </c>
+      <c r="P10" t="n">
+        <v>-0.6263604117310982</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.83111978828632</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.168122082858264</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.2584434089824482</v>
+      </c>
+      <c r="T10" t="n">
+        <v>-0.701564477713742</v>
+      </c>
+      <c r="U10" t="n">
+        <v>-0.06914658595661426</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.3539222980764235</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-0.8320647735730389</v>
+      </c>
+      <c r="X10" t="n">
+        <v>-1.325256495365197</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.329556154200657</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>-0.6218834431238804</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>-0.1662386772451152</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>OlferefS</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1.849817892667333</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.05484528178186816</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.930734664081591</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.80697928410952</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.2788832759311962</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-0.9805787268653793</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-0.2234871899330499</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.851942275472987</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.05159850326629842</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-0.001826621254097982</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-1.192485179356536</v>
+      </c>
+      <c r="M11" t="n">
+        <v>-0.8914578042149381</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.7265175345059538</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.090534418736147</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.099312745746926</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>-1.265771940870474</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.8767301788327715</v>
+      </c>
+      <c r="S11" t="n">
+        <v>-1.930949659373942</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.601082314859953</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-0.06914658595661426</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.9352087479563191</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.95685401287206</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2.277921931760277</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.1517816234098696</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>-0.8878561448613461</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>-0.1662386772451152</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>0ns5XwtA</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1.849817892667333</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-0.4886001902941271</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.312578260425378</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.7526645187743746</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.166002371608844</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-0.9805787268653793</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-0.2234871899330499</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-1.079470188898134</v>
+      </c>
+      <c r="J12" t="n">
+        <v>-0.9513654605594664</v>
+      </c>
+      <c r="K12" t="n">
+        <v>-0.001826621254097982</v>
+      </c>
+      <c r="L12" t="n">
+        <v>-0.0212614987234063</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.521064188875912</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.05907866795818074</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.090534418736147</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.099312745746926</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.949462043836611</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.168122082858264</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.68409470930754</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.5776837403827552</v>
+      </c>
+      <c r="U12" t="n">
+        <v>-0.06914658595661426</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.007770112821884761</v>
+      </c>
+      <c r="W12" t="n">
+        <v>-2.364896790425972</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-3.812584560801195</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>-0.2990476996137094</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0.4184561422253579</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-0.1662386772451152</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>CQ0ABdJj</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1.790197536946965</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1.24054449358404</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.7619787263775758</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.2044208408000993</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-0.3594097319344284</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-0.9805787268653793</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-0.2234871899330499</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.1533829271946464</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.054562467092063</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-0.001826621254097982</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-0.0212614987234063</v>
+      </c>
+      <c r="M13" t="n">
+        <v>2.191209186956704</v>
+      </c>
+      <c r="N13" t="n">
+        <v>-0.9420796318634789</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.04235341900418825</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.5240883599209177</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>-1.405564722814261</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.2939463707817866</v>
+      </c>
+      <c r="S13" t="n">
+        <v>-0.8107950662613702</v>
+      </c>
+      <c r="T13" t="n">
+        <v>-1.46911340857164</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.481422899073696</v>
+      </c>
+      <c r="V13" t="n">
         <v>0</v>
       </c>
-      <c r="M5" t="n">
-        <v>1.043601356795134</v>
-      </c>
-      <c r="N5" t="n">
-        <v>-0.8399071875857457</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0.05867079225544721</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0.04384578161981739</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>-0.05809667966731939</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.7906127047679753</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1.431844603482726</v>
-      </c>
-      <c r="T5" t="n">
-        <v>-2.339324931828108</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0.07348778384082316</v>
-      </c>
-      <c r="V5" t="n">
-        <v>-0.07265321001223485</v>
-      </c>
-      <c r="W5" t="n">
+      <c r="W13" t="n">
+        <v>0.5041945930142366</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.1969693416758896</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>-0.501928070821707</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-0.5805097296476226</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-0.1662386772451152</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>KhwykQ8L</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1.849817892667333</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1.042927958283678</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-0.1172445342958035</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1.798544765986838</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.2788832759311962</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-0.9805787268653793</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-0.2234871899330499</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.523219722853291</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.054562467092063</v>
+      </c>
+      <c r="K14" t="n">
         <v>0</v>
       </c>
-      <c r="X5" t="n">
-        <v>3.022944463192594</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>-0.2968871276919609</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0.1459756027605518</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>-0.08690027965431606</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0.05782969642979482</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0.9047442187912749</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0.09835131267592243</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>-0.1049165563694611</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>-0.3845885447895117</v>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>-1.159515803447255</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1.06023696777984</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.138715418468105</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.099312745746926</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.5515342243987474</v>
+      </c>
+      <c r="R14" t="n">
+        <v>-2.619972669473138</v>
+      </c>
+      <c r="S14" t="n">
+        <v>-0.1488855339675779</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.601082314859953</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-0.06914658595661426</v>
+      </c>
+      <c r="V14" t="n">
+        <v>-0.4214400364548588</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.917316943146621</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2.014210192941597</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.4082159705003586</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0.0445471445048916</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-0.1662386772451152</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>v1KiOZ2d</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1.879628070527517</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1.003404651223605</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.9699542994107144</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-0.5293822358731616</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.13354679493771</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-0.9805787268653793</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-0.2234871899330499</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.2903666067605108</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.054562467092063</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.521064188875912</v>
+      </c>
+      <c r="N15" t="n">
+        <v>-0.441500481952649</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.04235341900418825</v>
+      </c>
+      <c r="P15" t="n">
+        <v>-0.05113602590509021</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>-2.523906978364551</v>
+      </c>
+      <c r="R15" t="n">
+        <v>3.790649219087695</v>
+      </c>
+      <c r="S15" t="n">
+        <v>-3.102020370355267</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.601082314859953</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.481422899073696</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.5252510993865399</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.205650434630353</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.50343631154888</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>-0.09696709832476098</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0.2650083131944272</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-0.1662386772451152</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>f92vnwe3</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1.879628070527517</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1.91244071360527</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-0.2942303909457018</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-0.2510431378246833</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-0.1105836441224053</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-0.9805787268653793</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-0.2234871899330499</v>
+      </c>
+      <c r="I16" t="n">
+        <v>-0.2575681115029471</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.054562467092063</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-0.001826621254097982</v>
+      </c>
+      <c r="L16" t="n">
+        <v>-0.0212614987234063</v>
+      </c>
+      <c r="M16" t="n">
+        <v>-1.695631801911888</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1.06023696777984</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.04235341900418825</v>
+      </c>
+      <c r="P16" t="n">
+        <v>-1.201584797557106</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.83111978828632</v>
+      </c>
+      <c r="R16" t="n">
+        <v>-1.74579695739666</v>
+      </c>
+      <c r="S16" t="n">
+        <v>-0.6580467126551104</v>
+      </c>
+      <c r="T16" t="n">
+        <v>-0.4457148340944425</v>
+      </c>
+      <c r="U16" t="n">
+        <v>-1.720855041047545</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.3722574748536427</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.3699282929926103</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>-0.4598512288127478</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-0.1983834182997118</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-0.1662386772451152</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>0Y1WIvRG</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1.760387359086781</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-0.5577659776492538</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-0.8757553485096533</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1.80697928410952</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.4844352615150414</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-0.9805787268653793</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-0.2234871899330499</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-1.764388586727456</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.5530804851791808</v>
+      </c>
+      <c r="K17" t="n">
+        <v>-0.001826621254097982</v>
+      </c>
+      <c r="L17" t="n">
+        <v>-0.0212614987234063</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-1.025486803831096</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.5596578178690105</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.04235341900418825</v>
+      </c>
+      <c r="P17" t="n">
+        <v>-1.201584797557106</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.5515342243987474</v>
+      </c>
+      <c r="R17" t="n">
+        <v>-0.2888374372691982</v>
+      </c>
+      <c r="S17" t="n">
+        <v>-1.014459537736383</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.3218340967634558</v>
+      </c>
+      <c r="U17" t="n">
+        <v>-1.9961397835627</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.21861156715701</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.702602855466236</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.5279922109985465</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0.4411939543290155</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-0.1662386772451152</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>8CpDVHAM</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1.909438248387701</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-1.032045662370122</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.03445762854696641</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-0.5293822358731616</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-0.7164210753168965</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-0.9805787268653793</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-0.2234871899330499</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-2.449306984556779</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.054562467092063</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.9849481904112789</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.05907866795818074</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.04235341900418825</v>
+      </c>
+      <c r="P18" t="n">
+        <v>-0.05113602590509021</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.928011517443115</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.8767301788327715</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.956997656026371</v>
+      </c>
+      <c r="T18" t="n">
+        <v>-0.4457148340944425</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.582561869134317</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>-0.7489095003372619</v>
+      </c>
+      <c r="X18" t="n">
+        <v>-1.832857272361237</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>-0.2156369027536758</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.013357208599164</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-0.1662386772451152</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>4KmdZaBc</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1.760387359086781</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-1.269185504730557</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.9067450648928936</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-1.533089892472219</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-0.3377726808203395</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-0.9805787268653793</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-0.2234871899330499</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-1.490421227595728</v>
+      </c>
+      <c r="J19" t="n">
+        <v>-0.9513654605594664</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-0.001826621254097982</v>
+      </c>
+      <c r="L19" t="n">
+        <v>-0.0212614987234063</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.5828611915628038</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.05907866795818074</v>
+      </c>
+      <c r="O19" t="n">
+        <v>-1.00582758072777</v>
+      </c>
+      <c r="P19" t="n">
+        <v>-1.201584797557106</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>-1.685150286701833</v>
+      </c>
+      <c r="R19" t="n">
+        <v>-0.7259252933074368</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1.124017412751253</v>
+      </c>
+      <c r="T19" t="n">
+        <v>-1.724963052190939</v>
+      </c>
+      <c r="U19" t="n">
+        <v>-0.3444313284717694</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>-0.3590557801428499</v>
+      </c>
+      <c r="X19" t="n">
+        <v>-1.308932996646831</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>-0.5035105564953063</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0.4784868824972571</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-0.1662386772451152</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>hpMqQeYq</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1.760387359086781</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1.141736225933859</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-1.014815664448859</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.297200540149592</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.4844352615150414</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-0.9805787268653793</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-0.2234871899330499</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.01639924762878189</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.054562467092063</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-0.001826621254097982</v>
+      </c>
+      <c r="L20" t="n">
+        <v>-0.0212614987234063</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.3148031923304871</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-0.9420796318634789</v>
+      </c>
+      <c r="O20" t="n">
+        <v>-0.4817370808617911</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.5240883599209177</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>-0.4270152492077567</v>
+      </c>
+      <c r="R20" t="n">
+        <v>-1.163013149345675</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.429514119963773</v>
+      </c>
+      <c r="T20" t="n">
+        <v>-0.1898651904751431</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.857846611649472</v>
+      </c>
+      <c r="V20" t="n">
+        <v>-0.30543729340709</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0.6872772516810614</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.025042078690394</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0.7785233428811195</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0.7020116901136255</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-0.1662386772451152</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>ChPK4l66</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1.939248426247886</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1.042927958283678</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.235433084385562</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1.798544765986838</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-1.625177222108633</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-0.9805787268653793</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-0.2234871899330499</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.4273502863263753</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.054562467092063</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>-3.035921798073472</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.05907866795818074</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.090534418736147</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.099312745746926</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.83111978828632</v>
+      </c>
+      <c r="R21" t="n">
+        <v>-1.454405053371168</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.4621078804574613</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.601082314859953</v>
+      </c>
+      <c r="U21" t="n">
+        <v>-0.6197160709869246</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.02724331162278</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.872052629344219</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0.5233633852203328</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1.023050675549504</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-0.1662386772451152</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>MNr3HRkC</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1.939248426247886</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.9243580371034607</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1.627330338396051</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1.781675729741476</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-1.625177222108633</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-0.9805787268653793</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-0.2234871899330499</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-0.5315354706346761</v>
+      </c>
+      <c r="J22" t="n">
+        <v>-0.449883478646584</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-1.963689801144205</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-0.9420796318634789</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.04235341900418825</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.099312745746926</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>3.347389863274473</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.2939463707817866</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.2584434089824482</v>
+      </c>
+      <c r="T22" t="n">
+        <v>-0.9574141213330414</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.031992384104006</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>-1.286988401056429</v>
+      </c>
+      <c r="X22" t="n">
+        <v>-2.240616763538354</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>-0.8016005559993591</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>-1.348673028097558</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>-0.1662386772451152</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>hA5zaJZp</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1.939248426247886</v>
+      </c>
+      <c r="C23" t="n">
+        <v>-0.2119370408736204</v>
+      </c>
+      <c r="D23" t="n">
+        <v>-0.4712162475956001</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-1.533089892472219</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.3005203270452851</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-0.9805787268653793</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-0.2234871899330499</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.01639924762878189</v>
+      </c>
+      <c r="J23" t="n">
+        <v>-0.449883478646584</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-0.6233998049826214</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.05907866795818074</v>
+      </c>
+      <c r="O23" t="n">
+        <v>-1.00582758072777</v>
+      </c>
+      <c r="P23" t="n">
+        <v>-1.201584797557106</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>-0.566808031151543</v>
+      </c>
+      <c r="R23" t="n">
+        <v>-0.2888374372691982</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.8694368234074872</v>
+      </c>
+      <c r="T23" t="n">
+        <v>-0.4457148340944425</v>
+      </c>
+      <c r="U23" t="n">
+        <v>-0.06914658595661426</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>-1.199993349640122</v>
+      </c>
+      <c r="X23" t="n">
+        <v>-0.2960069598050356</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0.978024823462702</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0.02680029849421082</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-0.1662386772451152</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>IVonL9jm</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1.760387359086781</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.3413892579673929</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1.930734664081591</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-0.3606918734195383</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.2788832759311962</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-0.9805787268653793</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-0.2234871899330499</v>
+      </c>
+      <c r="I24" t="n">
+        <v>3.577974916341258</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.054562467092063</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.4488321919466454</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-1.943237931685138</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.04235341900418825</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.099312745746926</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-2.244321414476978</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.8767301788327715</v>
+      </c>
+      <c r="S24" t="n">
+        <v>-2.083698012980201</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0.5776837403827552</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.582561869134317</v>
+      </c>
+      <c r="V24" t="n">
+        <v>-0.2822367447975356</v>
+      </c>
+      <c r="W24" t="n">
+        <v>3.220939548563669</v>
+      </c>
+      <c r="X24" t="n">
+        <v>3.744200836688441</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>-0.2119248658375084</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-0.1711726156007531</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-0.1662386772451152</v>
       </c>
     </row>
   </sheetData>

--- a/data/spain/p6_deployment/data_preparation/df_selected_nan.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_selected_nan.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA24"/>
+  <dimension ref="A1:AA20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.820007714807149</v>
+        <v>1.939248426247886</v>
       </c>
       <c r="C2" t="n">
         <v>0.3413892579673929</v>
@@ -576,10 +576,10 @@
         <v>1.627330338396051</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.3606918734195383</v>
+        <v>1.140652352417708</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.625177222108633</v>
+        <v>0.1815165459177958</v>
       </c>
       <c r="G2" t="n">
         <v>-0.9805787268653793</v>
@@ -600,46 +600,46 @@
         <v>1.149962181909723</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.3553418057503047</v>
+        <v>0.4488321919466454</v>
       </c>
       <c r="N2" t="n">
-        <v>0.05907866795818074</v>
+        <v>0.7265175345059538</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04235341900418825</v>
+        <v>1.614624918602126</v>
       </c>
       <c r="P2" t="n">
         <v>-0.05113602590509021</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.125979158926688</v>
+        <v>-0.9861863769829019</v>
       </c>
       <c r="R2" t="n">
-        <v>1.168122082858264</v>
+        <v>0.4396423227945328</v>
       </c>
       <c r="S2" t="n">
-        <v>-2.694691427405241</v>
+        <v>-1.523620716423916</v>
       </c>
       <c r="T2" t="n">
-        <v>0.06598445314415635</v>
+        <v>1.601082314859953</v>
       </c>
       <c r="U2" t="n">
-        <v>1.582561869134317</v>
+        <v>1.031992384104006</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1648571606990701</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.721292351429077</v>
+        <v>1.716280934947868</v>
       </c>
       <c r="X2" t="n">
-        <v>1.881986879366817</v>
+        <v>1.825463930742316</v>
       </c>
       <c r="Y2" t="n">
-        <v>-1.149487400761321</v>
+        <v>-1.238187492661567</v>
       </c>
       <c r="Z2" t="n">
-        <v>-0.8523518863594111</v>
+        <v>-0.7074116682397645</v>
       </c>
       <c r="AA2" t="n">
         <v>-0.1662386772451152</v>
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.879628070527517</v>
+        <v>1.820007714807149</v>
       </c>
       <c r="C3" t="n">
         <v>0.7168606750380806</v>
@@ -661,10 +661,10 @@
         <v>0.9952379932178427</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.7402451889401905</v>
+        <v>-1.406572120632002</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.603540170994544</v>
+        <v>-0.5433246664041846</v>
       </c>
       <c r="G3" t="n">
         <v>-0.9805787268653793</v>
@@ -679,52 +679,52 @@
         <v>-0.449883478646584</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>-0.7380657395056173</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>-1.192485179356536</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.427573802679572</v>
+        <v>-2.097718800760363</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5596578178690105</v>
+        <v>-0.2746407653157057</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04235341900418825</v>
+        <v>-0.4817370808617911</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.201584797557106</v>
+        <v>-0.6263604117310982</v>
       </c>
       <c r="Q3" t="n">
         <v>-0.566808031151543</v>
       </c>
       <c r="R3" t="n">
-        <v>-1.74579695739666</v>
+        <v>-0.2888374372691982</v>
       </c>
       <c r="S3" t="n">
-        <v>3.517074952582656</v>
+        <v>2.651500948813851</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.46911340857164</v>
+        <v>-1.724963052190939</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.6197160709869246</v>
+        <v>-0.8950008135020797</v>
       </c>
       <c r="V3" t="n">
         <v>-0.05699808537978705</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.8597593171068049</v>
+        <v>-0.8129963041390017</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.273048769746285</v>
+        <v>-1.30672733488238</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.114454694362431</v>
+        <v>0.983379125737099</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.07458340839659147</v>
+        <v>0.08435005510987392</v>
       </c>
       <c r="AA3" t="n">
         <v>-0.1662386772451152</v>
@@ -764,10 +764,10 @@
         <v>-1.954329424385231</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.001826621254097982</v>
+        <v>0.7344124969974213</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.0212614987234063</v>
+        <v>-1.192485179356536</v>
       </c>
       <c r="M4" t="n">
         <v>-2.097718800760363</v>
@@ -797,7 +797,7 @@
         <v>0.481422899073696</v>
       </c>
       <c r="V4" t="n">
-        <v>1.005683709890313</v>
+        <v>0.203524741714994</v>
       </c>
       <c r="W4" t="n">
         <v>0.2611291216986705</v>
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.760387359086781</v>
+        <v>1.939248426247886</v>
       </c>
       <c r="C5" t="n">
         <v>0.9243580371034607</v>
@@ -831,10 +831,10 @@
         <v>-0.4712162475956001</v>
       </c>
       <c r="E5" t="n">
-        <v>1.781675729741476</v>
+        <v>1.123783316172346</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3005203270452851</v>
+        <v>0.744079874884109</v>
       </c>
       <c r="G5" t="n">
         <v>-0.9805787268653793</v>
@@ -852,49 +852,49 @@
         <v>-0.001826621254097982</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.192485179356536</v>
+        <v>-0.0212614987234063</v>
       </c>
       <c r="M5" t="n">
-        <v>-3.303979797305789</v>
+        <v>-1.293544803063413</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2746407653157058</v>
+        <v>0.05907866795818074</v>
       </c>
       <c r="O5" t="n">
         <v>-1.00582758072777</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.05113602590509021</v>
+        <v>-1.201584797557106</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.508633171611756</v>
+        <v>2.089254825780397</v>
       </c>
       <c r="R5" t="n">
-        <v>-2.037188861422153</v>
+        <v>-0.7259252933074368</v>
       </c>
       <c r="S5" t="n">
-        <v>1.174933530620007</v>
+        <v>1.633178591438786</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.46911340857164</v>
+        <v>-1.724963052190939</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6197160709869246</v>
+        <v>-0.8950008135020797</v>
       </c>
       <c r="V5" t="n">
-        <v>1.248416154185294</v>
+        <v>1.266525837464694</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.6292305203839251</v>
+        <v>-0.6350237599434502</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.3072502775665666</v>
+        <v>-0.309710156181023</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.650535058975039</v>
+        <v>0.6331255513021701</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.876927080553953</v>
+        <v>-0.8448589243896535</v>
       </c>
       <c r="AA5" t="n">
         <v>-0.1662386772451152</v>
@@ -937,7 +937,7 @@
         <v>-0.001826621254097982</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.0212614987234063</v>
+        <v>-1.192485179356536</v>
       </c>
       <c r="M6" t="n">
         <v>-0.3553418057503047</v>
@@ -988,23 +988,23 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>EJYZzDn2</t>
+          <t>xhKUdf9L</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.760387359086781</v>
+        <v>1.790197536946965</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.893714087659869</v>
+        <v>-0.2119370408736204</v>
       </c>
       <c r="D7" t="n">
-        <v>1.121656462253484</v>
+        <v>-1.292936296327271</v>
       </c>
       <c r="E7" t="n">
-        <v>1.781675729741476</v>
+        <v>-0.0823527753710601</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3377726808203395</v>
+        <v>-0.3594097319344284</v>
       </c>
       <c r="G7" t="n">
         <v>-0.9805787268653793</v>
@@ -1013,10 +1013,10 @@
         <v>-0.2234871899330499</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2575681115029471</v>
+        <v>-0.3945517910688116</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.449883478646584</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>-0.001826621254097982</v>
@@ -1025,46 +1025,46 @@
         <v>-0.0212614987234063</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2213128061341464</v>
+        <v>-0.3553418057503047</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.275799065137365</v>
+        <v>1.06023696777984</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.00582758072777</v>
+        <v>1.090534418736147</v>
       </c>
       <c r="P7" t="n">
-        <v>1.099312745746926</v>
+        <v>-0.05113602590509021</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.110705352173893</v>
+        <v>0.5515342243987474</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.5802293412946906</v>
+        <v>1.022426130845518</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1998016518363311</v>
+        <v>0.4621078804574613</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4457148340944425</v>
+        <v>0.5776837403827552</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3444313284717694</v>
+        <v>0.2061381565585409</v>
       </c>
       <c r="V7" t="n">
-        <v>0.7702733284664288</v>
+        <v>1.732256345266096</v>
       </c>
       <c r="W7" t="n">
-        <v>-1.436498406119787</v>
+        <v>-1.460124481080289</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.373309940190961</v>
+        <v>-0.2077165975072911</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.8049339449070689</v>
+        <v>0.2009889596348801</v>
       </c>
       <c r="Z7" t="n">
-        <v>-1.223904984434127</v>
+        <v>-0.304813494552062</v>
       </c>
       <c r="AA7" t="n">
         <v>-0.1662386772451152</v>
@@ -1073,23 +1073,23 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>xhKUdf9L</t>
+          <t>EJYZzDn2</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.790197536946965</v>
+        <v>1.760387359086781</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.2119370408736204</v>
+        <v>-0.893714087659869</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.292936296327271</v>
+        <v>1.121656462253484</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.533089892472219</v>
+        <v>1.781675729741476</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3594097319344284</v>
+        <v>-0.3377726808203395</v>
       </c>
       <c r="G8" t="n">
         <v>-0.9805787268653793</v>
@@ -1098,10 +1098,10 @@
         <v>-0.2234871899330499</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3945517910688116</v>
+        <v>-0.2575681115029471</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>-0.449883478646584</v>
       </c>
       <c r="K8" t="n">
         <v>-0.001826621254097982</v>
@@ -1110,46 +1110,46 @@
         <v>-0.0212614987234063</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4488321919466454</v>
+        <v>-0.2213128061341464</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3927981012320673</v>
+        <v>-1.275799065137365</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5664439188701677</v>
+        <v>-1.00582758072777</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.05113602590509021</v>
+        <v>1.099312745746926</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.6913270063425337</v>
+        <v>1.110705352173893</v>
       </c>
       <c r="R8" t="n">
-        <v>1.605209938896502</v>
+        <v>-0.5802293412946906</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5130239983262145</v>
+        <v>-0.1998016518363311</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3218340967634558</v>
+        <v>-0.4457148340944425</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2061381565585409</v>
+        <v>-0.3444313284717694</v>
       </c>
       <c r="V8" t="n">
-        <v>1.732256345266096</v>
+        <v>0.7702733284664288</v>
       </c>
       <c r="W8" t="n">
-        <v>-1.505066595391495</v>
+        <v>-1.436498406119787</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.216570710244497</v>
+        <v>-1.373309940190961</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.2289903123830555</v>
+        <v>-0.8049339449070689</v>
       </c>
       <c r="Z8" t="n">
-        <v>-0.2688337014755864</v>
+        <v>-1.223904984434127</v>
       </c>
       <c r="AA8" t="n">
         <v>-0.1662386772451152</v>
@@ -1162,7 +1162,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.879628070527517</v>
+        <v>1.909438248387701</v>
       </c>
       <c r="C9" t="n">
         <v>-0.07360546616336709</v>
@@ -1171,7 +1171,7 @@
         <v>-1.027457511352423</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2510431378246833</v>
+        <v>0.2803315039042297</v>
       </c>
       <c r="F9" t="n">
         <v>-1.603540170994544</v>
@@ -1192,49 +1192,49 @@
         <v>-0.001826621254097982</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.0212614987234063</v>
+        <v>-1.192485179356536</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1807741927143287</v>
+        <v>-0.489370805366463</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.442658781774309</v>
+        <v>-1.275799065137365</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.054008580459729</v>
+        <v>-1.00582758072777</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.05113602590509021</v>
+        <v>0.5240883599209177</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.642249233914841</v>
+        <v>-2.384114196420765</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2939463707817866</v>
+        <v>0.4396423227945328</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.185530248717708</v>
+        <v>-0.1998016518363311</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.46911340857164</v>
+        <v>-0.1898651904751431</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.170285556017235</v>
+        <v>0.481422899073696</v>
       </c>
       <c r="V9" t="n">
-        <v>1.256088519952595</v>
+        <v>0.8747832071566879</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.8177453192119756</v>
+        <v>-0.8490023269769209</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.6426963790388309</v>
+        <v>-0.643173608966387</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0.235925953078628</v>
+        <v>-0.1387279852933928</v>
       </c>
       <c r="Z9" t="n">
-        <v>-0.6168550375302072</v>
+        <v>-0.6134778449234966</v>
       </c>
       <c r="AA9" t="n">
         <v>-0.1662386772451152</v>
@@ -1274,10 +1274,10 @@
         <v>0.5530804851791808</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.001826621254097982</v>
+        <v>0.7344124969974213</v>
       </c>
       <c r="L10" t="n">
-        <v>1.149962181909723</v>
+        <v>-1.192485179356536</v>
       </c>
       <c r="M10" t="n">
         <v>0.1807741927143287</v>
@@ -1307,7 +1307,7 @@
         <v>-0.06914658595661426</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3539222980764235</v>
+        <v>-0.3199376362880607</v>
       </c>
       <c r="W10" t="n">
         <v>-0.8320647735730389</v>
@@ -1332,7 +1332,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.849817892667333</v>
+        <v>1.760387359086781</v>
       </c>
       <c r="C11" t="n">
         <v>0.05484528178186816</v>
@@ -1344,7 +1344,7 @@
         <v>1.80697928410952</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2788832759311962</v>
+        <v>-0.2620430019210281</v>
       </c>
       <c r="G11" t="n">
         <v>-0.9805787268653793</v>
@@ -1362,49 +1362,49 @@
         <v>-0.001826621254097982</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.192485179356536</v>
+        <v>-0.0212614987234063</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.8914578042149381</v>
+        <v>-1.829660801528047</v>
       </c>
       <c r="N11" t="n">
-        <v>0.7265175345059538</v>
+        <v>1.060236967779841</v>
       </c>
       <c r="O11" t="n">
-        <v>1.090534418736147</v>
+        <v>1.614624918602126</v>
       </c>
       <c r="P11" t="n">
-        <v>1.099312745746926</v>
+        <v>-0.6263604117310982</v>
       </c>
       <c r="Q11" t="n">
         <v>-1.265771940870474</v>
       </c>
       <c r="R11" t="n">
-        <v>0.8767301788327715</v>
+        <v>0.5853382748072791</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.930949659373942</v>
+        <v>-2.389194720192721</v>
       </c>
       <c r="T11" t="n">
-        <v>1.601082314859953</v>
+        <v>1.856931958479252</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.06914658595661426</v>
+        <v>-1.9961397835627</v>
       </c>
       <c r="V11" t="n">
-        <v>0.9352087479563191</v>
+        <v>1.098195897470909</v>
       </c>
       <c r="W11" t="n">
-        <v>1.95685401287206</v>
+        <v>1.935148508713701</v>
       </c>
       <c r="X11" t="n">
-        <v>2.277921931760277</v>
+        <v>2.298691914818507</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.1517816234098696</v>
+        <v>0.198144255904054</v>
       </c>
       <c r="Z11" t="n">
-        <v>-0.8878561448613461</v>
+        <v>-0.8840450003373657</v>
       </c>
       <c r="AA11" t="n">
         <v>-0.1662386772451152</v>
@@ -1417,7 +1417,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.849817892667333</v>
+        <v>1.939248426247886</v>
       </c>
       <c r="C12" t="n">
         <v>-0.4886001902941271</v>
@@ -1426,10 +1426,10 @@
         <v>0.312578260425378</v>
       </c>
       <c r="E12" t="n">
-        <v>0.7526645187743746</v>
+        <v>-0.0823527753710601</v>
       </c>
       <c r="F12" t="n">
-        <v>1.166002371608844</v>
+        <v>-0.2620430019210281</v>
       </c>
       <c r="G12" t="n">
         <v>-0.9805787268653793</v>
@@ -1450,46 +1450,46 @@
         <v>-0.0212614987234063</v>
       </c>
       <c r="M12" t="n">
-        <v>1.521064188875912</v>
+        <v>0.9849481904112789</v>
       </c>
       <c r="N12" t="n">
-        <v>0.05907866795818074</v>
+        <v>-1.442658781774309</v>
       </c>
       <c r="O12" t="n">
-        <v>1.090534418736147</v>
+        <v>-0.4817370808617911</v>
       </c>
       <c r="P12" t="n">
-        <v>1.099312745746926</v>
+        <v>1.674537131572934</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.949462043836611</v>
+        <v>0.9709125702301064</v>
       </c>
       <c r="R12" t="n">
-        <v>1.168122082858264</v>
+        <v>0.002554466756294189</v>
       </c>
       <c r="S12" t="n">
-        <v>1.68409470930754</v>
+        <v>1.022185177013747</v>
       </c>
       <c r="T12" t="n">
-        <v>0.5776837403827552</v>
+        <v>-0.701564477713742</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.06914658595661426</v>
+        <v>0.7567076415888512</v>
       </c>
       <c r="V12" t="n">
-        <v>0.007770112821884761</v>
+        <v>0.1310230273101374</v>
       </c>
       <c r="W12" t="n">
-        <v>-2.364896790425972</v>
+        <v>-2.285199579796523</v>
       </c>
       <c r="X12" t="n">
-        <v>-3.812584560801195</v>
+        <v>-3.702371329668092</v>
       </c>
       <c r="Y12" t="n">
-        <v>-0.2990476996137094</v>
+        <v>-0.2322361289673371</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.4184561422253579</v>
+        <v>0.3558418508597789</v>
       </c>
       <c r="AA12" t="n">
         <v>-0.1662386772451152</v>
@@ -1502,7 +1502,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.790197536946965</v>
+        <v>1.760387359086781</v>
       </c>
       <c r="C13" t="n">
         <v>1.24054449358404</v>
@@ -1529,10 +1529,10 @@
         <v>1.054562467092063</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.001826621254097982</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.0212614987234063</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>2.191209186956704</v>
@@ -1583,23 +1583,23 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>KhwykQ8L</t>
+          <t>v1KiOZ2d</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.849817892667333</v>
+        <v>1.790197536946965</v>
       </c>
       <c r="C14" t="n">
-        <v>1.042927958283678</v>
+        <v>1.003404651223605</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1172445342958035</v>
+        <v>0.9699542994107144</v>
       </c>
       <c r="E14" t="n">
-        <v>1.798544765986838</v>
+        <v>0.2803315039042297</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2788832759311962</v>
+        <v>0.1815165459177958</v>
       </c>
       <c r="G14" t="n">
         <v>-0.9805787268653793</v>
@@ -1608,58 +1608,58 @@
         <v>-0.2234871899330499</v>
       </c>
       <c r="I14" t="n">
-        <v>1.523219722853291</v>
+        <v>0.2903666067605108</v>
       </c>
       <c r="J14" t="n">
         <v>1.054562467092063</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>-0.001826621254097982</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>-0.0212614987234063</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.159515803447255</v>
+        <v>0.7168901911789621</v>
       </c>
       <c r="N14" t="n">
         <v>1.06023696777984</v>
       </c>
       <c r="O14" t="n">
-        <v>2.138715418468105</v>
+        <v>0.5664439188701677</v>
       </c>
       <c r="P14" t="n">
-        <v>1.099312745746926</v>
+        <v>-0.05113602590509021</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.5515342243987474</v>
+        <v>-0.9861863769829019</v>
       </c>
       <c r="R14" t="n">
-        <v>-2.619972669473138</v>
+        <v>2.042297794934741</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1488855339675779</v>
+        <v>-2.949272016749007</v>
       </c>
       <c r="T14" t="n">
         <v>1.601082314859953</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.06914658595661426</v>
+        <v>0.2061381565585409</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.4214400364548588</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.917316943146621</v>
+        <v>1.133361778341853</v>
       </c>
       <c r="X14" t="n">
-        <v>2.014210192941597</v>
+        <v>1.516422264206322</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.4082159705003586</v>
+        <v>-0.02399443288141778</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.0445471445048916</v>
+        <v>0.237013270062399</v>
       </c>
       <c r="AA14" t="n">
         <v>-0.1662386772451152</v>
@@ -1668,23 +1668,23 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>v1KiOZ2d</t>
+          <t>KhwykQ8L</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.879628070527517</v>
+        <v>1.939248426247886</v>
       </c>
       <c r="C15" t="n">
-        <v>1.003404651223605</v>
+        <v>1.042927958283678</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9699542994107144</v>
+        <v>-0.1172445342958035</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.5293822358731616</v>
+        <v>1.798544765986838</v>
       </c>
       <c r="F15" t="n">
-        <v>1.13354679493771</v>
+        <v>-0.5433246664041846</v>
       </c>
       <c r="G15" t="n">
         <v>-0.9805787268653793</v>
@@ -1693,7 +1693,7 @@
         <v>-0.2234871899330499</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2903666067605108</v>
+        <v>1.523219722853291</v>
       </c>
       <c r="J15" t="n">
         <v>1.054562467092063</v>
@@ -1705,46 +1705,46 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1.521064188875912</v>
+        <v>-0.6233998049826214</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.441500481952649</v>
+        <v>1.06023696777984</v>
       </c>
       <c r="O15" t="n">
-        <v>0.04235341900418825</v>
+        <v>2.138715418468105</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.05113602590509021</v>
+        <v>1.099312745746926</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.523906978364551</v>
+        <v>-0.2872224672639704</v>
       </c>
       <c r="R15" t="n">
-        <v>3.790649219087695</v>
+        <v>-3.057060525511376</v>
       </c>
       <c r="S15" t="n">
-        <v>-3.102020370355267</v>
+        <v>-1.218124009211396</v>
       </c>
       <c r="T15" t="n">
-        <v>1.601082314859953</v>
+        <v>1.345232671240653</v>
       </c>
       <c r="U15" t="n">
-        <v>0.481422899073696</v>
+        <v>-0.3444313284717694</v>
       </c>
       <c r="V15" t="n">
-        <v>0.5252510993865399</v>
+        <v>0.3804289248628422</v>
       </c>
       <c r="W15" t="n">
-        <v>1.205650434630353</v>
+        <v>1.933569293542791</v>
       </c>
       <c r="X15" t="n">
-        <v>1.50343631154888</v>
+        <v>2.025335335569067</v>
       </c>
       <c r="Y15" t="n">
-        <v>-0.09696709832476098</v>
+        <v>0.4232934496578126</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.2650083131944272</v>
+        <v>0.06138105884714241</v>
       </c>
       <c r="AA15" t="n">
         <v>-0.1662386772451152</v>
@@ -1766,10 +1766,10 @@
         <v>-0.2942303909457018</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.2510431378246833</v>
+        <v>1.140652352417708</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1105836441224053</v>
+        <v>0.744079874884109</v>
       </c>
       <c r="G16" t="n">
         <v>-0.9805787268653793</v>
@@ -1790,46 +1790,46 @@
         <v>-0.0212614987234063</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.695631801911888</v>
+        <v>0.04674519309817034</v>
       </c>
       <c r="N16" t="n">
-        <v>1.06023696777984</v>
+        <v>-0.441500481952649</v>
       </c>
       <c r="O16" t="n">
-        <v>0.04235341900418825</v>
+        <v>-1.00582758072777</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.201584797557106</v>
+        <v>0.5240883599209177</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.83111978828632</v>
+        <v>0.9709125702301064</v>
       </c>
       <c r="R16" t="n">
-        <v>-1.74579695739666</v>
+        <v>-0.8716212453201829</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6580467126551104</v>
+        <v>-0.1488855339675779</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4457148340944425</v>
+        <v>-0.9574141213330414</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.720855041047545</v>
+        <v>0.2061381565585409</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.3722574748536427</v>
+        <v>0.3490208647007955</v>
       </c>
       <c r="X16" t="n">
-        <v>0.3699282929926103</v>
+        <v>0.3403041971971741</v>
       </c>
       <c r="Y16" t="n">
-        <v>-0.4598512288127478</v>
+        <v>-0.4782125085587569</v>
       </c>
       <c r="Z16" t="n">
-        <v>-0.1983834182997118</v>
+        <v>-0.1662147697472167</v>
       </c>
       <c r="AA16" t="n">
         <v>-0.1662386772451152</v>
@@ -1842,7 +1842,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.760387359086781</v>
+        <v>1.849817892667333</v>
       </c>
       <c r="C17" t="n">
         <v>-0.5577659776492538</v>
@@ -1927,7 +1927,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.909438248387701</v>
+        <v>1.849817892667333</v>
       </c>
       <c r="C18" t="n">
         <v>-1.032045662370122</v>
@@ -1936,7 +1936,7 @@
         <v>0.03445762854696641</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.5293822358731616</v>
+        <v>-1.406572120632002</v>
       </c>
       <c r="F18" t="n">
         <v>-0.7164210753168965</v>
@@ -1954,52 +1954,52 @@
         <v>1.054562467092063</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>-0.001826621254097982</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-0.0212614987234063</v>
       </c>
       <c r="M18" t="n">
-        <v>0.9849481904112789</v>
+        <v>1.118977190027437</v>
       </c>
       <c r="N18" t="n">
-        <v>0.05907866795818074</v>
+        <v>-0.9420796318634789</v>
       </c>
       <c r="O18" t="n">
-        <v>0.04235341900418825</v>
+        <v>-1.00582758072777</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.05113602590509021</v>
+        <v>-0.6263604117310982</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.928011517443115</v>
+        <v>2.508633171611756</v>
       </c>
       <c r="R18" t="n">
-        <v>0.8767301788327715</v>
+        <v>1.168122082858264</v>
       </c>
       <c r="S18" t="n">
-        <v>2.956997656026371</v>
+        <v>2.040507534388812</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4457148340944425</v>
+        <v>-1.46911340857164</v>
       </c>
       <c r="U18" t="n">
-        <v>1.582561869134317</v>
+        <v>0.2061381565585409</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.7489095003372619</v>
+        <v>-0.7339048429684857</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.832857272361237</v>
+        <v>-1.843505185061151</v>
       </c>
       <c r="Y18" t="n">
-        <v>-0.2156369027536758</v>
+        <v>-0.327912349696365</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.013357208599164</v>
+        <v>1.993146101650202</v>
       </c>
       <c r="AA18" t="n">
         <v>-0.1662386772451152</v>
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.760387359086781</v>
+        <v>1.820007714807149</v>
       </c>
       <c r="C20" t="n">
         <v>1.141736225933859</v>
@@ -2172,346 +2172,6 @@
         <v>0.7020116901136255</v>
       </c>
       <c r="AA20" t="n">
-        <v>-0.1662386772451152</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>ChPK4l66</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>1.939248426247886</v>
-      </c>
-      <c r="C21" t="n">
-        <v>1.042927958283678</v>
-      </c>
-      <c r="D21" t="n">
-        <v>1.235433084385562</v>
-      </c>
-      <c r="E21" t="n">
-        <v>1.798544765986838</v>
-      </c>
-      <c r="F21" t="n">
-        <v>-1.625177222108633</v>
-      </c>
-      <c r="G21" t="n">
-        <v>-0.9805787268653793</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-0.2234871899330499</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0.4273502863263753</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1.054562467092063</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>-3.035921798073472</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0.05907866795818074</v>
-      </c>
-      <c r="O21" t="n">
-        <v>1.090534418736147</v>
-      </c>
-      <c r="P21" t="n">
-        <v>1.099312745746926</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0.83111978828632</v>
-      </c>
-      <c r="R21" t="n">
-        <v>-1.454405053371168</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0.4621078804574613</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1.601082314859953</v>
-      </c>
-      <c r="U21" t="n">
-        <v>-0.6197160709869246</v>
-      </c>
-      <c r="V21" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.02724331162278</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.872052629344219</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>0.5233633852203328</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1.023050675549504</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>-0.1662386772451152</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>MNr3HRkC</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>1.939248426247886</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0.9243580371034607</v>
-      </c>
-      <c r="D22" t="n">
-        <v>1.627330338396051</v>
-      </c>
-      <c r="E22" t="n">
-        <v>1.781675729741476</v>
-      </c>
-      <c r="F22" t="n">
-        <v>-1.625177222108633</v>
-      </c>
-      <c r="G22" t="n">
-        <v>-0.9805787268653793</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-0.2234871899330499</v>
-      </c>
-      <c r="I22" t="n">
-        <v>-0.5315354706346761</v>
-      </c>
-      <c r="J22" t="n">
-        <v>-0.449883478646584</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>-1.963689801144205</v>
-      </c>
-      <c r="N22" t="n">
-        <v>-0.9420796318634789</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0.04235341900418825</v>
-      </c>
-      <c r="P22" t="n">
-        <v>1.099312745746926</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>3.347389863274473</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0.2939463707817866</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0.2584434089824482</v>
-      </c>
-      <c r="T22" t="n">
-        <v>-0.9574141213330414</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.031992384104006</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" t="n">
-        <v>-1.286988401056429</v>
-      </c>
-      <c r="X22" t="n">
-        <v>-2.240616763538354</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>-0.8016005559993591</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>-1.348673028097558</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>-0.1662386772451152</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>hA5zaJZp</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>1.939248426247886</v>
-      </c>
-      <c r="C23" t="n">
-        <v>-0.2119370408736204</v>
-      </c>
-      <c r="D23" t="n">
-        <v>-0.4712162475956001</v>
-      </c>
-      <c r="E23" t="n">
-        <v>-1.533089892472219</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0.3005203270452851</v>
-      </c>
-      <c r="G23" t="n">
-        <v>-0.9805787268653793</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-0.2234871899330499</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0.01639924762878189</v>
-      </c>
-      <c r="J23" t="n">
-        <v>-0.449883478646584</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>-0.6233998049826214</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0.05907866795818074</v>
-      </c>
-      <c r="O23" t="n">
-        <v>-1.00582758072777</v>
-      </c>
-      <c r="P23" t="n">
-        <v>-1.201584797557106</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>-0.566808031151543</v>
-      </c>
-      <c r="R23" t="n">
-        <v>-0.2888374372691982</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0.8694368234074872</v>
-      </c>
-      <c r="T23" t="n">
-        <v>-0.4457148340944425</v>
-      </c>
-      <c r="U23" t="n">
-        <v>-0.06914658595661426</v>
-      </c>
-      <c r="V23" t="n">
-        <v>0</v>
-      </c>
-      <c r="W23" t="n">
-        <v>-1.199993349640122</v>
-      </c>
-      <c r="X23" t="n">
-        <v>-0.2960069598050356</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>0.978024823462702</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>0.02680029849421082</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>-0.1662386772451152</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>IVonL9jm</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>1.760387359086781</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0.3413892579673929</v>
-      </c>
-      <c r="D24" t="n">
-        <v>1.930734664081591</v>
-      </c>
-      <c r="E24" t="n">
-        <v>-0.3606918734195383</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0.2788832759311962</v>
-      </c>
-      <c r="G24" t="n">
-        <v>-0.9805787268653793</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-0.2234871899330499</v>
-      </c>
-      <c r="I24" t="n">
-        <v>3.577974916341258</v>
-      </c>
-      <c r="J24" t="n">
-        <v>1.054562467092063</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0.4488321919466454</v>
-      </c>
-      <c r="N24" t="n">
-        <v>-1.943237931685138</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0.04235341900418825</v>
-      </c>
-      <c r="P24" t="n">
-        <v>1.099312745746926</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>-2.244321414476978</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0.8767301788327715</v>
-      </c>
-      <c r="S24" t="n">
-        <v>-2.083698012980201</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0.5776837403827552</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.582561869134317</v>
-      </c>
-      <c r="V24" t="n">
-        <v>-0.2822367447975356</v>
-      </c>
-      <c r="W24" t="n">
-        <v>3.220939548563669</v>
-      </c>
-      <c r="X24" t="n">
-        <v>3.744200836688441</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>-0.2119248658375084</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>-0.1711726156007531</v>
-      </c>
-      <c r="AA24" t="n">
         <v>-0.1662386772451152</v>
       </c>
     </row>

--- a/data/spain/p6_deployment/data_preparation/df_selected_nan.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_selected_nan.xlsx
@@ -1401,7 +1401,7 @@
         <v>2.298691914818507</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.198144255904054</v>
+        <v>0.1981442559040627</v>
       </c>
       <c r="Z11" t="n">
         <v>-0.8840450003373657</v>
@@ -1826,7 +1826,7 @@
         <v>0.3403041971971741</v>
       </c>
       <c r="Y16" t="n">
-        <v>-0.4782125085587569</v>
+        <v>-0.4782125085587655</v>
       </c>
       <c r="Z16" t="n">
         <v>-0.1662147697472167</v>

--- a/data/spain/p6_deployment/data_preparation/df_selected_nan.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_selected_nan.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA20"/>
+  <dimension ref="A1:AA17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -679,10 +679,10 @@
         <v>-0.449883478646584</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.7380657395056173</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.192485179356536</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>-2.097718800760363</v>
@@ -715,16 +715,16 @@
         <v>-0.05699808537978705</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.8129963041390017</v>
+        <v>-0.8489120053807017</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.30672733488238</v>
+        <v>-1.286034722403727</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.983379125737099</v>
+        <v>0.9680690604209629</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.08435005510987392</v>
+        <v>0.08457768681341578</v>
       </c>
       <c r="AA3" t="n">
         <v>-0.1662386772451152</v>
@@ -737,7 +737,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.820007714807149</v>
+        <v>1.939248426247886</v>
       </c>
       <c r="C4" t="n">
         <v>0.8650730765133521</v>
@@ -746,7 +746,7 @@
         <v>1.235433084385562</v>
       </c>
       <c r="E4" t="n">
-        <v>0.297200540149592</v>
+        <v>-0.3606918734195383</v>
       </c>
       <c r="F4" t="n">
         <v>-1.625177222108633</v>
@@ -764,52 +764,52 @@
         <v>-1.954329424385231</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7344124969974213</v>
+        <v>-0.001826621254097982</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.192485179356536</v>
+        <v>-0.0212614987234063</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.097718800760363</v>
+        <v>-0.9808104706257106</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2746407653157058</v>
+        <v>0.05907866795818074</v>
       </c>
       <c r="O4" t="n">
         <v>0.5664439188701677</v>
       </c>
       <c r="P4" t="n">
-        <v>1.099312745746926</v>
+        <v>-0.8181018736731009</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.36884038966797</v>
+        <v>1.297095728098941</v>
       </c>
       <c r="R4" t="n">
-        <v>0.002554466756294189</v>
+        <v>0.3910770054569509</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4621078804574613</v>
+        <v>0.411191762588708</v>
       </c>
       <c r="T4" t="n">
-        <v>2.62448088933715</v>
+        <v>1.856931958479252</v>
       </c>
       <c r="U4" t="n">
-        <v>0.481422899073696</v>
+        <v>-0.2526697476333842</v>
       </c>
       <c r="V4" t="n">
-        <v>0.203524741714994</v>
+        <v>0.2426756674936158</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2611291216986705</v>
+        <v>0.2913718196737404</v>
       </c>
       <c r="X4" t="n">
-        <v>1.220740385822067</v>
+        <v>1.20088161618552</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.161901921165196</v>
+        <v>1.135796246644002</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.5910634540484747</v>
+        <v>0.6336026800513261</v>
       </c>
       <c r="AA4" t="n">
         <v>-0.1662386772451152</v>
@@ -818,23 +818,23 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>tQQLbGv9</t>
+          <t>vyy1kC1e</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.939248426247886</v>
+        <v>1.820007714807149</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9243580371034607</v>
+        <v>-0.8146674735397244</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.4712162475956001</v>
+        <v>-1.014815664448859</v>
       </c>
       <c r="E5" t="n">
-        <v>1.123783316172346</v>
+        <v>-1.533089892472219</v>
       </c>
       <c r="F5" t="n">
-        <v>0.744079874884109</v>
+        <v>0.2031535970318848</v>
       </c>
       <c r="G5" t="n">
         <v>-0.9805787268653793</v>
@@ -843,10 +843,10 @@
         <v>-0.2234871899330499</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2903666067605108</v>
+        <v>-0.6685191502005404</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.449883478646584</v>
+        <v>0.05159850326629842</v>
       </c>
       <c r="K5" t="n">
         <v>-0.001826621254097982</v>
@@ -855,46 +855,46 @@
         <v>-0.0212614987234063</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.293544803063413</v>
+        <v>-1.472250135884958</v>
       </c>
       <c r="N5" t="n">
-        <v>0.05907866795818074</v>
+        <v>-0.2746407653157057</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.00582758072777</v>
+        <v>-1.704614913882409</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.201584797557106</v>
+        <v>-1.776809183383114</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.089254825780397</v>
+        <v>1.110705352173893</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.7259252933074368</v>
+        <v>-1.163013149345675</v>
       </c>
       <c r="S5" t="n">
-        <v>1.633178591438786</v>
+        <v>0.2075272911136949</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.724963052190939</v>
+        <v>-0.2751484050149097</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.8950008135020797</v>
+        <v>-1.353808717694005</v>
       </c>
       <c r="V5" t="n">
-        <v>1.266525837464694</v>
+        <v>-0.30543729340709</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.6350237599434502</v>
+        <v>-0.3108990604341575</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.309710156181023</v>
+        <v>-0.469994144408062</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.6331255513021701</v>
+        <v>0.2590533236839396</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.8448589243896535</v>
+        <v>0.04849413887486684</v>
       </c>
       <c r="AA5" t="n">
         <v>-0.1662386772451152</v>
@@ -903,23 +903,23 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>vyy1kC1e</t>
+          <t>tQQLbGv9</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.760387359086781</v>
+        <v>1.939248426247886</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.8146674735397244</v>
+        <v>0.9243580371034607</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.014815664448859</v>
+        <v>-0.4712162475956001</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.533089892472219</v>
+        <v>1.123783316172346</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4844352615150414</v>
+        <v>0.744079874884109</v>
       </c>
       <c r="G6" t="n">
         <v>-0.9805787268653793</v>
@@ -928,58 +928,58 @@
         <v>-0.2234871899330499</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6685191502005404</v>
+        <v>0.2903666067605108</v>
       </c>
       <c r="J6" t="n">
-        <v>0.05159850326629842</v>
+        <v>-0.449883478646584</v>
       </c>
       <c r="K6" t="n">
         <v>-0.001826621254097982</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.192485179356536</v>
+        <v>-0.0212614987234063</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3553418057503047</v>
+        <v>-1.293544803063413</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6083601985895924</v>
+        <v>0.05907866795818074</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.52991808059375</v>
+        <v>-1.00582758072777</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.6263604117310982</v>
+        <v>-1.201584797557106</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.9709125702301064</v>
+        <v>2.089254825780397</v>
       </c>
       <c r="R6" t="n">
-        <v>-2.037188861422153</v>
+        <v>-0.7259252933074368</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2584434089824482</v>
+        <v>1.633178591438786</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3218340967634558</v>
+        <v>-1.724963052190939</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3444313284717694</v>
+        <v>-0.8950008135020797</v>
       </c>
       <c r="V6" t="n">
-        <v>0.114347632997023</v>
+        <v>1.266525837464694</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.2229059975078889</v>
+        <v>-0.6350237599434502</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.3880460794205367</v>
+        <v>-0.309710156181023</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.1523903976729984</v>
+        <v>0.6331255513021701</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.1175682589352894</v>
+        <v>-0.8448589243896535</v>
       </c>
       <c r="AA6" t="n">
         <v>-0.1662386772451152</v>
@@ -988,23 +988,23 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>xhKUdf9L</t>
+          <t>EJYZzDn2</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.790197536946965</v>
+        <v>1.820007714807149</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.2119370408736204</v>
+        <v>-0.893714087659869</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.292936296327271</v>
+        <v>1.121656462253484</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0823527753710601</v>
+        <v>1.781675729741476</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3594097319344284</v>
+        <v>0.2031535970318848</v>
       </c>
       <c r="G7" t="n">
         <v>-0.9805787268653793</v>
@@ -1013,10 +1013,10 @@
         <v>-0.2234871899330499</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3945517910688116</v>
+        <v>-0.2575681115029471</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>-0.449883478646584</v>
       </c>
       <c r="K7" t="n">
         <v>-0.001826621254097982</v>
@@ -1025,46 +1025,46 @@
         <v>-0.0212614987234063</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3553418057503047</v>
+        <v>-0.8467814710095521</v>
       </c>
       <c r="N7" t="n">
-        <v>1.06023696777984</v>
+        <v>-1.943237931685138</v>
       </c>
       <c r="O7" t="n">
-        <v>1.090534418736147</v>
+        <v>-1.704614913882409</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.05113602590509021</v>
+        <v>0.5240883599209177</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.5515342243987474</v>
+        <v>1.017510164211368</v>
       </c>
       <c r="R7" t="n">
-        <v>1.022426130845518</v>
+        <v>0.002554466756294189</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4621078804574613</v>
+        <v>-0.09796941609882462</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5776837403827552</v>
+        <v>-1.298546979492107</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2061381565585409</v>
+        <v>-0.5279544901485393</v>
       </c>
       <c r="V7" t="n">
-        <v>1.732256345266096</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>-1.460124481080289</v>
+        <v>-1.359854141755702</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2077165975072911</v>
+        <v>-1.377221851403092</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.2009889596348801</v>
+        <v>-0.7254637688259258</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0.304813494552062</v>
+        <v>-1.148850113078625</v>
       </c>
       <c r="AA7" t="n">
         <v>-0.1662386772451152</v>
@@ -1073,23 +1073,23 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>EJYZzDn2</t>
+          <t>xhKUdf9L</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1.760387359086781</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.893714087659869</v>
+        <v>-0.2119370408736204</v>
       </c>
       <c r="D8" t="n">
-        <v>1.121656462253484</v>
+        <v>-1.292936296327271</v>
       </c>
       <c r="E8" t="n">
-        <v>1.781675729741476</v>
+        <v>-0.0823527753710601</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3377726808203395</v>
+        <v>0.3005203270452851</v>
       </c>
       <c r="G8" t="n">
         <v>-0.9805787268653793</v>
@@ -1098,10 +1098,10 @@
         <v>-0.2234871899330499</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2575681115029471</v>
+        <v>-0.3945517910688116</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.449883478646584</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>-0.001826621254097982</v>
@@ -1110,46 +1110,46 @@
         <v>-0.0212614987234063</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2213128061341464</v>
+        <v>-0.534047138571849</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.275799065137365</v>
+        <v>1.06023696777984</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.00582758072777</v>
+        <v>1.265231252024807</v>
       </c>
       <c r="P8" t="n">
-        <v>1.099312745746926</v>
+        <v>0.3323468979789151</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.110705352173893</v>
+        <v>0.03896069060486416</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.5802293412946906</v>
+        <v>0.8767301788327715</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1998016518363311</v>
+        <v>0.5469680769053836</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4457148340944425</v>
+        <v>0.4924005258429888</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3444313284717694</v>
+        <v>-0.2526697476333842</v>
       </c>
       <c r="V8" t="n">
-        <v>0.7702733284664288</v>
+        <v>1.649498933805427</v>
       </c>
       <c r="W8" t="n">
-        <v>-1.436498406119787</v>
+        <v>-1.423410474555568</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.373309940190961</v>
+        <v>-0.2213957554724003</v>
       </c>
       <c r="Y8" t="n">
-        <v>-0.8049339449070689</v>
+        <v>0.1403824501080417</v>
       </c>
       <c r="Z8" t="n">
-        <v>-1.223904984434127</v>
+        <v>-0.279932172234474</v>
       </c>
       <c r="AA8" t="n">
         <v>-0.1662386772451152</v>
@@ -1189,16 +1189,16 @@
         <v>-0.9513654605594664</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.001826621254097982</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.192485179356536</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
         <v>-0.489370805366463</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.275799065137365</v>
+        <v>-1.609518498411252</v>
       </c>
       <c r="O9" t="n">
         <v>-1.00582758072777</v>
@@ -1222,19 +1222,19 @@
         <v>0.481422899073696</v>
       </c>
       <c r="V9" t="n">
-        <v>0.8747832071566879</v>
+        <v>0.4949816336225141</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.8490023269769209</v>
+        <v>-0.8813230365663158</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.643173608966387</v>
+        <v>-0.6682000572952248</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0.1387279852933928</v>
+        <v>-0.1288751712568524</v>
       </c>
       <c r="Z9" t="n">
-        <v>-0.6134778449234966</v>
+        <v>-0.6566994388461117</v>
       </c>
       <c r="AA9" t="n">
         <v>-0.1662386772451152</v>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.849817892667333</v>
+        <v>1.939248426247886</v>
       </c>
       <c r="C10" t="n">
         <v>-0.5577659776492538</v>
@@ -1259,7 +1259,7 @@
         <v>1.80697928410952</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.9219730609007416</v>
+        <v>-1.625177222108633</v>
       </c>
       <c r="G10" t="n">
         <v>-0.9805787268653793</v>
@@ -1274,52 +1274,52 @@
         <v>0.5530804851791808</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7344124969974213</v>
+        <v>-0.001826621254097982</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.192485179356536</v>
+        <v>-0.0212614987234063</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1807741927143287</v>
+        <v>-0.489370805366463</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2746407653157058</v>
+        <v>-0.9420796318634789</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.00582758072777</v>
+        <v>-1.52991808059375</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.6263604117310982</v>
+        <v>0.5240883599209177</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.83111978828632</v>
+        <v>0.6913270063425337</v>
       </c>
       <c r="R10" t="n">
-        <v>1.168122082858264</v>
+        <v>0.4396423227945328</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2584434089824482</v>
+        <v>-0.4543822411800974</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.701564477713742</v>
+        <v>-0.9574141213330414</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.06914658595661426</v>
+        <v>-0.6197160709869246</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.3199376362880607</v>
+        <v>0.3249651133431279</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.8320647735730389</v>
+        <v>-0.8183946619239365</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.325256495365197</v>
+        <v>-1.268505665249525</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.329556154200657</v>
+        <v>0.3279516815393565</v>
       </c>
       <c r="Z10" t="n">
-        <v>-0.6218834431238804</v>
+        <v>-0.5981761218423225</v>
       </c>
       <c r="AA10" t="n">
         <v>-0.1662386772451152</v>
@@ -1359,16 +1359,16 @@
         <v>0.05159850326629842</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.001826621254097982</v>
+        <v>-0.7380657395056173</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.0212614987234063</v>
+        <v>-1.192485179356536</v>
       </c>
       <c r="M11" t="n">
         <v>-1.829660801528047</v>
       </c>
       <c r="N11" t="n">
-        <v>1.060236967779841</v>
+        <v>1.727675834327614</v>
       </c>
       <c r="O11" t="n">
         <v>1.614624918602126</v>
@@ -1395,16 +1395,16 @@
         <v>1.098195897470909</v>
       </c>
       <c r="W11" t="n">
-        <v>1.935148508713701</v>
+        <v>1.959427527989247</v>
       </c>
       <c r="X11" t="n">
-        <v>2.298691914818507</v>
+        <v>2.296571562015515</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.1981442559040627</v>
+        <v>0.2489013905043799</v>
       </c>
       <c r="Z11" t="n">
-        <v>-0.8840450003373657</v>
+        <v>-0.8878561448613461</v>
       </c>
       <c r="AA11" t="n">
         <v>-0.1662386772451152</v>
@@ -1511,7 +1511,7 @@
         <v>-0.7619787263775758</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2044208408000993</v>
+        <v>-0.9595426601299006</v>
       </c>
       <c r="F13" t="n">
         <v>-0.3594097319344284</v>
@@ -1529,52 +1529,52 @@
         <v>1.054562467092063</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>-0.001826621254097982</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>-0.0212614987234063</v>
       </c>
       <c r="M13" t="n">
-        <v>2.191209186956704</v>
+        <v>1.118977190027437</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.9420796318634789</v>
+        <v>-1.442658781774309</v>
       </c>
       <c r="O13" t="n">
-        <v>0.04235341900418825</v>
+        <v>-0.4817370808617911</v>
       </c>
       <c r="P13" t="n">
-        <v>0.5240883599209177</v>
+        <v>1.674537131572934</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.405564722814261</v>
+        <v>-0.8463935950391156</v>
       </c>
       <c r="R13" t="n">
         <v>0.2939463707817866</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.8107950662613702</v>
+        <v>-0.6580467126551104</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.46911340857164</v>
+        <v>-0.701564477713742</v>
       </c>
       <c r="U13" t="n">
-        <v>0.481422899073696</v>
+        <v>1.031992384104006</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>0.5041945930142366</v>
+        <v>0.5029599931178573</v>
       </c>
       <c r="X13" t="n">
-        <v>0.1969693416758896</v>
+        <v>0.2218408276874538</v>
       </c>
       <c r="Y13" t="n">
-        <v>-0.501928070821707</v>
+        <v>-0.5759516592341621</v>
       </c>
       <c r="Z13" t="n">
-        <v>-0.5805097296476226</v>
+        <v>-0.5414819720027552</v>
       </c>
       <c r="AA13" t="n">
         <v>-0.1662386772451152</v>
@@ -1583,23 +1583,23 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>v1KiOZ2d</t>
+          <t>KhwykQ8L</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.790197536946965</v>
+        <v>1.939248426247886</v>
       </c>
       <c r="C14" t="n">
-        <v>1.003404651223605</v>
+        <v>1.042927958283678</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9699542994107144</v>
+        <v>-0.1172445342958035</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2803315039042297</v>
+        <v>-0.9595426601299006</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1815165459177958</v>
+        <v>-0.5433246664041846</v>
       </c>
       <c r="G14" t="n">
         <v>-0.9805787268653793</v>
@@ -1608,7 +1608,7 @@
         <v>-0.2234871899330499</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2903666067605108</v>
+        <v>1.523219722853291</v>
       </c>
       <c r="J14" t="n">
         <v>1.054562467092063</v>
@@ -1620,25 +1620,25 @@
         <v>-0.0212614987234063</v>
       </c>
       <c r="M14" t="n">
-        <v>0.7168901911789621</v>
+        <v>0.04674519309817034</v>
       </c>
       <c r="N14" t="n">
-        <v>1.06023696777984</v>
+        <v>2.0613952676015</v>
       </c>
       <c r="O14" t="n">
-        <v>0.5664439188701677</v>
+        <v>2.662805918334085</v>
       </c>
       <c r="P14" t="n">
         <v>-0.05113602590509021</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9861863769829019</v>
+        <v>-0.1474296853201841</v>
       </c>
       <c r="R14" t="n">
-        <v>2.042297794934741</v>
+        <v>-2.328580765447645</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.949272016749007</v>
+        <v>-0.5052983590488507</v>
       </c>
       <c r="T14" t="n">
         <v>1.601082314859953</v>
@@ -1647,19 +1647,19 @@
         <v>0.2061381565585409</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.3804289248628422</v>
       </c>
       <c r="W14" t="n">
-        <v>1.133361778341853</v>
+        <v>1.952219891483083</v>
       </c>
       <c r="X14" t="n">
-        <v>1.516422264206322</v>
+        <v>1.993610953782234</v>
       </c>
       <c r="Y14" t="n">
-        <v>-0.02399443288141778</v>
+        <v>0.4150451082825728</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.237013270062399</v>
+        <v>0.08089533148819972</v>
       </c>
       <c r="AA14" t="n">
         <v>-0.1662386772451152</v>
@@ -1668,23 +1668,23 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>KhwykQ8L</t>
+          <t>v1KiOZ2d</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.939248426247886</v>
+        <v>1.790197536946965</v>
       </c>
       <c r="C15" t="n">
-        <v>1.042927958283678</v>
+        <v>1.003404651223605</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1172445342958035</v>
+        <v>0.9699542994107144</v>
       </c>
       <c r="E15" t="n">
-        <v>1.798544765986838</v>
+        <v>0.2803315039042297</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.5433246664041846</v>
+        <v>0.1815165459177958</v>
       </c>
       <c r="G15" t="n">
         <v>-0.9805787268653793</v>
@@ -1693,58 +1693,58 @@
         <v>-0.2234871899330499</v>
       </c>
       <c r="I15" t="n">
-        <v>1.523219722853291</v>
+        <v>0.2903666067605108</v>
       </c>
       <c r="J15" t="n">
         <v>1.054562467092063</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>-0.001826621254097982</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>-0.0212614987234063</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.6233998049826214</v>
+        <v>0.7168901911789621</v>
       </c>
       <c r="N15" t="n">
         <v>1.06023696777984</v>
       </c>
       <c r="O15" t="n">
-        <v>2.138715418468105</v>
+        <v>0.5664439188701677</v>
       </c>
       <c r="P15" t="n">
-        <v>1.099312745746926</v>
+        <v>-0.05113602590509021</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.2872224672639704</v>
+        <v>-0.9861863769829019</v>
       </c>
       <c r="R15" t="n">
-        <v>-3.057060525511376</v>
+        <v>2.042297794934741</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.218124009211396</v>
+        <v>-2.949272016749007</v>
       </c>
       <c r="T15" t="n">
-        <v>1.345232671240653</v>
+        <v>1.601082314859953</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3444313284717694</v>
+        <v>0.2061381565585409</v>
       </c>
       <c r="V15" t="n">
-        <v>0.3804289248628422</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.933569293542791</v>
+        <v>1.133361778341853</v>
       </c>
       <c r="X15" t="n">
-        <v>2.025335335569067</v>
+        <v>1.516422264206322</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.4232934496578126</v>
+        <v>-0.02399443288141778</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.06138105884714241</v>
+        <v>0.237013270062399</v>
       </c>
       <c r="AA15" t="n">
         <v>-0.1662386772451152</v>
@@ -1753,23 +1753,23 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>f92vnwe3</t>
+          <t>0Y1WIvRG</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.879628070527517</v>
+        <v>1.849817892667333</v>
       </c>
       <c r="C16" t="n">
-        <v>1.91244071360527</v>
+        <v>-0.5577659776492538</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2942303909457018</v>
+        <v>-0.8757553485096533</v>
       </c>
       <c r="E16" t="n">
-        <v>1.140652352417708</v>
+        <v>1.80697928410952</v>
       </c>
       <c r="F16" t="n">
-        <v>0.744079874884109</v>
+        <v>0.4844352615150414</v>
       </c>
       <c r="G16" t="n">
         <v>-0.9805787268653793</v>
@@ -1778,10 +1778,10 @@
         <v>-0.2234871899330499</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2575681115029471</v>
+        <v>-1.764388586727456</v>
       </c>
       <c r="J16" t="n">
-        <v>1.054562467092063</v>
+        <v>0.5530804851791808</v>
       </c>
       <c r="K16" t="n">
         <v>-0.001826621254097982</v>
@@ -1790,46 +1790,46 @@
         <v>-0.0212614987234063</v>
       </c>
       <c r="M16" t="n">
-        <v>0.04674519309817034</v>
+        <v>-1.025486803831096</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.441500481952649</v>
+        <v>0.5596578178690105</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.00582758072777</v>
+        <v>0.04235341900418825</v>
       </c>
       <c r="P16" t="n">
-        <v>0.5240883599209177</v>
+        <v>-1.201584797557106</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.9709125702301064</v>
+        <v>0.5515342243987474</v>
       </c>
       <c r="R16" t="n">
-        <v>-0.8716212453201829</v>
+        <v>-0.2888374372691982</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1488855339675779</v>
+        <v>-1.014459537736383</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.9574141213330414</v>
+        <v>0.3218340967634558</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2061381565585409</v>
+        <v>-1.9961397835627</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.3490208647007955</v>
+        <v>1.145779706209465</v>
       </c>
       <c r="X16" t="n">
-        <v>0.3403041971971741</v>
+        <v>0.6877875171134189</v>
       </c>
       <c r="Y16" t="n">
-        <v>-0.4782125085587655</v>
+        <v>0.5300977667951319</v>
       </c>
       <c r="Z16" t="n">
-        <v>-0.1662147697472167</v>
+        <v>0.4106610766603242</v>
       </c>
       <c r="AA16" t="n">
         <v>-0.1662386772451152</v>
@@ -1838,23 +1838,23 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>0Y1WIvRG</t>
+          <t>f92vnwe3</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.849817892667333</v>
+        <v>1.879628070527517</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.5577659776492538</v>
+        <v>1.91244071360527</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.8757553485096533</v>
+        <v>-0.2942303909457018</v>
       </c>
       <c r="E17" t="n">
-        <v>1.80697928410952</v>
+        <v>1.140652352417708</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4844352615150414</v>
+        <v>0.744079874884109</v>
       </c>
       <c r="G17" t="n">
         <v>-0.9805787268653793</v>
@@ -1863,10 +1863,10 @@
         <v>-0.2234871899330499</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.764388586727456</v>
+        <v>-0.2575681115029471</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5530804851791808</v>
+        <v>1.054562467092063</v>
       </c>
       <c r="K17" t="n">
         <v>-0.001826621254097982</v>
@@ -1875,303 +1875,48 @@
         <v>-0.0212614987234063</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.025486803831096</v>
+        <v>0.04674519309817034</v>
       </c>
       <c r="N17" t="n">
-        <v>0.5596578178690105</v>
+        <v>-0.441500481952649</v>
       </c>
       <c r="O17" t="n">
-        <v>0.04235341900418825</v>
+        <v>-1.00582758072777</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.201584797557106</v>
+        <v>0.5240883599209177</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.5515342243987474</v>
+        <v>0.9709125702301064</v>
       </c>
       <c r="R17" t="n">
-        <v>-0.2888374372691982</v>
+        <v>-0.8716212453201829</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.014459537736383</v>
+        <v>-0.1488855339675779</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3218340967634558</v>
+        <v>-0.9574141213330414</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.9961397835627</v>
+        <v>0.2061381565585409</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.21861156715701</v>
+        <v>0.2942723976407662</v>
       </c>
       <c r="X17" t="n">
-        <v>0.702602855466236</v>
+        <v>0.3405975108639174</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.5279922109985465</v>
+        <v>-0.5546961417158552</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.4411939543290155</v>
+        <v>-0.2110145074802249</v>
       </c>
       <c r="AA17" t="n">
-        <v>-0.1662386772451152</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>8CpDVHAM</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1.849817892667333</v>
-      </c>
-      <c r="C18" t="n">
-        <v>-1.032045662370122</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0.03445762854696641</v>
-      </c>
-      <c r="E18" t="n">
-        <v>-1.406572120632002</v>
-      </c>
-      <c r="F18" t="n">
-        <v>-0.7164210753168965</v>
-      </c>
-      <c r="G18" t="n">
-        <v>-0.9805787268653793</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-0.2234871899330499</v>
-      </c>
-      <c r="I18" t="n">
-        <v>-2.449306984556779</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1.054562467092063</v>
-      </c>
-      <c r="K18" t="n">
-        <v>-0.001826621254097982</v>
-      </c>
-      <c r="L18" t="n">
-        <v>-0.0212614987234063</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1.118977190027437</v>
-      </c>
-      <c r="N18" t="n">
-        <v>-0.9420796318634789</v>
-      </c>
-      <c r="O18" t="n">
-        <v>-1.00582758072777</v>
-      </c>
-      <c r="P18" t="n">
-        <v>-0.6263604117310982</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2.508633171611756</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.168122082858264</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.040507534388812</v>
-      </c>
-      <c r="T18" t="n">
-        <v>-1.46911340857164</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0.2061381565585409</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
-        <v>-0.7339048429684857</v>
-      </c>
-      <c r="X18" t="n">
-        <v>-1.843505185061151</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>-0.327912349696365</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.993146101650202</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>-0.1662386772451152</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>4KmdZaBc</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>1.760387359086781</v>
-      </c>
-      <c r="C19" t="n">
-        <v>-1.269185504730557</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0.9067450648928936</v>
-      </c>
-      <c r="E19" t="n">
-        <v>-1.533089892472219</v>
-      </c>
-      <c r="F19" t="n">
-        <v>-0.3377726808203395</v>
-      </c>
-      <c r="G19" t="n">
-        <v>-0.9805787268653793</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-0.2234871899330499</v>
-      </c>
-      <c r="I19" t="n">
-        <v>-1.490421227595728</v>
-      </c>
-      <c r="J19" t="n">
-        <v>-0.9513654605594664</v>
-      </c>
-      <c r="K19" t="n">
-        <v>-0.001826621254097982</v>
-      </c>
-      <c r="L19" t="n">
-        <v>-0.0212614987234063</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0.5828611915628038</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0.05907866795818074</v>
-      </c>
-      <c r="O19" t="n">
-        <v>-1.00582758072777</v>
-      </c>
-      <c r="P19" t="n">
-        <v>-1.201584797557106</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>-1.685150286701833</v>
-      </c>
-      <c r="R19" t="n">
-        <v>-0.7259252933074368</v>
-      </c>
-      <c r="S19" t="n">
-        <v>1.124017412751253</v>
-      </c>
-      <c r="T19" t="n">
-        <v>-1.724963052190939</v>
-      </c>
-      <c r="U19" t="n">
-        <v>-0.3444313284717694</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" t="n">
-        <v>-0.3590557801428499</v>
-      </c>
-      <c r="X19" t="n">
-        <v>-1.308932996646831</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>-0.5035105564953063</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>0.4784868824972571</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>-0.1662386772451152</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>hpMqQeYq</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>1.820007714807149</v>
-      </c>
-      <c r="C20" t="n">
-        <v>1.141736225933859</v>
-      </c>
-      <c r="D20" t="n">
-        <v>-1.014815664448859</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0.297200540149592</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0.4844352615150414</v>
-      </c>
-      <c r="G20" t="n">
-        <v>-0.9805787268653793</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-0.2234871899330499</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0.01639924762878189</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1.054562467092063</v>
-      </c>
-      <c r="K20" t="n">
-        <v>-0.001826621254097982</v>
-      </c>
-      <c r="L20" t="n">
-        <v>-0.0212614987234063</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0.3148031923304871</v>
-      </c>
-      <c r="N20" t="n">
-        <v>-0.9420796318634789</v>
-      </c>
-      <c r="O20" t="n">
-        <v>-0.4817370808617911</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0.5240883599209177</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>-0.4270152492077567</v>
-      </c>
-      <c r="R20" t="n">
-        <v>-1.163013149345675</v>
-      </c>
-      <c r="S20" t="n">
-        <v>1.429514119963773</v>
-      </c>
-      <c r="T20" t="n">
-        <v>-0.1898651904751431</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.857846611649472</v>
-      </c>
-      <c r="V20" t="n">
-        <v>-0.30543729340709</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0.6872772516810614</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.025042078690394</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>0.7785233428811195</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>0.7020116901136255</v>
-      </c>
-      <c r="AA20" t="n">
         <v>-0.1662386772451152</v>
       </c>
     </row>

--- a/data/spain/p6_deployment/data_preparation/df_selected_nan.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_selected_nan.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA17"/>
+  <dimension ref="A1:AA11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.939248426247886</v>
+        <v>1.909438248387701</v>
       </c>
       <c r="C2" t="n">
         <v>0.3413892579673929</v>
@@ -576,7 +576,7 @@
         <v>1.627330338396051</v>
       </c>
       <c r="E2" t="n">
-        <v>1.140652352417708</v>
+        <v>0.7526645187743746</v>
       </c>
       <c r="F2" t="n">
         <v>0.1815165459177958</v>
@@ -600,46 +600,46 @@
         <v>1.149962181909723</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4488321919466454</v>
+        <v>0.1807741927143287</v>
       </c>
       <c r="N2" t="n">
         <v>0.7265175345059538</v>
       </c>
       <c r="O2" t="n">
-        <v>1.614624918602126</v>
+        <v>1.265231252024807</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.05113602590509021</v>
+        <v>0.1406054360369124</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.9861863769829019</v>
+        <v>-0.566808031151543</v>
       </c>
       <c r="R2" t="n">
-        <v>0.4396423227945328</v>
+        <v>0.7310342268200253</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.523620716423916</v>
+        <v>-1.235096048500981</v>
       </c>
       <c r="T2" t="n">
-        <v>1.601082314859953</v>
+        <v>1.856931958479252</v>
       </c>
       <c r="U2" t="n">
-        <v>1.031992384104006</v>
+        <v>0.9402308032656214</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.716280934947868</v>
+        <v>1.701179032123172</v>
       </c>
       <c r="X2" t="n">
-        <v>1.825463930742316</v>
+        <v>1.754676846394154</v>
       </c>
       <c r="Y2" t="n">
-        <v>-1.238187492661567</v>
+        <v>-1.267517991172074</v>
       </c>
       <c r="Z2" t="n">
-        <v>-0.7074116682397645</v>
+        <v>-0.6937006269931842</v>
       </c>
       <c r="AA2" t="n">
         <v>-0.1662386772451152</v>
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.820007714807149</v>
+        <v>1.760387359086781</v>
       </c>
       <c r="C3" t="n">
         <v>0.7168606750380806</v>
@@ -664,7 +664,7 @@
         <v>-1.406572120632002</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.5433246664041846</v>
+        <v>1.13354679493771</v>
       </c>
       <c r="G3" t="n">
         <v>-0.9805787268653793</v>
@@ -679,52 +679,52 @@
         <v>-0.449883478646584</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>-0.7380657395056173</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>-1.192485179356536</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.097718800760363</v>
+        <v>-2.231747800376521</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2746407653157057</v>
+        <v>0.05907866795818074</v>
       </c>
       <c r="O3" t="n">
         <v>-0.4817370808617911</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.6263604117310982</v>
+        <v>-1.009843335615104</v>
       </c>
       <c r="Q3" t="n">
         <v>-0.566808031151543</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.2888374372691982</v>
+        <v>0.1482504187690404</v>
       </c>
       <c r="S3" t="n">
-        <v>2.651500948813851</v>
+        <v>2.210227927284656</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.724963052190939</v>
+        <v>-1.127980550412574</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.8950008135020797</v>
+        <v>-1.07852397517885</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.05699808537978705</v>
+        <v>-0.005280195770989188</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.8489120053807017</v>
+        <v>-0.7567333730014582</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.286034722403727</v>
+        <v>-1.180302107898821</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.9680690604209629</v>
+        <v>0.9525833105682177</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.08457768681341578</v>
+        <v>0.1312106473738017</v>
       </c>
       <c r="AA3" t="n">
         <v>-0.1662386772451152</v>
@@ -737,7 +737,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.939248426247886</v>
+        <v>1.790197536946965</v>
       </c>
       <c r="C4" t="n">
         <v>0.8650730765133521</v>
@@ -749,7 +749,7 @@
         <v>-0.3606918734195383</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.625177222108633</v>
+        <v>-1.538629017652277</v>
       </c>
       <c r="G4" t="n">
         <v>-0.9805787268653793</v>
@@ -770,46 +770,46 @@
         <v>-0.0212614987234063</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.9808104706257106</v>
+        <v>0.2701268591251006</v>
       </c>
       <c r="N4" t="n">
-        <v>0.05907866795818074</v>
+        <v>-0.6083601985895923</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5664439188701677</v>
+        <v>-0.6564339141504508</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.8181018736731009</v>
+        <v>-0.05113602590509021</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.297095728098941</v>
+        <v>1.203900540136417</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3910770054569509</v>
+        <v>0.5853382748072791</v>
       </c>
       <c r="S4" t="n">
-        <v>0.411191762588708</v>
+        <v>0.4281638018782922</v>
       </c>
       <c r="T4" t="n">
-        <v>1.856931958479252</v>
+        <v>1.601082314859953</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2526697476333842</v>
+        <v>0.6649460607504661</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2426756674936158</v>
+        <v>0.6225846509750571</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2913718196737404</v>
+        <v>0.244607373544286</v>
       </c>
       <c r="X4" t="n">
-        <v>1.20088161618552</v>
+        <v>1.156122503572948</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.135796246644002</v>
+        <v>1.22103364042808</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.6336026800513261</v>
+        <v>0.5022823154623396</v>
       </c>
       <c r="AA4" t="n">
         <v>-0.1662386772451152</v>
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.820007714807149</v>
+        <v>1.939248426247886</v>
       </c>
       <c r="C5" t="n">
         <v>-0.8146674735397244</v>
@@ -831,7 +831,7 @@
         <v>-1.014815664448859</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.533089892472219</v>
+        <v>-1.651173146189756</v>
       </c>
       <c r="F5" t="n">
         <v>0.2031535970318848</v>
@@ -855,46 +855,46 @@
         <v>-0.0212614987234063</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.472250135884958</v>
+        <v>-1.516926469090344</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2746407653157057</v>
+        <v>-0.6083601985895924</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.704614913882409</v>
+        <v>-2.054008580459729</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.776809183383114</v>
+        <v>-0.4346189497890955</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.110705352173893</v>
+        <v>0.83111978828632</v>
       </c>
       <c r="R5" t="n">
         <v>-1.163013149345675</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2075272911136949</v>
+        <v>0.6657723519324743</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2751484050149097</v>
+        <v>-1.127980550412574</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.353808717694005</v>
+        <v>-0.9867623943404646</v>
       </c>
       <c r="V5" t="n">
         <v>-0.30543729340709</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.3108990604341575</v>
+        <v>-0.3480210032492177</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.469994144408062</v>
+        <v>-0.49249398191418</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.2590533236839396</v>
+        <v>0.2635796994773766</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.04849413887486684</v>
+        <v>0.001620015804766217</v>
       </c>
       <c r="AA5" t="n">
         <v>-0.1662386772451152</v>
@@ -907,7 +907,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.939248426247886</v>
+        <v>1.760387359086781</v>
       </c>
       <c r="C6" t="n">
         <v>0.9243580371034607</v>
@@ -916,10 +916,10 @@
         <v>-0.4712162475956001</v>
       </c>
       <c r="E6" t="n">
-        <v>1.123783316172346</v>
+        <v>-0.5293822358731616</v>
       </c>
       <c r="F6" t="n">
-        <v>0.744079874884109</v>
+        <v>1.166002371608844</v>
       </c>
       <c r="G6" t="n">
         <v>-0.9805787268653793</v>
@@ -940,46 +940,46 @@
         <v>-0.0212614987234063</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.293544803063413</v>
+        <v>-2.231747800376522</v>
       </c>
       <c r="N6" t="n">
-        <v>0.05907866795818074</v>
+        <v>0.7265175345059537</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.00582758072777</v>
+        <v>-0.3070402475731312</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.201584797557106</v>
+        <v>-0.8181018736731009</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.089254825780397</v>
+        <v>1.110705352173892</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.7259252933074368</v>
+        <v>-0.1917068025940339</v>
       </c>
       <c r="S6" t="n">
-        <v>1.633178591438786</v>
+        <v>0.9712690591449937</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.724963052190939</v>
+        <v>-0.7868476922535084</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.8950008135020797</v>
+        <v>-1.904378202724315</v>
       </c>
       <c r="V6" t="n">
-        <v>1.266525837464694</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.6350237599434502</v>
+        <v>-0.6331206185193767</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.309710156181023</v>
+        <v>-0.2834180900309805</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.6331255513021701</v>
+        <v>0.7023767944066482</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.8448589243896535</v>
+        <v>-0.7756567073229399</v>
       </c>
       <c r="AA6" t="n">
         <v>-0.1662386772451152</v>
@@ -988,23 +988,23 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>EJYZzDn2</t>
+          <t>xhKUdf9L</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1.820007714807149</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.893714087659869</v>
+        <v>-0.2119370408736204</v>
       </c>
       <c r="D7" t="n">
-        <v>1.121656462253484</v>
+        <v>-1.292936296327271</v>
       </c>
       <c r="E7" t="n">
-        <v>1.781675729741476</v>
+        <v>-0.2510431378246833</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2031535970318848</v>
+        <v>0.3005203270452851</v>
       </c>
       <c r="G7" t="n">
         <v>-0.9805787268653793</v>
@@ -1013,10 +1013,10 @@
         <v>-0.2234871899330499</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2575681115029471</v>
+        <v>-0.3945517910688116</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.449883478646584</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>-0.001826621254097982</v>
@@ -1025,46 +1025,46 @@
         <v>-0.0212614987234063</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.8467814710095521</v>
+        <v>-0.6233998049826214</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.943237931685138</v>
+        <v>1.06023696777984</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.704614913882409</v>
+        <v>0.7411407521588275</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5240883599209177</v>
+        <v>-0.05113602590509021</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.017510164211368</v>
+        <v>0.7379246003237957</v>
       </c>
       <c r="R7" t="n">
-        <v>0.002554466756294189</v>
+        <v>0.9738608135079357</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.09796941609882462</v>
+        <v>0.4621078804574613</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.298546979492107</v>
+        <v>-0.1045819759353765</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5279544901485393</v>
+        <v>-0.8032392326636945</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.649498933805427</v>
       </c>
       <c r="W7" t="n">
-        <v>-1.359854141755702</v>
+        <v>-1.346889815924053</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.377221851403092</v>
+        <v>-0.2138979794810296</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.7254637688259258</v>
+        <v>0.1043713924943138</v>
       </c>
       <c r="Z7" t="n">
-        <v>-1.148850113078625</v>
+        <v>-0.288845345638417</v>
       </c>
       <c r="AA7" t="n">
         <v>-0.1662386772451152</v>
@@ -1073,23 +1073,23 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>xhKUdf9L</t>
+          <t>EJYZzDn2</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.760387359086781</v>
+        <v>1.909438248387701</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.2119370408736204</v>
+        <v>-0.893714087659869</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.292936296327271</v>
+        <v>1.121656462253484</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0823527753710601</v>
+        <v>-0.7402451889401905</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3005203270452851</v>
+        <v>0.2031535970318848</v>
       </c>
       <c r="G8" t="n">
         <v>-0.9805787268653793</v>
@@ -1098,10 +1098,10 @@
         <v>-0.2234871899330499</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3945517910688116</v>
+        <v>-0.2575681115029471</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>-0.449883478646584</v>
       </c>
       <c r="K8" t="n">
         <v>-0.001826621254097982</v>
@@ -1110,46 +1110,46 @@
         <v>-0.0212614987234063</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.534047138571849</v>
+        <v>-0.8021051378041663</v>
       </c>
       <c r="N8" t="n">
-        <v>1.06023696777984</v>
+        <v>-2.276957364959025</v>
       </c>
       <c r="O8" t="n">
-        <v>1.265231252024807</v>
+        <v>-2.054008580459729</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3323468979789151</v>
+        <v>-0.05113602590509021</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.03896069060486416</v>
+        <v>0.8311197882863203</v>
       </c>
       <c r="R8" t="n">
-        <v>0.8767301788327715</v>
+        <v>0.2939463707817866</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5469680769053836</v>
+        <v>-0.2846618482842534</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4924005258429888</v>
+        <v>-1.810246266730706</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2526697476333842</v>
+        <v>-0.9867623943404644</v>
       </c>
       <c r="V8" t="n">
-        <v>1.649498933805427</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>-1.423410474555568</v>
+        <v>-1.367450076413118</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2213957554724003</v>
+        <v>-1.386958078695931</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.1403824501080417</v>
+        <v>-0.806479530365346</v>
       </c>
       <c r="Z8" t="n">
-        <v>-0.279932172234474</v>
+        <v>-1.184373756773509</v>
       </c>
       <c r="AA8" t="n">
         <v>-0.1662386772451152</v>
@@ -1162,7 +1162,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.909438248387701</v>
+        <v>1.790197536946965</v>
       </c>
       <c r="C9" t="n">
         <v>-0.07360546616336709</v>
@@ -1171,10 +1171,10 @@
         <v>-1.027457511352423</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2803315039042297</v>
+        <v>-0.9595426601299006</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.603540170994544</v>
+        <v>1.78265832836038</v>
       </c>
       <c r="G9" t="n">
         <v>-0.9805787268653793</v>
@@ -1189,52 +1189,52 @@
         <v>-0.9513654605594664</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>-0.001826621254097982</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-0.0212614987234063</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.489370805366463</v>
+        <v>-0.08728380651798802</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.609518498411252</v>
+        <v>-0.9420796318634789</v>
       </c>
       <c r="O9" t="n">
         <v>-1.00582758072777</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5240883599209177</v>
+        <v>-0.4346189497890956</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.384114196420765</v>
+        <v>-2.337516602439503</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4396423227945328</v>
+        <v>-0.1917068025940339</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1998016518363311</v>
+        <v>-0.182829612546747</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1898651904751431</v>
+        <v>-0.6162812631739756</v>
       </c>
       <c r="U9" t="n">
-        <v>0.481422899073696</v>
+        <v>0.6649460607504661</v>
       </c>
       <c r="V9" t="n">
         <v>0.4949816336225141</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.8813230365663158</v>
+        <v>-0.8812727218261887</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.6682000572952248</v>
+        <v>-0.677065725487926</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0.1288751712568524</v>
+        <v>-0.006782796592234719</v>
       </c>
       <c r="Z9" t="n">
-        <v>-0.6566994388461117</v>
+        <v>-0.6535624676346825</v>
       </c>
       <c r="AA9" t="n">
         <v>-0.1662386772451152</v>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.939248426247886</v>
+        <v>1.879628070527517</v>
       </c>
       <c r="C10" t="n">
         <v>-0.5577659776492538</v>
@@ -1256,10 +1256,10 @@
         <v>1.033163533928535</v>
       </c>
       <c r="E10" t="n">
-        <v>1.80697928410952</v>
+        <v>-0.7402451889401905</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.625177222108633</v>
+        <v>0.2788832759311962</v>
       </c>
       <c r="G10" t="n">
         <v>-0.9805787268653793</v>
@@ -1280,46 +1280,46 @@
         <v>-0.0212614987234063</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.489370805366463</v>
+        <v>-0.8914578042149379</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.9420796318634789</v>
+        <v>-0.2746407653157059</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.52991808059375</v>
+        <v>-0.6564339141504508</v>
       </c>
       <c r="P10" t="n">
-        <v>0.5240883599209177</v>
+        <v>0.3323468979789151</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.6913270063425337</v>
+        <v>1.203900540136417</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4396423227945328</v>
+        <v>0.2939463707817866</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4543822411800974</v>
+        <v>0.05477893750743516</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9574141213330414</v>
+        <v>-1.127980550412574</v>
       </c>
       <c r="U10" t="n">
         <v>-0.6197160709869246</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3249651133431279</v>
+        <v>0.9734929486945569</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.8183946619239365</v>
+        <v>-0.9001988750619974</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.268505665249525</v>
+        <v>-1.197878483477588</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.3279516815393565</v>
+        <v>0.4938612014217748</v>
       </c>
       <c r="Z10" t="n">
-        <v>-0.5981761218423225</v>
+        <v>-0.6007268565440711</v>
       </c>
       <c r="AA10" t="n">
         <v>-0.1662386772451152</v>
@@ -1341,10 +1341,10 @@
         <v>1.930734664081591</v>
       </c>
       <c r="E11" t="n">
-        <v>1.80697928410952</v>
+        <v>-1.634304109944393</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2620430019210281</v>
+        <v>-0.1105836441224053</v>
       </c>
       <c r="G11" t="n">
         <v>-0.9805787268653793</v>
@@ -1359,564 +1359,54 @@
         <v>0.05159850326629842</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.7380657395056173</v>
+        <v>-0.001826621254097982</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.192485179356536</v>
+        <v>-0.0212614987234063</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.829660801528047</v>
+        <v>-1.248868469858027</v>
       </c>
       <c r="N11" t="n">
         <v>1.727675834327614</v>
       </c>
       <c r="O11" t="n">
-        <v>1.614624918602126</v>
+        <v>1.789321751890786</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.6263604117310982</v>
+        <v>-0.05113602590509021</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.265771940870474</v>
+        <v>-1.032783970964164</v>
       </c>
       <c r="R11" t="n">
-        <v>0.5853382748072791</v>
+        <v>0.1968157361066223</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.389194720192721</v>
+        <v>-1.778201305767682</v>
       </c>
       <c r="T11" t="n">
-        <v>1.856931958479252</v>
+        <v>1.771648743939486</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.9961397835627</v>
+        <v>-0.8032392326636948</v>
       </c>
       <c r="V11" t="n">
         <v>1.098195897470909</v>
       </c>
       <c r="W11" t="n">
-        <v>1.959427527989247</v>
+        <v>1.786938164667953</v>
       </c>
       <c r="X11" t="n">
-        <v>2.296571562015515</v>
+        <v>2.186253717864907</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.2489013905043799</v>
+        <v>0.2330737135011751</v>
       </c>
       <c r="Z11" t="n">
-        <v>-0.8878561448613461</v>
+        <v>-0.8768403924759218</v>
       </c>
       <c r="AA11" t="n">
-        <v>-0.1662386772451152</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>0ns5XwtA</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1.939248426247886</v>
-      </c>
-      <c r="C12" t="n">
-        <v>-0.4886001902941271</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.312578260425378</v>
-      </c>
-      <c r="E12" t="n">
-        <v>-0.0823527753710601</v>
-      </c>
-      <c r="F12" t="n">
-        <v>-0.2620430019210281</v>
-      </c>
-      <c r="G12" t="n">
-        <v>-0.9805787268653793</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-0.2234871899330499</v>
-      </c>
-      <c r="I12" t="n">
-        <v>-1.079470188898134</v>
-      </c>
-      <c r="J12" t="n">
-        <v>-0.9513654605594664</v>
-      </c>
-      <c r="K12" t="n">
-        <v>-0.001826621254097982</v>
-      </c>
-      <c r="L12" t="n">
-        <v>-0.0212614987234063</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0.9849481904112789</v>
-      </c>
-      <c r="N12" t="n">
-        <v>-1.442658781774309</v>
-      </c>
-      <c r="O12" t="n">
-        <v>-0.4817370808617911</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1.674537131572934</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0.9709125702301064</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0.002554466756294189</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1.022185177013747</v>
-      </c>
-      <c r="T12" t="n">
-        <v>-0.701564477713742</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0.7567076415888512</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0.1310230273101374</v>
-      </c>
-      <c r="W12" t="n">
-        <v>-2.285199579796523</v>
-      </c>
-      <c r="X12" t="n">
-        <v>-3.702371329668092</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>-0.2322361289673371</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>0.3558418508597789</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>-0.1662386772451152</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>CQ0ABdJj</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1.760387359086781</v>
-      </c>
-      <c r="C13" t="n">
-        <v>1.24054449358404</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-0.7619787263775758</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-0.9595426601299006</v>
-      </c>
-      <c r="F13" t="n">
-        <v>-0.3594097319344284</v>
-      </c>
-      <c r="G13" t="n">
-        <v>-0.9805787268653793</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-0.2234871899330499</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0.1533829271946464</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1.054562467092063</v>
-      </c>
-      <c r="K13" t="n">
-        <v>-0.001826621254097982</v>
-      </c>
-      <c r="L13" t="n">
-        <v>-0.0212614987234063</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1.118977190027437</v>
-      </c>
-      <c r="N13" t="n">
-        <v>-1.442658781774309</v>
-      </c>
-      <c r="O13" t="n">
-        <v>-0.4817370808617911</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1.674537131572934</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>-0.8463935950391156</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0.2939463707817866</v>
-      </c>
-      <c r="S13" t="n">
-        <v>-0.6580467126551104</v>
-      </c>
-      <c r="T13" t="n">
-        <v>-0.701564477713742</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.031992384104006</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0.5029599931178573</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0.2218408276874538</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>-0.5759516592341621</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>-0.5414819720027552</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>-0.1662386772451152</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>KhwykQ8L</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1.939248426247886</v>
-      </c>
-      <c r="C14" t="n">
-        <v>1.042927958283678</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-0.1172445342958035</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-0.9595426601299006</v>
-      </c>
-      <c r="F14" t="n">
-        <v>-0.5433246664041846</v>
-      </c>
-      <c r="G14" t="n">
-        <v>-0.9805787268653793</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-0.2234871899330499</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1.523219722853291</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1.054562467092063</v>
-      </c>
-      <c r="K14" t="n">
-        <v>-0.001826621254097982</v>
-      </c>
-      <c r="L14" t="n">
-        <v>-0.0212614987234063</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0.04674519309817034</v>
-      </c>
-      <c r="N14" t="n">
-        <v>2.0613952676015</v>
-      </c>
-      <c r="O14" t="n">
-        <v>2.662805918334085</v>
-      </c>
-      <c r="P14" t="n">
-        <v>-0.05113602590509021</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>-0.1474296853201841</v>
-      </c>
-      <c r="R14" t="n">
-        <v>-2.328580765447645</v>
-      </c>
-      <c r="S14" t="n">
-        <v>-0.5052983590488507</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.601082314859953</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0.2061381565585409</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0.3804289248628422</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.952219891483083</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.993610953782234</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0.4150451082825728</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>0.08089533148819972</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>-0.1662386772451152</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>v1KiOZ2d</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1.790197536946965</v>
-      </c>
-      <c r="C15" t="n">
-        <v>1.003404651223605</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0.9699542994107144</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0.2803315039042297</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0.1815165459177958</v>
-      </c>
-      <c r="G15" t="n">
-        <v>-0.9805787268653793</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-0.2234871899330499</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0.2903666067605108</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1.054562467092063</v>
-      </c>
-      <c r="K15" t="n">
-        <v>-0.001826621254097982</v>
-      </c>
-      <c r="L15" t="n">
-        <v>-0.0212614987234063</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0.7168901911789621</v>
-      </c>
-      <c r="N15" t="n">
-        <v>1.06023696777984</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0.5664439188701677</v>
-      </c>
-      <c r="P15" t="n">
-        <v>-0.05113602590509021</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>-0.9861863769829019</v>
-      </c>
-      <c r="R15" t="n">
-        <v>2.042297794934741</v>
-      </c>
-      <c r="S15" t="n">
-        <v>-2.949272016749007</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.601082314859953</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0.2061381565585409</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.133361778341853</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.516422264206322</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>-0.02399443288141778</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>0.237013270062399</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>-0.1662386772451152</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>0Y1WIvRG</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1.849817892667333</v>
-      </c>
-      <c r="C16" t="n">
-        <v>-0.5577659776492538</v>
-      </c>
-      <c r="D16" t="n">
-        <v>-0.8757553485096533</v>
-      </c>
-      <c r="E16" t="n">
-        <v>1.80697928410952</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0.4844352615150414</v>
-      </c>
-      <c r="G16" t="n">
-        <v>-0.9805787268653793</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-0.2234871899330499</v>
-      </c>
-      <c r="I16" t="n">
-        <v>-1.764388586727456</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0.5530804851791808</v>
-      </c>
-      <c r="K16" t="n">
-        <v>-0.001826621254097982</v>
-      </c>
-      <c r="L16" t="n">
-        <v>-0.0212614987234063</v>
-      </c>
-      <c r="M16" t="n">
-        <v>-1.025486803831096</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0.5596578178690105</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0.04235341900418825</v>
-      </c>
-      <c r="P16" t="n">
-        <v>-1.201584797557106</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0.5515342243987474</v>
-      </c>
-      <c r="R16" t="n">
-        <v>-0.2888374372691982</v>
-      </c>
-      <c r="S16" t="n">
-        <v>-1.014459537736383</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0.3218340967634558</v>
-      </c>
-      <c r="U16" t="n">
-        <v>-1.9961397835627</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.145779706209465</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0.6877875171134189</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0.5300977667951319</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>0.4106610766603242</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>-0.1662386772451152</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>f92vnwe3</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1.879628070527517</v>
-      </c>
-      <c r="C17" t="n">
-        <v>1.91244071360527</v>
-      </c>
-      <c r="D17" t="n">
-        <v>-0.2942303909457018</v>
-      </c>
-      <c r="E17" t="n">
-        <v>1.140652352417708</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0.744079874884109</v>
-      </c>
-      <c r="G17" t="n">
-        <v>-0.9805787268653793</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-0.2234871899330499</v>
-      </c>
-      <c r="I17" t="n">
-        <v>-0.2575681115029471</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1.054562467092063</v>
-      </c>
-      <c r="K17" t="n">
-        <v>-0.001826621254097982</v>
-      </c>
-      <c r="L17" t="n">
-        <v>-0.0212614987234063</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0.04674519309817034</v>
-      </c>
-      <c r="N17" t="n">
-        <v>-0.441500481952649</v>
-      </c>
-      <c r="O17" t="n">
-        <v>-1.00582758072777</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0.5240883599209177</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0.9709125702301064</v>
-      </c>
-      <c r="R17" t="n">
-        <v>-0.8716212453201829</v>
-      </c>
-      <c r="S17" t="n">
-        <v>-0.1488855339675779</v>
-      </c>
-      <c r="T17" t="n">
-        <v>-0.9574141213330414</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0.2061381565585409</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0.2942723976407662</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0.3405975108639174</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>-0.5546961417158552</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>-0.2110145074802249</v>
-      </c>
-      <c r="AA17" t="n">
         <v>-0.1662386772451152</v>
       </c>
     </row>

--- a/data/spain/p6_deployment/data_preparation/df_selected_nan.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_selected_nan.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA11"/>
+  <dimension ref="A1:AA6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -721,7 +721,7 @@
         <v>-1.180302107898821</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.9525833105682177</v>
+        <v>0.9525833105682263</v>
       </c>
       <c r="Z3" t="n">
         <v>0.1312106473738017</v>
@@ -979,434 +979,9 @@
         <v>0.7023767944066482</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.7756567073229399</v>
+        <v>-0.7756567073229435</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.1662386772451152</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>xhKUdf9L</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1.820007714807149</v>
-      </c>
-      <c r="C7" t="n">
-        <v>-0.2119370408736204</v>
-      </c>
-      <c r="D7" t="n">
-        <v>-1.292936296327271</v>
-      </c>
-      <c r="E7" t="n">
-        <v>-0.2510431378246833</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.3005203270452851</v>
-      </c>
-      <c r="G7" t="n">
-        <v>-0.9805787268653793</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-0.2234871899330499</v>
-      </c>
-      <c r="I7" t="n">
-        <v>-0.3945517910688116</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>-0.001826621254097982</v>
-      </c>
-      <c r="L7" t="n">
-        <v>-0.0212614987234063</v>
-      </c>
-      <c r="M7" t="n">
-        <v>-0.6233998049826214</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1.06023696777984</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0.7411407521588275</v>
-      </c>
-      <c r="P7" t="n">
-        <v>-0.05113602590509021</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0.7379246003237957</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0.9738608135079357</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0.4621078804574613</v>
-      </c>
-      <c r="T7" t="n">
-        <v>-0.1045819759353765</v>
-      </c>
-      <c r="U7" t="n">
-        <v>-0.8032392326636945</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.649498933805427</v>
-      </c>
-      <c r="W7" t="n">
-        <v>-1.346889815924053</v>
-      </c>
-      <c r="X7" t="n">
-        <v>-0.2138979794810296</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0.1043713924943138</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>-0.288845345638417</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>-0.1662386772451152</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>EJYZzDn2</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1.909438248387701</v>
-      </c>
-      <c r="C8" t="n">
-        <v>-0.893714087659869</v>
-      </c>
-      <c r="D8" t="n">
-        <v>1.121656462253484</v>
-      </c>
-      <c r="E8" t="n">
-        <v>-0.7402451889401905</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.2031535970318848</v>
-      </c>
-      <c r="G8" t="n">
-        <v>-0.9805787268653793</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-0.2234871899330499</v>
-      </c>
-      <c r="I8" t="n">
-        <v>-0.2575681115029471</v>
-      </c>
-      <c r="J8" t="n">
-        <v>-0.449883478646584</v>
-      </c>
-      <c r="K8" t="n">
-        <v>-0.001826621254097982</v>
-      </c>
-      <c r="L8" t="n">
-        <v>-0.0212614987234063</v>
-      </c>
-      <c r="M8" t="n">
-        <v>-0.8021051378041663</v>
-      </c>
-      <c r="N8" t="n">
-        <v>-2.276957364959025</v>
-      </c>
-      <c r="O8" t="n">
-        <v>-2.054008580459729</v>
-      </c>
-      <c r="P8" t="n">
-        <v>-0.05113602590509021</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0.8311197882863203</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0.2939463707817866</v>
-      </c>
-      <c r="S8" t="n">
-        <v>-0.2846618482842534</v>
-      </c>
-      <c r="T8" t="n">
-        <v>-1.810246266730706</v>
-      </c>
-      <c r="U8" t="n">
-        <v>-0.9867623943404644</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>-1.367450076413118</v>
-      </c>
-      <c r="X8" t="n">
-        <v>-1.386958078695931</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>-0.806479530365346</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>-1.184373756773509</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>-0.1662386772451152</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>GOO6q4Wr</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1.790197536946965</v>
-      </c>
-      <c r="C9" t="n">
-        <v>-0.07360546616336709</v>
-      </c>
-      <c r="D9" t="n">
-        <v>-1.027457511352423</v>
-      </c>
-      <c r="E9" t="n">
-        <v>-0.9595426601299006</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1.78265832836038</v>
-      </c>
-      <c r="G9" t="n">
-        <v>-0.9805787268653793</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-0.2234871899330499</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.4273502863263753</v>
-      </c>
-      <c r="J9" t="n">
-        <v>-0.9513654605594664</v>
-      </c>
-      <c r="K9" t="n">
-        <v>-0.001826621254097982</v>
-      </c>
-      <c r="L9" t="n">
-        <v>-0.0212614987234063</v>
-      </c>
-      <c r="M9" t="n">
-        <v>-0.08728380651798802</v>
-      </c>
-      <c r="N9" t="n">
-        <v>-0.9420796318634789</v>
-      </c>
-      <c r="O9" t="n">
-        <v>-1.00582758072777</v>
-      </c>
-      <c r="P9" t="n">
-        <v>-0.4346189497890956</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>-2.337516602439503</v>
-      </c>
-      <c r="R9" t="n">
-        <v>-0.1917068025940339</v>
-      </c>
-      <c r="S9" t="n">
-        <v>-0.182829612546747</v>
-      </c>
-      <c r="T9" t="n">
-        <v>-0.6162812631739756</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0.6649460607504661</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0.4949816336225141</v>
-      </c>
-      <c r="W9" t="n">
-        <v>-0.8812727218261887</v>
-      </c>
-      <c r="X9" t="n">
-        <v>-0.677065725487926</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>-0.006782796592234719</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>-0.6535624676346825</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>-0.1662386772451152</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>SM0npHPF</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1.879628070527517</v>
-      </c>
-      <c r="C10" t="n">
-        <v>-0.5577659776492538</v>
-      </c>
-      <c r="D10" t="n">
-        <v>1.033163533928535</v>
-      </c>
-      <c r="E10" t="n">
-        <v>-0.7402451889401905</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.2788832759311962</v>
-      </c>
-      <c r="G10" t="n">
-        <v>-0.9805787268653793</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-0.2234871899330499</v>
-      </c>
-      <c r="I10" t="n">
-        <v>-2.312323304990914</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.5530804851791808</v>
-      </c>
-      <c r="K10" t="n">
-        <v>-0.001826621254097982</v>
-      </c>
-      <c r="L10" t="n">
-        <v>-0.0212614987234063</v>
-      </c>
-      <c r="M10" t="n">
-        <v>-0.8914578042149379</v>
-      </c>
-      <c r="N10" t="n">
-        <v>-0.2746407653157059</v>
-      </c>
-      <c r="O10" t="n">
-        <v>-0.6564339141504508</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0.3323468979789151</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.203900540136417</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0.2939463707817866</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0.05477893750743516</v>
-      </c>
-      <c r="T10" t="n">
-        <v>-1.127980550412574</v>
-      </c>
-      <c r="U10" t="n">
-        <v>-0.6197160709869246</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0.9734929486945569</v>
-      </c>
-      <c r="W10" t="n">
-        <v>-0.9001988750619974</v>
-      </c>
-      <c r="X10" t="n">
-        <v>-1.197878483477588</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0.4938612014217748</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>-0.6007268565440711</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>-0.1662386772451152</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>OlferefS</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1.760387359086781</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0.05484528178186816</v>
-      </c>
-      <c r="D11" t="n">
-        <v>1.930734664081591</v>
-      </c>
-      <c r="E11" t="n">
-        <v>-1.634304109944393</v>
-      </c>
-      <c r="F11" t="n">
-        <v>-0.1105836441224053</v>
-      </c>
-      <c r="G11" t="n">
-        <v>-0.9805787268653793</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-0.2234871899330499</v>
-      </c>
-      <c r="I11" t="n">
-        <v>3.851942275472987</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.05159850326629842</v>
-      </c>
-      <c r="K11" t="n">
-        <v>-0.001826621254097982</v>
-      </c>
-      <c r="L11" t="n">
-        <v>-0.0212614987234063</v>
-      </c>
-      <c r="M11" t="n">
-        <v>-1.248868469858027</v>
-      </c>
-      <c r="N11" t="n">
-        <v>1.727675834327614</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.789321751890786</v>
-      </c>
-      <c r="P11" t="n">
-        <v>-0.05113602590509021</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>-1.032783970964164</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0.1968157361066223</v>
-      </c>
-      <c r="S11" t="n">
-        <v>-1.778201305767682</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.771648743939486</v>
-      </c>
-      <c r="U11" t="n">
-        <v>-0.8032392326636948</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.098195897470909</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.786938164667953</v>
-      </c>
-      <c r="X11" t="n">
-        <v>2.186253717864907</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0.2330737135011751</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>-0.8768403924759218</v>
-      </c>
-      <c r="AA11" t="n">
         <v>-0.1662386772451152</v>
       </c>
     </row>

--- a/data/spain/p6_deployment/data_preparation/df_selected_nan.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_selected_nan.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA6"/>
+  <dimension ref="A1:AA11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,23 +563,23 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>YN50iYWr</t>
+          <t>fVeJ32M5</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.909438248387701</v>
+        <v>1.939248426247886</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3413892579673929</v>
+        <v>-1.032045662370122</v>
       </c>
       <c r="D2" t="n">
-        <v>1.627330338396051</v>
+        <v>-0.7619787263775758</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7526645187743746</v>
+        <v>0.2803315039042297</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1815165459177958</v>
+        <v>0.2031535970318848</v>
       </c>
       <c r="G2" t="n">
         <v>-0.9805787268653793</v>
@@ -588,58 +588,58 @@
         <v>-0.2234871899330499</v>
       </c>
       <c r="I2" t="n">
-        <v>2.756072838946071</v>
+        <v>0.01639924762878189</v>
       </c>
       <c r="J2" t="n">
-        <v>0.5530804851791808</v>
+        <v>-0.9513654605594664</v>
       </c>
       <c r="K2" t="n">
-        <v>0.7344124969974213</v>
+        <v>-0.001826621254097982</v>
       </c>
       <c r="L2" t="n">
-        <v>1.149962181909723</v>
+        <v>-0.0212614987234063</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1807741927143287</v>
+        <v>0.649875691370883</v>
       </c>
       <c r="N2" t="n">
-        <v>0.7265175345059538</v>
+        <v>-0.9420796318634789</v>
       </c>
       <c r="O2" t="n">
-        <v>1.265231252024807</v>
+        <v>-0.3070402475731312</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1406054360369124</v>
+        <v>-0.9139726046441022</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.566808031151543</v>
+        <v>1.134004149164524</v>
       </c>
       <c r="R2" t="n">
-        <v>0.7310342268200253</v>
+        <v>0.9981434721767265</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.235096048500981</v>
+        <v>0.1141810750209809</v>
       </c>
       <c r="T2" t="n">
-        <v>1.856931958479252</v>
+        <v>0.4497589185731055</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9402308032656214</v>
+        <v>0.1602573661393483</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>0.5945506547385115</v>
       </c>
       <c r="W2" t="n">
-        <v>1.701179032123172</v>
+        <v>0.755487085854752</v>
       </c>
       <c r="X2" t="n">
-        <v>1.754676846394154</v>
+        <v>0.4077132214547135</v>
       </c>
       <c r="Y2" t="n">
-        <v>-1.267517991172074</v>
+        <v>-0.4808869034398218</v>
       </c>
       <c r="Z2" t="n">
-        <v>-0.6937006269931842</v>
+        <v>1.216100486084536</v>
       </c>
       <c r="AA2" t="n">
         <v>-0.1662386772451152</v>
@@ -648,23 +648,23 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>h4pRxZHk</t>
+          <t>SdHeBgOE</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.760387359086781</v>
+        <v>1.909438248387701</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7168606750380806</v>
+        <v>1.042927958283678</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9952379932178427</v>
+        <v>-0.8757553485096533</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.406572120632002</v>
+        <v>-0.7402451889401905</v>
       </c>
       <c r="F3" t="n">
-        <v>1.13354679493771</v>
+        <v>-0.3377726808203395</v>
       </c>
       <c r="G3" t="n">
         <v>-0.9805787268653793</v>
@@ -676,55 +676,55 @@
         <v>0.5643339658922398</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.449883478646584</v>
+        <v>1.556044449004946</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.7380657395056173</v>
+        <v>-0.001826621254097982</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.192485179356536</v>
+        <v>-0.0212614987234063</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.231747800376521</v>
+        <v>-0.7574288045987798</v>
       </c>
       <c r="N3" t="n">
-        <v>0.05907866795818074</v>
+        <v>1.811105692646085</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.4817370808617911</v>
+        <v>0.8284891688031573</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.009843335615104</v>
+        <v>-1.48919699047011</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.566808031151543</v>
+        <v>-0.9861863769829019</v>
       </c>
       <c r="R3" t="n">
-        <v>0.1482504187690404</v>
+        <v>-0.7987732693138099</v>
       </c>
       <c r="S3" t="n">
-        <v>2.210227927284656</v>
+        <v>-0.3780080643769675</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.127980550412574</v>
+        <v>1.089383027621354</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.07852397517885</v>
+        <v>-1.44557029853239</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.005280195770989188</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.7567333730014582</v>
+        <v>2.023676991822783</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.180302107898821</v>
+        <v>1.621455553105827</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.9525833105682263</v>
+        <v>0.2729765483707488</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.1312106473738017</v>
+        <v>0.7577120140879664</v>
       </c>
       <c r="AA3" t="n">
         <v>-0.1662386772451152</v>
@@ -733,23 +733,23 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>n1v9mjW7</t>
+          <t>dzUhmsxP</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.790197536946965</v>
+        <v>1.879628070527517</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8650730765133521</v>
+        <v>-0.4886001902941271</v>
       </c>
       <c r="D4" t="n">
-        <v>1.235433084385562</v>
+        <v>-0.5217836352098567</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.3606918734195383</v>
+        <v>1.123783316172346</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.538629017652277</v>
+        <v>-0.9219730609007416</v>
       </c>
       <c r="G4" t="n">
         <v>-0.9805787268653793</v>
@@ -758,10 +758,10 @@
         <v>-0.2234871899330499</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2575681115029471</v>
+        <v>-0.1205844319370826</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.954329424385231</v>
+        <v>-0.9513654605594664</v>
       </c>
       <c r="K4" t="n">
         <v>-0.001826621254097982</v>
@@ -770,46 +770,46 @@
         <v>-0.0212614987234063</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2701268591251006</v>
+        <v>2.861354185037496</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6083601985895923</v>
+        <v>-0.441500481952649</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.6564339141504508</v>
+        <v>0.3917470855815078</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.05113602590509021</v>
+        <v>0.8117005528339217</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.203900540136417</v>
+        <v>0.1554546755580197</v>
       </c>
       <c r="R4" t="n">
-        <v>0.5853382748072791</v>
+        <v>1.653775256234085</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4281638018782922</v>
+        <v>-0.9380853609332535</v>
       </c>
       <c r="T4" t="n">
-        <v>1.601082314859953</v>
+        <v>1.259949456700887</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6649460607504661</v>
+        <v>1.995488982907049</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6225846509750571</v>
+        <v>-0.3982394878453044</v>
       </c>
       <c r="W4" t="n">
-        <v>0.244607373544286</v>
+        <v>-0.2923529910110318</v>
       </c>
       <c r="X4" t="n">
-        <v>1.156122503572948</v>
+        <v>-0.4756269102676662</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.22103364042808</v>
+        <v>-1.851799653406305</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.5022823154623396</v>
+        <v>0.2214477060924234</v>
       </c>
       <c r="AA4" t="n">
         <v>-0.1662386772451152</v>
@@ -818,23 +818,23 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>vyy1kC1e</t>
+          <t>na927pNt</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.939248426247886</v>
+        <v>1.760387359086781</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.8146674735397244</v>
+        <v>1.24054449358404</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.014815664448859</v>
+        <v>0.03445762854696641</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.651173146189756</v>
+        <v>0.297200540149592</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2031535970318848</v>
+        <v>-0.2620430019210281</v>
       </c>
       <c r="G5" t="n">
         <v>-0.9805787268653793</v>
@@ -843,10 +843,10 @@
         <v>-0.2234871899330499</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.6685191502005404</v>
+        <v>-0.2575681115029471</v>
       </c>
       <c r="J5" t="n">
-        <v>0.05159850326629842</v>
+        <v>0.5530804851791808</v>
       </c>
       <c r="K5" t="n">
         <v>-0.001826621254097982</v>
@@ -855,46 +855,46 @@
         <v>-0.0212614987234063</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.516926469090344</v>
+        <v>0.605199358165497</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6083601985895924</v>
+        <v>-0.9420796318634789</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.054008580459729</v>
+        <v>-1.26787283066076</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.4346189497890955</v>
+        <v>0.2364761670079138</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.83111978828632</v>
+        <v>0.5981318183800094</v>
       </c>
       <c r="R5" t="n">
-        <v>-1.163013149345675</v>
+        <v>-1.187295808014467</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6657723519324743</v>
+        <v>0.8694368234074872</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.127980550412574</v>
+        <v>-1.000055728602924</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.9867623943404646</v>
+        <v>0.573184479912081</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.30543729340709</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.3480210032492177</v>
+        <v>0.8337403276680835</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.49249398191418</v>
+        <v>-0.581317915355185</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.2635796994773766</v>
+        <v>-0.5806590612911301</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.001620015804766217</v>
+        <v>1.602959793748849</v>
       </c>
       <c r="AA5" t="n">
         <v>-0.1662386772451152</v>
@@ -903,23 +903,23 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>tQQLbGv9</t>
+          <t>SfxxiPx0</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1.760387359086781</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9243580371034607</v>
+        <v>-1.012284008840086</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.4712162475956001</v>
+        <v>1.930734664081591</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.5293822358731616</v>
+        <v>-1.533089892472219</v>
       </c>
       <c r="F6" t="n">
-        <v>1.166002371608844</v>
+        <v>-0.2620430019210281</v>
       </c>
       <c r="G6" t="n">
         <v>-0.9805787268653793</v>
@@ -928,10 +928,10 @@
         <v>-0.2234871899330499</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2903666067605108</v>
+        <v>1.386236043287427</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.449883478646584</v>
+        <v>0.05159850326629842</v>
       </c>
       <c r="K6" t="n">
         <v>-0.001826621254097982</v>
@@ -940,48 +940,473 @@
         <v>-0.0212614987234063</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.231747800376522</v>
+        <v>-0.1542983063260672</v>
       </c>
       <c r="N6" t="n">
-        <v>0.7265175345059537</v>
+        <v>0.5596578178690105</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.3070402475731312</v>
+        <v>2.400760668401095</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.8181018736731009</v>
+        <v>-0.3387482188180942</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.110705352173892</v>
+        <v>-1.475461113786154</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.1917068025940339</v>
+        <v>1.31381803487101</v>
       </c>
       <c r="S6" t="n">
-        <v>0.9712690591449937</v>
+        <v>-1.294498186014526</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7868476922535084</v>
+        <v>1.473157493050303</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.904378202724315</v>
+        <v>-0.3444313284717694</v>
       </c>
       <c r="V6" t="n">
+        <v>1.098195897470909</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.8212058627967606</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.7872606230756608</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>-0.242581257691509</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.7026630009917714</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-0.1662386772451152</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>jckS1tiI</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1.909438248387701</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1.003404651223605</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.312578260425378</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-1.406572120632002</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.1815165459177958</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-0.9805787268653793</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-0.2234871899330499</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-2.586290664122644</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-1.452847442472349</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-0.001826621254097982</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-0.0212614987234063</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.051962690219358</v>
+      </c>
+      <c r="N7" t="n">
+        <v>-0.9420796318634789</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-1.00582758072777</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.5240883599209177</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.739772870920931</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.2210983947754135</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.2839014679168249</v>
+      </c>
+      <c r="T7" t="n">
+        <v>-2.364587161239188</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.2061381565585409</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.1310230273101374</v>
+      </c>
+      <c r="W7" t="n">
+        <v>-1.564260219089635</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-1.516287359412144</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.250280165082232</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>-0.6401747541024558</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>-0.1662386772451152</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>8EcB5Oig</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1.760387359086781</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.8650730765133521</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.6918336675323028</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.297200540149592</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-0.5433246664041846</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-0.9805787268653793</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-0.2234871899330499</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.8383013250239688</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1.054562467092063</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.7344124969974213</v>
+      </c>
+      <c r="L8" t="n">
+        <v>-0.0212614987234063</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2.01250385413516</v>
+      </c>
+      <c r="N8" t="n">
+        <v>-0.441500481952649</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.4790955022258377</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.291054207688929</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>-0.6367044221234361</v>
+      </c>
+      <c r="R8" t="n">
+        <v>-1.04159985600172</v>
+      </c>
+      <c r="S8" t="n">
+        <v>-1.03991759667076</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.88033053295645</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.490800288295931</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.8004555236483012</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.020974500695768</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.645465869457071</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.07073251437887094</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.066606909221437</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>-0.1662386772451152</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>CjIFsr1e</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.760387359086781</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-0.07360546616336709</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.9699542994107144</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.2803315039042297</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.744079874884109</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-0.9805787268653793</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-0.2234871899330499</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.1533829271946464</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.05159850326629842</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-0.001826621254097982</v>
+      </c>
+      <c r="L9" t="n">
+        <v>-0.0212614987234063</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.253006189643596</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-0.6917900569080639</v>
+      </c>
+      <c r="O9" t="n">
+        <v>-0.7437823307947806</v>
+      </c>
+      <c r="P9" t="n">
+        <v>-0.05113602590509021</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>-1.685150286701833</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.2939463707817866</v>
+      </c>
+      <c r="S9" t="n">
+        <v>-0.6580467126551104</v>
+      </c>
+      <c r="T9" t="n">
+        <v>-0.1898651904751431</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.481422899073696</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.960442640101683</v>
+      </c>
+      <c r="W9" t="n">
+        <v>-0.08984989726271236</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.001384402268705091</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>-0.01778582969380999</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.7119822595401548</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>-0.1662386772451152</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>08zpk37C</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1.909438248387701</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-1.269185504730557</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.121656462253484</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-0.0823527753710601</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-0.3377726808203395</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-0.9805787268653793</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0.2234871899330499</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-0.5315354706346761</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.05159850326629842</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-0.001826621254097982</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-0.0212614987234063</v>
+      </c>
+      <c r="M10" t="n">
+        <v>-1.427573802679572</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-0.6917900569080639</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-1.791963330526739</v>
+      </c>
+      <c r="P10" t="n">
+        <v>-1.48919699047011</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.250498134117679</v>
+      </c>
+      <c r="R10" t="n">
+        <v>-0.7259252933074368</v>
+      </c>
+      <c r="S10" t="n">
+        <v>-0.3270919465082143</v>
+      </c>
+      <c r="T10" t="n">
+        <v>-0.701564477713742</v>
+      </c>
+      <c r="U10" t="n">
+        <v>-1.44557029853239</v>
+      </c>
+      <c r="V10" t="n">
         <v>0</v>
       </c>
-      <c r="W6" t="n">
-        <v>-0.6331206185193767</v>
-      </c>
-      <c r="X6" t="n">
-        <v>-0.2834180900309805</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0.7023767944066482</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>-0.7756567073229435</v>
-      </c>
-      <c r="AA6" t="n">
+      <c r="W10" t="n">
+        <v>-0.2593907357828251</v>
+      </c>
+      <c r="X10" t="n">
+        <v>-1.131463381572056</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.7496591483450681</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0.7663238710680422</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>-0.1662386772451152</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>YeqTho8m</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1.820007714807149</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1.606135083889709</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.2942303909457018</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.140652352417708</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-0.3594097319344284</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-0.9805787268653793</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-0.2234871899330499</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.2903666067605108</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-0.7380657395056173</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-0.0212614987234063</v>
+      </c>
+      <c r="M11" t="n">
+        <v>-0.04260747331260206</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-0.5249303402711207</v>
+      </c>
+      <c r="O11" t="n">
+        <v>-0.3943886642174612</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.2364761670079138</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.1088570815767573</v>
+      </c>
+      <c r="R11" t="n">
+        <v>-0.8230559279826011</v>
+      </c>
+      <c r="S11" t="n">
+        <v>-0.3440639857977985</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.06598445314415635</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-0.1150273763758069</v>
+      </c>
+      <c r="V11" t="n">
+        <v>-0.1038825273615937</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.5590090697704427</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.8652825548802219</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.4588800325662478</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>-0.8401780195719284</v>
+      </c>
+      <c r="AA11" t="n">
         <v>-0.1662386772451152</v>
       </c>
     </row>

--- a/data/spain/p6_deployment/data_preparation/df_selected_nan.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_selected_nan.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA11"/>
+  <dimension ref="A1:AA27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,23 +563,23 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>fVeJ32M5</t>
+          <t>f5SjRHyR</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.939248426247886</v>
+        <v>1.760387359086781</v>
       </c>
       <c r="C2" t="n">
-        <v>-1.032045662370122</v>
+        <v>0.3413892579673929</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.7619787263775758</v>
+        <v>0.9699542994107144</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2803315039042297</v>
+        <v>1.140652352417708</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2031535970318848</v>
+        <v>0.744079874884109</v>
       </c>
       <c r="G2" t="n">
         <v>-0.9805787268653793</v>
@@ -588,58 +588,58 @@
         <v>-0.2234871899330499</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01639924762878189</v>
+        <v>2.482105479814342</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.9513654605594664</v>
+        <v>1.556044449004946</v>
       </c>
       <c r="K2" t="n">
         <v>-0.001826621254097982</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.0212614987234063</v>
+        <v>-0.6068733390399711</v>
       </c>
       <c r="M2" t="n">
-        <v>0.649875691370883</v>
+        <v>-0.6233998049826214</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.9420796318634789</v>
+        <v>-0.441500481952649</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.3070402475731312</v>
+        <v>-0.4817370808617911</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.9139726046441022</v>
+        <v>-0.05113602590509021</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.134004149164524</v>
+        <v>-0.566808031151543</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9981434721767265</v>
+        <v>1.168122082858264</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1141810750209809</v>
+        <v>-2.083698012980201</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4497589185731055</v>
+        <v>1.601082314859953</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1602573661393483</v>
+        <v>-0.8950008135020797</v>
       </c>
       <c r="V2" t="n">
-        <v>0.5945506547385115</v>
+        <v>0.4789345875009053</v>
       </c>
       <c r="W2" t="n">
-        <v>0.755487085854752</v>
+        <v>2.310971385146272</v>
       </c>
       <c r="X2" t="n">
-        <v>0.4077132214547135</v>
+        <v>2.788503079096979</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0.4808869034398218</v>
+        <v>-0.7144574559276111</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.216100486084536</v>
+        <v>0.616641596314445</v>
       </c>
       <c r="AA2" t="n">
         <v>-0.1662386772451152</v>
@@ -648,23 +648,23 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>SdHeBgOE</t>
+          <t>rkN7RQV9</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.909438248387701</v>
+        <v>1.760387359086781</v>
       </c>
       <c r="C3" t="n">
-        <v>1.042927958283678</v>
+        <v>0.8650730765133521</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.8757553485096533</v>
+        <v>1.930734664081591</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.7402451889401905</v>
+        <v>0.297200540149592</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.3377726808203395</v>
+        <v>-0.2620430019210281</v>
       </c>
       <c r="G3" t="n">
         <v>-0.9805787268653793</v>
@@ -676,55 +676,55 @@
         <v>0.5643339658922398</v>
       </c>
       <c r="J3" t="n">
-        <v>1.556044449004946</v>
+        <v>0.5530804851791808</v>
       </c>
       <c r="K3" t="n">
         <v>-0.001826621254097982</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.0212614987234063</v>
+        <v>-1.192485179356536</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.7574288045987798</v>
+        <v>-1.159515803447255</v>
       </c>
       <c r="N3" t="n">
-        <v>1.811105692646085</v>
+        <v>0.05907866795818074</v>
       </c>
       <c r="O3" t="n">
-        <v>0.8284891688031573</v>
+        <v>0.04235341900418825</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.48919699047011</v>
+        <v>-2.92725795503513</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9861863769829019</v>
+        <v>-1.265771940870474</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.7987732693138099</v>
+        <v>0.5853382748072791</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3780080643769675</v>
+        <v>-0.9126273019988768</v>
       </c>
       <c r="T3" t="n">
-        <v>1.089383027621354</v>
+        <v>2.112781602098551</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.44557029853239</v>
+        <v>-0.8950008135020797</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.5039235117324468</v>
       </c>
       <c r="W3" t="n">
-        <v>2.023676991822783</v>
+        <v>1.208514211061822</v>
       </c>
       <c r="X3" t="n">
-        <v>1.621455553105827</v>
+        <v>1.246480342184062</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.2729765483707488</v>
+        <v>0.06784663164349317</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.7577120140879664</v>
+        <v>0.7823616650849402</v>
       </c>
       <c r="AA3" t="n">
         <v>-0.1662386772451152</v>
@@ -733,23 +733,23 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>dzUhmsxP</t>
+          <t>bwZsTw7E</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.879628070527517</v>
+        <v>1.939248426247886</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.4886001902941271</v>
+        <v>-0.893714087659869</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.5217836352098567</v>
+        <v>-0.7619787263775758</v>
       </c>
       <c r="E4" t="n">
-        <v>1.123783316172346</v>
+        <v>0.5249325294619833</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.9219730609007416</v>
+        <v>0.2031535970318848</v>
       </c>
       <c r="G4" t="n">
         <v>-0.9805787268653793</v>
@@ -758,58 +758,58 @@
         <v>-0.2234871899330499</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1205844319370826</v>
+        <v>2.619089159380207</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.9513654605594664</v>
+        <v>0.5530804851791808</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.001826621254097982</v>
+        <v>0.3662929378716617</v>
       </c>
       <c r="L4" t="n">
         <v>-0.0212614987234063</v>
       </c>
       <c r="M4" t="n">
-        <v>2.861354185037496</v>
+        <v>-0.08728380651798802</v>
       </c>
       <c r="N4" t="n">
         <v>-0.441500481952649</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3917470855815078</v>
+        <v>-1.00582758072777</v>
       </c>
       <c r="P4" t="n">
-        <v>0.8117005528339217</v>
+        <v>-2.352033569209122</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1554546755580197</v>
+        <v>-0.566808031151543</v>
       </c>
       <c r="R4" t="n">
-        <v>1.653775256234085</v>
+        <v>0.7310342268200253</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.9380853609332535</v>
+        <v>-0.9126273019988768</v>
       </c>
       <c r="T4" t="n">
-        <v>1.259949456700887</v>
+        <v>0.5776837403827552</v>
       </c>
       <c r="U4" t="n">
-        <v>1.995488982907049</v>
+        <v>-0.3444313284717694</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.3982394878453044</v>
+        <v>0.5014262304585004</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.2923529910110318</v>
+        <v>-0.2311800568173215</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.4756269102676662</v>
+        <v>0.09902914058696964</v>
       </c>
       <c r="Y4" t="n">
-        <v>-1.851799653406305</v>
+        <v>0.3448629312527355</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.2214477060924234</v>
+        <v>-0.123615907182663</v>
       </c>
       <c r="AA4" t="n">
         <v>-0.1662386772451152</v>
@@ -818,23 +818,23 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>na927pNt</t>
+          <t>445r4WXo</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.760387359086781</v>
+        <v>1.820007714807149</v>
       </c>
       <c r="C5" t="n">
-        <v>1.24054449358404</v>
+        <v>1.606135083889709</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03445762854696641</v>
+        <v>-1.292936296327271</v>
       </c>
       <c r="E5" t="n">
-        <v>0.297200540149592</v>
+        <v>1.140652352417708</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2620430019210281</v>
+        <v>-0.3594097319344284</v>
       </c>
       <c r="G5" t="n">
         <v>-0.9805787268653793</v>
@@ -843,58 +843,58 @@
         <v>-0.2234871899330499</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2575681115029471</v>
+        <v>0.1533829271946464</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5530804851791808</v>
+        <v>2.55900841283071</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.001826621254097982</v>
+        <v>-1.842424416882896</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.0212614987234063</v>
+        <v>-1.7780970196731</v>
       </c>
       <c r="M5" t="n">
-        <v>0.605199358165497</v>
+        <v>0.8509191907951206</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.9420796318634789</v>
+        <v>-0.6917900569080639</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.26787283066076</v>
+        <v>-0.4817370808617911</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2364761670079138</v>
+        <v>1.099312745746926</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.5981318183800094</v>
+        <v>0.1321558785673885</v>
       </c>
       <c r="R5" t="n">
-        <v>-1.187295808014467</v>
+        <v>0.7310342268200253</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8694368234074872</v>
+        <v>-0.6580467126551104</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.000055728602924</v>
+        <v>-0.4457148340944425</v>
       </c>
       <c r="U5" t="n">
-        <v>0.573184479912081</v>
+        <v>-0.06914658595661426</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.3765138322849776</v>
       </c>
       <c r="W5" t="n">
-        <v>0.8337403276680835</v>
+        <v>0.5422750528677946</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.581317915355185</v>
+        <v>1.157926595386333</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.5806590612911301</v>
+        <v>0.2843383729920568</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.602959793748849</v>
+        <v>-1.037964697026253</v>
       </c>
       <c r="AA5" t="n">
         <v>-0.1662386772451152</v>
@@ -903,23 +903,23 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>SfxxiPx0</t>
+          <t>QiF6bS1N</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.760387359086781</v>
+        <v>1.879628070527517</v>
       </c>
       <c r="C6" t="n">
-        <v>-1.012284008840086</v>
+        <v>-1.032045662370122</v>
       </c>
       <c r="D6" t="n">
-        <v>1.930734664081591</v>
+        <v>1.033163533928535</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.533089892472219</v>
+        <v>0.2803315039042297</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2620430019210281</v>
+        <v>-0.9219730609007416</v>
       </c>
       <c r="G6" t="n">
         <v>-0.9805787268653793</v>
@@ -928,58 +928,58 @@
         <v>-0.2234871899330499</v>
       </c>
       <c r="I6" t="n">
-        <v>1.386236043287427</v>
+        <v>-2.312323304990914</v>
       </c>
       <c r="J6" t="n">
-        <v>0.05159850326629842</v>
+        <v>-2.455811406298114</v>
       </c>
       <c r="K6" t="n">
         <v>-0.001826621254097982</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.0212614987234063</v>
+        <v>-0.6068733390399711</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1542983063260672</v>
+        <v>1.253006189643596</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5596578178690105</v>
+        <v>-1.442658781774309</v>
       </c>
       <c r="O6" t="n">
-        <v>2.400760668401095</v>
+        <v>-0.6564339141504507</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.3387482188180942</v>
+        <v>1.482795669630931</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.475461113786154</v>
+        <v>2.322242795686707</v>
       </c>
       <c r="R6" t="n">
-        <v>1.31381803487101</v>
+        <v>0.7795995441576071</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.294498186014526</v>
+        <v>0.2584434089824482</v>
       </c>
       <c r="T6" t="n">
-        <v>1.473157493050303</v>
+        <v>-0.7868476922535084</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3444313284717694</v>
+        <v>0.481422899073696</v>
       </c>
       <c r="V6" t="n">
-        <v>1.098195897470909</v>
+        <v>0.6152378105820319</v>
       </c>
       <c r="W6" t="n">
-        <v>0.8212058627967606</v>
+        <v>-1.368361075526761</v>
       </c>
       <c r="X6" t="n">
-        <v>0.7872606230756608</v>
+        <v>-1.549255244406202</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.242581257691509</v>
+        <v>-0.8037626147134115</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.7026630009917714</v>
+        <v>0.6762116456830926</v>
       </c>
       <c r="AA6" t="n">
         <v>-0.1662386772451152</v>
@@ -988,23 +988,23 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>jckS1tiI</t>
+          <t>pxdwg6Pp</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.909438248387701</v>
+        <v>1.760387359086781</v>
       </c>
       <c r="C7" t="n">
-        <v>1.003404651223605</v>
+        <v>1.141736225933859</v>
       </c>
       <c r="D7" t="n">
-        <v>0.312578260425378</v>
+        <v>0.03445762854696641</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.406572120632002</v>
+        <v>0.5249325294619833</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1815165459177958</v>
+        <v>-0.2620430019210281</v>
       </c>
       <c r="G7" t="n">
         <v>-0.9805787268653793</v>
@@ -1013,58 +1013,58 @@
         <v>-0.2234871899330499</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.586290664122644</v>
+        <v>-2.997241702820237</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.452847442472349</v>
+        <v>-0.9513654605594664</v>
       </c>
       <c r="K7" t="n">
         <v>-0.001826621254097982</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.0212614987234063</v>
+        <v>0.5643503415931583</v>
       </c>
       <c r="M7" t="n">
-        <v>1.051962690219358</v>
+        <v>3.129412184269813</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.9420796318634789</v>
+        <v>-0.441500481952649</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.00582758072777</v>
+        <v>-1.35522124730509</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5240883599209177</v>
+        <v>1.099312745746926</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.739772870920931</v>
+        <v>-0.1008320913389221</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2210983947754135</v>
+        <v>-0.6773599759698549</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2839014679168249</v>
+        <v>2.396920359470085</v>
       </c>
       <c r="T7" t="n">
-        <v>-2.364587161239188</v>
+        <v>-0.4457148340944425</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2061381565585409</v>
+        <v>2.683700839194937</v>
       </c>
       <c r="V7" t="n">
-        <v>0.1310230273101374</v>
+        <v>0.3403113095588215</v>
       </c>
       <c r="W7" t="n">
-        <v>-1.564260219089635</v>
+        <v>0.7837859284308158</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.516287359412144</v>
+        <v>-0.1241565842300631</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.250280165082232</v>
+        <v>-0.01952409677653744</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0.6401747541024558</v>
+        <v>1.401232784071228</v>
       </c>
       <c r="AA7" t="n">
         <v>-0.1662386772451152</v>
@@ -1073,23 +1073,23 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>8EcB5Oig</t>
+          <t>OAmz0KLU</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.760387359086781</v>
+        <v>1.939248426247886</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8650730765133521</v>
+        <v>-0.5577659776492538</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6918336675323028</v>
+        <v>-1.014815664448859</v>
       </c>
       <c r="E8" t="n">
-        <v>0.297200540149592</v>
+        <v>-0.7402451889401905</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5433246664041846</v>
+        <v>0.2031535970318848</v>
       </c>
       <c r="G8" t="n">
         <v>-0.9805787268653793</v>
@@ -1098,58 +1098,58 @@
         <v>-0.2234871899330499</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8383013250239688</v>
+        <v>1.112268684155698</v>
       </c>
       <c r="J8" t="n">
-        <v>1.054562467092063</v>
+        <v>-0.449883478646584</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7344124969974213</v>
+        <v>0.145421202396206</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.0212614987234063</v>
+        <v>0.6814727096564709</v>
       </c>
       <c r="M8" t="n">
-        <v>2.01250385413516</v>
+        <v>-2.14239513396575</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.441500481952649</v>
+        <v>0.05907866795818074</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4790955022258377</v>
+        <v>-2.054008580459729</v>
       </c>
       <c r="P8" t="n">
-        <v>1.291054207688929</v>
+        <v>-1.968550645325116</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.6367044221234361</v>
+        <v>1.576681291986514</v>
       </c>
       <c r="R8" t="n">
-        <v>-1.04159985600172</v>
+        <v>-0.8716212453201829</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.03991759667076</v>
+        <v>0.4960519590366303</v>
       </c>
       <c r="T8" t="n">
-        <v>2.88033053295645</v>
+        <v>-1.46911340857164</v>
       </c>
       <c r="U8" t="n">
-        <v>1.490800288295931</v>
+        <v>-2.087901364401085</v>
       </c>
       <c r="V8" t="n">
-        <v>0.8004555236483012</v>
+        <v>-0.1583071476415053</v>
       </c>
       <c r="W8" t="n">
-        <v>1.020974500695768</v>
+        <v>0.2827148302415615</v>
       </c>
       <c r="X8" t="n">
-        <v>1.645465869457071</v>
+        <v>-0.2310316938673156</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.07073251437887094</v>
+        <v>1.001603900695382</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.066606909221437</v>
+        <v>-0.7219638594978889</v>
       </c>
       <c r="AA8" t="n">
         <v>-0.1662386772451152</v>
@@ -1158,23 +1158,23 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>CjIFsr1e</t>
+          <t>dCNk2A2b</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.760387359086781</v>
+        <v>1.820007714807149</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.07360546616336709</v>
+        <v>0.7168606750380806</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9699542994107144</v>
+        <v>-0.2942303909457018</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2803315039042297</v>
+        <v>-1.406572120632002</v>
       </c>
       <c r="F9" t="n">
-        <v>0.744079874884109</v>
+        <v>-0.3594097319344284</v>
       </c>
       <c r="G9" t="n">
         <v>-0.9805787268653793</v>
@@ -1183,83 +1183,83 @@
         <v>-0.2234871899330499</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1533829271946464</v>
+        <v>-0.2575681115029471</v>
       </c>
       <c r="J9" t="n">
-        <v>0.05159850326629842</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.001826621254097982</v>
+        <v>-0.811689651330769</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.0212614987234063</v>
+        <v>0.3301056054665323</v>
       </c>
       <c r="M9" t="n">
-        <v>1.253006189643596</v>
+        <v>-2.589158466019611</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6917900569080639</v>
+        <v>-0.1411529920061511</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.7437823307947806</v>
+        <v>-0.6564339141504507</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.05113602590509021</v>
+        <v>-0.8181018736731008</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.685150286701833</v>
+        <v>0.3651438484736992</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2939463707817866</v>
+        <v>1.0709914481831</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6580467126551104</v>
+        <v>-0.6071305947863572</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1898651904751431</v>
+        <v>-1.042697335872808</v>
       </c>
       <c r="U9" t="n">
-        <v>0.481422899073696</v>
+        <v>-1.62909346020916</v>
       </c>
       <c r="V9" t="n">
-        <v>0.960442640101683</v>
+        <v>0.3984093500352457</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.08984989726271236</v>
+        <v>0.02256213097696337</v>
       </c>
       <c r="X9" t="n">
-        <v>0.001384402268705091</v>
+        <v>-0.1148567799932221</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0.01778582969380999</v>
+        <v>-0.2725081579683824</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.7119822595401548</v>
+        <v>-0.5578947129122305</v>
       </c>
       <c r="AA9" t="n">
-        <v>-0.1662386772451152</v>
+        <v>6.015447286827976</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>08zpk37C</t>
+          <t>ImLNuMV7</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.909438248387701</v>
+        <v>1.790197536946965</v>
       </c>
       <c r="C10" t="n">
-        <v>-1.269185504730557</v>
+        <v>0.3413892579673929</v>
       </c>
       <c r="D10" t="n">
-        <v>1.121656462253484</v>
+        <v>-0.1172445342958035</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0823527753710601</v>
+        <v>1.140652352417708</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3377726808203395</v>
+        <v>-1.603540170994544</v>
       </c>
       <c r="G10" t="n">
         <v>-0.9805787268653793</v>
@@ -1268,58 +1268,58 @@
         <v>-0.2234871899330499</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5315354706346761</v>
+        <v>4.947811711999903</v>
       </c>
       <c r="J10" t="n">
-        <v>0.05159850326629842</v>
+        <v>1.054562467092063</v>
       </c>
       <c r="K10" t="n">
         <v>-0.001826621254097982</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.0212614987234063</v>
+        <v>-0.6068733390399711</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.427573802679572</v>
+        <v>-2.231747800376522</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.6917900569080639</v>
+        <v>0.8099473928244254</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.791963330526739</v>
+        <v>1.439928085313467</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.48919699047011</v>
+        <v>-0.4346189497890955</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.250498134117679</v>
+        <v>-0.4736128431890191</v>
       </c>
       <c r="R10" t="n">
-        <v>-0.7259252933074368</v>
+        <v>0.7795995441576071</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3270919465082143</v>
+        <v>-2.117642091559371</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.701564477713742</v>
+        <v>2.795047318416684</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.44557029853239</v>
+        <v>-1.720855041047545</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.7032790591076619</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.2593907357828251</v>
+        <v>2.265839610348248</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.131463381572056</v>
+        <v>2.788503079096979</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.7496591483450681</v>
+        <v>-1.19919303219508</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.7663238710680422</v>
+        <v>-0.03469841500352146</v>
       </c>
       <c r="AA10" t="n">
         <v>-0.1662386772451152</v>
@@ -1328,23 +1328,23 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>YeqTho8m</t>
+          <t>xWrPG9Hi</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.820007714807149</v>
+        <v>1.790197536946965</v>
       </c>
       <c r="C11" t="n">
-        <v>1.606135083889709</v>
+        <v>-0.893714087659869</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.2942303909457018</v>
+        <v>1.235433084385562</v>
       </c>
       <c r="E11" t="n">
-        <v>1.140652352417708</v>
+        <v>0.5249325294619833</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3594097319344284</v>
+        <v>-1.625177222108633</v>
       </c>
       <c r="G11" t="n">
         <v>-0.9805787268653793</v>
@@ -1353,60 +1353,1420 @@
         <v>-0.2234871899330499</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2903666067605108</v>
+        <v>0.01639924762878189</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>-0.9513654605594664</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.7380657395056173</v>
+        <v>0.3662929378716617</v>
       </c>
       <c r="L11" t="n">
         <v>-0.0212614987234063</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.04260747331260206</v>
+        <v>0.002068859892783901</v>
       </c>
       <c r="N11" t="n">
+        <v>-1.192369206818894</v>
+      </c>
+      <c r="O11" t="n">
+        <v>-1.35522124730509</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.7158298218629204</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>-0.007636903376397777</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.7795995441576077</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.2923874875616173</v>
+      </c>
+      <c r="T11" t="n">
+        <v>-0.4457148340944427</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.1143765757201559</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.8889559496984945</v>
+      </c>
+      <c r="W11" t="n">
+        <v>-0.8646257659064015</v>
+      </c>
+      <c r="X11" t="n">
+        <v>-0.750655081292074</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>-0.2964670275503895</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>-0.2978295335184983</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>-0.1662386772451152</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>4b2YCRGG</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1.760387359086781</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-0.8146674735397244</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.4712162475956001</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-1.533089892472219</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.744079874884109</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-0.9805787268653793</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-0.2234871899330499</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.01639924762878189</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.05159850326629842</v>
+      </c>
+      <c r="K12" t="n">
+        <v>-0.3699461803798577</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.5643503415931583</v>
+      </c>
+      <c r="M12" t="n">
+        <v>-1.606279135501117</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.310526542735255</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.7411407521588274</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.332346897978915</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.2719486605111748</v>
+      </c>
+      <c r="R12" t="n">
+        <v>-0.8716212453201829</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.310709844936682</v>
+      </c>
+      <c r="T12" t="n">
+        <v>-0.9574141213330414</v>
+      </c>
+      <c r="U12" t="n">
+        <v>-1.537331879370775</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>-0.3921361617511639</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-0.08586432750993818</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>-0.006447437154554888</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-0.05156750576022407</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-0.1662386772451152</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>dYbQEmn4</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1.760387359086781</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1.91244071360527</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.9952379932178427</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1.80697928410952</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-0.5433246664041846</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-0.9805787268653793</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-0.2234871899330499</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-0.805502829766405</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.054562467092063</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-0.7380657395056173</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-0.7239957071032835</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.359479525535873</v>
+      </c>
+      <c r="N13" t="n">
+        <v>-0.6417321419169809</v>
+      </c>
+      <c r="O13" t="n">
+        <v>-0.6564339141504507</v>
+      </c>
+      <c r="P13" t="n">
+        <v>3.016727365166953</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>-0.9395887830016399</v>
+      </c>
+      <c r="R13" t="n">
+        <v>-0.5802293412946906</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.37859800209502</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.2365508822236893</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.949608192487857</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.7146222818795492</v>
+      </c>
+      <c r="W13" t="n">
+        <v>-0.7608284444673531</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-0.8876970247293534</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.3061098139220294</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0.2864217867141564</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-0.1662386772451152</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>IRBb0lXA</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1.790197536946965</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.9243580371034607</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.9067450648928936</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1.123783316172346</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-1.625177222108633</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-0.9805787268653793</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-0.2234871899330499</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-0.805502829766405</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.5530804851791808</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-0.001826621254097982</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.5643503415931583</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.4488321919466454</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1.56081611769067</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.090534418736147</v>
+      </c>
+      <c r="P14" t="n">
+        <v>-1.201584797557106</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.017510164211369</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.3910770054569503</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.718038787886708</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-1.639679837651173</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-0.4361929093101544</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.4013094186114393</v>
+      </c>
+      <c r="W14" t="n">
+        <v>-1.120560892966782</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-1.382418162669989</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>-0.4752310456531741</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-0.946965982060688</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-0.1662386772451152</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>xjut9IFr</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1.879628070527517</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-0.2119370408736204</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.5217836352098567</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-0.0823527753710601</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-0.9219730609007416</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-0.9805787268653793</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-0.2234871899330499</v>
+      </c>
+      <c r="I15" t="n">
+        <v>-0.1205844319370826</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.3662929378716617</v>
+      </c>
+      <c r="L15" t="n">
+        <v>-0.6068733390399711</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.8062428575897346</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.3093682429135957</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.04235341900418825</v>
+      </c>
+      <c r="P15" t="n">
+        <v>-0.4346189497890956</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>-0.1940272793014465</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.0709914481831</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.05477893750743516</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.2365508822236891</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.481422899073696</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.5993841023655058</v>
+      </c>
+      <c r="W15" t="n">
+        <v>-0.8605652767992406</v>
+      </c>
+      <c r="X15" t="n">
+        <v>-0.5745411651636397</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>-0.6028975051045805</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0.4627329256900065</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-0.1662386772451152</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>8b5vHIeT</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1.760387359086781</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1.606135083889709</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.6918336675323028</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1.140652352417708</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-0.5433246664041846</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-0.9805787268653793</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-0.2234871899330499</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.4273502863263753</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.5530804851791808</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-0.001826621254097982</v>
+      </c>
+      <c r="L16" t="n">
+        <v>-0.0212614987234063</v>
+      </c>
+      <c r="M16" t="n">
+        <v>2.995383184653654</v>
+      </c>
+      <c r="N16" t="n">
+        <v>-0.2746407653157058</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.04235341900418825</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.099312745746926</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.4117414424549611</v>
+      </c>
+      <c r="R16" t="n">
+        <v>-1.163013149345675</v>
+      </c>
+      <c r="S16" t="n">
+        <v>-0.1488855339675779</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.089383027621354</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.133131354164627</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.6104043629550436</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.225610177412911</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.506519267573832</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.7262020404749298</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0.1068901835442262</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-0.1662386772451152</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>AyPaTn1c</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1.760387359086781</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-1.269185504730557</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.9952379932178427</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-0.0823527753710601</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-0.5433246664041846</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-0.9805787268653793</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-0.2234871899330499</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-0.9424865093322694</v>
+      </c>
+      <c r="J17" t="n">
+        <v>-2.455811406298114</v>
+      </c>
+      <c r="K17" t="n">
+        <v>-0.001826621254097982</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.5643503415931583</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-0.5563853051745422</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.2593103279225126</v>
+      </c>
+      <c r="O17" t="n">
+        <v>-0.2196918309288014</v>
+      </c>
+      <c r="P17" t="n">
+        <v>-0.6263604117310982</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>-0.9162899860110088</v>
+      </c>
+      <c r="R17" t="n">
+        <v>-1.818644933403033</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.327681884226267</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.5776837403827552</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.481422899073696</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.6593759755030494</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0.1625943522428826</v>
+      </c>
+      <c r="X17" t="n">
+        <v>-0.6778109775651914</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.6576236300896326</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.24111361473719</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-0.1662386772451152</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>fVeJ32M5</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1.939248426247886</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-1.032045662370122</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-0.7619787263775758</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.2803315039042297</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.2031535970318848</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-0.9805787268653793</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-0.2234871899330499</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.01639924762878189</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-0.9513654605594664</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-0.001826621254097982</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-0.0212614987234063</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.649875691370883</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-0.9420796318634789</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-0.3070402475731312</v>
+      </c>
+      <c r="P18" t="n">
+        <v>-0.9139726046441022</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.48348610402399</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.289535376202219</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.08872301608660424</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0.4497589185731055</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0.1602573661393483</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0.5750235263254728</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0.5897272334203767</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0.3509383883535987</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>-0.2567125727852079</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.195362735802936</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-0.1662386772451152</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>SdHeBgOE</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1.909438248387701</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1.042927958283678</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-0.8757553485096533</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-0.7402451889401905</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-0.3377726808203395</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-0.9805787268653793</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-0.2234871899330499</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.5643339658922398</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.556044449004946</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-0.001826621254097982</v>
+      </c>
+      <c r="L19" t="n">
+        <v>-0.0212614987234063</v>
+      </c>
+      <c r="M19" t="n">
+        <v>-0.6904143047907007</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1.811105692646085</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.8284891688031573</v>
+      </c>
+      <c r="P19" t="n">
+        <v>-1.48919699047011</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>-0.566808031151543</v>
+      </c>
+      <c r="R19" t="n">
+        <v>-0.5073813652883176</v>
+      </c>
+      <c r="S19" t="n">
+        <v>-0.3525500054425909</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.089383027621354</v>
+      </c>
+      <c r="U19" t="n">
+        <v>-1.44557029853239</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>2.203421807440068</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.803933296710242</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0.2057876252748363</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0.6806172007120584</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-0.1662386772451152</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>dzUhmsxP</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1.879628070527517</v>
+      </c>
+      <c r="C20" t="n">
+        <v>-0.4886001902941271</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-0.5217836352098567</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1.123783316172346</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-0.9219730609007416</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-0.9805787268653793</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-0.2234871899330499</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-0.1205844319370826</v>
+      </c>
+      <c r="J20" t="n">
+        <v>-0.9513654605594664</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-0.001826621254097982</v>
+      </c>
+      <c r="L20" t="n">
+        <v>-0.0212614987234063</v>
+      </c>
+      <c r="M20" t="n">
+        <v>2.325238186572863</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-0.441500481952649</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.3917470855815078</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.8117005528339217</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>-0.5901068281421742</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.9738608135079357</v>
+      </c>
+      <c r="S20" t="n">
+        <v>-1.065375655605137</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.43051588578042</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.811965821230279</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0.5993841023655058</v>
+      </c>
+      <c r="W20" t="n">
+        <v>-0.2985570006685368</v>
+      </c>
+      <c r="X20" t="n">
+        <v>-0.4870710015606541</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>-1.604569220076344</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0.2345943499333683</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-0.1662386772451152</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>na927pNt</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1.760387359086781</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1.24054449358404</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.03445762854696641</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.297200540149592</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-0.2620430019210281</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-0.9805787268653793</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-0.2234871899330499</v>
+      </c>
+      <c r="I21" t="n">
+        <v>-0.2575681115029471</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.5530804851791808</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-0.001826621254097982</v>
+      </c>
+      <c r="L21" t="n">
+        <v>-0.0212614987234063</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.5381848583574178</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-0.9420796318634789</v>
+      </c>
+      <c r="O21" t="n">
+        <v>-1.26787283066076</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.2364761670079138</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.3884426454643299</v>
+      </c>
+      <c r="R21" t="n">
+        <v>-1.551535688046332</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.9458110002106171</v>
+      </c>
+      <c r="T21" t="n">
+        <v>-1.127980550412574</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0.7108268511696585</v>
+      </c>
+      <c r="V21" t="n">
+        <v>-0.04249774249881632</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0.6696453327415574</v>
+      </c>
+      <c r="X21" t="n">
+        <v>-0.4253540532857122</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>-0.4742005760529463</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1.378262854816724</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-0.1662386772451152</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>SfxxiPx0</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1.760387359086781</v>
+      </c>
+      <c r="C22" t="n">
+        <v>-1.012284008840086</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1.930734664081591</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-1.533089892472219</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-0.2620430019210281</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-0.9805787268653793</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-0.2234871899330499</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1.386236043287427</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.05159850326629842</v>
+      </c>
+      <c r="K22" t="n">
+        <v>-0.001826621254097982</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-0.0212614987234063</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-0.1542983063260672</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.5596578178690105</v>
+      </c>
+      <c r="O22" t="n">
+        <v>2.400760668401095</v>
+      </c>
+      <c r="P22" t="n">
+        <v>-0.3387482188180942</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>-1.475461113786154</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.31381803487101</v>
+      </c>
+      <c r="S22" t="n">
+        <v>-1.294498186014526</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.473157493050303</v>
+      </c>
+      <c r="U22" t="n">
+        <v>-0.3444313284717694</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0.7456925620345022</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0.8236828710970533</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0.7872606230756608</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>-0.2093470597389521</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0.7026630009917714</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>-0.1662386772451152</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>jckS1tiI</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1.909438248387701</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1.003404651223605</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.312578260425378</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-1.406572120632002</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.1815165459177958</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-0.9805787268653793</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-0.2234871899330499</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-2.586290664122644</v>
+      </c>
+      <c r="J23" t="n">
+        <v>-1.452847442472349</v>
+      </c>
+      <c r="K23" t="n">
+        <v>-0.001826621254097982</v>
+      </c>
+      <c r="L23" t="n">
+        <v>-0.0212614987234063</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.051962690219358</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-0.9420796318634789</v>
+      </c>
+      <c r="O23" t="n">
+        <v>-1.00582758072777</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.5240883599209177</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.809669261892824</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.2210983947754135</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.3348175857855781</v>
+      </c>
+      <c r="T23" t="n">
+        <v>-2.364587161239188</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0.2061381565585409</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0.3526849354839148</v>
+      </c>
+      <c r="W23" t="n">
+        <v>-1.602712654584936</v>
+      </c>
+      <c r="X23" t="n">
+        <v>-1.757946222538173</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0.8247333425136832</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-0.6438335575289738</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-0.1662386772451152</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>8EcB5Oig</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1.760387359086781</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.8650730765133521</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.6918336675323028</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.297200540149592</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-0.5433246664041846</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-0.9805787268653793</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-0.2234871899330499</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.8383013250239688</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.054562467092063</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.7344124969974213</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-0.0212614987234063</v>
+      </c>
+      <c r="M24" t="n">
+        <v>2.01250385413516</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-0.441500481952649</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.4790955022258377</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.291054207688929</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-0.6367044221234361</v>
+      </c>
+      <c r="R24" t="n">
+        <v>-1.04159985600172</v>
+      </c>
+      <c r="S24" t="n">
+        <v>-1.090833714539513</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.88033053295645</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.490800288295931</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0.7617879426323803</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0.9684265388967028</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.385186967207399</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0.1581964829587629</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0.9725247176323855</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-0.1662386772451152</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>CjIFsr1e</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1.760387359086781</v>
+      </c>
+      <c r="C25" t="n">
+        <v>-0.07360546616336709</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.9699542994107144</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.2803315039042297</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.744079874884109</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-0.9805787268653793</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-0.2234871899330499</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.1533829271946464</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.05159850326629842</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-0.001826621254097982</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-0.0212614987234063</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.185991689835516</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-0.6917900569080639</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-0.7437823307947806</v>
+      </c>
+      <c r="P25" t="n">
+        <v>-0.05113602590509021</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-1.475461113786154</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.4396423227945328</v>
+      </c>
+      <c r="S25" t="n">
+        <v>-0.6835047715894871</v>
+      </c>
+      <c r="T25" t="n">
+        <v>-0.1898651904751431</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.481422899073696</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0.9454589524580144</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0.05220849563582881</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0.001384402268705091</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0.4865358335671527</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0.6702651130227424</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-0.1662386772451152</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>08zpk37C</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1.909438248387701</v>
+      </c>
+      <c r="C26" t="n">
+        <v>-1.269185504730557</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1.121656462253484</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-0.0823527753710601</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-0.3377726808203395</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-0.9805787268653793</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-0.2234871899330499</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-0.5315354706346761</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.05159850326629842</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-0.001826621254097982</v>
+      </c>
+      <c r="L26" t="n">
+        <v>-0.0212614987234063</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-1.360559302871493</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-0.6917900569080639</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-1.791963330526739</v>
+      </c>
+      <c r="P26" t="n">
+        <v>-1.48919699047011</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1.180601743145786</v>
+      </c>
+      <c r="R26" t="n">
+        <v>-0.9444692213265561</v>
+      </c>
+      <c r="S26" t="n">
+        <v>-0.1998016518363311</v>
+      </c>
+      <c r="T26" t="n">
+        <v>-0.701564477713742</v>
+      </c>
+      <c r="U26" t="n">
+        <v>-1.44557029853239</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0.3615784791175781</v>
+      </c>
+      <c r="W26" t="n">
+        <v>-0.2044844427979938</v>
+      </c>
+      <c r="X26" t="n">
+        <v>-0.9173672325647583</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0.08326848086095896</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0.6884077952895487</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-0.1662386772451152</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>YeqTho8m</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1.820007714807149</v>
+      </c>
+      <c r="C27" t="n">
+        <v>1.606135083889709</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-0.2942303909457018</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1.140652352417708</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-0.3594097319344284</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-0.9805787268653793</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-0.2234871899330499</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.2903666067605108</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-0.7380657395056173</v>
+      </c>
+      <c r="L27" t="n">
+        <v>-0.0212614987234063</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.1360978595089427</v>
+      </c>
+      <c r="N27" t="n">
         <v>-0.5249303402711207</v>
       </c>
-      <c r="O11" t="n">
+      <c r="O27" t="n">
         <v>-0.3943886642174612</v>
       </c>
-      <c r="P11" t="n">
+      <c r="P27" t="n">
         <v>0.2364761670079138</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0.1088570815767573</v>
-      </c>
-      <c r="R11" t="n">
-        <v>-0.8230559279826011</v>
-      </c>
-      <c r="S11" t="n">
-        <v>-0.3440639857977985</v>
-      </c>
-      <c r="T11" t="n">
+      <c r="Q27" t="n">
+        <v>0.3884426454643299</v>
+      </c>
+      <c r="R27" t="n">
+        <v>-0.7259252933074368</v>
+      </c>
+      <c r="S27" t="n">
+        <v>-0.4374102018905132</v>
+      </c>
+      <c r="T27" t="n">
         <v>0.06598445314415635</v>
       </c>
-      <c r="U11" t="n">
+      <c r="U27" t="n">
         <v>-0.1150273763758069</v>
       </c>
-      <c r="V11" t="n">
-        <v>-0.1038825273615937</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0.5590090697704427</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0.8652825548802219</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0.4588800325662478</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>-0.8401780195719284</v>
-      </c>
-      <c r="AA11" t="n">
+      <c r="V27" t="n">
+        <v>-0.1766742486240655</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.24109558755207</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.390278085311905</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0.4518936252068633</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-0.4699296310727803</v>
+      </c>
+      <c r="AA27" t="n">
         <v>-0.1662386772451152</v>
       </c>
     </row>

--- a/data/spain/p6_deployment/data_preparation/df_selected_nan.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_selected_nan.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA7"/>
+  <dimension ref="A1:AA32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,23 +563,23 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>AyPaTn1c</t>
+          <t>YJVCWCD6</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.760387359086781</v>
+        <v>1.820007714807149</v>
       </c>
       <c r="C2" t="n">
-        <v>-1.269185504730557</v>
+        <v>1.141736225933859</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9952379932178427</v>
+        <v>-0.4712162475956001</v>
       </c>
       <c r="E2" t="n">
         <v>-0.3606918734195383</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.5433246664041846</v>
+        <v>-0.7164210753168965</v>
       </c>
       <c r="G2" t="n">
         <v>-0.9805787268653793</v>
@@ -588,58 +588,58 @@
         <v>-0.2234871899330499</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.9424865093322694</v>
+        <v>0.4273502863263753</v>
       </c>
       <c r="J2" t="n">
-        <v>-2.455811406298114</v>
+        <v>-0.9513654605594664</v>
       </c>
       <c r="K2" t="n">
-        <v>0.7344124969974213</v>
+        <v>0.3662929378716617</v>
       </c>
       <c r="L2" t="n">
-        <v>2.711593756087229</v>
+        <v>0.5643503415931583</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.073880906556372</v>
+        <v>0.9849481904112789</v>
       </c>
       <c r="N2" t="n">
-        <v>0.05907866795818074</v>
+        <v>1.06023696777984</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.1148737309556056</v>
+        <v>0.5664439188701677</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.2812257802354933</v>
+        <v>-1.776809183383114</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.014144933371659</v>
+        <v>0.5515342243987474</v>
       </c>
       <c r="R2" t="n">
-        <v>-1.774936147799209</v>
+        <v>0.1482504187690404</v>
       </c>
       <c r="S2" t="n">
-        <v>1.134200636325004</v>
+        <v>2.346004241601332</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7311935265543347</v>
+        <v>-1.46911340857164</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4263659505706652</v>
+        <v>0.481422899073696</v>
       </c>
       <c r="V2" t="n">
-        <v>0.03677079858382917</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0.1998674295234754</v>
+        <v>0.451381156380284</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.6692010649306898</v>
+        <v>1.091472279216978</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.7014776991883891</v>
+        <v>0.7716264094044483</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.178586310130842</v>
+        <v>0.1552260217488904</v>
       </c>
       <c r="AA2" t="n">
         <v>-0.1662386772451152</v>
@@ -648,23 +648,23 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>fVeJ32M5</t>
+          <t>n37VJZT0</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.879628070527517</v>
+        <v>1.939248426247886</v>
       </c>
       <c r="C3" t="n">
-        <v>-1.032045662370122</v>
+        <v>1.042927958283678</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.7619787263775758</v>
+        <v>0.312578260425378</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2803315039042297</v>
+        <v>-0.9595426601299006</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2031535970318848</v>
+        <v>1.166002371608844</v>
       </c>
       <c r="G3" t="n">
         <v>-0.9805787268653793</v>
@@ -673,58 +673,58 @@
         <v>-0.2234871899330499</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01639924762878189</v>
+        <v>-3.545176421083695</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.9513654605594664</v>
+        <v>0.05159850326629842</v>
       </c>
       <c r="K3" t="n">
         <v>-0.001826621254097982</v>
       </c>
       <c r="L3" t="n">
-        <v>1.930777968998476</v>
+        <v>-0.6068733390399711</v>
       </c>
       <c r="M3" t="n">
-        <v>0.649875691370883</v>
+        <v>-1.293544803063413</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.9420796318634789</v>
+        <v>0.05907866795818074</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.3070402475731312</v>
+        <v>0.04235341900418825</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.9139726046441022</v>
+        <v>-0.05113602590509021</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.48348610402399</v>
+        <v>0.1321558785673885</v>
       </c>
       <c r="R3" t="n">
-        <v>1.289535376202219</v>
+        <v>-1.163013149345675</v>
       </c>
       <c r="S3" t="n">
-        <v>0.08872301608660424</v>
+        <v>0.5639401161949678</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4497589185731055</v>
+        <v>-1.980812695810239</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1602573661393483</v>
+        <v>-0.6197160709869246</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5750235263254728</v>
+        <v>0.1561569549704894</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5897272334203767</v>
+        <v>0.1266936677182884</v>
       </c>
       <c r="X3" t="n">
-        <v>0.3509383883535987</v>
+        <v>-0.7168672964484724</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.2567125727852079</v>
+        <v>0.6451929887671244</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.195362735802936</v>
+        <v>0.4671319975843274</v>
       </c>
       <c r="AA3" t="n">
         <v>-0.1662386772451152</v>
@@ -733,23 +733,23 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>SdHeBgOE</t>
+          <t>4rQsoH7m</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.849817892667333</v>
+        <v>1.879628070527517</v>
       </c>
       <c r="C4" t="n">
-        <v>1.042927958283678</v>
+        <v>1.606135083889709</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.8757553485096533</v>
+        <v>-0.1172445342958035</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.7402451889401905</v>
+        <v>0.2044208408000993</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3377726808203395</v>
+        <v>1.13354679493771</v>
       </c>
       <c r="G4" t="n">
         <v>-0.9805787268653793</v>
@@ -758,58 +758,58 @@
         <v>-0.2234871899330499</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5643339658922398</v>
+        <v>-0.3945517910688116</v>
       </c>
       <c r="J4" t="n">
-        <v>1.556044449004946</v>
+        <v>0.5530804851791808</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.001826621254097982</v>
+        <v>-1.400680945931985</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7595542883653463</v>
+        <v>0.3301056054665323</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.6904143047907007</v>
+        <v>-1.56160280229573</v>
       </c>
       <c r="N4" t="n">
-        <v>1.811105692646085</v>
+        <v>-0.741847971899147</v>
       </c>
       <c r="O4" t="n">
-        <v>0.8284891688031573</v>
+        <v>-1.52991808059375</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.48919699047011</v>
+        <v>-0.6263604117310982</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.566808031151543</v>
+        <v>-0.4270152492077567</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.5073813652883176</v>
+        <v>-0.4345333892819445</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3525500054425909</v>
+        <v>-1.014459537736383</v>
       </c>
       <c r="T4" t="n">
-        <v>1.089383027621354</v>
+        <v>-0.4457148340944425</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.44557029853239</v>
+        <v>-0.8950008135020797</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.9504294942358781</v>
       </c>
       <c r="W4" t="n">
-        <v>2.203421807440068</v>
+        <v>1.238814438435236</v>
       </c>
       <c r="X4" t="n">
-        <v>1.803933296710242</v>
+        <v>1.501265037378084</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.2057876252748363</v>
+        <v>0.2739661720484229</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.6806172007120584</v>
+        <v>-0.562034752507757</v>
       </c>
       <c r="AA4" t="n">
         <v>-0.1662386772451152</v>
@@ -818,23 +818,23 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>dzUhmsxP</t>
+          <t>jyEMLeal</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.820007714807149</v>
+        <v>1.939248426247886</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.4886001902941271</v>
+        <v>-0.5577659776492538</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.5217836352098567</v>
+        <v>0.9067450648928936</v>
       </c>
       <c r="E5" t="n">
-        <v>1.123783316172346</v>
+        <v>0.7526645187743746</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.9219730609007416</v>
+        <v>-1.419625236524788</v>
       </c>
       <c r="G5" t="n">
         <v>-0.9805787268653793</v>
@@ -843,58 +843,58 @@
         <v>-0.2234871899330499</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1205844319370826</v>
+        <v>-0.9424865093322694</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.9513654605594664</v>
+        <v>-0.449883478646584</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7344124969974213</v>
+        <v>0.3662929378716617</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.0212614987234063</v>
+        <v>1.149962181909723</v>
       </c>
       <c r="M5" t="n">
-        <v>2.325238186572863</v>
+        <v>-0.489370805366463</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.441500481952649</v>
+        <v>0.05907866795818074</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3917470855815078</v>
+        <v>1.090534418736147</v>
       </c>
       <c r="P5" t="n">
-        <v>0.8117005528339217</v>
+        <v>0.5240883599209177</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.5901068281421742</v>
+        <v>-0.007636903376397777</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9738608135079357</v>
+        <v>-1.74579695739666</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.065375655605137</v>
+        <v>1.022185177013747</v>
       </c>
       <c r="T5" t="n">
-        <v>1.43051588578042</v>
+        <v>-0.9574141213330414</v>
       </c>
       <c r="U5" t="n">
-        <v>1.811965821230279</v>
+        <v>-0.3444313284717694</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5993841023655058</v>
+        <v>0.09087157787273242</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.2985570006685368</v>
+        <v>0.03873985765856323</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.4870710015606541</v>
+        <v>-0.6157059853997483</v>
       </c>
       <c r="Y5" t="n">
-        <v>-1.604569220076344</v>
+        <v>0.6746622038198948</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.2345943499333683</v>
+        <v>-0.5358337973491174</v>
       </c>
       <c r="AA5" t="n">
         <v>-0.1662386772451152</v>
@@ -903,23 +903,23 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>na927pNt</t>
+          <t>h0AwIDbD</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1.760387359086781</v>
       </c>
       <c r="C6" t="n">
-        <v>1.24054449358404</v>
+        <v>-1.012284008840086</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03445762854696641</v>
+        <v>1.235433084385562</v>
       </c>
       <c r="E6" t="n">
-        <v>0.297200540149592</v>
+        <v>1.781675729741476</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2620430019210281</v>
+        <v>1.78265832836038</v>
       </c>
       <c r="G6" t="n">
         <v>-0.9805787268653793</v>
@@ -928,58 +928,58 @@
         <v>-0.2234871899330499</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2575681115029471</v>
+        <v>0.1533829271946464</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5530804851791808</v>
+        <v>-0.449883478646584</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.7380657395056173</v>
+        <v>-0.3699461803798577</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.192485179356536</v>
+        <v>1.149962181909723</v>
       </c>
       <c r="M6" t="n">
-        <v>0.5381848583574178</v>
+        <v>-2.767863798841155</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.9420796318634789</v>
+        <v>0.05907866795818074</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.26787283066076</v>
+        <v>1.090534418736147</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2364761670079138</v>
+        <v>-0.05113602590509021</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.3884426454643299</v>
+        <v>-0.4270152492077567</v>
       </c>
       <c r="R6" t="n">
-        <v>-1.551535688046332</v>
+        <v>3.499257315062203</v>
       </c>
       <c r="S6" t="n">
-        <v>0.9458110002106171</v>
+        <v>-0.5052983590488507</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.127980550412574</v>
+        <v>0.5776837403827552</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7108268511696585</v>
+        <v>-2.546709268593011</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.04249774249881632</v>
+        <v>0.2994082590154144</v>
       </c>
       <c r="W6" t="n">
-        <v>0.6696453327415574</v>
+        <v>-0.2500110112724856</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.4253540532857122</v>
+        <v>-0.1570892430083669</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.4742005760529463</v>
+        <v>0.2180741937124433</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.378262854816724</v>
+        <v>0.3752155209160349</v>
       </c>
       <c r="AA6" t="n">
         <v>-0.1662386772451152</v>
@@ -988,23 +988,23 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>SfxxiPx0</t>
+          <t>4vvdzeEs</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1.760387359086781</v>
       </c>
       <c r="C7" t="n">
-        <v>-1.012284008840086</v>
+        <v>-0.8146674735397244</v>
       </c>
       <c r="D7" t="n">
-        <v>1.930734664081591</v>
+        <v>0.03445762854696641</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.533089892472219</v>
+        <v>-1.634304109944393</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2620430019210281</v>
+        <v>1.78265832836038</v>
       </c>
       <c r="G7" t="n">
         <v>-0.9805787268653793</v>
@@ -1013,10 +1013,10 @@
         <v>-0.2234871899330499</v>
       </c>
       <c r="I7" t="n">
-        <v>1.386236043287427</v>
+        <v>-3.819143780215424</v>
       </c>
       <c r="J7" t="n">
-        <v>0.05159850326629842</v>
+        <v>-2.455811406298114</v>
       </c>
       <c r="K7" t="n">
         <v>-0.001826621254097982</v>
@@ -1025,48 +1025,2173 @@
         <v>-0.0212614987234063</v>
       </c>
       <c r="M7" t="n">
+        <v>1.923151187724387</v>
+      </c>
+      <c r="N7" t="n">
+        <v>-0.6917900569080639</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-3.626280080057667</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.249761517398942</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3.347389863274473</v>
+      </c>
+      <c r="R7" t="n">
+        <v>-0.4345333892819445</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.040507534388812</v>
+      </c>
+      <c r="T7" t="n">
+        <v>-3.260060913906736</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.7567076415888512</v>
+      </c>
+      <c r="V7" t="n">
+        <v>-2.382147663652129e-05</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.149335295638073</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-1.281241187046249</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>-1.199346842564142</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1.433084459430859</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>-0.1662386772451152</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>YemQuHjK</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1.849817892667333</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1.003404651223605</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.8757553485096533</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-0.5293822358731616</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.4844352615150414</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-0.9805787268653793</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-0.2234871899330499</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-0.2575681115029471</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.5530804851791808</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1.470651615248941</v>
+      </c>
+      <c r="L8" t="n">
+        <v>-0.6068733390399711</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.118977190027437</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.05907866795818074</v>
+      </c>
+      <c r="O8" t="n">
+        <v>-0.4817370808617911</v>
+      </c>
+      <c r="P8" t="n">
+        <v>-1.201584797557106</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.6913270063425337</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.2939463707817866</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.4621078804574613</v>
+      </c>
+      <c r="T8" t="n">
+        <v>-1.213263764952341</v>
+      </c>
+      <c r="U8" t="n">
+        <v>-0.06914658595661426</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.053631510350054</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.6836174733304541</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.7698216309701966</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.1953137365742141</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>-0.1167795427314404</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>-0.1662386772451152</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>KSw0hfzQ</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.849817892667333</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-1.032045662370122</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.2942303909457018</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-1.634304109944393</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-0.1105836441224053</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-0.9805787268653793</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-0.2234871899330499</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.5643339658922398</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.3662929378716617</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.5643503415931583</v>
+      </c>
+      <c r="M9" t="n">
+        <v>-1.56160280229573</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.8099473928244254</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.138715418468105</v>
+      </c>
+      <c r="P9" t="n">
+        <v>-0.05113602590509021</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>-0.1474296853201841</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.1482504187690404</v>
+      </c>
+      <c r="S9" t="n">
+        <v>-1.523620716423916</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.368631245717851</v>
+      </c>
+      <c r="U9" t="n">
+        <v>-0.3444313284717694</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.5341688102583378</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.7819324542653415</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.3538365709355867</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>-1.386043286977469</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.9528725564116126</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>6.015447286827976</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hMoEUjrJ</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1.879628070527517</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.7168606750380806</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.9699542994107144</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.297200540149592</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.13354679493771</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-0.9805787268653793</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0.2234871899330499</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-0.3945517910688116</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.05159850326629842</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-0.6644418276804657</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.2129832374032198</v>
+      </c>
+      <c r="M10" t="n">
+        <v>-1.427573802679572</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-0.391442566961566</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-2.054008580459729</v>
+      </c>
+      <c r="P10" t="n">
+        <v>-1.201584797557106</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.2719486605111748</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.31381803487101</v>
+      </c>
+      <c r="S10" t="n">
+        <v>-0.1488855339675779</v>
+      </c>
+      <c r="T10" t="n">
+        <v>-1.213263764952341</v>
+      </c>
+      <c r="U10" t="n">
+        <v>-1.9961397835627</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.415089027217629</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-0.02145122553316822</v>
+      </c>
+      <c r="X10" t="n">
+        <v>-0.06911120009609636</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.3818253414486891</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>-0.08182603264137718</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>-0.1662386772451152</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>06X4YYrf</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1.939248426247886</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1.91244071360527</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-1.292936296327271</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.781675729741476</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-0.3377726808203395</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-0.9805787268653793</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-0.2234871899330499</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.4273502863263753</v>
+      </c>
+      <c r="J11" t="n">
+        <v>-0.449883478646584</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-0.3699461803798577</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-0.6068733390399711</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.521064188875912</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-0.6917900569080639</v>
+      </c>
+      <c r="O11" t="n">
+        <v>-0.4817370808617911</v>
+      </c>
+      <c r="P11" t="n">
+        <v>4.550659060702974</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>-0.1474296853201841</v>
+      </c>
+      <c r="R11" t="n">
+        <v>-0.143141485256452</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.174933530620007</v>
+      </c>
+      <c r="T11" t="n">
+        <v>-1.213263764952341</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.958985581710092</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.6027675157043972</v>
+      </c>
+      <c r="W11" t="n">
+        <v>-0.9435518837039772</v>
+      </c>
+      <c r="X11" t="n">
+        <v>-0.2213543484130254</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>-0.4242485954733371</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>-0.8078153920938197</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>-0.1662386772451152</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>pGrl7dpe</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1.849817892667333</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-1.012284008840086</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.033163533928535</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.781675729741476</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.4844352615150414</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-0.9805787268653793</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-0.2234871899330499</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-2.312323304990914</v>
+      </c>
+      <c r="J12" t="n">
+        <v>-2.455811406298114</v>
+      </c>
+      <c r="K12" t="n">
+        <v>-0.3699461803798577</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2.125981915770664</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.1807741927143287</v>
+      </c>
+      <c r="N12" t="n">
+        <v>-0.6083601985895924</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.265231252024807</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.249761517398942</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.017510164211368</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2.042297794934741</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.1566111732449417</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.2365508822236891</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0.7567076415888512</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.7723006912210856</v>
+      </c>
+      <c r="W12" t="n">
+        <v>-1.451451798580181</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-1.050772800490691</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.3633725959209541</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0.08601422966642577</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-0.1662386772451152</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>6VWd5zF7</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1.849817892667333</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-0.4886001902941271</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.627330338396051</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.7526645187743746</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-0.1105836441224053</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-0.9805787268653793</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-0.2234871899330499</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-0.9424865093322694</v>
+      </c>
+      <c r="J13" t="n">
+        <v>-0.449883478646584</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-0.001826621254097982</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-1.192485179356536</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.9402718572058925</v>
+      </c>
+      <c r="N13" t="n">
+        <v>-0.6917900569080639</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.04235341900418825</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.099312745746926</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>-0.8463935950391156</v>
+      </c>
+      <c r="R13" t="n">
+        <v>-0.2402721199316163</v>
+      </c>
+      <c r="S13" t="n">
+        <v>-0.8277671055509545</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.004099813081587</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.8484692224272363</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.8328205086607965</v>
+      </c>
+      <c r="W13" t="n">
+        <v>-0.6314557152688139</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-1.306153988496743</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>-1.084016193577394</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0.3484189232868034</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-0.1662386772451152</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>bqbA3PNE</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1.939248426247886</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-0.07360546616336709</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.121656462253484</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.2803315039042297</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-0.3377726808203395</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-0.9805787268653793</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-0.2234871899330499</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-1.079470188898134</v>
+      </c>
+      <c r="J14" t="n">
+        <v>-1.452847442472349</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-0.6153592197970306</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-0.8020772858121596</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.074300856822051</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.3927981012320672</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.2170502522928481</v>
+      </c>
+      <c r="P14" t="n">
+        <v>-0.05113602590509021</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.7845221943050581</v>
+      </c>
+      <c r="R14" t="n">
+        <v>-0.2888374372691982</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.2584434089824482</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-0.01929876139561005</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.2061381565585409</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.3528782733889975</v>
+      </c>
+      <c r="W14" t="n">
+        <v>-1.030432996195487</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-1.281045719023498</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.04562464132325893</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0.134090214291167</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-0.1662386772451152</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>QDjsB5oT</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1.939248426247886</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.05484528178186816</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.6918336675323028</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-1.651173146189756</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-1.419625236524788</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-0.9805787268653793</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-0.2234871899330499</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3.30400755720953</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.054562467092063</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-0.001826621254097982</v>
+      </c>
+      <c r="L15" t="n">
+        <v>-1.192485179356536</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.4041558587412593</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1.811105692646085</v>
+      </c>
+      <c r="O15" t="n">
+        <v>4.584471084509341</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.1406054360369124</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>-2.104528632533192</v>
+      </c>
+      <c r="R15" t="n">
+        <v>-1.017317197332929</v>
+      </c>
+      <c r="S15" t="n">
+        <v>-1.69334110931976</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.62448088933715</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.6649460607504661</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.5569464322005279</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0.2442582028138239</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.451385981678782</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.2209898949208773</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-0.8587527520715845</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-0.1662386772451152</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>ddsD5q9j</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1.879628070527517</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1.24054449358404</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-1.027457511352423</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-1.651173146189756</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-1.538629017652277</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-0.9805787268653793</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-0.2234871899330499</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.01639924762878189</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.054562467092063</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-1.106185298631377</v>
+      </c>
+      <c r="L16" t="n">
+        <v>-0.6068733390399711</v>
+      </c>
+      <c r="M16" t="n">
+        <v>-0.08728380651798802</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.8099473928244254</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.7411407521588275</v>
+      </c>
+      <c r="P16" t="n">
+        <v>-0.4346189497890957</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>-0.7531984070765912</v>
+      </c>
+      <c r="R16" t="n">
+        <v>-2.037188861422153</v>
+      </c>
+      <c r="S16" t="n">
+        <v>-0.01310921965090227</v>
+      </c>
+      <c r="T16" t="n">
+        <v>-0.2751484050149097</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.297899737396926</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.706514282013406</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.1322812937570582</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.5795827442466812</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.8862895513113459</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-0.9914690467830091</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-0.1662386772451152</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>f5SjRHyR</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1.879628070527517</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.3413892579673929</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.9699542994107144</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-0.5293822358731616</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.13354679493771</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-0.9805787268653793</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-0.2234871899330499</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.482105479814342</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.556044449004946</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1.102532056123181</v>
+      </c>
+      <c r="L17" t="n">
+        <v>-1.192485179356536</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-0.2659891393395328</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.3093682429135957</v>
+      </c>
+      <c r="O17" t="n">
+        <v>-0.3070402475731312</v>
+      </c>
+      <c r="P17" t="n">
+        <v>-1.201584797557106</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>-0.8463935950391156</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.2939463707817866</v>
+      </c>
+      <c r="S17" t="n">
+        <v>-1.065375655605137</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.259949456700887</v>
+      </c>
+      <c r="U17" t="n">
+        <v>-0.9867623943404646</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.8595202536501272</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2.061889805824386</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.587829816304714</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>-0.7734079529810258</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0.3391194605704998</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-0.1662386772451152</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>rkN7RQV9</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1.760387359086781</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.8650730765133521</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.930734664081591</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.297200540149592</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-0.2620430019210281</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-0.9805787268653793</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-0.2234871899330499</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.5643339658922398</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.5530804851791808</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-1.106185298631377</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-0.6068733390399711</v>
+      </c>
+      <c r="M18" t="n">
+        <v>-0.6233998049826214</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.8099473928244254</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.04235341900418825</v>
+      </c>
+      <c r="P18" t="n">
+        <v>-3.118999416977133</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>-0.4736128431890191</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.4882076401321147</v>
+      </c>
+      <c r="S18" t="n">
+        <v>-1.099319734184306</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.942215173019018</v>
+      </c>
+      <c r="U18" t="n">
+        <v>-0.986762394340465</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0.5964840337893093</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.129464788009119</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.108239957917107</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.1300224653822077</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0.4942200987010446</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-0.1662386772451152</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>bwZsTw7E</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1.879628070527517</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-0.893714087659869</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-0.7619787263775758</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-0.9595426601299006</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-1.538629017652277</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-0.9805787268653793</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-0.2234871899330499</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.619089159380207</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.5530804851791808</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-0.001826621254097982</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.5643503415931583</v>
+      </c>
+      <c r="M19" t="n">
+        <v>-0.3553418057503047</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-0.441500481952649</v>
+      </c>
+      <c r="O19" t="n">
+        <v>-1.00582758072777</v>
+      </c>
+      <c r="P19" t="n">
+        <v>-1.585067721441111</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>-1.032783970964164</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.2939463707817866</v>
+      </c>
+      <c r="S19" t="n">
+        <v>-1.065375655605137</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0.2365508822236894</v>
+      </c>
+      <c r="U19" t="n">
+        <v>-0.4361929093101546</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0.4340801935224347</v>
+      </c>
+      <c r="W19" t="n">
+        <v>-0.4007604668096931</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0.005294295697209665</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0.3071690287427919</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-0.3753131708182029</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-0.1662386772451152</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>445r4WXo</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1.939248426247886</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1.606135083889709</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-1.292936296327271</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.2044208408000993</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-0.3377726808203395</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-0.9805787268653793</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-0.2234871899330499</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.1533829271946464</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.55900841283071</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-2.210543976008656</v>
+      </c>
+      <c r="L20" t="n">
+        <v>-0.0212614987234063</v>
+      </c>
+      <c r="M20" t="n">
+        <v>-1.070163137036483</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.05907866795818074</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.04235341900418825</v>
+      </c>
+      <c r="P20" t="n">
+        <v>-0.05113602590509021</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.08555828458612609</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.265252717533428</v>
+      </c>
+      <c r="S20" t="n">
+        <v>-0.7938230269717853</v>
+      </c>
+      <c r="T20" t="n">
+        <v>-0.2751484050149095</v>
+      </c>
+      <c r="U20" t="n">
+        <v>-0.8032392326636945</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0.5081286111679235</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0.4363713014326394</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.144062452556084</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0.06740880060574982</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-0.9784387647266726</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-0.1662386772451152</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>QiF6bS1N</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1.849817892667333</v>
+      </c>
+      <c r="C21" t="n">
+        <v>-1.032045662370122</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.033163533928535</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-1.634304109944393</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.4844352615150414</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-0.9805787268653793</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-0.2234871899330499</v>
+      </c>
+      <c r="I21" t="n">
+        <v>-2.312323304990914</v>
+      </c>
+      <c r="J21" t="n">
+        <v>-2.455811406298114</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-0.001826621254097982</v>
+      </c>
+      <c r="L21" t="n">
+        <v>-0.0212614987234063</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.9179336906031997</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-1.442658781774309</v>
+      </c>
+      <c r="O21" t="n">
+        <v>-0.4817370808617911</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.38692493865993</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.879565652864717</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.095274106851891</v>
+      </c>
+      <c r="S21" t="n">
+        <v>-0.1488855339675779</v>
+      </c>
+      <c r="T21" t="n">
+        <v>-0.4457148340944425</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0.481422899073696</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.095875842609952</v>
+      </c>
+      <c r="W21" t="n">
+        <v>-1.319568639389144</v>
+      </c>
+      <c r="X21" t="n">
+        <v>-1.470497497191595</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>-0.737390634503467</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0.740117958942952</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-0.1662386772451152</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>pxdwg6Pp</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1.760387359086781</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1.141736225933859</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.03445762854696641</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-0.3606918734195383</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1.78265832836038</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-0.9805787268653793</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-0.2234871899330499</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-2.997241702820237</v>
+      </c>
+      <c r="J22" t="n">
+        <v>-0.9513654605594664</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.7344124969974213</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-0.8020772858121585</v>
+      </c>
+      <c r="M22" t="n">
+        <v>2.392252686380942</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-0.441500481952649</v>
+      </c>
+      <c r="O22" t="n">
+        <v>-1.52991808059375</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0.8117005528339217</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.341845051483068</v>
+      </c>
+      <c r="R22" t="n">
+        <v>-0.6530773173010637</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.015049475454436</v>
+      </c>
+      <c r="T22" t="n">
+        <v>-0.9574141213330414</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2.133131354164627</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0.2204418084094603</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0.8359061698591645</v>
+      </c>
+      <c r="X22" t="n">
+        <v>-0.166187055849168</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>-0.1932317472419256</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1.515226569673981</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>-0.1662386772451152</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>OAmz0KLU</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1.760387359086781</v>
+      </c>
+      <c r="C23" t="n">
+        <v>-0.5577659776492538</v>
+      </c>
+      <c r="D23" t="n">
+        <v>-1.014815664448859</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.7526645187743746</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-0.2620430019210281</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-0.9805787268653793</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-0.2234871899330499</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.112268684155698</v>
+      </c>
+      <c r="J23" t="n">
+        <v>-0.449883478646584</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.7344124969974213</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.1739424480487823</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-1.025486803831096</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-0.04103716202398529</v>
+      </c>
+      <c r="O23" t="n">
+        <v>-1.52991808059375</v>
+      </c>
+      <c r="P23" t="n">
+        <v>-1.201584797557106</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.040808961202</v>
+      </c>
+      <c r="R23" t="n">
+        <v>-1.163013149345675</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.8185207055387339</v>
+      </c>
+      <c r="T23" t="n">
+        <v>-1.46911340857164</v>
+      </c>
+      <c r="U23" t="n">
+        <v>-0.8950008135020797</v>
+      </c>
+      <c r="V23" t="n">
+        <v>-0.1470935491468847</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0.2970142124347265</v>
+      </c>
+      <c r="X23" t="n">
+        <v>-0.2609187105353131</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0.8016431720162335</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-0.6733280722063718</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-0.1662386772451152</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>dCNk2A2b</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1.849817892667333</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.7168606750380806</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-0.2942303909457018</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.297200540149592</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-0.1105836441224053</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-0.9805787268653793</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-0.2234871899330499</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-0.2575681115029471</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-0.7380657395056173</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-0.6068733390399711</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-2.053042467554977</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-0.1912109069972341</v>
+      </c>
+      <c r="O24" t="n">
+        <v>-0.4817370808617911</v>
+      </c>
+      <c r="P24" t="n">
+        <v>-0.8181018736731009</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.06225948759549538</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.435231328214966</v>
+      </c>
+      <c r="S24" t="n">
+        <v>-0.479840300114474</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0.06598445314415635</v>
+      </c>
+      <c r="U24" t="n">
+        <v>-1.216166346436427</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0.2837116378467662</v>
+      </c>
+      <c r="W24" t="n">
+        <v>-0.09438016374574737</v>
+      </c>
+      <c r="X24" t="n">
+        <v>-0.1129708472877459</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>-0.1350118322120429</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-0.637472689917992</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>6.015447286827976</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>ImLNuMV7</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1.879628070527517</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.3413892579673929</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-0.1172445342958035</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-0.5293822358731616</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.13354679493771</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-0.9805787268653793</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-0.2234871899330499</v>
+      </c>
+      <c r="I25" t="n">
+        <v>4.947811711999903</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.054562467092063</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-0.001826621254097982</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-1.192485179356536</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-2.231747800376521</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0.8099473928244254</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.8284891688031573</v>
+      </c>
+      <c r="P25" t="n">
+        <v>-0.9139726046441022</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-0.9162899860110088</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.4396423227945328</v>
+      </c>
+      <c r="S25" t="n">
+        <v>-1.956407718308318</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.4965560675275</v>
+      </c>
+      <c r="U25" t="n">
+        <v>-1.858497412305123</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>2.061916538231271</v>
+      </c>
+      <c r="X25" t="n">
+        <v>2.658325418669515</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>-1.221415054233189</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-0.2939181318625825</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-0.1662386772451152</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>xWrPG9Hi</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1.760387359086781</v>
+      </c>
+      <c r="C26" t="n">
+        <v>-0.893714087659869</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1.235433084385562</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-0.9595426601299006</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.78265832836038</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-0.9805787268653793</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-0.2234871899330499</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.01639924762878189</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-0.9513654605594664</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-0.001826621254097982</v>
+      </c>
+      <c r="L26" t="n">
+        <v>2.125981915770664</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-0.4223563055583839</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-1.192369206818894</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-1.26787283066076</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0.2364761670079138</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-0.3571188582358635</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.022426130845518</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.1566111732449417</v>
+      </c>
+      <c r="T26" t="n">
+        <v>-0.701564477713742</v>
+      </c>
+      <c r="U26" t="n">
+        <v>-0.482073699729347</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0.8889559496984945</v>
+      </c>
+      <c r="W26" t="n">
+        <v>-1.022837600963748</v>
+      </c>
+      <c r="X26" t="n">
+        <v>-0.8723354744089766</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>-0.3082462727460765</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-0.4187827647102994</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-0.1662386772451152</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>4b2YCRGG</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1.820007714807149</v>
+      </c>
+      <c r="C27" t="n">
+        <v>-0.8146674735397244</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-0.4712162475956001</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-1.634304109944393</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-0.7164210753168965</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-0.9805787268653793</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-0.2234871899330499</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.01639924762878189</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.05159850326629842</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-0.001826621254097982</v>
+      </c>
+      <c r="L27" t="n">
+        <v>-0.8020772858121596</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-0.6904143047907007</v>
+      </c>
+      <c r="N27" t="n">
+        <v>1.310526542735255</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.3043986689371779</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0.2364761670079138</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0.6913270063425337</v>
+      </c>
+      <c r="R27" t="n">
+        <v>-0.6530773173010637</v>
+      </c>
+      <c r="S27" t="n">
+        <v>1.735010827176293</v>
+      </c>
+      <c r="T27" t="n">
+        <v>-1.213263764952341</v>
+      </c>
+      <c r="U27" t="n">
+        <v>-0.8950008135020797</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>-0.2351897178408075</v>
+      </c>
+      <c r="X27" t="n">
+        <v>-0.02358185198010324</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>-0.2344886859177678</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0.07308391150576897</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-0.1662386772451152</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>dYbQEmn4</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1.939248426247886</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1.91244071360527</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.9952379932178427</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1.781675729741476</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1.166002371608844</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-0.9805787268653793</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-0.2234871899330499</v>
+      </c>
+      <c r="I28" t="n">
+        <v>-0.805502829766405</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.054562467092063</v>
+      </c>
+      <c r="K28" t="n">
+        <v>-0.7380657395056173</v>
+      </c>
+      <c r="L28" t="n">
+        <v>-1.543852283546474</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.1137596929062495</v>
+      </c>
+      <c r="N28" t="n">
+        <v>-0.6917900569080639</v>
+      </c>
+      <c r="O28" t="n">
+        <v>-0.2196918309288014</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.537373710311946</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>-0.4969116401796498</v>
+      </c>
+      <c r="R28" t="n">
+        <v>-0.07029350925007891</v>
+      </c>
+      <c r="S28" t="n">
+        <v>1.0731012948825</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0.06598445314415635</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.444919497876739</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0.6929745881712476</v>
+      </c>
+      <c r="W28" t="n">
+        <v>-0.7607511543587331</v>
+      </c>
+      <c r="X28" t="n">
+        <v>-0.8038748758161437</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0.3333660045974889</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0.3358387599138035</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-0.1662386772451152</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>IRBb0lXA</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1.939248426247886</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.9243580371034607</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.9067450648928936</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.2803315039042297</v>
+      </c>
+      <c r="F29" t="n">
+        <v>-1.419625236524788</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-0.9805787268653793</v>
+      </c>
+      <c r="H29" t="n">
+        <v>-0.2234871899330499</v>
+      </c>
+      <c r="I29" t="n">
+        <v>-0.805502829766405</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.5530804851791808</v>
+      </c>
+      <c r="K29" t="n">
+        <v>-0.001826621254097982</v>
+      </c>
+      <c r="L29" t="n">
+        <v>2.125981915770664</v>
+      </c>
+      <c r="M29" t="n">
         <v>-0.1542983063260672</v>
       </c>
-      <c r="N7" t="n">
-        <v>0.5596578178690105</v>
-      </c>
-      <c r="O7" t="n">
-        <v>2.400760668401095</v>
-      </c>
-      <c r="P7" t="n">
+      <c r="N29" t="n">
+        <v>0.8099473928244254</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.090534418736147</v>
+      </c>
+      <c r="P29" t="n">
+        <v>-0.05113602590509021</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.4117414424549611</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0.4396423227945328</v>
+      </c>
+      <c r="S29" t="n">
+        <v>1.22584964848876</v>
+      </c>
+      <c r="T29" t="n">
+        <v>-0.9574141213330414</v>
+      </c>
+      <c r="U29" t="n">
+        <v>-0.482073699729347</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0.491936561617507</v>
+      </c>
+      <c r="W29" t="n">
+        <v>-0.9670991463874381</v>
+      </c>
+      <c r="X29" t="n">
+        <v>-1.169439385155165</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>-0.3549375707046548</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-0.6790710061448948</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>-0.1662386772451152</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>xjut9IFr</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1.760387359086781</v>
+      </c>
+      <c r="C30" t="n">
+        <v>-0.2119370408736204</v>
+      </c>
+      <c r="D30" t="n">
+        <v>-0.5217836352098567</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.2044208408000993</v>
+      </c>
+      <c r="F30" t="n">
+        <v>-0.7164210753168965</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-0.9805787268653793</v>
+      </c>
+      <c r="H30" t="n">
+        <v>-0.2234871899330499</v>
+      </c>
+      <c r="I30" t="n">
+        <v>-0.1205844319370826</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>-0.001826621254097982</v>
+      </c>
+      <c r="L30" t="n">
+        <v>-0.0212614987234063</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.5158466917547246</v>
+      </c>
+      <c r="N30" t="n">
+        <v>-0.441500481952649</v>
+      </c>
+      <c r="O30" t="n">
+        <v>-0.7437823307947806</v>
+      </c>
+      <c r="P30" t="n">
         <v>-0.3387482188180942</v>
       </c>
-      <c r="Q7" t="n">
-        <v>-1.475461113786154</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.31381803487101</v>
-      </c>
-      <c r="S7" t="n">
-        <v>-1.294498186014526</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.473157493050303</v>
-      </c>
-      <c r="U7" t="n">
-        <v>-0.3444313284717694</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0.7456925620345022</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0.8236828710970533</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0.7872606230756608</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>-0.2093470597389521</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0.7026630009917714</v>
-      </c>
-      <c r="AA7" t="n">
+      <c r="Q30" t="n">
+        <v>0.2719486605111748</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.022426130845518</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0.02932087857305853</v>
+      </c>
+      <c r="T30" t="n">
+        <v>-0.3177900122847928</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0.2061381565585409</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0.5993841023655058</v>
+      </c>
+      <c r="W30" t="n">
+        <v>-0.9258333449956175</v>
+      </c>
+      <c r="X30" t="n">
+        <v>-0.5084893502950626</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>-0.5109623435641335</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0.4313345501856132</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>-0.1662386772451152</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>8b5vHIeT</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1.879628070527517</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1.606135083889709</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.6918336675323028</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.2044208408000993</v>
+      </c>
+      <c r="F31" t="n">
+        <v>-1.419625236524788</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-0.9805787268653793</v>
+      </c>
+      <c r="H31" t="n">
+        <v>-0.2234871899330499</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.4273502863263753</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.5530804851791808</v>
+      </c>
+      <c r="K31" t="n">
+        <v>-0.001826621254097982</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1.540370075454099</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.342358856054368</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0.7265175345059537</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0.7411407521588274</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0.3323468979789151</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>-0.1008320913389221</v>
+      </c>
+      <c r="R31" t="n">
+        <v>-0.8716212453201835</v>
+      </c>
+      <c r="S31" t="n">
+        <v>-0.929599341288461</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0.7482501694622882</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0.664946060750466</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0.7617879426323803</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.267315652399323</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1.501265037378084</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0.3419481891515813</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0.1717539742714783</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>-0.1662386772451152</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>AyPaTn1c</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>1.790197536946965</v>
+      </c>
+      <c r="C32" t="n">
+        <v>-1.269185504730557</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.9952379932178427</v>
+      </c>
+      <c r="E32" t="n">
+        <v>-0.3606918734195383</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1.166002371608844</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-0.9805787268653793</v>
+      </c>
+      <c r="H32" t="n">
+        <v>-0.2234871899330499</v>
+      </c>
+      <c r="I32" t="n">
+        <v>-0.9424865093322694</v>
+      </c>
+      <c r="J32" t="n">
+        <v>-2.455811406298114</v>
+      </c>
+      <c r="K32" t="n">
+        <v>-0.001826621254097982</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1.345166128681912</v>
+      </c>
+      <c r="M32" t="n">
+        <v>-0.1945070062109143</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0.2593103279225126</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0.04235341900418825</v>
+      </c>
+      <c r="P32" t="n">
+        <v>-0.5113155345658965</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>-0.7904764822616008</v>
+      </c>
+      <c r="R32" t="n">
+        <v>-1.396126672566069</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0.9305361648499912</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0.7823634552781946</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0.04096731104944789</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0.6535626562207685</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0.1898774501830488</v>
+      </c>
+      <c r="X32" t="n">
+        <v>-0.5811361251344132</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0.7594148573705102</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>1.162579253712399</v>
+      </c>
+      <c r="AA32" t="n">
         <v>-0.1662386772451152</v>
       </c>
     </row>

--- a/data/spain/p6_deployment/data_preparation/df_selected_nan.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_selected_nan.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA7"/>
+  <dimension ref="A1:BV30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,95 +466,330 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>h2h_35</t>
+          <t>dif_mean_last_60_matches_expected_points</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>h2h_3</t>
+          <t>dif_mean_last_60_matches_expected_points_against</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_n_matches_last_days</t>
+          <t>dif_mean_last_180_matches_expected_points</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_n_matches_last_days_against</t>
+          <t>dif_mean_last_180_matches_expected_points_against</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_goal_attempts_against</t>
+          <t>dif_mean_last_60_matches_shots_on_goal</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_points</t>
+          <t>dif_mean_last_60_matches_shots_on_goal_against</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_goals</t>
+          <t>dif_mean_last_180_matches_shots_on_goal</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_goals_against</t>
+          <t>dif_mean_last_180_matches_shots_on_goal_against</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_fouls</t>
+          <t>dif_mean_last_60_matches_goal_attempts</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_fouls_against</t>
+          <t>dif_mean_last_60_matches_goal_attempts_against</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_ball_possession_against</t>
+          <t>dif_mean_last_180_matches_goal_attempts</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_shots_on_goal</t>
+          <t>dif_mean_last_180_matches_goal_attempts_against</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_shots_on_goal_against</t>
+          <t>dif_mean_last_60_matches_goals</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>mean_last_match_mean_rat_player_start_away_against</t>
+          <t>dif_mean_last_60_matches_goals_against</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_180_matches_goals</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_goals_against</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_points</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_points_against</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_points</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_points_against</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_goal_ratio</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_goal_ratio_against</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_goal_ratio</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_goal_ratio_against</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_attacks</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_attacks_against</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_attacks</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_attacks_against</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_dangerous_attacks</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_dangerous_attacks_against</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_dangerous_attacks</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_dangerous_attacks_against</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_dead_balls</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_dead_balls_against</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_dead_balls</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_dead_balls_against</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_ball_possession</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_ball_possession_against</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_ball_possession</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_ball_possession_against</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_yellow_cards</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_yellow_cards_against</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_yellow_cards</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_yellow_cards_against</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_red_cards</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_red_cards_against</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_red_cards</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_red_cards_against</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_defensive_actions</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_defensive_actions_against</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_defensive_actions</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_defensive_actions_against</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_KGP</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_KGP_against</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_KGP</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_KGP_against</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_clean_sheet</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_clean_sheet_against</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_clean_sheet</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_clean_sheet_against</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>mean_last_180_matches_mean_rat_player_start_home_against</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>mean_last_180_matches_mean_rat_player_start_away_against</t>
+        </is>
+      </c>
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_rat_player_sub</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_hei_player_sub</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_age_player_sub</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>is_rival_match</t>
         </is>
@@ -563,511 +798,6555 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>AyPaTn1c</t>
+          <t>CvbDaBsg</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.760387359086781</v>
+        <v>1.726288768371042</v>
       </c>
       <c r="C2" t="n">
-        <v>-1.269185504730557</v>
+        <v>1.00109687296112</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9952379932178427</v>
+        <v>1.029731353381095</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.3606918734195383</v>
+        <v>-0.2442691251257562</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.5433246664041846</v>
+        <v>-0.9107289017826093</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.9805787268653793</v>
+        <v>-1.075864642027034</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.2234871899330499</v>
+        <v>-0.2426890271087325</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.9424865093322694</v>
+        <v>-4.500280948701362</v>
       </c>
       <c r="J2" t="n">
-        <v>-2.455811406298114</v>
+        <v>2.328731485670523</v>
       </c>
       <c r="K2" t="n">
-        <v>0.7344124969974213</v>
+        <v>-7.305220724911038</v>
       </c>
       <c r="L2" t="n">
-        <v>2.711593756087229</v>
+        <v>6.289342890217291</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.073880906556372</v>
+        <v>-1.248551111902612</v>
       </c>
       <c r="N2" t="n">
-        <v>0.05907866795818074</v>
+        <v>0.9679230342969772</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.1148737309556056</v>
+        <v>-0.9311668062301615</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.2812257802354933</v>
+        <v>0.8412639619557208</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.014144933371659</v>
+        <v>-0.9420934067646739</v>
       </c>
       <c r="R2" t="n">
-        <v>-1.774936147799209</v>
+        <v>1.162551897865014</v>
       </c>
       <c r="S2" t="n">
-        <v>1.134200636325004</v>
+        <v>-1.083315528869484</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7311935265543347</v>
+        <v>0.6271072567102369</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4263659505706652</v>
+        <v>-1.554109941698167</v>
       </c>
       <c r="V2" t="n">
-        <v>0.03677079858382917</v>
+        <v>0.6881144237174461</v>
       </c>
       <c r="W2" t="n">
-        <v>0.1998674295234754</v>
+        <v>-1.689200921571108</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.6692010649306898</v>
+        <v>0.4339871539144249</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.7014776991883891</v>
+        <v>-1.180136671197523</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.178586310130842</v>
+        <v>1.513604278138559</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0.1662386772451152</v>
+        <v>-1.574507063565001</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.613591339426504</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>-0.1462403712923664</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>-0.6521772194143276</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.5153998532583212</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>-0.2639324130048224</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.06233227739979475</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>-1.740443820595297</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.7493512043316359</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>-1.650596077970946</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>-0.2685148174945253</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>-0.2938954550850308</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0.1084916974913391</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>-1.006689897410518</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>2.105192987700333</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1.805258667833191</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>1.577995479425412</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>1.579197590807515</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>0.8304733032861441</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>-0.8305640964386827</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>0.5200438155245927</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>-0.5201665107494807</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>1.352957207622586</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0.2608855156935493</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>0.6521339605130126</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>-0.08006249331958859</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>-0.7730130989283042</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>0.7601876498453485</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>1.093005185231473</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>1.438584351091683</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>0.8614738834288282</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>0.5390063756662093</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>0.7378211499262369</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>-1.199302906456688</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>1.470752135126084</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>-1.480100993929798</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>-0.4212037850277991</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>1.316189903460199</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>-0.6983740810435184</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>1.751333427001665</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>0.7920657392790454</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>1.14429867612721</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>-1.503821171740739</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>0.02643586651482573</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>-0.857896188956897</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>-0.1632674400202885</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>fVeJ32M5</t>
+          <t>YgnMckC5</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.879628070527517</v>
+        <v>1.726288768371042</v>
       </c>
       <c r="C3" t="n">
-        <v>-1.032045662370122</v>
+        <v>0.8628195559282473</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.7619787263775758</v>
+        <v>1.62296357805945</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2803315039042297</v>
+        <v>1.128073981885582</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2031535970318848</v>
+        <v>-1.406436653606188</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.9805787268653793</v>
+        <v>-1.075864642027034</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.2234871899330499</v>
+        <v>-0.2426890271087325</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01639924762878189</v>
+        <v>-5.254216831647605</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.9513654605594664</v>
+        <v>3.897149002966561</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.001826621254097982</v>
+        <v>-2.80488398208558</v>
       </c>
       <c r="L3" t="n">
-        <v>1.930777968998476</v>
+        <v>2.282394614237646</v>
       </c>
       <c r="M3" t="n">
-        <v>0.649875691370883</v>
+        <v>0.6224448339411501</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.9420796318634789</v>
+        <v>0.8185762018608566</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.3070402475731312</v>
+        <v>-0.2985690052716051</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.9139726046441022</v>
+        <v>0.8368571744820037</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.48348610402399</v>
+        <v>-0.3600230986599166</v>
       </c>
       <c r="R3" t="n">
-        <v>1.289535376202219</v>
+        <v>0.06302043987926038</v>
       </c>
       <c r="S3" t="n">
-        <v>0.08872301608660424</v>
+        <v>-0.5168306118820648</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4497589185731055</v>
+        <v>0.5094681837677739</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1602573661393483</v>
+        <v>-0.1814004597691522</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5750235263254728</v>
+        <v>0.7360852890471727</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5897272334203767</v>
+        <v>-0.2705571559342115</v>
       </c>
       <c r="X3" t="n">
-        <v>0.3509383883535987</v>
+        <v>0.5831354122114268</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.2567125727852079</v>
+        <v>-0.5706040384437669</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.195362735802936</v>
+        <v>0.7370865385965407</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0.1662386772451152</v>
+        <v>-0.9380525552823665</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.287214103087997</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>-0.2531073031266035</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>-0.03425758315565623</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>-0.187145070508528</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>-0.3537080364823985</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>-0.04531784451651812</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>-0.6735520295075437</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>-0.1863435098156025</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>-0.5708621159302854</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>-0.5897120858211243</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>-1.636877510288522</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>-0.6063940875376717</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>-0.559826322317638</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0.9560097637492823</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1.229059517464755</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0.1607731406922727</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0.554292260790507</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>0.3493170456509294</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>-0.3493416597014023</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>-0.03537731780852533</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0.03530867702636992</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0.641732918406556</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>0.371440634501249</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>1.428771617689573</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>-0.01069321126883072</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>1.590162172286133</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>-1.55630480654459</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>1.508641836265826</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>-1.488443076113538</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>0.4086065201839735</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>0.214053581103566</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>0.2517957912443757</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>-0.125537238857957</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>1.378442723663242</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>0.0911609309648472</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>0.203836577534718</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>0.2400320552150981</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>0.02996751381211523</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>-0.03102768165429799</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>0.01469586498536652</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>-0.01822268719146627</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>0.7310962239765085</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>0.9236250656793045</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>-0.1071583857752074</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>-0.07368892727932114</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>0.4620297714635739</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>6.124919946535174</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>SdHeBgOE</t>
+          <t>hzRnqjcC</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.849817892667333</v>
+        <v>1.726288768371042</v>
       </c>
       <c r="C4" t="n">
-        <v>1.042927958283678</v>
+        <v>0.9220812632280497</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.8757553485096533</v>
+        <v>0.03259633743237113</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.7402451889401905</v>
+        <v>1.128073981885582</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3377726808203395</v>
+        <v>1.772558711349371</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.9805787268653793</v>
+        <v>-1.075864642027034</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.2234871899330499</v>
+        <v>-0.2426890271087325</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5643339658922398</v>
+        <v>-3.746345065755119</v>
       </c>
       <c r="J4" t="n">
-        <v>1.556044449004946</v>
+        <v>3.112940244318542</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.001826621254097982</v>
+        <v>-1.679799796379216</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7595542883653463</v>
+        <v>1.709973431954839</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.6904143047907007</v>
+        <v>-2.37809974793832</v>
       </c>
       <c r="N4" t="n">
-        <v>1.811105692646085</v>
+        <v>0.3959564419884305</v>
       </c>
       <c r="O4" t="n">
-        <v>0.8284891688031573</v>
+        <v>-1.867205828786723</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.48919699047011</v>
+        <v>-0.08856819499869641</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.566808031151543</v>
+        <v>-1.985704312710072</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.5073813652883176</v>
+        <v>0.4631235422379613</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3525500054425909</v>
+        <v>-1.756868535056955</v>
       </c>
       <c r="T4" t="n">
-        <v>1.089383027621354</v>
+        <v>0.3754489867447163</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.44557029853239</v>
+        <v>-2.743791492703313</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.4482600970688121</v>
       </c>
       <c r="W4" t="n">
-        <v>2.203421807440068</v>
+        <v>-2.59145326264269</v>
       </c>
       <c r="X4" t="n">
-        <v>1.803933296710242</v>
+        <v>0.2848388956174229</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.2057876252748363</v>
+        <v>-1.180136671197523</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.6806172007120584</v>
+        <v>1.047693634413348</v>
       </c>
       <c r="AA4" t="n">
-        <v>-0.1662386772451152</v>
+        <v>-1.256279809423684</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.9608368667494901</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>2.002858020293063</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>-1.644522435882081</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.747097865125824</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>-1.694777113660417</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>-1.008075538635988</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.914494073092046</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>-2.101048424234339</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>2.16037401986802</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>-0.431746216152305</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>-0.5910659524066538</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>-0.5347519902548785</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0.9413107198231654</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>-0.4911098515964849</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.990465537594474</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>-0.07924031989962983</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1.810627826617808</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>-2.54407897341721</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>2.544452322289225</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>-2.923447249772846</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>2.923659680418075</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0.473537985146009</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>-0.8597413704026732</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>0.9035220581589918</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0.4545885585838103</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>-0.8061690805030673</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>0.8047562165610213</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>-0.392737276395949</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>0.3854158621855339</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>0.8441329433960184</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>-0.005733992996865275</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>0.6243768475793189</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>0.4197293166490513</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>1.868675370507984</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>-1.224700299853531</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>-0.5961521628204405</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>-1.208647007667445</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>0.4811388126520296</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>0.418044846717201</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>0.371230837999809</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>1.043510981324413</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>1.093891351101723</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>0.6385912377369708</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>-0.05600035921724018</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>-0.5711944707931651</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>1.038009005412862</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>-0.1632674400202885</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>dzUhmsxP</t>
+          <t>4Ef51XCt</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.820007714807149</v>
+        <v>1.726288768371042</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.4886001902941271</v>
+        <v>1.238143702160329</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.5217836352098567</v>
+        <v>-0.5227700005643867</v>
       </c>
       <c r="E5" t="n">
-        <v>1.123783316172346</v>
+        <v>0.5303048984634655</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.9219730609007416</v>
+        <v>0.2100016675576556</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.9805787268653793</v>
+        <v>-1.075864642027034</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.2234871899330499</v>
+        <v>-0.2426890271087325</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1205844319370826</v>
+        <v>1.531206114868578</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.9513654605594664</v>
+        <v>-0.8081035489215523</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7344124969974213</v>
+        <v>2.25799485359306</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.0212614987234063</v>
+        <v>-2.869396026307612</v>
       </c>
       <c r="M5" t="n">
-        <v>2.325238186572863</v>
+        <v>0.1271812012178015</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.441500481952649</v>
+        <v>0.7454915817325423</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3917470855815078</v>
+        <v>0.8480502247404468</v>
       </c>
       <c r="P5" t="n">
-        <v>0.8117005528339217</v>
+        <v>1.193806959853131</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.5901068281421742</v>
+        <v>0.454287382880577</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9738608135079357</v>
+        <v>0.5383308923053867</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.065375655605137</v>
+        <v>0.8253956216285333</v>
       </c>
       <c r="T5" t="n">
-        <v>1.43051588578042</v>
+        <v>0.4606256319638152</v>
       </c>
       <c r="U5" t="n">
-        <v>1.811965821230279</v>
+        <v>-0.2729144252310866</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5993841023655058</v>
+        <v>0.9279687503660803</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.2985570006685368</v>
+        <v>1.315547700529663</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.4870710015606541</v>
+        <v>0.7422268877282286</v>
       </c>
       <c r="Y5" t="n">
-        <v>-1.604569220076344</v>
+        <v>-0.7229871966322058</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.2345943499333683</v>
+        <v>0.5817829906881371</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.1662386772451152</v>
+        <v>-0.08944654423885377</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.1992899819596404</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-1.25372646058424</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.1546621923604579</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>-1.803347865635365</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>-0.4413559584056523</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>-0.9837019261266349</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>-1.386202405585692</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>-1.140888481813213</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>-1.343853475118485</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0.8635739151320134</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>-0.1795991099613292</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0.2748037090406791</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>-0.1946848796347393</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>-1.44876253822236</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>-2.10466413823834</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>-1.462175021405354</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>-1.73796912247334</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>1.182998301889127</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>-1.183137581967676</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0.9507051262515671</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>-0.9508697341005178</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>-0.6077151572432249</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0.07997713946276958</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>-0.7380788040156889</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0.9779600524301756</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>-1.604946164766134</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>1.591776557596225</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>-2.294116389057725</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>1.509731225164977</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>-1.05351790059932</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>-0.6650967152981589</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>-1.17078642385268</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>-0.2788934575943031</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>0.4237383373097746</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>-0.3542223448855308</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>0.1569363623185074</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>0.8236887464121632</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>0.02996751381211523</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>0.418044846717201</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>-0.341839108029076</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>0.6895997584857863</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>0.9208633935397683</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>0.6613377248045036</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>0.09016800165222891</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>-0.9192806616335983</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>0.3344315520490536</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>-0.1632674400202885</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>na927pNt</t>
+          <t>CQIvoCSa</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.760387359086781</v>
+        <v>1.726288768371042</v>
       </c>
       <c r="C6" t="n">
-        <v>1.24054449358404</v>
+        <v>0.3393411414466596</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03445762854696641</v>
+        <v>1.118085088971489</v>
       </c>
       <c r="E6" t="n">
-        <v>0.297200540149592</v>
+        <v>1.144912547615783</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2620430019210281</v>
+        <v>1.772558711349371</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.9805787268653793</v>
+        <v>-1.075864642027034</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.2234871899330499</v>
+        <v>-0.2426890271087325</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2575681115029471</v>
+        <v>5.300885529599791</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5530804851791808</v>
+        <v>-3.944938583513628</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.7380657395056173</v>
+        <v>5.633247410712153</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.192485179356536</v>
+        <v>-4.586659573156032</v>
       </c>
       <c r="M6" t="n">
-        <v>0.5381848583574178</v>
+        <v>2.284908723901399</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.9420796318634789</v>
+        <v>-3.05173107276031</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.26787283066076</v>
+        <v>2.534406241568539</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2364761670079138</v>
+        <v>-2.402131618700445</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.3884426454643299</v>
+        <v>2.129944330454879</v>
       </c>
       <c r="R6" t="n">
-        <v>-1.551535688046332</v>
+        <v>-1.905907984885927</v>
       </c>
       <c r="S6" t="n">
-        <v>0.9458110002106171</v>
+        <v>1.12578906760134</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.127980550412574</v>
+        <v>-2.063700399074938</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7108268511696585</v>
+        <v>0.2456647123865411</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.04249774249881632</v>
+        <v>-2.429991822714797</v>
       </c>
       <c r="W6" t="n">
-        <v>0.6696453327415574</v>
+        <v>0.6367890586226004</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.4253540532857122</v>
+        <v>-2.399829753728609</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.4742005760529463</v>
+        <v>0.4960780688753054</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.378262854816724</v>
+        <v>-0.5053418446706883</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.1662386772451152</v>
+        <v>0.8652352181850981</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-0.7798417270558806</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-0.930687599541449</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.2953454612279971</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>-0.1889085493493453</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>-0.4261834044557116</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>3.074504556680753</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>-2.111355419840649</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>2.082104541284602</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>-1.464096575436651</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>3.011909742627956</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>-0.6767882112494299</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1.836601429805561</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>-0.7464541708000079</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0.5303863474711155</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>-0.8493731320785329</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0.8236674604222893</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>-0.404490144709275</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>2.259410511363881</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>-2.259697843124903</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>1.836020021283621</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>-1.836270789345826</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>-2.385775880283297</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>-1.21150765751808</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>-2.357728938329389</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>-1.744925262537766</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0.791385088023066</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>-0.7692844655093862</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0.7480901912011164</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>-0.7388995007939092</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0.4086065201839735</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>-0.03713221786835545</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>-0.2223982804546429</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>0.2663730979127052</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>-0.7503872292558712</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>-2.186430780912677</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>-1.074466386391874</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>-1.111566432251469</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>1.383481410331858</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>-0.03102768165429799</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>2.510440676086464</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>0.33568853564716</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>0.7656388144507646</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>0.7349504691133101</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>1.051118221734035</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>-0.9741978686652311</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>-0.2140503588915135</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>-0.1632674400202885</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>SfxxiPx0</t>
+          <t>EB22wLQj</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.760387359086781</v>
+        <v>1.726288768371042</v>
       </c>
       <c r="C7" t="n">
-        <v>-1.012284008840086</v>
+        <v>1.909776384891423</v>
       </c>
       <c r="D7" t="n">
-        <v>1.930734664081591</v>
+        <v>-1.027648489652348</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.533089892472219</v>
+        <v>-0.2442691251257562</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2620430019210281</v>
+        <v>-0.9107289017826093</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.9805787268653793</v>
+        <v>-1.075864642027034</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2234871899330499</v>
+        <v>-0.2426890271087325</v>
       </c>
       <c r="I7" t="n">
-        <v>1.386236043287427</v>
+        <v>-2.992409182808877</v>
       </c>
       <c r="J7" t="n">
-        <v>0.05159850326629842</v>
+        <v>3.897149002966561</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.001826621254097982</v>
+        <v>-2.242341889232398</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.0212614987234063</v>
+        <v>2.854815796520452</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1542983063260672</v>
+        <v>-1.161662755284481</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5596578178690105</v>
+        <v>1.174466525963953</v>
       </c>
       <c r="O7" t="n">
-        <v>2.400760668401095</v>
+        <v>-0.7528736590765301</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.3387482188180942</v>
+        <v>0.9029589865877677</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.475461113786154</v>
+        <v>-0.6995641117210248</v>
       </c>
       <c r="R7" t="n">
-        <v>1.31381803487101</v>
+        <v>0.7789944125211471</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.294498186014526</v>
+        <v>-0.9172595245739571</v>
       </c>
       <c r="T7" t="n">
-        <v>1.473157493050303</v>
+        <v>0.5496739428746918</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3444313284717694</v>
+        <v>-1.249063390158386</v>
       </c>
       <c r="V7" t="n">
-        <v>0.7456925620345022</v>
+        <v>1.407677403663348</v>
       </c>
       <c r="W7" t="n">
-        <v>0.8236828710970533</v>
+        <v>0.1401363938125565</v>
       </c>
       <c r="X7" t="n">
-        <v>0.7872606230756608</v>
+        <v>0.1356906373204217</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.2093470597389521</v>
+        <v>-0.4182208802553281</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.7026630009917714</v>
+        <v>0.4264794427797335</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0.1662386772451152</v>
+        <v>0.6530837154242198</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>-0.6710493149430449</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.002782697466697</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>-0.1783827050626816</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.4702565368103523</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>-0.04733797428325461</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>-1.020262344890664</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.7642513608255627</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>-0.3098728591329395</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.0704344190999248</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.405472893092437</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.1118565701041092</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>-0.6135582972659506</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0.1947993258936853</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>-0.4485475099686682</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>-1.425572282446969</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>-0.7307054272205082</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>-0.52571550632419</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>-0.8298925298286645</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0.8300301063963411</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>-0.1523396515017838</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0.1522823936746315</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>-0.1656027612440714</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0.7583835503281958</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0.1195674916954382</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0.9790880082358789</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>-1.381454414980072</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>1.359822510101051</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>-0.4002282657812528</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>-0.5395038158121983</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>-0.3917533060614353</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>-0.7389621138033412</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>1.084352934263935</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>-1.001309944189581</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>-0.5576915080458792</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>0.6223909805919066</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>0.932310111491944</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>1.316189903460199</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>1.797370730057579</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>-0.7260451328687189</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>-0.1327612022768098</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>0.7153075906058464</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>-0.9533031898426065</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>1.142099516272126</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>-1.276286268632089</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>-0.1632674400202885</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>KApUeTtI</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1.726288768371042</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-0.4903227607505739</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-1.015026527425149</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-1.524000120620992</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.2100016675576556</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-1.075864642027034</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-0.2426890271087325</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-4.500280948701362</v>
+      </c>
+      <c r="J8" t="n">
+        <v>4.68135776161458</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-7.305220724911038</v>
+      </c>
+      <c r="L8" t="n">
+        <v>6.289342890217291</v>
+      </c>
+      <c r="M8" t="n">
+        <v>-0.04659551201846147</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.06230926314177792</v>
+      </c>
+      <c r="O8" t="n">
+        <v>-0.7528736590765305</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.3080426776358898</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.07212000887240334</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.8316395575683444</v>
+      </c>
+      <c r="S8" t="n">
+        <v>-0.5254419863485578</v>
+      </c>
+      <c r="T8" t="n">
+        <v>-0.08915089626855116</v>
+      </c>
+      <c r="U8" t="n">
+        <v>-1.462595976236233</v>
+      </c>
+      <c r="V8" t="n">
+        <v>-0.2713028828770899</v>
+      </c>
+      <c r="W8" t="n">
+        <v>-2.094800597832645</v>
+      </c>
+      <c r="X8" t="n">
+        <v>-0.01345762097658052</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>-1.027753513009084</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.7370865385965407</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>-1.786658566325879</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.396006515200833</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.6296856317153834</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>-1.676638436564525</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.1914215327911443</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>-0.9002287659685954</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.6615169182547389</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.1266168138082713</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.448148148041634</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>-0.5479586682506361</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>-0.02103495501337508</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.04327876302988858</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>-0.5132593610700411</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>-0.965539036409747</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0.3601369809598488</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0.3853393329966873</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1.155114620287298</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0.4000054369169789</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0.2061542217907872</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>-0.2061591449674911</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0.6933879921263969</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>-0.6935275574743407</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>-0.8720214809383707</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>-0.6838582268449701</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>-0.7271034400851989</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0.8098946373803729</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>-0.8061690805030673</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>0.8047562165610213</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>-0.01246145386359385</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>0.0106440745257196</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>0.1286252481190875</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>-0.1627251173543162</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>0.03163425795554563</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>-0.09145807913876898</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>0.4528129471205133</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>-1.535600431086755</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>1.484306151873538</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>-1.762003361127752</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>0.02996751381211523</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>0.418044846717201</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>0.371230837999809</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>1.397422204163039</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>0.8322547259868965</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>0.61032011131552</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>-0.1123707769229463</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>-0.7537036934914242</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>-0.3616385770403579</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>-0.1632674400202885</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>40FWnYcm</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.726288768371042</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.7146652876787414</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.7625872828811685</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-1.027262431580078</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.7488144412789369</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-1.075864642027034</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-0.2426890271087325</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-0.7306015339701493</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-0.8081035489215523</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-0.5547156106728512</v>
+      </c>
+      <c r="L9" t="n">
+        <v>-0.5797112971763864</v>
+      </c>
+      <c r="M9" t="n">
+        <v>-0.1479652614062814</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-0.4937693682693087</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.3614585106336625</v>
+      </c>
+      <c r="P9" t="n">
+        <v>-0.2207718192102249</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.101032169663641</v>
+      </c>
+      <c r="R9" t="n">
+        <v>-1.43210167946115</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.7899454634081401</v>
+      </c>
+      <c r="T9" t="n">
+        <v>-1.047388154983416</v>
+      </c>
+      <c r="U9" t="n">
+        <v>-1.035530804080539</v>
+      </c>
+      <c r="V9" t="n">
+        <v>-1.47057451612026</v>
+      </c>
+      <c r="W9" t="n">
+        <v>-1.101495268212555</v>
+      </c>
+      <c r="X9" t="n">
+        <v>-1.206643687352595</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>-0.8753703548206447</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.4264794427797335</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>-0.7259010525214884</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.5256672182981474</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-2.000071192070074</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.808073229386609</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>-1.121986553967723</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.606355841839619</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.4421544056705554</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.5267012354661793</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.06633015924258999</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>-0.2044069530558807</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0.2001172625229723</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>-0.6424993077123197</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>-0.678036184820464</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>-0.9411962735642202</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1.126259130260549</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1.126166812041819</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0.8922427348771187</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>1.435931254353525</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>-0.05756676953052789</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0.05759811901602999</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0.09058211847652298</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>-0.09066301782560476</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0.2717040652333517</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0.3362640057897081</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>1.224943430409049</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>1.072144362206408</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>-0.007391996240000759</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>0.01773587552581747</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>-0.5828751876621265</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>1.134959437505163</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0.9374600340843137</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>0.93621275314784</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>1.437280970491922</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>0.8286792332793075</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>-1.095465908728297</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>-0.8077539427627765</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>-0.03564513481387328</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>-0.4303294738077565</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>0.4811388126520296</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>0.8671173750887</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>0.7277658110142515</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>1.397422204163039</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>0.9070530595881656</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>0.6496527597698976</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>-0.1640243424917391</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>0.8925901678516441</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>-0.4426109626222284</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>-0.1632674400202885</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>0AJjqex0</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1.726288768371042</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-0.07549080965195716</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-1.292709696423528</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.144912547615783</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-0.5335599601777125</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-1.075864642027034</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0.2426890271087325</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.531206114868578</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-0.8081035489215523</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3.720604295011334</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-2.411459080481366</v>
+      </c>
+      <c r="M10" t="n">
+        <v>-0.5534442589575612</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1.396897978528388</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-0.7404921905241947</v>
+      </c>
+      <c r="P10" t="n">
+        <v>-0.1693592986835195</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-0.2879992474045296</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.516026443181913</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.09027128800564108</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.3754489867447163</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.4591972984643881</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.167823077014714</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.1677282085242255</v>
+      </c>
+      <c r="X10" t="n">
+        <v>-0.328326166270251</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>-0.1134545638784502</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0.2711758948713299</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.3772867618350781</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>-0.4969814555625077</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>-0.005616015136799792</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.049098293503416</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>-0.2774983809203277</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0.7066344521055979</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>-0.7541837416635537</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>-0.217205736053993</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>-0.08256092623138354</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>-0.6181365641346054</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>-1.440095017538269</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>-0.03101386130051674</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>-0.5597966225823084</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>-0.1824794047065906</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0.2750122977042154</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0.0972397578124693</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0.5493663626029721</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>-0.1025287894139416</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>-0.5850087521731573</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0.5851126469830713</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0.01460658547919252</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>-0.01468009077203301</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0.8099278516671037</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0.8990900651743584</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>1.096026457257264</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>1.652101638972225</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>1.508641836265827</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>-1.488443076113538</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>-0.08913796348693501</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>0.9676109780193302</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>0.5261509327273791</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>1.142207502695837</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>0.3726640003773616</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>2.248373030749256</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>-0.7952799106270132</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>0.9661363651587079</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>-0.8723750838677136</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>0.418044846717201</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>1.155607778631583</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>1.114293225892138</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>0.2353022563415614</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>0.9260727393364704</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>-0.7469396873795034</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>-0.1337501212603811</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>-0.3869175380814028</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>-0.1632674400202885</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>QmPfsURO</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1.726288768371042</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-0.2137681266848294</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.8761849429259599</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-1.027262431580078</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-1.611185507620275</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-1.075864642027034</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-0.2426890271087325</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.285141997814821</v>
+      </c>
+      <c r="J11" t="n">
+        <v>-4.729147342161647</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.945621132152607</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-4.586659573156032</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.09821841567842451</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-0.5890971336540667</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.1311631955602227</v>
+      </c>
+      <c r="P11" t="n">
+        <v>-1.926198571538942</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>-0.3320954828670113</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.1848563469884891</v>
+      </c>
+      <c r="S11" t="n">
+        <v>-0.2735592832036584</v>
+      </c>
+      <c r="T11" t="n">
+        <v>-1.091912310438854</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-0.3034190803850648</v>
+      </c>
+      <c r="V11" t="n">
+        <v>-0.7852764399813064</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.0325283164370468</v>
+      </c>
+      <c r="X11" t="n">
+        <v>-1.494996986726798</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.1913117524984276</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>-0.3500382967622847</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.9713109695655371</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>-1.323803787620059</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.09903760585054834</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.2216283637856084</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>-0.8328680198901071</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0.3987390722647484</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>-0.6059109322316519</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0.1391194519850811</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0.02702536627798184</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>-0.2330362626554428</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>-1.774456108337269</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1.586279422199857</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>-0.8356487988426081</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>-0.5030265423447425</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0.0409194187512236</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>2.257986571694105</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0.2864944771927931</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>1.568177103387978</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>-0.2943774556149739</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0.29444137647062</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>-0.02038214682220988</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0.02031204668684895</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0.08909242340761471</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>-0.8094890436719012</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0.7911552369658829</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0.3542004918762105</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>-0.01246145386359385</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>0.0106440745257196</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>1.093005185231473</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>1.030407427762311</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>0.7767963706254321</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>0.4538084763682393</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>-1.946411799664776</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>1.229564766816835</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>-0.853444045915856</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>0.2123792664842351</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>0.02996751381211523</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>0.8671173750887</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>0.371230837999809</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>0.6895997584857863</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>-0.1408525909269984</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>1.174168405891189</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>0.142594625907214</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>0.8390806066731785</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>0.5468211692917415</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>-0.1632674400202885</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>YJVCWCD6</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1.726288768371042</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.139374189993992</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.4722821516555906</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-0.3368812366418588</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.7488144412789369</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-1.075864642027034</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-0.2426890271087325</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.608257376220353</v>
+      </c>
+      <c r="J12" t="n">
+        <v>-2.712610534209599</v>
+      </c>
+      <c r="K12" t="n">
+        <v>5.40823057357088</v>
+      </c>
+      <c r="L12" t="n">
+        <v>-5.502533464808523</v>
+      </c>
+      <c r="M12" t="n">
+        <v>-0.1479652614062811</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.508113704810605</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.3614585106336629</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.365671671328118</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.7923585214262699</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.1472526719547761</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.601567506875039</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.565986186966214</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.099795056697928</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.2084057704201778</v>
+      </c>
+      <c r="W12" t="n">
+        <v>2.250910219255247</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-0.1626058792735822</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.606298221391074</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-1.636839122289057</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.392726038063421</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>-2.45524487359355</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0.1219292773228369</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.4034912603767494</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>-0.6686876337764396</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0.005691153392006011</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>-1.227438051220172</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0.414177491874893</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>-1.124043570542667</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0.8147964686885617</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>-0.2105939986159582</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1.209101483291643</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0.1028626755619766</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>1.939363996489753</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>-1.126504808754605</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>-0.311391272295759</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>-1.952107260010412</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>-0.4559190860004506</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>-1.752915999453265</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>1.753180530338663</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>-1.645858681738786</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>1.645946775490903</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>2.491877184272578</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0.7232069216166551</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>2.534147556403183</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0.7845156317520471</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0.791385088023066</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>-0.7692844655093862</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>0.7480901912011163</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>-0.7388995007939092</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>-0.1780209069995974</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>0.0256642318746249</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>0.3567959071205873</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>-0.008532123822078503</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>-1.51037441685365</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>1.435839536772741</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>-2.133544471550481</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>2.331882849106855</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>0.02996751381211523</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>-0.5442534283645826</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>0.3949998362007718</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>-2.283254513358675</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>0.7544095868607804</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>0.8448102713272514</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>0.4640015818170871</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>0.7718158975704784</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>0.1056354869829633</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>-0.1632674400202885</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>n37VJZT0</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1.726288768371042</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1.040604677827655</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.3102795064307501</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-1.625031515002195</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.285435455878635</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-1.075864642027034</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-0.2426890271087325</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-1.699947669186746</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.8723437910384881</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-2.392353113993246</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.213875073976407</v>
+      </c>
+      <c r="M13" t="n">
+        <v>-1.972620750387041</v>
+      </c>
+      <c r="N13" t="n">
+        <v>-0.2713379157048738</v>
+      </c>
+      <c r="O13" t="n">
+        <v>-2.535805130612839</v>
+      </c>
+      <c r="P13" t="n">
+        <v>-0.5512808797390463</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>-2.294377960947443</v>
+      </c>
+      <c r="R13" t="n">
+        <v>-0.0633279082340138</v>
+      </c>
+      <c r="S13" t="n">
+        <v>-1.616933699976455</v>
+      </c>
+      <c r="T13" t="n">
+        <v>-0.6699007500351366</v>
+      </c>
+      <c r="U13" t="n">
+        <v>-0.6084656319248455</v>
+      </c>
+      <c r="V13" t="n">
+        <v>-0.03144855622845609</v>
+      </c>
+      <c r="W13" t="n">
+        <v>-1.225658434415067</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.2848388956174229</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>-0.3093757672635858</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0.1380585680926982</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-0.4359606654149548</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.5619313556690926</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.074663330186449</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>-0.1272616526859948</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.449907732050071</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0.6503346772658007</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>-2.190195745339642</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>2.827186659999148</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>-1.921369370681847</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>2.068760229149419</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>-1.916625391039207</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>-0.1967435617298841</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>-1.552069771670535</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>-0.1216565910981604</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>-0.3239006523443485</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0.6058237017601197</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>-0.1234332745482977</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0.3786991612392059</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>-1.225474016810636</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>1.225666002371621</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>-1.16901224437396</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>1.169053930694142</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>-0.5019926277651664</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0.758383550328196</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0.4958656835979444</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>1.275176407233015</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>-0.01246145386359385</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>0.0106440745257196</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>-0.2135740844046621</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>-0.7278931650411393</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>0.3206668349911379</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>-0.2811654015755821</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>0.1951753107432104</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>0.9864243301260859</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>0.5672206193122714</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>0.5803714327989157</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>0.5455918553434459</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>0.4821980650559866</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>-0.3656081062300387</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>0.3592826171697351</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>0.9870877613899446</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>0.6427383419210194</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>0.1142707037561741</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>0.4525248988316147</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>0.5417065449609908</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>-0.1632674400202885</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>4rQsoH7m</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1.726288768371042</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1.603590897175777</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-0.1188672092940174</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.2103721495896566</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.285435455878635</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-1.075864642027034</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-0.2426890271087325</v>
+      </c>
+      <c r="I14" t="n">
+        <v>4.331539394383193</v>
+      </c>
+      <c r="J14" t="n">
+        <v>-3.60884911552162</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.4578601564628752</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-0.4652270607198254</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.007649881614867</v>
+      </c>
+      <c r="N14" t="n">
+        <v>-2.250977843528344</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.426164551328422</v>
+      </c>
+      <c r="P14" t="n">
+        <v>-0.07117298128665275</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.738957709354208</v>
+      </c>
+      <c r="R14" t="n">
+        <v>-2.295482058235189</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.130434677510894</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-0.623581834572781</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.03213212630869454</v>
+      </c>
+      <c r="V14" t="n">
+        <v>-1.038836728152719</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0.5508299435593241</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.4261372455830037</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.3872329558835634</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-0.7493902770981796</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.299497877489423</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>-0.3374192511303489</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>-0.0895122889053869</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.1362464521785502</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>-0.06807709708955222</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0.2892869534085858</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.270857230988581</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0.05160098474741438</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0.06321073122952565</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0.6716499206907461</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>2.237876981250741</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>-0.2653213688041052</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1.015901404266013</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0.6848101261360431</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>-0.05636593354092908</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>-1.134532915679239</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>-0.08685979483905489</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>-0.5352665954211226</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>1.68299177319015</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>-1.683199823275207</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0.6484024791674514</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>-0.6485376664557787</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>-0.3674366811567285</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>-0.1562087961718605</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>-1.284536397607441</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>-0.1162164451971332</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>-2.294116389057725</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>2.259274800484606</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>0.3197235766713111</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>-0.6920094794737222</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>-0.7361085247952466</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>-0.4356575923025677</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>-0.01241929032600616</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>-2.2741944519932</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>0.555232814361195</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>-0.4760004838103662</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>0.5455918553434459</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>-0.5442534283645826</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>-1.031140055856998</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>-1.05636227418477</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>1.035499591041764</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>0.1532836320179089</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>1.069212808140836</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>-0.06206501095550593</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>-0.3975955421812814</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>-0.1632674400202885</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>jyEMLeal</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1.726288768371042</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-0.55946141926701</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.903511731109105</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-0.7325875313015698</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.3069879668274862</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-1.075864642027034</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-0.2426890271087325</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.608257376220353</v>
+      </c>
+      <c r="J15" t="n">
+        <v>-2.712610534209599</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1.095407861696484</v>
+      </c>
+      <c r="L15" t="n">
+        <v>-0.7323569457851342</v>
+      </c>
+      <c r="M15" t="n">
+        <v>-0.9299604709694638</v>
+      </c>
+      <c r="N15" t="n">
+        <v>-0.9545202342956383</v>
+      </c>
+      <c r="O15" t="n">
+        <v>-0.3558928236172743</v>
+      </c>
+      <c r="P15" t="n">
+        <v>-1.402341710600761</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>-1.338959525927008</v>
+      </c>
+      <c r="R15" t="n">
+        <v>-0.559696418679019</v>
+      </c>
+      <c r="S15" t="n">
+        <v>-0.4204908600381831</v>
+      </c>
+      <c r="T15" t="n">
+        <v>-0.346858643877473</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.9777764360820159</v>
+      </c>
+      <c r="V15" t="n">
+        <v>-0.5111572095257242</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0.6367890586226012</v>
+      </c>
+      <c r="X15" t="n">
+        <v>-0.4795459281547114</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.2579938598175</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-0.9268800461363552</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.176390755567719</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>-1.178747238136278</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.658202037307428</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.2362179316310939</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.630617934972048</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0.3542488035760307</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.453659324808734</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0.1141141756314624</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>2.343601735294032</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>-0.01954341107013148</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>-0.4001530422185418</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0.3690233466324378</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1.149860754423361</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>-0.2700315265375604</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0.9408089274536333</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>1.570075341152196</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0.8869091024195205</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0.6446602576307169</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>-1.128596917957908</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>1.128775578867471</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>-0.0769889172955497</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0.07692432621853963</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>-0.1271582050702317</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>-0.1813349595372471</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>-1.05832424441605</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>-0.2190125491346727</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>-0.007391996240000759</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>0.01773587552581747</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>0.7480901912011164</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>0.0106440745257196</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>0.6397021733168948</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>0.06154791744204212</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>0.6255058810833641</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>0.4844797201155087</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>-0.4159527837966958</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>1.055649165749909</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>0.2686517153563941</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>0.0300104255106953</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>0.02996751381211523</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>-0.5442534283645826</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>0.2761548451959577</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>-1.174332681797645</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>0.689572880174554</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>0.6754433240880178</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>0.03992960889391736</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>0.6466465512869052</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>-0.4347781282324544</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>-0.1632674400202885</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>h0AwIDbD</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1.726288768371042</v>
+      </c>
+      <c r="C16" t="n">
+        <v>-1.013801175232162</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.23168274901628</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-0.7325875313015698</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-1.611185507620275</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-1.075864642027034</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-0.2426890271087325</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.8849753580575129</v>
+      </c>
+      <c r="J16" t="n">
+        <v>-1.816371952897576</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1.807961179310516</v>
+      </c>
+      <c r="L16" t="n">
+        <v>-0.007290114893579867</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.8657322324719187</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.1735249894239961</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.2500252936626433</v>
+      </c>
+      <c r="P16" t="n">
+        <v>-0.4190772555275177</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.3807936571097746</v>
+      </c>
+      <c r="R16" t="n">
+        <v>-0.1159730532812117</v>
+      </c>
+      <c r="S16" t="n">
+        <v>-0.2175853491714587</v>
+      </c>
+      <c r="T16" t="n">
+        <v>-0.2924133450868558</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.313327642775776</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.6881144237174459</v>
+      </c>
+      <c r="W16" t="n">
+        <v>-0.3565162709974886</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.8814319288054303</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.3872329558835634</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-0.2169209699836529</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-0.09651826099754968</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.2137956369080184</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0.5815620455189465</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>-0.8209237534928056</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.105329305344655</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0.04186633185766852</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>-0.5571637072129447</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.439393822373281</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>-0.2817980070153636</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.38738266067982</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>-0.7476779554899442</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0.04327876302988919</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>-0.4846025221569235</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0.2921703772757904</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0.7705595609423666</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>-0.1702812762871623</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0.7909037181827604</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0.4962510270476079</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>-0.001055128533103281</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0.001078705305275518</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>-0.4672382422144046</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0.4672116308045682</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0.3053430518854615</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0.5121471493474111</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0.4253097726162245</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>-1.406538520826755</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0.791385088023066</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>-0.7692844655093862</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>0.7480901912011163</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>-0.7388995007939093</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>-0.07136137478440262</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>1.102174798897146</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>0.3567959071205868</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>0.3368033613323608</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>0.423976302025469</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>1.427812721964048</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>0.4050941537173997</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>-0.2211940783832793</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>-1.001281169250546</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>-1.057479175074867</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>-1.506520019876255</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>-0.3957279915526677</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>0.5960639988965488</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>0.9446369908164631</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>-0.3475548741586223</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>0.1825765312032158</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>0.305944603924492</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>-0.1632674400202885</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>4vvdzeEs</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1.726288768371042</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-0.8162621508994871</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.03259633743237113</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-1.524000120620992</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.772558711349371</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-1.075864642027034</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-0.2426890271087325</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-6.869793723675266</v>
+      </c>
+      <c r="J17" t="n">
+        <v>6.249775278910618</v>
+      </c>
+      <c r="K17" t="n">
+        <v>-5.392577609210219</v>
+      </c>
+      <c r="L17" t="n">
+        <v>5.487953235021362</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-2.88494849487742</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.7296036208350827</v>
+      </c>
+      <c r="O17" t="n">
+        <v>-2.981537998496916</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.1097372413185965</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>-2.654497217224376</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.042220137757134</v>
+      </c>
+      <c r="S17" t="n">
+        <v>-2.372581809411154</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.5496739428746912</v>
+      </c>
+      <c r="U17" t="n">
+        <v>-2.95732407878116</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.407677403663348</v>
+      </c>
+      <c r="W17" t="n">
+        <v>-2.839779595047712</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.328876703696436</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>-1.35428885198431</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.202997182321752</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-2.246320155641116</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.838428991126364</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>4.236049513777278</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>-2.020047096273094</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>3.930627174746143</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>-1.388400102074888</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>-1.300558888748232</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>2.152044198451429</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>-1.303722624095159</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>2.251987810586622</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>-0.6844916076224161</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0.5747567678551001</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>-0.4631098929720854</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>1.338909179633432</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>-0.3968646665634631</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.217300351130705</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>-0.2331537136760249</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0.9664584902812177</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>-2.073148631772005</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>2.073457208032938</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>-2.203679042429713</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>2.203821424121077</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0.3389820385375711</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>-1.528097315921945</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>-0.2332120632131601</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>-0.1629672450387862</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>-1.604946164766134</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>1.591776557596225</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>-0.01246145386359385</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>0.0106440745257196</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>0.3197235766713116</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>-0.404939994934383</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>0.08582786614971899</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>-0.1357609867737133</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>0.9525804313831422</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>-1.137845862620661</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>-0.3622556386148197</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>-1.002032389656645</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>0.02996751381211523</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>0.4821980650559866</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>-1.506520019876255</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>1.491798530253339</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>0.6130970455269295</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>0.633545146695234</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>0.3411264115128655</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>-1.278689664637765</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>1.552018252239079</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>-0.1632674400202885</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>YemQuHjK</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1.726288768371042</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1.00109687296112</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-0.8761849429259599</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-0.2442691251257562</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-1.611185507620275</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-1.075864642027034</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-0.2426890271087325</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3.469898385301773</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-7.193803440769705</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1.020402249316059</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-2.068006371111684</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.2719951289146872</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-0.5890971336540667</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.2351675313998411</v>
+      </c>
+      <c r="P18" t="n">
+        <v>-0.762806678477492</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.2411555781452495</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.6361004473930389</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.1910243692636012</v>
+      </c>
+      <c r="T18" t="n">
+        <v>-0.7628207266377891</v>
+      </c>
+      <c r="U18" t="n">
+        <v>-0.4864470113089334</v>
+      </c>
+      <c r="V18" t="n">
+        <v>-0.9908658628229926</v>
+      </c>
+      <c r="W18" t="n">
+        <v>-0.2157980159679758</v>
+      </c>
+      <c r="X18" t="n">
+        <v>-1.127097949594194</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.03892859430998871</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-0.03943120094547738</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0.4480039294220376</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>-0.4897286280883187</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>-0.5044672612756927</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>-0.2653229848659816</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>-0.2117403537945358</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0.5084782910465889</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>-0.2910851039858334</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>-0.5776984701520034</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0.8869179797077624</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>-1.509494480658814</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>-0.2685148174945253</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0.5290382298056191</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0.01740388808893119</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>-0.8849760831828855</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>1.597485055425663</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0.9585986917816116</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1.10787387566286</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0.9451522146034453</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>1.433264140592007</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>-1.43343784268673</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>1.362172618116058</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>-1.362377270616968</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0.3774265947114106</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>-0.05570414271031619</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>1.059790335074061</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0.7405253553296154</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>1.590162172286133</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>-1.55630480654459</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>0.3678143686687612</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>-0.3641277131340949</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>1.279659366608063</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>1.245709541166815</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>0.9924417698980812</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>0.05281036367246031</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>-1.279606312145612</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>0.02071703447101183</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>0.1546734281861322</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>-0.4018581377294628</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>1.061216196874777</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>0.9954238117662711</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>0.8703798002200287</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>0.8547583291438118</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>0.8652362003113235</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>1.040455830572502</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>0.6633381376308312</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>0.1810493372956324</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>-0.1311237825641883</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>-0.1632674400202885</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>KSw0hfzQ</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1.726288768371042</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-1.033555077665429</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-0.295574680474804</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-1.625031515002195</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-0.1025097412006875</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-1.075864642027034</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-0.2426890271087325</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.746616367138933</v>
+      </c>
+      <c r="J19" t="n">
+        <v>-0.920133371585556</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1.882966791690938</v>
+      </c>
+      <c r="L19" t="n">
+        <v>-1.762715073894186</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.9236578035506727</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-0.1760101503201163</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.252924246401817</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.4732972079002999</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.402356445323932</v>
+      </c>
+      <c r="R19" t="n">
+        <v>-0.2588670184093194</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.483156967882187</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0.1286302988939177</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.008281091235994</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0.002816347578491836</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0.09357520648661458</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0.6949966059341778</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0.5613851366703508</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-0.5719005080600039</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-0.181378862101901</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.4748974259788243</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>-0.2896275093982629</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>-0.8597832261652826</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>-0.5557372027982243</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>-0.1211360765424979</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>-0.1549991008086095</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>-0.2984728842032553</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0.3743513939040028</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>-0.7655414212073144</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1.463844219873526</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>-1.088255053694754</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1.210756537113735</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>-0.4485451207380885</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>-0.2266153000521952</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>-1.205087913683537</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0.5036495129664192</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>-0.679267631036415</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0.8008719675255895</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>-0.80095868925686</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>1.010535858486965</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>-1.010706289155206</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0.4879546937111985</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0.1101285355012329</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>0.1715044817236494</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0.08130568413385066</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>1.128366013733471</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>-1.113671288453724</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>0.1064045122409216</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>-0.404939994934383</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>0.1761505464733422</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>-0.0005803198876012675</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>0.6001551524725387</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>-0.3675967328538813</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>0.9202251535028072</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>-0.8687660367833159</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>0.02996751381211523</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>-1.570704921785152</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>-0.6270670864406299</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>-0.2069753393720669</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>0.824497124751797</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>-0.2898729440285797</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>0.7407455730990745</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>-1.472807105318472</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>0.9832221711019438</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>6.124919946535174</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>hMoEUjrJ</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1.726288768371042</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.7146652876787414</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.9666215422451002</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-1.027262431580078</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.3069879668274862</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-1.075864642027034</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-0.2426890271087325</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-3.423229687349588</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.76858237235051</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-4.192487811123429</v>
+      </c>
+      <c r="L20" t="n">
+        <v>3.045622857281387</v>
+      </c>
+      <c r="M20" t="n">
+        <v>-0.6548140083453814</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-0.1601221894226564</v>
+      </c>
+      <c r="O20" t="n">
+        <v>-0.7528736590765308</v>
+      </c>
+      <c r="P20" t="n">
+        <v>-0.02246638289293197</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.4322392651493369</v>
+      </c>
+      <c r="R20" t="n">
+        <v>-0.8530050839419767</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.1742321890539413</v>
+      </c>
+      <c r="T20" t="n">
+        <v>-0.8731631988534413</v>
+      </c>
+      <c r="U20" t="n">
+        <v>-1.249063390158386</v>
+      </c>
+      <c r="V20" t="n">
+        <v>-0.5111572095257243</v>
+      </c>
+      <c r="W20" t="n">
+        <v>-1.349821600617578</v>
+      </c>
+      <c r="X20" t="n">
+        <v>-0.1626058792735822</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>-1.005984490410735</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0.4930381061690494</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-1.68058281494544</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.374248032778266</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0.2331203014141412</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.432548568995596</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.061542755652596</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.912732853425149</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0.1496710555583114</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0.7642513608255618</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>0.8636559593817705</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>-0.1127931623372786</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>-0.05262812894713883</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0.5233234125494344</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>-0.606394087537671</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>-0.5435978137539537</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>1.451557026987435</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0.2295303790705289</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0.8030948780858411</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0.5667821465326497</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0.4133635721146769</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>-0.4133969952402569</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>0.8103503258196563</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>-0.8105012741226032</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>0.1371481186249138</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>-0.332091939729564</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>0.08820930903689682</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>0.454588558583811</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>-0.8061690805030673</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>0.8047562165610213</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>-0.2025993651297713</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>0.7601876498453486</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>0.4263831088865058</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>0.6715705720881371</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>0.9529255972564962</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>0.3004522576318932</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>-2.011560847853138</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>-0.7208995055299064</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>0.1982513893917476</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>-0.2237148557969563</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>0.02996751381211523</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>0.9954238117662711</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>-1.126216048660849</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>1.86930383461454</v>
+      </c>
+      <c r="BQ20" t="n">
+        <v>0.9978743433880763</v>
+      </c>
+      <c r="BR20" t="n">
+        <v>1.12773108475977</v>
+      </c>
+      <c r="BS20" t="n">
+        <v>0.2331024282383666</v>
+      </c>
+      <c r="BT20" t="n">
+        <v>0.1850949740070448</v>
+      </c>
+      <c r="BU20" t="n">
+        <v>0.07139828420398801</v>
+      </c>
+      <c r="BV20" t="n">
+        <v>-0.1632674400202885</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>06X4YYrf</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1.726288768371042</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1.909776384891423</v>
+      </c>
+      <c r="D21" t="n">
+        <v>-1.292709696423528</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-0.2442691251257562</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-0.5335599601777125</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-1.075864642027034</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-0.2426890271087325</v>
+      </c>
+      <c r="I21" t="n">
+        <v>-0.8383066601053271</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.76858237235051</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1.695452760739878</v>
+      </c>
+      <c r="L21" t="n">
+        <v>-1.724553661741999</v>
+      </c>
+      <c r="M21" t="n">
+        <v>-1.060293005896661</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.729603620835083</v>
+      </c>
+      <c r="O21" t="n">
+        <v>-0.1808498119586313</v>
+      </c>
+      <c r="P21" t="n">
+        <v>-0.2075514567890721</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>-0.3908904634836536</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.1472526719547767</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.5044783998439203</v>
+      </c>
+      <c r="T21" t="n">
+        <v>-0.2478891896314178</v>
+      </c>
+      <c r="U21" t="n">
+        <v>-0.394933045846999</v>
+      </c>
+      <c r="V21" t="n">
+        <v>2.127240383609251</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0.247744471188066</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0.4041575022550244</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>-0.4835279480503735</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0.4930381061690491</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0.8652352181850981</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>-0.7798417270558806</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0.5837644979764495</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.639262911558168</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>-0.2749541741048976</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.207820109736203</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>-1.205095573086596</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>0.4579367254937268</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>-0.4787765170631615</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>-0.9863142972336584</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0.1869534400505703</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>-0.6139252214313941</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>0.1291655598500881</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>-0.5429023062440811</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0.5516675182850245</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0.06490205039383291</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0.332211326829346</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>-0.2502033208357469</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>-0.3777994018492676</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>0.3778747967103055</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>0.4972511556253931</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>-0.4973716326334087</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>1.146317718188198</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1.250856352289765</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>0.8423736019748348</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>2.580785252334669</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>1.057644116110755</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>-1.031624579187787</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>0.1396488751493483</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>-0.1392646405382061</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>0.6752553507219601</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>0.3486174019813812</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>-0.01917224972649208</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>0.3515709972106753</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>1.921765805932537</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>-0.2850790277162059</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>0.09472175086621838</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>0.457970752252654</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>0.02996751381211523</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>0.9954238117662711</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>1.797370730057579</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>0.33568853564716</v>
+      </c>
+      <c r="BQ21" t="n">
+        <v>-0.2135356822262024</v>
+      </c>
+      <c r="BR21" t="n">
+        <v>1.081959513018584</v>
+      </c>
+      <c r="BS21" t="n">
+        <v>-0.883530460813014</v>
+      </c>
+      <c r="BT21" t="n">
+        <v>-0.4363748578517313</v>
+      </c>
+      <c r="BU21" t="n">
+        <v>-0.7043010719850984</v>
+      </c>
+      <c r="BV21" t="n">
+        <v>-0.1632674400202885</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>pGrl7dpe</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1.726288768371042</v>
+      </c>
+      <c r="C22" t="n">
+        <v>-1.013801175232162</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1.029731353381095</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-0.7325875313015698</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-0.9107289017826093</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-1.075864642027034</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-0.2426890271087325</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-1.987161338880553</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1.021716887923825</v>
+      </c>
+      <c r="K22" t="n">
+        <v>-1.192263315906458</v>
+      </c>
+      <c r="L22" t="n">
+        <v>2.435040262846395</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.1561439867571788</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1.508113704810605</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.07916102764041355</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.088044060483908</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>-0.3394448554440919</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.6737041224267513</v>
+      </c>
+      <c r="S22" t="n">
+        <v>-0.4097625226820117</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0.9445838434359687</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0.8862624706200818</v>
+      </c>
+      <c r="V22" t="n">
+        <v>2.367094710257884</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0.247744471188066</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.935412954104243</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>-0.5706040384437669</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1.202997182321752</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>-1.114845474249765</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.258202793191241</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>-0.5955707060655436</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>-0.239384360758221</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0.4492817419516063</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>-0.4011748060425462</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>-0.1184386820445785</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>-1.436212958292929</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>0.8087094630945119</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>-1.068194122688408</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>-0.5739154988542428</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>-0.7625104700922058</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>0.3433754307256373</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>-0.440430866456246</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0.7502917792148346</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0.2412895454045783</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0.2788750022533681</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>-0.1032634885752447</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>0.6959217771017999</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>-0.6959940637940292</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>0.463661972616047</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>-0.4637791806728822</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>1.112678731536089</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>0.5121471493474111</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>-0.01370478460336537</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>-0.9750954251452146</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>-1.533564743993014</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>1.509731225164977</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>-0.04765925651435945</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>1.239728926905579</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>-0.4199791436625672</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>0.3004522576318932</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>1.77587082333678</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>1.224987713438357</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>1.155778376007282</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>-0.3260221713628055</v>
+      </c>
+      <c r="BM22" t="n">
+        <v>-2.376279413334094</v>
+      </c>
+      <c r="BN22" t="n">
+        <v>-0.6297910528162967</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>-2.647431933522471</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>0.3592826171697352</v>
+      </c>
+      <c r="BQ22" t="n">
+        <v>0.4565219122684102</v>
+      </c>
+      <c r="BR22" t="n">
+        <v>1.028717703731552</v>
+      </c>
+      <c r="BS22" t="n">
+        <v>-1.449900829399714</v>
+      </c>
+      <c r="BT22" t="n">
+        <v>0.4731490992147748</v>
+      </c>
+      <c r="BU22" t="n">
+        <v>0.005869217449604431</v>
+      </c>
+      <c r="BV22" t="n">
+        <v>-0.1632674400202885</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>6VWd5zF7</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1.726288768371042</v>
+      </c>
+      <c r="C23" t="n">
+        <v>-0.4903227607505739</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1.62296357805945</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-1.524000120620992</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-1.406436653606188</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-1.075864642027034</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-0.2426890271087325</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-7.013400558522169</v>
+      </c>
+      <c r="J23" t="n">
+        <v>5.204163600713259</v>
+      </c>
+      <c r="K23" t="n">
+        <v>-6.592667407297006</v>
+      </c>
+      <c r="L23" t="n">
+        <v>6.098535829456355</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.4197053351655104</v>
+      </c>
+      <c r="N23" t="n">
+        <v>1.041007654425291</v>
+      </c>
+      <c r="O23" t="n">
+        <v>-0.7417303373794286</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.3432969774256306</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>-1.080261611213783</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.010633050728816</v>
+      </c>
+      <c r="S23" t="n">
+        <v>-1.19899499253603</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0.4780481275768134</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0.2456647123865414</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.695502595641709</v>
+      </c>
+      <c r="W23" t="n">
+        <v>-1.068385090558553</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.358706355355836</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>-1.383314215448775</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1.617139976744162</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-2.133172687501981</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>2.302609949474463</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0.3226000039367734</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>-1.06538146649824</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0.1093237644038105</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>-0.4373861310708006</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0.369033568142495</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>-0.2359596933192072</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>0.495875396641514</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>-0.8236180206807135</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>-1.12679604269511</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>-1.053966150157644</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>-0.6944115213422452</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>-1.148689347342756</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>1.601538611771168</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>1.009555079229161</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>1.241976634596748</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0.2376369222691229</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>0.4623403276457786</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>-0.4623804871229112</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>0.6873899237318712</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>-0.6875289053385328</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>-0.5356316144172758</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>0.01967434738584252</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>-0.7746633504506546</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>0.2932908783682286</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>-0.007391996240000759</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>0.01773587552581747</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>1.128366013733471</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>-1.113671288453724</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>-0.2135740844046621</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>0.402442930332507</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>-0.2393337830153222</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>-0.04488322752254559</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>2.132539578249518</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>0.7446237480363179</v>
+      </c>
+      <c r="BK23" t="n">
+        <v>1.855860434376358</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>-0.7850242523248331</v>
+      </c>
+      <c r="BM23" t="n">
+        <v>-1.17315594976099</v>
+      </c>
+      <c r="BN23" t="n">
+        <v>-0.6297910528162967</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>-1.126216048660849</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>1.114293225892138</v>
+      </c>
+      <c r="BQ23" t="n">
+        <v>0.9391992275951132</v>
+      </c>
+      <c r="BR23" t="n">
+        <v>1.031191846763627</v>
+      </c>
+      <c r="BS23" t="n">
+        <v>-0.4906815470983383</v>
+      </c>
+      <c r="BT23" t="n">
+        <v>-0.8931208666823927</v>
+      </c>
+      <c r="BU23" t="n">
+        <v>0.2439713713949575</v>
+      </c>
+      <c r="BV23" t="n">
+        <v>-0.1632674400202885</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>bqbA3PNE</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1.726288768371042</v>
+      </c>
+      <c r="C24" t="n">
+        <v>-0.07549080965195716</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1.118085088971489</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1.144912547615783</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.772558711349371</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-1.075864642027034</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-0.2426890271087325</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-0.9819134949522306</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2.067328566121183</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.9236844859834075</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-0.1358338189851578</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-1.060293005896661</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-0.493769368269309</v>
+      </c>
+      <c r="O24" t="n">
+        <v>-0.9718301555809891</v>
+      </c>
+      <c r="P24" t="n">
+        <v>-2.071390621988797</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-1.162574584077082</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.8842847026155424</v>
+      </c>
+      <c r="S24" t="n">
+        <v>-1.182399212094904</v>
+      </c>
+      <c r="T24" t="n">
+        <v>-1.369042065218698</v>
+      </c>
+      <c r="U24" t="n">
+        <v>-1.249063390158386</v>
+      </c>
+      <c r="V24" t="n">
+        <v>-0.9908658628229923</v>
+      </c>
+      <c r="W24" t="n">
+        <v>-1.722311099225111</v>
+      </c>
+      <c r="X24" t="n">
+        <v>-2.123512980462585</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>-0.7737815826950186</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0.9959257851105469</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-0.3347234570799392</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0.1893650601528552</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0.6849989545399179</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>-0.5499144287802558</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0.8331766077629806</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>-0.1868819982301545</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>-0.2524935508460238</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>-0.3734887132641131</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>0.2948505428281983</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>-0.3823176627103073</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>-0.6686950206555342</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>-0.1967435617298841</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>-0.5051854104238848</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>-1.315289155494547</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>-0.04420526450440977</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>0.6528603670963183</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>0.7293062786724567</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>0.7158874079001498</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>-0.2459389061886097</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>0.2459961647185445</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>0.1781539170366043</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>-0.1782433390084064</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>-1.712996147241107</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>-0.507975083287267</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>-0.7696570440963958</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>-0.730833627115397</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>0.7480901912011164</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>-0.7388995007939092</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>0.2012129853210952</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>0.4861715299898143</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>0.6829083213416661</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>0.3320203213717723</v>
+      </c>
+      <c r="BI24" t="n">
+        <v>-0.4792679229970757</v>
+      </c>
+      <c r="BJ24" t="n">
+        <v>0.03390746185434199</v>
+      </c>
+      <c r="BK24" t="n">
+        <v>-0.7451815083674475</v>
+      </c>
+      <c r="BL24" t="n">
+        <v>-0.9489472967987551</v>
+      </c>
+      <c r="BM24" t="n">
+        <v>0.6315292455986677</v>
+      </c>
+      <c r="BN24" t="n">
+        <v>1.765262431831698</v>
+      </c>
+      <c r="BO24" t="n">
+        <v>1.956247718032435</v>
+      </c>
+      <c r="BP24" t="n">
+        <v>2.664051843796017</v>
+      </c>
+      <c r="BQ24" t="n">
+        <v>0.1498274968126411</v>
+      </c>
+      <c r="BR24" t="n">
+        <v>0.9057225485719969</v>
+      </c>
+      <c r="BS24" t="n">
+        <v>-0.9888377220718767</v>
+      </c>
+      <c r="BT24" t="n">
+        <v>0.1590406468355902</v>
+      </c>
+      <c r="BU24" t="n">
+        <v>0.1100065345727104</v>
+      </c>
+      <c r="BV24" t="n">
+        <v>-0.1632674400202885</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>QDjsB5oT</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1.726288768371042</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.05290955616428136</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.6889383732467214</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-0.3368812366418588</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-0.1025097412006875</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-1.075864642027034</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-0.2426890271087325</v>
+      </c>
+      <c r="I25" t="n">
+        <v>9.070564944331004</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-6.297564859457684</v>
+      </c>
+      <c r="K25" t="n">
+        <v>7.208365270701064</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-5.502533464808522</v>
+      </c>
+      <c r="M25" t="n">
+        <v>3.197236468391778</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-0.3825536419870914</v>
+      </c>
+      <c r="O25" t="n">
+        <v>2.36725641611201</v>
+      </c>
+      <c r="P25" t="n">
+        <v>-0.1458564321570252</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.769825074177945</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.199897817001974</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1.470961660799906</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.3212456670598345</v>
+      </c>
+      <c r="U25" t="n">
+        <v>4.089251261787783</v>
+      </c>
+      <c r="V25" t="n">
+        <v>-0.03144855622845609</v>
+      </c>
+      <c r="W25" t="n">
+        <v>3.84019874664739</v>
+      </c>
+      <c r="X25" t="n">
+        <v>-0.2918677031309838</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>2.883414213827515</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-2.110145173057526</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>3.411053251315637</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>-2.803380592354624</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>-1.455966361536599</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>-0.5946947701559117</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>-2.2018508082497</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>-0.5921623303230499</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0.978373880876337</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>-2.786497881388368</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>1.220607650590961</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>-2.158152838157484</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>0.6582182845625476</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>-0.1624546581927737</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1.095105722928656</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>-0.5459161721201943</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>-0.8954520970607434</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>-2.941524809011544</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>-0.6354619904776894</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>-2.348504125515729</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>2.240573297698073</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>-2.240858038554652</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>2.04235357405532</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>-2.042624422817632</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>-0.7038265476778233</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>1.250856352289765</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>-0.869783171181565</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>-1.217041945468589</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>1.590162172286133</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>-1.55630480654459</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>0.1776764574025837</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>-0.7388995007939093</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>-1.499414000554509</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>-0.686028865212486</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>-1.594173987869661</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>-0.7355541978314226</v>
+      </c>
+      <c r="BI25" t="n">
+        <v>0.2407439383997436</v>
+      </c>
+      <c r="BJ25" t="n">
+        <v>1.900732026386089</v>
+      </c>
+      <c r="BK25" t="n">
+        <v>0.3106294197960974</v>
+      </c>
+      <c r="BL25" t="n">
+        <v>1.40517421640183</v>
+      </c>
+      <c r="BM25" t="n">
+        <v>-0.5715942179744372</v>
+      </c>
+      <c r="BN25" t="n">
+        <v>-1.827317795140294</v>
+      </c>
+      <c r="BO25" t="n">
+        <v>1.155607778631583</v>
+      </c>
+      <c r="BP25" t="n">
+        <v>-3.415770426442278</v>
+      </c>
+      <c r="BQ25" t="n">
+        <v>0.6609226208375184</v>
+      </c>
+      <c r="BR25" t="n">
+        <v>0.9756399896985086</v>
+      </c>
+      <c r="BS25" t="n">
+        <v>-0.136830728430345</v>
+      </c>
+      <c r="BT25" t="n">
+        <v>0.367852496862248</v>
+      </c>
+      <c r="BU25" t="n">
+        <v>-1.062893901539838</v>
+      </c>
+      <c r="BV25" t="n">
+        <v>-0.1632674400202885</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>ddsD5q9j</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1.726288768371042</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1.238143702160329</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-1.027648489652348</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.5303048984634655</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-0.9107289017826093</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-1.075864642027034</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-0.2426890271087325</v>
+      </c>
+      <c r="I26" t="n">
+        <v>2.03383003683274</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-1.069506468470892</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1.20791628026712</v>
+      </c>
+      <c r="L26" t="n">
+        <v>-0.6178727093285733</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-0.0465955120184612</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0.3959564419884305</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.3391718672394584</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.458214208276188</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-0.3908904634836536</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.1472526719547767</v>
+      </c>
+      <c r="S26" t="n">
+        <v>-0.9321859069825438</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0.7548722245388844</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0.03213212630869454</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0.6881144237174461</v>
+      </c>
+      <c r="W26" t="n">
+        <v>2.565456906968274</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0.6825675844094277</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>-0.164248949941263</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0.3747115934769325</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.034956420393801</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>-0.7145662797881794</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>-0.5647577778494959</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.7998798526202078</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>0.2176426963511438</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>-0.2232442220256273</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0.9661870746216599</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>-1.661260445475503</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>0.5740839132547635</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>-1.30213648113055</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>0.6582182845625482</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>-0.7110771147865407</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>0.09058117317064078</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>0.2376889556691364</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>-0.7252027305494767</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>-2.475077877760906</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>-1.488843183693344</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>-1.831275915958758</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>0.9031311274256903</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>-0.9032319140667958</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>0.8163483942141828</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>-0.8164999262584119</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>-0.838382494286261</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>0.4417938919243303</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>-1.33858800192677</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>0.7845156317520471</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>-2.294116389057725</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>2.259274800484606</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>-1.374977879636782</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>-1.313993362642289</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>-1.46772223541659</v>
+      </c>
+      <c r="BH26" t="n">
+        <v>-0.880958612633291</v>
+      </c>
+      <c r="BI26" t="n">
+        <v>0.7785821674862887</v>
+      </c>
+      <c r="BJ26" t="n">
+        <v>0.1103591194417052</v>
+      </c>
+      <c r="BK26" t="n">
+        <v>-0.2157367781577004</v>
+      </c>
+      <c r="BL26" t="n">
+        <v>2.399591422854981</v>
+      </c>
+      <c r="BM26" t="n">
+        <v>0.6315292455986677</v>
+      </c>
+      <c r="BN26" t="n">
+        <v>0.5677356895077007</v>
+      </c>
+      <c r="BO26" t="n">
+        <v>0.01469586498536652</v>
+      </c>
+      <c r="BP26" t="n">
+        <v>-1.905749208997473</v>
+      </c>
+      <c r="BQ26" t="n">
+        <v>1.023369284773895</v>
+      </c>
+      <c r="BR26" t="n">
+        <v>0.7612642001307957</v>
+      </c>
+      <c r="BS26" t="n">
+        <v>0.2217444957149707</v>
+      </c>
+      <c r="BT26" t="n">
+        <v>1.060665537513786</v>
+      </c>
+      <c r="BU26" t="n">
+        <v>-1.056832932398852</v>
+      </c>
+      <c r="BV26" t="n">
+        <v>-0.1632674400202885</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>f5SjRHyR</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1.726288768371042</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.3393411414466596</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.9666215422451002</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1.144912547615783</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.3069879668274862</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-1.075864642027034</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-0.2426890271087325</v>
+      </c>
+      <c r="I27" t="n">
+        <v>5.049573568617711</v>
+      </c>
+      <c r="J27" t="n">
+        <v>-4.206341503062968</v>
+      </c>
+      <c r="K27" t="n">
+        <v>4.208140775484092</v>
+      </c>
+      <c r="L27" t="n">
+        <v>-3.060203087068548</v>
+      </c>
+      <c r="M27" t="n">
+        <v>2.791757470840498</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-0.6049850945515263</v>
+      </c>
+      <c r="O27" t="n">
+        <v>2.471260751951629</v>
+      </c>
+      <c r="P27" t="n">
+        <v>-0.2075514567890721</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2.69584601889006</v>
+      </c>
+      <c r="R27" t="n">
+        <v>-0.1159730532812111</v>
+      </c>
+      <c r="S27" t="n">
+        <v>1.862779199025304</v>
+      </c>
+      <c r="T27" t="n">
+        <v>-0.1665842101040962</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0.8862624706200815</v>
+      </c>
+      <c r="V27" t="n">
+        <v>-0.9908658628229926</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.986028798023222</v>
+      </c>
+      <c r="X27" t="n">
+        <v>-1.266302990671396</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0.8516387713149963</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-1.074788187001502</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.487546292950341</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>-1.642928196484377</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>-0.5841126456686525</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.1059197196424618</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0.3064673557937776</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>-0.05862169656281087</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>2.209241312598698</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>-0.9986206221045938</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>1.773281167991258</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>-0.7013299696768653</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>2.206283807316977</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>1.466268259819971</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1.421077265565362</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>0.4411249023067512</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>-0.04420526450440977</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>-2.914086754232096</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>-0.6598443102838522</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>-1.984093341509681</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>2.428945434356155</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>-2.429256084257166</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>2.437026474415138</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>-2.437335733353819</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>-0.7038265476778233</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>-1.387390801075783</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>-1.345382274836121</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>-1.730261837063623</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>0.791385088023066</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>-0.7692844655093862</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>1.508641836265827</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>-1.488443076113538</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>-0.9187121029384493</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>0.1093928315319322</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>-0.835463473151231</v>
+      </c>
+      <c r="BH27" t="n">
+        <v>-0.08123433122301267</v>
+      </c>
+      <c r="BI27" t="n">
+        <v>-2.631501645560723</v>
+      </c>
+      <c r="BJ27" t="n">
+        <v>-0.6861283158294119</v>
+      </c>
+      <c r="BK27" t="n">
+        <v>-1.627268765098062</v>
+      </c>
+      <c r="BL27" t="n">
+        <v>0.7888291856464734</v>
+      </c>
+      <c r="BM27" t="n">
+        <v>0.6315292455986677</v>
+      </c>
+      <c r="BN27" t="n">
+        <v>-0.6297910528162967</v>
+      </c>
+      <c r="BO27" t="n">
+        <v>1.535911749846987</v>
+      </c>
+      <c r="BP27" t="n">
+        <v>-1.15073860027507</v>
+      </c>
+      <c r="BQ27" t="n">
+        <v>0.7814553516736265</v>
+      </c>
+      <c r="BR27" t="n">
+        <v>1.024645509365531</v>
+      </c>
+      <c r="BS27" t="n">
+        <v>2.090945995370447</v>
+      </c>
+      <c r="BT27" t="n">
+        <v>-0.6010986055508151</v>
+      </c>
+      <c r="BU27" t="n">
+        <v>0.2910222880033363</v>
+      </c>
+      <c r="BV27" t="n">
+        <v>-0.1632674400202885</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>bwZsTw7E</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1.726288768371042</v>
+      </c>
+      <c r="C28" t="n">
+        <v>-0.8952777606325569</v>
+      </c>
+      <c r="D28" t="n">
+        <v>-0.7625872828811685</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.5303048984634655</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.7488144412789369</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-1.075864642027034</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-0.2426890271087325</v>
+      </c>
+      <c r="I28" t="n">
+        <v>-3.997657026737201</v>
+      </c>
+      <c r="J28" t="n">
+        <v>5.20416360071326</v>
+      </c>
+      <c r="K28" t="n">
+        <v>-3.404928881128974</v>
+      </c>
+      <c r="L28" t="n">
+        <v>3.274591330194511</v>
+      </c>
+      <c r="M28" t="n">
+        <v>-0.2493350107941013</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.3959564419884308</v>
+      </c>
+      <c r="O28" t="n">
+        <v>-0.1320977795338103</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0.4942294484004589</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>-0.1851080313254062</v>
+      </c>
+      <c r="R28" t="n">
+        <v>-0.168618198328409</v>
+      </c>
+      <c r="S28" t="n">
+        <v>-0.248137788164034</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0.4838556261144792</v>
+      </c>
+      <c r="U28" t="n">
+        <v>-0.6084656319248457</v>
+      </c>
+      <c r="V28" t="n">
+        <v>-0.2713028828770899</v>
+      </c>
+      <c r="W28" t="n">
+        <v>-0.8893831926165987</v>
+      </c>
+      <c r="X28" t="n">
+        <v>-0.3527699086022598</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>-1.180136671197523</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1.202997182321751</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-0.7541879195562721</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0.8012746623173312</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>-0.6444179057066276</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.2362180384799327</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0.2503553871483704</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>-0.9176381104976129</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0.6249564994907079</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>0.4641880445821313</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>-0.8687763199078996</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>1.251734265196178</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>0.4844558279268467</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>-0.6424993077123197</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>0.028491355525554</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>0.005118972229098161</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0.2679185740995796</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>0.3236037097429263</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>0.1226757659951449</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>0.01649247471706657</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>0.09313093979593799</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>-0.09312031754598217</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>-0.2516826592861232</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>0.2516350696739575</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>-0.06468580128774327</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>0.3362640057897081</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>-0.3805955217083082</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>-0.7478123302959847</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>-0.007391996240000759</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>0.01773587552581747</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>-0.01246145386359385</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>0.0106440745257196</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>-0.5039250332126919</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>0.1512571313605856</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>-0.1117529970582053</v>
+      </c>
+      <c r="BH28" t="n">
+        <v>0.8025518774945967</v>
+      </c>
+      <c r="BI28" t="n">
+        <v>0.4645765793609814</v>
+      </c>
+      <c r="BJ28" t="n">
+        <v>-0.991622437531446</v>
+      </c>
+      <c r="BK28" t="n">
+        <v>-0.05750741129920411</v>
+      </c>
+      <c r="BL28" t="n">
+        <v>-0.576187852474267</v>
+      </c>
+      <c r="BM28" t="n">
+        <v>0.02996751381211523</v>
+      </c>
+      <c r="BN28" t="n">
+        <v>0.5677356895077007</v>
+      </c>
+      <c r="BO28" t="n">
+        <v>1.036762787626768</v>
+      </c>
+      <c r="BP28" t="n">
+        <v>0.5952234323954859</v>
+      </c>
+      <c r="BQ28" t="n">
+        <v>1.048233024269319</v>
+      </c>
+      <c r="BR28" t="n">
+        <v>0.6061633643622639</v>
+      </c>
+      <c r="BS28" t="n">
+        <v>-0.3724931611719819</v>
+      </c>
+      <c r="BT28" t="n">
+        <v>0.4103903496525498</v>
+      </c>
+      <c r="BU28" t="n">
+        <v>-0.4235572829469354</v>
+      </c>
+      <c r="BV28" t="n">
+        <v>-0.1632674400202885</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>rkN7RQV9</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1.726288768371042</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.8628195559282473</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1.925890671512227</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1.128073981885582</v>
+      </c>
+      <c r="F29" t="n">
+        <v>-0.5335599601777125</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-1.075864642027034</v>
+      </c>
+      <c r="H29" t="n">
+        <v>-0.2426890271087325</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.028582192904416</v>
+      </c>
+      <c r="J29" t="n">
+        <v>-2.11511814666825</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.04532928837054301</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.145355533715168</v>
+      </c>
+      <c r="M29" t="n">
+        <v>2.082169225125758</v>
+      </c>
+      <c r="N29" t="n">
+        <v>-0.7162008208337437</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0.5796818938685752</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0.7834248763631776</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1.409705817901012</v>
+      </c>
+      <c r="R29" t="n">
+        <v>-0.8003599388947793</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0.06205109626440697</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0.3771428404848688</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0.6727298845422349</v>
+      </c>
+      <c r="V29" t="n">
+        <v>-1.230720189471626</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0.3563872416152633</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0.1431480502352713</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0.03892859430998871</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-0.03943120094547738</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>-0.7046859022454006</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0.917319901904356</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>-1.192004091868775</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>-0.2192862033510594</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>-0.2953120856885252</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>-0.4146098377187408</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>1.636461418628885</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>-1.261176023817596</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>0.09927131906054559</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>0.3134836245956436</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>-0.03683154198025667</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>-1.242555119611752</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>-0.3391690646728543</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>0.3351372856634506</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>0.8637913568890132</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>0.3784798193018242</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>-0.1180996420906995</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>0.001063792329712754</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>1.788480169718676</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>-1.788702728868616</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>0.06059177650389298</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>-0.06066975714656373</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>-0.03104681463563346</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>-0.1562087961718605</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>0.6996938708784681</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>-0.7230677998083671</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>-0.007391996240000759</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>0.01773587552581747</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>0.5959798621881742</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>-0.5889907857299834</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>-0.047659256514359</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>0.3187143306751997</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>-0.06884972390448456</v>
+      </c>
+      <c r="BH29" t="n">
+        <v>-0.1368969587643528</v>
+      </c>
+      <c r="BI29" t="n">
+        <v>-0.215697859236136</v>
+      </c>
+      <c r="BJ29" t="n">
+        <v>0.365374463769559</v>
+      </c>
+      <c r="BK29" t="n">
+        <v>-0.0924677979580832</v>
+      </c>
+      <c r="BL29" t="n">
+        <v>0.4668510990381768</v>
+      </c>
+      <c r="BM29" t="n">
+        <v>-0.5715942179744373</v>
+      </c>
+      <c r="BN29" t="n">
+        <v>-1.228554423978295</v>
+      </c>
+      <c r="BO29" t="n">
+        <v>-1.649134009082032</v>
+      </c>
+      <c r="BP29" t="n">
+        <v>-0.6316688067784184</v>
+      </c>
+      <c r="BQ29" t="n">
+        <v>0.8110792440756064</v>
+      </c>
+      <c r="BR29" t="n">
+        <v>-0.3092728148385131</v>
+      </c>
+      <c r="BS29" t="n">
+        <v>1.085221415602212</v>
+      </c>
+      <c r="BT29" t="n">
+        <v>0.1729531316644807</v>
+      </c>
+      <c r="BU29" t="n">
+        <v>0.3663133004936507</v>
+      </c>
+      <c r="BV29" t="n">
+        <v>-0.1632674400202885</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>445r4WXo</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1.726288768371042</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1.603590897175777</v>
+      </c>
+      <c r="D30" t="n">
+        <v>-1.292709696423528</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.2103721495896566</v>
+      </c>
+      <c r="F30" t="n">
+        <v>-0.5335599601777125</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-1.075864642027034</v>
+      </c>
+      <c r="H30" t="n">
+        <v>-0.2426890271087325</v>
+      </c>
+      <c r="I30" t="n">
+        <v>8.065317100402682</v>
+      </c>
+      <c r="J30" t="n">
+        <v>-5.461075516899798</v>
+      </c>
+      <c r="K30" t="n">
+        <v>4.347436912762023</v>
+      </c>
+      <c r="L30" t="n">
+        <v>-2.705847117083954</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.3994313852879467</v>
+      </c>
+      <c r="N30" t="n">
+        <v>-0.8051734018595174</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0.7375456179108527</v>
+      </c>
+      <c r="P30" t="n">
+        <v>-0.361238169934974</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1.378838453077275</v>
+      </c>
+      <c r="R30" t="n">
+        <v>-0.7161277068192631</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0.926381927611627</v>
+      </c>
+      <c r="T30" t="n">
+        <v>-0.7061976158955479</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0.4591972984643881</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0.1604349050904513</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0.962717369904193</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0.4153436216272995</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0.3640126651119919</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-0.453573995367887</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0.8955425757223663</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>-0.8886341391687163</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>-0.355132290765722</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.454234291362765</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0.2217912681158599</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0.750419389548137</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0.476683690058807</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>-0.1296872688163254</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>-0.2282051196694891</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>-0.4082374126513395</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>0.7398339838914381</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>-0.2196028307546243</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>0.4897300008890572</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>0.06910083322407617</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>1.476689076329574</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>-0.07699189003703463</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>0.898773713396626</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>-0.3415159308833457</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>1.061363722218479</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>-1.061486272456908</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>0.7327503159654745</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>-0.7328937121155829</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>0.4735379851460088</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>0.7232069216166553</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>-0.01370478460336537</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>1.801790774020777</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>-0.5399100524153786</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>0.54241610288262</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>-0.7730130989283039</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>0.7601876498453486</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>0.906351003854882</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>1.156000327248271</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>-0.1014304050212199</v>
+      </c>
+      <c r="BH30" t="n">
+        <v>0.8627583929984954</v>
+      </c>
+      <c r="BI30" t="n">
+        <v>0.3276252230331591</v>
+      </c>
+      <c r="BJ30" t="n">
+        <v>-0.0108654949114941</v>
+      </c>
+      <c r="BK30" t="n">
+        <v>0.2349106673389709</v>
+      </c>
+      <c r="BL30" t="n">
+        <v>0.6144214206518769</v>
+      </c>
+      <c r="BM30" t="n">
+        <v>-0.3309695252598162</v>
+      </c>
+      <c r="BN30" t="n">
+        <v>0.2084776668105016</v>
+      </c>
+      <c r="BO30" t="n">
+        <v>-0.1381048377351089</v>
+      </c>
+      <c r="BP30" t="n">
+        <v>-0.1698989255508776</v>
+      </c>
+      <c r="BQ30" t="n">
+        <v>1.082462173408428</v>
+      </c>
+      <c r="BR30" t="n">
+        <v>1.026311369884634</v>
+      </c>
+      <c r="BS30" t="n">
+        <v>0.3088493405644057</v>
+      </c>
+      <c r="BT30" t="n">
+        <v>-0.1897327989079295</v>
+      </c>
+      <c r="BU30" t="n">
+        <v>-0.8000175429550216</v>
+      </c>
+      <c r="BV30" t="n">
+        <v>-0.1632674400202885</v>
       </c>
     </row>
   </sheetData>

--- a/data/spain/p6_deployment/data_preparation/df_selected_nan.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_selected_nan.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BV10"/>
+  <dimension ref="A1:BV6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -798,23 +798,23 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>n37VJZT0</t>
+          <t>YJVCWCD6</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1.726288768371042</v>
       </c>
       <c r="C2" t="n">
-        <v>1.040604677827655</v>
+        <v>1.139374189993992</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3102795064307501</v>
+        <v>-0.4722821516555906</v>
       </c>
       <c r="E2" t="n">
-        <v>1.784778045363401</v>
+        <v>0.2861456953755587</v>
       </c>
       <c r="F2" t="n">
-        <v>1.136759638358259</v>
+        <v>0.1884491566088044</v>
       </c>
       <c r="G2" t="n">
         <v>-1.075864642027034</v>
@@ -823,199 +823,199 @@
         <v>-0.2426890271087325</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.699947669186746</v>
+        <v>3.469898385301773</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8723437910384881</v>
+        <v>-4.505087696833642</v>
       </c>
       <c r="K2" t="n">
-        <v>-2.392353113993246</v>
+        <v>6.008275472614274</v>
       </c>
       <c r="L2" t="n">
-        <v>1.213875073976407</v>
+        <v>-6.723698653678509</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.856769608229532</v>
+        <v>0.05477423736935869</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.1442342285251969</v>
+        <v>0.999698956091897</v>
       </c>
       <c r="O2" t="n">
-        <v>-2.468945200430228</v>
+        <v>0.443176203079077</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.4543315553172582</v>
+        <v>1.088044060483907</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.044499293326714</v>
+        <v>0.9981409535845173</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.1535767283149235</v>
+        <v>-0.01820349819355893</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.559093968143183</v>
+        <v>1.679931014520119</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6815157471104683</v>
+        <v>1.378210400915019</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.8830075283106487</v>
+        <v>1.130299711851907</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.4426274019118289</v>
+        <v>0.1741408666132302</v>
       </c>
       <c r="W2" t="n">
-        <v>-1.37465423385808</v>
+        <v>2.217800041601243</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.01345762097658052</v>
+        <v>-0.1526626620537822</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0.3093757672635858</v>
+        <v>1.954602582964649</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.1380585680926982</v>
+        <v>-1.814328891327233</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0.4359606654149548</v>
+        <v>2.619020974341691</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.5619313556690926</v>
+        <v>-2.571290113180575</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.434842496463831</v>
+        <v>-0.5868069145104062</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.3940127144568519</v>
+        <v>1.032331242330415</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.077225485123837</v>
+        <v>-1.161266888269343</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.9935641747558817</v>
+        <v>0.5262232421808395</v>
       </c>
       <c r="AG2" t="n">
-        <v>-2.190195745339642</v>
+        <v>-1.227438051220172</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.827186659999148</v>
+        <v>0.414177491874893</v>
       </c>
       <c r="AI2" t="n">
-        <v>-1.921369370681847</v>
+        <v>-1.124043570542667</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2.068760229149419</v>
+        <v>0.8147964686885617</v>
       </c>
       <c r="AK2" t="n">
-        <v>-1.916625391039207</v>
+        <v>-0.2105939986159582</v>
       </c>
       <c r="AL2" t="n">
-        <v>-0.1967435617298841</v>
+        <v>1.209101483291643</v>
       </c>
       <c r="AM2" t="n">
-        <v>-1.552069771670535</v>
+        <v>0.1028626755619766</v>
       </c>
       <c r="AN2" t="n">
-        <v>-0.1216565910981604</v>
+        <v>1.939363996489753</v>
       </c>
       <c r="AO2" t="n">
-        <v>-0.4698286807825766</v>
+        <v>-1.19946882297372</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.605823701760119</v>
+        <v>-0.4760196009724539</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-0.1965802339667821</v>
+        <v>-1.988680739719655</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.3786991612392053</v>
+        <v>-0.5382053920663326</v>
       </c>
       <c r="AS2" t="n">
-        <v>-1.497268099703011</v>
+        <v>-1.674876114266346</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.497497468313822</v>
+        <v>1.675129911404765</v>
       </c>
       <c r="AU2" t="n">
-        <v>-1.324962022631639</v>
+        <v>-1.627264669715754</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.325018886225159</v>
+        <v>1.627350953869897</v>
       </c>
       <c r="AW2" t="n">
-        <v>-0.7038265476778233</v>
+        <v>1.987292384490936</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.9493423919051305</v>
+        <v>1.074973208732062</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.271654677589368</v>
+        <v>2.269170912938502</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.393047788929016</v>
+        <v>1.041125577549564</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>0.791385088023066</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>-0.7692844655093862</v>
       </c>
       <c r="BC2" t="n">
-        <v>-0.01246145386359385</v>
+        <v>0.7480901912011163</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.0106440745257196</v>
+        <v>-0.7388995007939092</v>
       </c>
       <c r="BE2" t="n">
-        <v>-0.0002550199742726515</v>
+        <v>-0.3557867940249216</v>
       </c>
       <c r="BF2" t="n">
-        <v>-0.763776850608557</v>
+        <v>0.2050826597117119</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.4290540513794851</v>
+        <v>0.2664732267969645</v>
       </c>
       <c r="BH2" t="n">
-        <v>-0.2993409534258161</v>
+        <v>0.08234563542909018</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.1951753107432104</v>
+        <v>-1.51037441685365</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.9864243301260859</v>
+        <v>1.435839536772741</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.5672206193122714</v>
+        <v>-2.133544471550481</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.5803714327989157</v>
+        <v>2.331882849106855</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.061216196874777</v>
+        <v>0.02996751381211523</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.4821980650559866</v>
+        <v>-0.5442534283645826</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.01469586498536652</v>
+        <v>0.3949998362007718</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.3592826171697351</v>
+        <v>-2.283254513358675</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.020525971963942</v>
+        <v>0.759078812737111</v>
       </c>
       <c r="BR2" t="n">
-        <v>0.6125690168202887</v>
+        <v>0.8337801259128935</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.06540791019667526</v>
+        <v>0.3981965850154833</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.3174560471392686</v>
+        <v>0.8355789906232948</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.4778014284392474</v>
+        <v>0.05836502959525035</v>
       </c>
       <c r="BV2" t="n">
         <v>-0.1632674400202885</v>
@@ -1024,23 +1024,23 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>4rQsoH7m</t>
+          <t>n37VJZT0</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1.726288768371042</v>
       </c>
       <c r="C3" t="n">
-        <v>1.603590897175777</v>
+        <v>1.040604677827655</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.1188672092940174</v>
+        <v>0.3102795064307501</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7576255358211719</v>
+        <v>1.784778045363401</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.3288111061636256</v>
+        <v>1.136759638358259</v>
       </c>
       <c r="G3" t="n">
         <v>-1.075864642027034</v>
@@ -1049,136 +1049,136 @@
         <v>-0.2426890271087325</v>
       </c>
       <c r="I3" t="n">
-        <v>6.054821412546034</v>
+        <v>-1.699947669186746</v>
       </c>
       <c r="J3" t="n">
-        <v>-4.505087696833641</v>
+        <v>0.8723437910384881</v>
       </c>
       <c r="K3" t="n">
-        <v>1.657949954549666</v>
+        <v>-2.392353113993246</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.075809655154819</v>
+        <v>1.213875073976407</v>
       </c>
       <c r="M3" t="n">
-        <v>1.271211230023199</v>
+        <v>-1.856769608229532</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.860134005450838</v>
+        <v>-0.1442342285251969</v>
       </c>
       <c r="O3" t="n">
-        <v>1.535221729395066</v>
+        <v>-2.468945200430228</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.06873765136696679</v>
+        <v>-0.4543315553172582</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.659584485521742</v>
+        <v>-2.044499293326714</v>
       </c>
       <c r="R3" t="n">
-        <v>-2.500046050418585</v>
+        <v>-0.1535767283149235</v>
       </c>
       <c r="S3" t="n">
-        <v>1.196689384042126</v>
+        <v>-1.559093968143183</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8780027809681618</v>
+        <v>-0.6815157471104683</v>
       </c>
       <c r="U3" t="n">
-        <v>0.03213212630869454</v>
+        <v>-0.8830075283106487</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.8538062475952015</v>
+        <v>-0.4426274019118289</v>
       </c>
       <c r="W3" t="n">
-        <v>0.4795157147660868</v>
+        <v>-1.37465423385808</v>
       </c>
       <c r="X3" t="n">
-        <v>0.438958762524325</v>
+        <v>-0.01345762097658052</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.3872329558835634</v>
+        <v>-0.3093757672635858</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.7493902770981796</v>
+        <v>0.1380585680926982</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.2712110104546394</v>
+        <v>-0.4359606654149548</v>
       </c>
       <c r="AB3" t="n">
-        <v>-0.2793966313368364</v>
+        <v>0.5619313556690926</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.4768995921036905</v>
+        <v>1.434842496463831</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.8747258668377962</v>
+        <v>0.3940127144568519</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0.3710923176551593</v>
+        <v>1.077225485123837</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.7310862193275155</v>
+        <v>0.9935641747558817</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.270857230988581</v>
+        <v>-2.190195745339642</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.05160098474741438</v>
+        <v>2.827186659999148</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.06321073122952565</v>
+        <v>-1.921369370681847</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.6716499206907461</v>
+        <v>2.068760229149419</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.237876981250741</v>
+        <v>-1.916625391039207</v>
       </c>
       <c r="AL3" t="n">
-        <v>-0.2653213688041052</v>
+        <v>-0.1967435617298841</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.015901404266013</v>
+        <v>-1.552069771670535</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.6848101261360431</v>
+        <v>-0.1216565910981604</v>
       </c>
       <c r="AO3" t="n">
-        <v>1.524521041206547</v>
+        <v>-0.4698286807825766</v>
       </c>
       <c r="AP3" t="n">
-        <v>-0.07620794561476435</v>
+        <v>0.605823701760119</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.8213816179404625</v>
+        <v>-0.1965802339667821</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.08188070007298981</v>
+        <v>0.3786991612392053</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.376752499594582</v>
+        <v>-1.497268099703011</v>
       </c>
       <c r="AT3" t="n">
-        <v>-1.376918428975976</v>
+        <v>1.497497468313822</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.6085153243438524</v>
+        <v>-1.324962022631639</v>
       </c>
       <c r="AV3" t="n">
-        <v>-0.608646629752653</v>
+        <v>1.325018886225159</v>
       </c>
       <c r="AW3" t="n">
-        <v>-0.6077151572432249</v>
+        <v>-0.7038265476778233</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.1704313275781595</v>
+        <v>0.9493423919051305</v>
       </c>
       <c r="AY3" t="n">
-        <v>-1.321602319653393</v>
+        <v>0.271654677589368</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.09166877809875001</v>
+        <v>1.393047788929016</v>
       </c>
       <c r="BA3" t="n">
         <v>0</v>
@@ -1187,61 +1187,61 @@
         <v>0</v>
       </c>
       <c r="BC3" t="n">
-        <v>-2.294116389057725</v>
+        <v>-0.01246145386359385</v>
       </c>
       <c r="BD3" t="n">
-        <v>2.259274800484606</v>
+        <v>0.0106440745257196</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.7463617055320896</v>
+        <v>-0.0002550199742726515</v>
       </c>
       <c r="BF3" t="n">
-        <v>-0.01021945369279321</v>
+        <v>-0.763776850608557</v>
       </c>
       <c r="BG3" t="n">
-        <v>-0.442559813743473</v>
+        <v>0.4290540513794851</v>
       </c>
       <c r="BH3" t="n">
-        <v>-0.008532123822078019</v>
+        <v>-0.2993409534258161</v>
       </c>
       <c r="BI3" t="n">
-        <v>-0.01241929032600616</v>
+        <v>0.1951753107432104</v>
       </c>
       <c r="BJ3" t="n">
-        <v>-2.2741944519932</v>
+        <v>0.9864243301260859</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.555232814361195</v>
+        <v>0.5672206193122714</v>
       </c>
       <c r="BL3" t="n">
-        <v>-0.4760004838103662</v>
+        <v>0.5803714327989157</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.5455918553434459</v>
+        <v>1.061216196874777</v>
       </c>
       <c r="BN3" t="n">
-        <v>-0.5442534283645826</v>
+        <v>0.4821980650559866</v>
       </c>
       <c r="BO3" t="n">
-        <v>-1.031140055856998</v>
+        <v>0.01469586498536652</v>
       </c>
       <c r="BP3" t="n">
-        <v>-1.05636227418477</v>
+        <v>0.3592826171697351</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.021123290317275</v>
+        <v>1.020525971963942</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.1606598326482637</v>
+        <v>0.6125690168202887</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.8760828935658085</v>
+        <v>0.06540791019667526</v>
       </c>
       <c r="BT3" t="n">
-        <v>-0.2404443296733849</v>
+        <v>0.3174560471392686</v>
       </c>
       <c r="BU3" t="n">
-        <v>-0.3371992117236695</v>
+        <v>0.4778014284392474</v>
       </c>
       <c r="BV3" t="n">
         <v>-0.1632674400202885</v>
@@ -1250,23 +1250,23 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>jyEMLeal</t>
+          <t>4rQsoH7m</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.756185861472116</v>
+        <v>1.726288768371042</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.55946141926701</v>
+        <v>1.603590897175777</v>
       </c>
       <c r="D4" t="n">
-        <v>0.903511731109105</v>
+        <v>-0.1188672092940174</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.7325875313015698</v>
+        <v>0.7576255358211719</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2533773178426463</v>
+        <v>-0.3288111061636256</v>
       </c>
       <c r="G4" t="n">
         <v>-1.075864642027034</v>
@@ -1275,199 +1275,199 @@
         <v>-0.2426890271087325</v>
       </c>
       <c r="I4" t="n">
-        <v>2.608257376220353</v>
+        <v>6.054821412546034</v>
       </c>
       <c r="J4" t="n">
-        <v>-2.712610534209599</v>
+        <v>-4.505087696833641</v>
       </c>
       <c r="K4" t="n">
-        <v>1.095407861696484</v>
+        <v>1.657949954549666</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.7323569457851342</v>
+        <v>-1.075809655154819</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.9009976854300867</v>
+        <v>1.271211230023199</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.716200820833744</v>
+        <v>-1.860134005450838</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.3856083481428794</v>
+        <v>1.535221729395066</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.221663424178339</v>
+        <v>-0.06873765136696679</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.691729409626861</v>
+        <v>1.659584485521742</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.379198778517199</v>
+        <v>-2.500046050418585</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6742393609841558</v>
+        <v>1.196689384042126</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2190936760488248</v>
+        <v>-0.8780027809681618</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7642438500041692</v>
+        <v>0.03213212630869454</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.4426274019118289</v>
+        <v>-0.8538062475952015</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5374585256605923</v>
+        <v>0.4795157147660868</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.4397730592755105</v>
+        <v>0.438958762524325</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.9096894982439255</v>
+        <v>0.3872329558835634</v>
       </c>
       <c r="Z4" t="n">
         <v>-0.7493902770981796</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.9500958192894494</v>
+        <v>0.2712110104546394</v>
       </c>
       <c r="AB4" t="n">
-        <v>-1.062701998549253</v>
+        <v>-0.2793966313368364</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.297136236162119</v>
+        <v>-0.4768995921036905</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.3213449357494562</v>
+        <v>0.8747258668377962</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.42438541737119</v>
+        <v>-0.3710923176551593</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.4142635704534618</v>
+        <v>0.7310862193275155</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.453659324808734</v>
+        <v>1.270857230988581</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.1141141756314624</v>
+        <v>0.05160098474741438</v>
       </c>
       <c r="AI4" t="n">
-        <v>2.343601735294032</v>
+        <v>0.06321073122952565</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-0.01954341107013148</v>
+        <v>0.6716499206907461</v>
       </c>
       <c r="AK4" t="n">
-        <v>-0.4001530422185418</v>
+        <v>2.237876981250741</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.3690233466324378</v>
+        <v>-0.2653213688041052</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.149860754423361</v>
+        <v>1.015901404266013</v>
       </c>
       <c r="AN4" t="n">
-        <v>-0.2700315265375604</v>
+        <v>0.6848101261360431</v>
       </c>
       <c r="AO4" t="n">
-        <v>-0.3725433284904245</v>
+        <v>1.524521041206547</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.4882320384196223</v>
+        <v>-0.07620794561476435</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.2285864676531589</v>
+        <v>0.8213816179404625</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.1039216749120653</v>
+        <v>0.08188070007298981</v>
       </c>
       <c r="AS4" t="n">
-        <v>-1.093613521149979</v>
+        <v>1.376752499594582</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.093787370379862</v>
+        <v>-1.376918428975976</v>
       </c>
       <c r="AU4" t="n">
-        <v>-0.1057796455892749</v>
+        <v>0.6085153243438524</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.1057178564704195</v>
+        <v>-0.608646629752653</v>
       </c>
       <c r="AW4" t="n">
-        <v>-0.4635480715913266</v>
+        <v>-0.6077151572432249</v>
       </c>
       <c r="AX4" t="n">
-        <v>-0.4325965931911088</v>
+        <v>0.1704313275781595</v>
       </c>
       <c r="AY4" t="n">
-        <v>-1.262152431696574</v>
+        <v>-1.321602319653393</v>
       </c>
       <c r="AZ4" t="n">
-        <v>-0.4023053675614708</v>
+        <v>0.09166877809875001</v>
       </c>
       <c r="BA4" t="n">
-        <v>-0.007391996240000759</v>
+        <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.01773587552581747</v>
+        <v>0</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.5579522799349388</v>
+        <v>-2.294116389057725</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.1980299683556268</v>
+        <v>2.259274800484606</v>
       </c>
       <c r="BE4" t="n">
-        <v>-0.07136137478440306</v>
+        <v>0.7463617055320896</v>
       </c>
       <c r="BF4" t="n">
-        <v>-0.5125910516366355</v>
+        <v>-0.01021945369279321</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.2642151597888736</v>
+        <v>-0.442559813743473</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.1936708905117705</v>
+        <v>-0.008532123822078019</v>
       </c>
       <c r="BI4" t="n">
-        <v>-0.4159527837966958</v>
+        <v>-0.01241929032600616</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1.055649165749909</v>
+        <v>-2.2741944519932</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.2686517153563941</v>
+        <v>0.555232814361195</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.0300104255106953</v>
+        <v>-0.4760004838103662</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.02996751381211523</v>
+        <v>0.5455918553434459</v>
       </c>
       <c r="BN4" t="n">
         <v>-0.5442534283645826</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.2761548451959577</v>
+        <v>-1.031140055856998</v>
       </c>
       <c r="BP4" t="n">
-        <v>-1.174332681797645</v>
+        <v>-1.05636227418477</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.689572880174554</v>
+        <v>1.021123290317275</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.691693116227442</v>
+        <v>0.1606598326482637</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.07629023403101545</v>
+        <v>0.8760828935658085</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.6940998239240637</v>
+        <v>-0.2404443296733849</v>
       </c>
       <c r="BU4" t="n">
-        <v>-0.3598407305756544</v>
+        <v>-0.3371992117236695</v>
       </c>
       <c r="BV4" t="n">
         <v>-0.1632674400202885</v>
@@ -1476,23 +1476,23 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>h0AwIDbD</t>
+          <t>jyEMLeal</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1.756185861472116</v>
       </c>
       <c r="C5" t="n">
-        <v>-1.013801175232162</v>
+        <v>-0.55946141926701</v>
       </c>
       <c r="D5" t="n">
-        <v>1.23168274901628</v>
+        <v>0.903511731109105</v>
       </c>
       <c r="E5" t="n">
-        <v>1.784778045363401</v>
+        <v>-0.7325875313015698</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.589632996671424</v>
+        <v>-0.2533773178426463</v>
       </c>
       <c r="G5" t="n">
         <v>-1.075864642027034</v>
@@ -1501,199 +1501,199 @@
         <v>-0.2426890271087325</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8849753580575129</v>
+        <v>2.608257376220353</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.816371952897576</v>
+        <v>-2.712610534209599</v>
       </c>
       <c r="K5" t="n">
-        <v>1.807961179310516</v>
+        <v>1.095407861696484</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.007290114893579867</v>
+        <v>-0.7323569457851342</v>
       </c>
       <c r="M5" t="n">
-        <v>1.097434516786936</v>
+        <v>-0.9009976854300867</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3324045983985919</v>
+        <v>-0.716200820833744</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4431762030790767</v>
+        <v>-0.3856083481428794</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.2692464814211185</v>
+        <v>-1.221663424178339</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.2926011861848117</v>
+        <v>-1.691729409626861</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1622941419682611</v>
+        <v>-0.379198778517199</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2269143381768246</v>
+        <v>-0.6742393609841558</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1123808904192152</v>
+        <v>-0.2190936760488248</v>
       </c>
       <c r="U5" t="n">
-        <v>1.130299711851907</v>
+        <v>0.7642438500041692</v>
       </c>
       <c r="V5" t="n">
-        <v>0.7909091351382892</v>
+        <v>-0.4426274019118289</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.3316836377569864</v>
+        <v>0.5374585256605923</v>
       </c>
       <c r="X5" t="n">
-        <v>0.9609776665638314</v>
+        <v>-0.4397730592755105</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.2130807750967762</v>
+        <v>0.9096894982439255</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.1380585680926981</v>
+        <v>-0.7493902770981796</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.2096657291366851</v>
+        <v>0.9500958192894494</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.4458861160820678</v>
+        <v>-1.062701998549253</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.5361657819435864</v>
+        <v>1.297136236162119</v>
       </c>
       <c r="AD5" t="n">
-        <v>-1.039593000335574</v>
+        <v>0.3213449357494562</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.041712772534988</v>
+        <v>1.42438541737119</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.1889124129224306</v>
+        <v>0.4142635704534618</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.5571637072129447</v>
+        <v>1.453659324808734</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.439393822373281</v>
+        <v>0.1141141756314624</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0.2817980070153636</v>
+        <v>2.343601735294032</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.38738266067982</v>
+        <v>-0.01954341107013148</v>
       </c>
       <c r="AK5" t="n">
-        <v>-0.7476779554899442</v>
+        <v>-0.4001530422185418</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.04327876302988919</v>
+        <v>0.3690233466324378</v>
       </c>
       <c r="AM5" t="n">
-        <v>-0.4846025221569235</v>
+        <v>1.149860754423361</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.2921703772757904</v>
+        <v>-0.2700315265375604</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.08068727161396709</v>
+        <v>-0.3725433284904245</v>
       </c>
       <c r="AP5" t="n">
-        <v>-0.2173179416233605</v>
+        <v>0.4882320384196223</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.3642131215749325</v>
+        <v>0.2285864676531589</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.4727406538859268</v>
+        <v>0.1039216749120653</v>
       </c>
       <c r="AS5" t="n">
-        <v>-0.189427265191185</v>
+        <v>-1.093613521149979</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.1894767510077901</v>
+        <v>1.093787370379862</v>
       </c>
       <c r="AU5" t="n">
-        <v>-0.5356162219120024</v>
+        <v>-0.1057796455892749</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.5355962651527832</v>
+        <v>0.1057178564704195</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.08909242340761471</v>
+        <v>-0.4635480715913266</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.09505283748200123</v>
+        <v>-0.4325965931911088</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.2920374963174203</v>
+        <v>-1.262152431696574</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-1.524973880425609</v>
+        <v>-0.4023053675614708</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.791385088023066</v>
+        <v>-0.007391996240000759</v>
       </c>
       <c r="BB5" t="n">
-        <v>-0.7692844655093862</v>
+        <v>0.01773587552581747</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.7480901912011163</v>
+        <v>0.5579522799349388</v>
       </c>
       <c r="BD5" t="n">
-        <v>-0.7388995007939093</v>
+        <v>0.1980299683556268</v>
       </c>
       <c r="BE5" t="n">
-        <v>-0.03580819737933742</v>
+        <v>-0.07136137478440306</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.066291113329727</v>
+        <v>-0.5125910516366355</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.3748604431853117</v>
+        <v>0.2642151597888736</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.3186278094821272</v>
+        <v>0.1936708905117705</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.423976302025469</v>
+        <v>-0.4159527837966958</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1.427812721964048</v>
+        <v>1.055649165749909</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.4050941537173997</v>
+        <v>0.2686517153563941</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0.2211940783832793</v>
+        <v>0.0300104255106953</v>
       </c>
       <c r="BM5" t="n">
-        <v>-1.516905510781877</v>
+        <v>0.02996751381211523</v>
       </c>
       <c r="BN5" t="n">
-        <v>-1.057479175074867</v>
+        <v>-0.5442534283645826</v>
       </c>
       <c r="BO5" t="n">
-        <v>-1.88682399109166</v>
+        <v>0.2761548451959577</v>
       </c>
       <c r="BP5" t="n">
-        <v>-0.3957279915526675</v>
+        <v>-1.174332681797645</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.5962188950659689</v>
+        <v>0.689572880174554</v>
       </c>
       <c r="BR5" t="n">
-        <v>0.926934109303609</v>
+        <v>0.691693116227442</v>
       </c>
       <c r="BS5" t="n">
-        <v>-0.4048722540091247</v>
+        <v>0.07629023403101545</v>
       </c>
       <c r="BT5" t="n">
-        <v>0.06659441979211961</v>
+        <v>0.6940998239240637</v>
       </c>
       <c r="BU5" t="n">
-        <v>0.2043807326224983</v>
+        <v>-0.3598407305756544</v>
       </c>
       <c r="BV5" t="n">
         <v>-0.1632674400202885</v>
@@ -1702,23 +1702,23 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>4vvdzeEs</t>
+          <t>h0AwIDbD</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.726288768371042</v>
+        <v>1.756185861472116</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.8162621508994871</v>
+        <v>-1.013801175232162</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03259633743237113</v>
+        <v>1.23168274901628</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5303048984634655</v>
+        <v>1.784778045363401</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.9969389455780144</v>
+        <v>-1.589632996671424</v>
       </c>
       <c r="G6" t="n">
         <v>-1.075864642027034</v>
@@ -1727,1105 +1727,201 @@
         <v>-0.2426890271087325</v>
       </c>
       <c r="I6" t="n">
-        <v>-8.593075741838106</v>
+        <v>0.8849753580575129</v>
       </c>
       <c r="J6" t="n">
-        <v>7.14601386022264</v>
+        <v>-1.816371952897576</v>
       </c>
       <c r="K6" t="n">
-        <v>-6.592667407297007</v>
+        <v>1.807961179310516</v>
       </c>
       <c r="L6" t="n">
-        <v>6.098535829456354</v>
+        <v>-0.007290114893579867</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.638764817792715</v>
+        <v>1.097434516786936</v>
       </c>
       <c r="N6" t="n">
-        <v>0.7137156599376231</v>
+        <v>0.3324045983985919</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.8849625437887</v>
+        <v>0.4431762030790767</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1626186910032081</v>
+        <v>-0.2692464814211185</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.529557883414011</v>
+        <v>0.2926011861848117</v>
       </c>
       <c r="R6" t="n">
-        <v>1.019657932736907</v>
+        <v>0.1622941419682611</v>
       </c>
       <c r="S6" t="n">
-        <v>-2.368850213809008</v>
+        <v>-0.2269143381768246</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5922622654842412</v>
+        <v>-0.1123808904192152</v>
       </c>
       <c r="U6" t="n">
-        <v>-2.713286837549335</v>
+        <v>1.130299711851907</v>
       </c>
       <c r="V6" t="n">
-        <v>1.202087980821662</v>
+        <v>0.7909091351382892</v>
       </c>
       <c r="W6" t="n">
-        <v>-2.765281695326205</v>
+        <v>-0.3316836377569864</v>
       </c>
       <c r="X6" t="n">
-        <v>1.239387748718235</v>
+        <v>0.9609776665638314</v>
       </c>
       <c r="Y6" t="n">
-        <v>-1.702593213557885</v>
+        <v>0.2130807750967762</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.380486951359927</v>
+        <v>0.1380585680926981</v>
       </c>
       <c r="AA6" t="n">
-        <v>-2.472615091919386</v>
+        <v>-0.2096657291366851</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.954474230713389</v>
+        <v>0.4458861160820678</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.184384450244839</v>
+        <v>0.5361657819435864</v>
       </c>
       <c r="AD6" t="n">
-        <v>-1.406893574535924</v>
+        <v>-1.039593000335574</v>
       </c>
       <c r="AE6" t="n">
-        <v>3.315189795011498</v>
+        <v>1.041712772534988</v>
       </c>
       <c r="AF6" t="n">
-        <v>-1.040015122550191</v>
+        <v>-0.1889124129224306</v>
       </c>
       <c r="AG6" t="n">
-        <v>-1.300558888748232</v>
+        <v>-0.5571637072129447</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.152044198451429</v>
+        <v>1.439393822373281</v>
       </c>
       <c r="AI6" t="n">
-        <v>-1.303722624095159</v>
+        <v>-0.2817980070153636</v>
       </c>
       <c r="AJ6" t="n">
-        <v>2.251987810586622</v>
+        <v>1.38738266067982</v>
       </c>
       <c r="AK6" t="n">
-        <v>-0.6844916076224161</v>
+        <v>-0.7476779554899442</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.5747567678551001</v>
+        <v>0.04327876302988919</v>
       </c>
       <c r="AM6" t="n">
-        <v>-0.4631098929720854</v>
+        <v>-0.4846025221569235</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.338909179633432</v>
+        <v>0.2921703772757904</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.4941500188556152</v>
+        <v>-0.08068727161396709</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.664148671824593</v>
+        <v>-0.2173179416233605</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.2819183532883477</v>
+        <v>0.3642131215749325</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.189807035317183</v>
+        <v>0.4727406538859268</v>
       </c>
       <c r="AS6" t="n">
-        <v>-2.256138707382712</v>
+        <v>-0.189427265191185</v>
       </c>
       <c r="AT6" t="n">
-        <v>2.256472452429668</v>
+        <v>0.1894767510077901</v>
       </c>
       <c r="AU6" t="n">
-        <v>-2.307445625655016</v>
+        <v>-0.5356162219120024</v>
       </c>
       <c r="AV6" t="n">
-        <v>2.307598106070561</v>
+        <v>0.5355962651527832</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.5936772231892572</v>
+        <v>0.08909242340761471</v>
       </c>
       <c r="AX6" t="n">
-        <v>-1.161255330787307</v>
+        <v>0.09505283748200123</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.02049905751271614</v>
+        <v>0.2920374963174203</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-0.051299620274152</v>
+        <v>-1.524973880425609</v>
       </c>
       <c r="BA6" t="n">
-        <v>-1.604946164766134</v>
+        <v>0.791385088023066</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.591776557596225</v>
+        <v>-0.7692844655093862</v>
       </c>
       <c r="BC6" t="n">
-        <v>-0.01246145386359385</v>
+        <v>0.7480901912011163</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.0106440745257196</v>
+        <v>-0.7388995007939093</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.4619362862915706</v>
+        <v>-0.03580819737933742</v>
       </c>
       <c r="BF6" t="n">
-        <v>-0.6920094794737222</v>
+        <v>1.066291113329727</v>
       </c>
       <c r="BG6" t="n">
-        <v>0.1580860104086173</v>
+        <v>0.3748604431853117</v>
       </c>
       <c r="BH6" t="n">
-        <v>-0.2811654015755821</v>
+        <v>0.3186278094821272</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.9525804313831422</v>
+        <v>0.423976302025469</v>
       </c>
       <c r="BJ6" t="n">
-        <v>-1.137845862620661</v>
+        <v>1.427812721964048</v>
       </c>
       <c r="BK6" t="n">
-        <v>-0.3622556386148197</v>
+        <v>0.4050941537173997</v>
       </c>
       <c r="BL6" t="n">
-        <v>-1.002032389656645</v>
+        <v>-0.2211940783832793</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.02996751381211523</v>
+        <v>-1.516905510781877</v>
       </c>
       <c r="BN6" t="n">
-        <v>0.9954238117662711</v>
+        <v>-1.057479175074867</v>
       </c>
       <c r="BO6" t="n">
-        <v>-1.506520019876255</v>
+        <v>-1.88682399109166</v>
       </c>
       <c r="BP6" t="n">
-        <v>1.86930383461454</v>
+        <v>-0.3957279915526675</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.5937004493113501</v>
+        <v>0.5962188950659689</v>
       </c>
       <c r="BR6" t="n">
-        <v>0.6395600253559748</v>
+        <v>0.926934109303609</v>
       </c>
       <c r="BS6" t="n">
-        <v>0.2915203704375548</v>
+        <v>-0.4048722540091247</v>
       </c>
       <c r="BT6" t="n">
-        <v>-1.228106028466889</v>
+        <v>0.06659441979211961</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.625332574766952</v>
+        <v>0.2043807326224983</v>
       </c>
       <c r="BV6" t="n">
-        <v>-0.1632674400202885</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>YemQuHjK</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1.726288768371042</v>
-      </c>
-      <c r="C7" t="n">
-        <v>1.00109687296112</v>
-      </c>
-      <c r="D7" t="n">
-        <v>-0.8761849429259599</v>
-      </c>
-      <c r="E7" t="n">
-        <v>-0.2442691251257562</v>
-      </c>
-      <c r="F7" t="n">
-        <v>-1.52497546382487</v>
-      </c>
-      <c r="G7" t="n">
-        <v>-1.075864642027034</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-0.2426890271087325</v>
-      </c>
-      <c r="I7" t="n">
-        <v>3.469898385301773</v>
-      </c>
-      <c r="J7" t="n">
-        <v>-7.193803440769705</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1.020402249316059</v>
-      </c>
-      <c r="L7" t="n">
-        <v>-2.068006371111684</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0.3154393072237531</v>
-      </c>
-      <c r="N7" t="n">
-        <v>-0.3348897592947123</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0.2806694283296738</v>
-      </c>
-      <c r="P7" t="n">
-        <v>-0.6047131778578724</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0.2044087152598477</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0.7489114724941767</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0.179596357732027</v>
-      </c>
-      <c r="T7" t="n">
-        <v>-0.6578017947483319</v>
-      </c>
-      <c r="U7" t="n">
-        <v>-0.3339237355390429</v>
-      </c>
-      <c r="V7" t="n">
-        <v>-0.6482168247535152</v>
-      </c>
-      <c r="W7" t="n">
-        <v>-0.1216409482644048</v>
-      </c>
-      <c r="X7" t="n">
-        <v>-0.9269907030457166</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0.03892859430998871</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>-0.03943120094547738</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0.4480039294220376</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>-0.4897286280883187</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>-0.6605381910045027</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>-0.06685981469693703</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>-0.3209472189536206</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>0.6361965263407937</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>-0.2910851039858334</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>-0.5776984701520034</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>0.8869179797077624</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>-1.509494480658814</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>-0.2685148174945253</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0.5290382298056191</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>0.01740388808893119</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>-0.8849760831828855</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0.332775475627681</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>-0.1937996089552605</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>0.5135548303876725</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>0.4051483310460968</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>1.328313950168218</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>-1.3284732172239</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>1.296043914066408</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>-1.296242130819682</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>0.4014544423200602</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>-0.1310826328064749</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>1.032613243436657</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>0.6305496642735365</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>1.590162172286133</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>-1.55630480654459</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>0.3678143686687612</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>-0.3641277131340949</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>0.9241275925574143</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>0.7792216287903896</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>0.8230867442912889</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>-0.1687041745022618</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>-1.279606312145612</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>0.02071703447101183</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>0.1546734281861322</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>-0.4018581377294628</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>0.5455918553434459</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>0.4821980650559866</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>0.5138448272055861</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>0.5008471063051857</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>0.8652362003113235</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>1.077257977044864</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>0.6286278386305324</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>0.170257293491269</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>-0.1278193258329912</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>-0.1632674400202885</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>KSw0hfzQ</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1.756185861472116</v>
-      </c>
-      <c r="C8" t="n">
-        <v>-1.033555077665429</v>
-      </c>
-      <c r="D8" t="n">
-        <v>-0.295574680474804</v>
-      </c>
-      <c r="E8" t="n">
-        <v>-1.641870080732395</v>
-      </c>
-      <c r="F8" t="n">
-        <v>-0.1025097412006875</v>
-      </c>
-      <c r="G8" t="n">
-        <v>-1.075864642027034</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-0.2426890271087325</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1.746616367138933</v>
-      </c>
-      <c r="J8" t="n">
-        <v>-0.920133371585556</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1.882966791690938</v>
-      </c>
-      <c r="L8" t="n">
-        <v>-1.762715073894186</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0.5761043770781469</v>
-      </c>
-      <c r="N8" t="n">
-        <v>-0.5255452900642281</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.015200050196976</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0.2705849841092898</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0.9540447181220355</v>
-      </c>
-      <c r="R8" t="n">
-        <v>-0.2889499584362892</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.143581768086841</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0.1383094631233607</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0.7642438500041692</v>
-      </c>
-      <c r="V8" t="n">
-        <v>-0.2370379790701423</v>
-      </c>
-      <c r="W8" t="n">
-        <v>-0.005755326475394206</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0.5259619131975759</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0.5613851366703508</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>-0.5719005080600039</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>-0.181378862101901</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>0.4748974259788243</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>-0.09745543522946014</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>-0.5624472984530077</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>-0.3808177059715563</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>0.05968117774159281</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>-0.1549991008086095</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>-0.2984728842032553</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>0.3743513939040028</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>-0.7655414212073144</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1.463844219873526</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>-1.088255053694754</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1.210756537113735</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>-0.4485451207380885</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>0.5030248421389478</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>0.3000853770748276</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>0.8693843100588422</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>0.07306431013736013</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>0.4725662436357894</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>-0.4726078096039055</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>0.8215967040593928</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>-0.821748746877244</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>0.6897886136238556</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>0.3211883077704766</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>0.304776758022453</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>0.1659023695616033</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>1.128366013733471</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>-1.113671288453724</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>0.6752553507219596</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>-0.04610313926020954</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>0.4651831235089345</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>0.1811751986147352</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>0.6001551524725387</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>-0.3675967328538813</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>0.9202251535028072</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>-0.8687660367833159</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>0.5455918553434459</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>-1.057479175074867</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>-0.2467631152252246</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>0.1705299649891344</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>0.8256330299942235</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>-0.2898729440285797</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>0.7556292956037119</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>-1.542193275777223</v>
-      </c>
-      <c r="BU8" t="n">
-        <v>0.9645244881684194</v>
-      </c>
-      <c r="BV8" t="n">
-        <v>6.124919946535174</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>hMoEUjrJ</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1.726288768371042</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.7146652876787414</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.9666215422451002</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1.784778045363401</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1.136759638358259</v>
-      </c>
-      <c r="G9" t="n">
-        <v>-1.075864642027034</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-0.2426890271087325</v>
-      </c>
-      <c r="I9" t="n">
-        <v>-4.284870696431007</v>
-      </c>
-      <c r="J9" t="n">
-        <v>3.561059534974553</v>
-      </c>
-      <c r="K9" t="n">
-        <v>-4.792532710166823</v>
-      </c>
-      <c r="L9" t="n">
-        <v>4.266788046151374</v>
-      </c>
-      <c r="M9" t="n">
-        <v>-0.7272209721938242</v>
-      </c>
-      <c r="N9" t="n">
-        <v>-0.1442342285251971</v>
-      </c>
-      <c r="O9" t="n">
-        <v>-0.8048758269963393</v>
-      </c>
-      <c r="P9" t="n">
-        <v>-0.02246638289293197</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0.1603124797973668</v>
-      </c>
-      <c r="R9" t="n">
-        <v>-0.5145720086385641</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0.03429735397344136</v>
-      </c>
-      <c r="T9" t="n">
-        <v>-0.6815157471104675</v>
-      </c>
-      <c r="U9" t="n">
-        <v>-1.432091321082255</v>
-      </c>
-      <c r="V9" t="n">
-        <v>-0.8538062475952017</v>
-      </c>
-      <c r="W9" t="n">
-        <v>-1.49053985564709</v>
-      </c>
-      <c r="X9" t="n">
-        <v>-0.4310727442081855</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>-1.005984490410735</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>0.4930381061690494</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>-1.68058281494544</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.374248032778266</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>0.41535947694464</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.173617646436405</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.134355775023741</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.763540164194363</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>0.1496710555583114</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>0.7642513608255618</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>0.8636559593817705</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>-0.1127931623372786</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>-0.05262812894713883</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>0.5233234125494344</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>-0.606394087537671</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>-0.5435978137539537</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>1.548842379279586</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>0.6763786997644171</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>0.8518595176981627</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>0.790130691568614</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>0.2142273133618476</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>-0.2142333469261701</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>0.6819916621767984</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>-0.6821301184163061</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>0.257287356668162</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>-0.7341105535757427</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>0.1765348568584569</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>0.1173297726785017</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>-0.8061690805030673</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>0.8047562165610213</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>-0.2025993651297713</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>0.7601876498453486</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>0.6397021733168957</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>0.6715705720881375</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>1.061312813644843</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>0.3004522576318927</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>-2.011560847853138</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>-0.7208995055299064</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>0.1982513893917476</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>-0.2237148557969563</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>0.02996751381211523</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>1.508649558476556</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>-1.126216048660849</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>2.246809138975741</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>0.9566534803924921</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>1.107809906054893</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>0.3140727874469534</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>0.2066851321053056</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>0.1073787197411249</v>
-      </c>
-      <c r="BV9" t="n">
-        <v>-0.1632674400202885</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>06X4YYrf</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1.726288768371042</v>
-      </c>
-      <c r="C10" t="n">
-        <v>1.909776384891423</v>
-      </c>
-      <c r="D10" t="n">
-        <v>-1.292709696423528</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0.3029842611057592</v>
-      </c>
-      <c r="F10" t="n">
-        <v>-0.3503636171124769</v>
-      </c>
-      <c r="G10" t="n">
-        <v>-1.075864642027034</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-0.2426890271087325</v>
-      </c>
-      <c r="I10" t="n">
-        <v>-0.8383066601053271</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1.76858237235051</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1.695452760739878</v>
-      </c>
-      <c r="L10" t="n">
-        <v>-1.724553661741999</v>
-      </c>
-      <c r="M10" t="n">
-        <v>-1.248551111902613</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0.523060129168108</v>
-      </c>
-      <c r="O10" t="n">
-        <v>-0.3628573996779628</v>
-      </c>
-      <c r="P10" t="n">
-        <v>-0.2538227252631069</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>-0.2806498748274494</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0.3879161921705365</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0.4995806806161031</v>
-      </c>
-      <c r="T10" t="n">
-        <v>-0.08189152309646905</v>
-      </c>
-      <c r="U10" t="n">
-        <v>-0.5169516664629115</v>
-      </c>
-      <c r="V10" t="n">
-        <v>2.024445672188407</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0.1246159980372425</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0.5085612830629258</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>-1.005984490410735</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.025507413283576</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0.5470079640437807</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>-0.4534644907173735</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0.4185805636637382</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.367345910827832</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>-0.3324050598712813</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.12337003808401</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>-1.205095573086596</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0.4579367254937268</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>-0.4787765170631615</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>-0.9863142972336584</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>0.1869534400505703</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>-0.6139252214313941</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>0.1291655598500881</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>-0.5429023062440811</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0.6489528705771759</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>-0.02917128027856449</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>0.3779281764658989</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>-0.2942852705138977</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>-0.2217196314754276</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>0.2217735588425068</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>0.5145705781145876</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>-0.5146927406755556</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>1.122289870579549</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>1.376487169116696</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>0.8780435347489264</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>2.612861495559359</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>0.2588670318476882</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>-0.2446042381525837</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>-0.01246145386359385</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>0.0106440745257196</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>0.7463617055320896</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>0.4562684586836333</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>0.01469875539486639</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>0.4026897367894572</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>1.921765805932537</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>-0.2850790277162059</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>0.09472175086621838</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>0.457970752252654</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>0.02996751381211523</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>0.9954238117662711</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>1.797370730057579</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>0.33568853564716</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>-0.1821633993118731</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>1.090691804411837</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>-0.8612339451461711</v>
-      </c>
-      <c r="BT10" t="n">
-        <v>-0.3724822348657724</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>-0.647308514417538</v>
-      </c>
-      <c r="BV10" t="n">
         <v>-0.1632674400202885</v>
       </c>
     </row>

--- a/data/spain/p6_deployment/data_preparation/df_selected_nan.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_selected_nan.xlsx
@@ -573,1063 +573,1063 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>ll7vCuXF</t>
+          <t>2Xrca2mA</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.4018186250117249</v>
+        <v>0.4239096439895982</v>
       </c>
       <c r="C2" t="n">
         <v>-0.3097959401686102</v>
       </c>
       <c r="D2" t="n">
-        <v>-2.71031282951045</v>
+        <v>3.508392814279567</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.379434139523683</v>
+        <v>1.998254918622938</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.233349274399689</v>
+        <v>0.1943965853200431</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7208058826432722</v>
+        <v>-0.09801446591336728</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3382780871930121</v>
+        <v>-1.370367033875862</v>
       </c>
       <c r="I2" t="n">
-        <v>1.024259725215397</v>
+        <v>1.356970320789266</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7553934803152608</v>
+        <v>0.5145874538729694</v>
       </c>
       <c r="K2" t="n">
-        <v>0.5968391393997149</v>
+        <v>-0.06339331463549755</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6867775587184087</v>
+        <v>-1.354454925720055</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.2741274646668614</v>
+        <v>0.8854584686140449</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01038063174353976</v>
+        <v>-1.436407270222881</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.5399534478153962</v>
+        <v>1.07679995559127</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.09122261294135862</v>
+        <v>-0.7024761930270691</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>0.750694454908817</v>
+        <v>1.176270662791933</v>
       </c>
       <c r="T2" t="n">
-        <v>0.02711451441102743</v>
+        <v>0.7185346318922269</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6884846073335283</v>
+        <v>-0.02252654504998304</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.086532355109817</v>
+        <v>0.7021791925354133</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.002997864758714988</v>
+        <v>-1.458504174687621</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.6147217934960196</v>
+        <v>-0.06216137689557534</v>
       </c>
       <c r="Y2" t="n">
-        <v>-1.183569633170075</v>
+        <v>-0.1646117133838152</v>
       </c>
       <c r="Z2" t="n">
-        <v>-0.4314007377642196</v>
+        <v>-0.7132575737233142</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.426796664744119</v>
+        <v>-1.32359045641759</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.08177452209805446</v>
+        <v>-0.4205251519600463</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.2841122119346325</v>
+        <v>-0.543872280971335</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>YNHbsZ6C</t>
+          <t>f1xuAJ1S</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4018186250117249</v>
+        <v>-1.453826969129633</v>
       </c>
       <c r="C3" t="n">
         <v>-0.3097959401686102</v>
       </c>
       <c r="D3" t="n">
-        <v>1.435490933016228</v>
+        <v>0.283878776758817</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5086074365685306</v>
+        <v>0.7961440435697303</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4323542286066655</v>
+        <v>1.304865587324279</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.390711441871958</v>
+        <v>0.5570418129319442</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.426961266174586</v>
+        <v>2.004864251435575</v>
       </c>
       <c r="I3" t="n">
-        <v>1.356970320789266</v>
+        <v>1.024259725215397</v>
       </c>
       <c r="J3" t="n">
-        <v>1.718617586084426</v>
+        <v>0.7553934803152608</v>
       </c>
       <c r="K3" t="n">
-        <v>0.942882376956333</v>
+        <v>-0.4672463016328856</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6257041549599262</v>
+        <v>-0.3318725279673022</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5477290655459808</v>
+        <v>0.1897069086455015</v>
       </c>
       <c r="O3" t="n">
-        <v>0.08886063801998015</v>
+        <v>1.70878382100847</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.2704945472476187</v>
+        <v>-0.2031298221056741</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.2542235676308814</v>
+        <v>-0.009722135596597209</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8306142490208803</v>
+        <v>-0.6832340099333994</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7185346318922269</v>
+        <v>-0.6643056030701721</v>
       </c>
       <c r="U3" t="n">
         <v>-0.7335376974334945</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.4840189916924765</v>
+        <v>-0.31994169183329</v>
       </c>
       <c r="W3" t="n">
-        <v>-2.224560127281782</v>
+        <v>-2.914010484616526</v>
       </c>
       <c r="X3" t="n">
-        <v>0.9766870473361574</v>
+        <v>0.3800154697293414</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.6175164397521969</v>
+        <v>-0.009313015429009945</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.4314007377642196</v>
+        <v>-0.7132575737233142</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.1154399343858682</v>
+        <v>0.2213184512292846</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8346942843785784</v>
+        <v>0.2017539966970474</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.133640527046181</v>
+        <v>0.544974656154859</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Gz9WD123</t>
+          <t>65kl1OIc</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.2498664348355377</v>
+        <v>0.6116833053015214</v>
       </c>
       <c r="C4" t="n">
         <v>-0.3097959401686102</v>
       </c>
       <c r="D4" t="n">
-        <v>1.435490933016228</v>
+        <v>0.05355634550733503</v>
       </c>
       <c r="E4" t="n">
-        <v>1.270752659945204</v>
+        <v>1.007466128233262</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2815187012532004</v>
+        <v>0.3530350141777914</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.81753719788231</v>
+        <v>0.3113957083649523</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.8446300735469773</v>
+        <v>-0.4012585703362851</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6915491296415284</v>
+        <v>0.3588385340676596</v>
       </c>
       <c r="J4" t="n">
         <v>0.5145874538729694</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.7638002930696478</v>
+        <v>0.2944141041964158</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.310139041040365</v>
+        <v>0.6780670468337456</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1389750240644616</v>
+        <v>0.2549336173925521</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.07049571060240875</v>
+        <v>0.4147623434732851</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.001035646679840764</v>
+        <v>-0.6746828980992853</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.07177834174816419</v>
+        <v>-0.7160596059178626</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2932587258359444</v>
+        <v>-0.8797295675091525</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6643056030701721</v>
+        <v>-0.2033588580827057</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.02252654504998304</v>
+        <v>-0.9705414148946649</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.3710477360517253</v>
+        <v>2.133148430651598</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.7307510197231677</v>
+        <v>-1.822380752169847</v>
       </c>
       <c r="X4" t="n">
-        <v>2.337312926218249</v>
+        <v>0.3146098042699321</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0636470673600357</v>
+        <v>-0.9124105230311773</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0.4314007377642196</v>
+        <v>-0.7132575737233142</v>
       </c>
       <c r="AA4" t="n">
-        <v>-0.6261981465119313</v>
+        <v>0.2931448593450513</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.06108854096989604</v>
+        <v>-0.4205251519600463</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.2124800969117998</v>
+        <v>2.005233133266385</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>CvbDaBsg</t>
+          <t>0SQqjbAd</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.307550403104531</v>
+        <v>-1.520100026063253</v>
       </c>
       <c r="C5" t="n">
         <v>-0.3097959401686102</v>
       </c>
       <c r="D5" t="n">
-        <v>0.05355634550733503</v>
+        <v>1.896135795519192</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.6129585455596424</v>
+        <v>-0.07339437037365608</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4125244249994469</v>
+        <v>-0.02373125435936023</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3318662170788685</v>
+        <v>0.04527909508404478</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4532830472649555</v>
+        <v>0.09293417237286632</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.722470901547414</v>
+        <v>0.6915491296415285</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.9302487047807788</v>
+        <v>0.5145874538729694</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.5274141898268482</v>
+        <v>-1.274520158852697</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4404262838013197</v>
+        <v>0.6660679736556924</v>
       </c>
       <c r="M5" t="n">
-        <v>0.09272344995743113</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0.08804403475586697</v>
+        <v>-0.3997492741056258</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.9682823607100958</v>
+        <v>0.4170089085384505</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2684232538879369</v>
+        <v>-0.2704945472476183</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.17272309028612</v>
+        <v>0.07177834174816419</v>
       </c>
       <c r="R5" t="n">
-        <v>-1.583126244040831</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1.391625012703264</v>
+        <v>-0.9454951898895119</v>
       </c>
       <c r="T5" t="n">
-        <v>0.02711451441102743</v>
+        <v>-0.6643056030701721</v>
       </c>
       <c r="U5" t="n">
-        <v>2.110506912100552</v>
+        <v>-0.7335376974334945</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.6840722568896406</v>
+        <v>0.3444368830063673</v>
       </c>
       <c r="W5" t="n">
-        <v>1.702673592189221</v>
+        <v>-1.458504174687621</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1879874262999243</v>
+        <v>0.4284879951853053</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.8041601387817557</v>
+        <v>0.9118642122551711</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.9870613572264346</v>
+        <v>-0.7132575737233142</v>
       </c>
       <c r="AA5" t="n">
-        <v>-1.299643867988773</v>
+        <v>-0.9985437045781238</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.4210280012893089</v>
+        <v>0.2634027060161795</v>
       </c>
       <c r="AC5" t="n">
-        <v>-1.789189546331395</v>
+        <v>0.02631547403007915</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>YgnMckC5</t>
+          <t>8Uo5ctIM</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4018186250117249</v>
+        <v>1.307550403104531</v>
       </c>
       <c r="C6" t="n">
         <v>-0.3097959401686102</v>
       </c>
       <c r="D6" t="n">
-        <v>-5.059601628275568</v>
+        <v>-1.789023104504522</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.7038963278943591</v>
+        <v>-2.210865292298236</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.6344892054616895</v>
+        <v>-1.828243382616244</v>
       </c>
       <c r="G6" t="n">
-        <v>0.712617679157706</v>
+        <v>-0.4869541314777712</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5912889993512876</v>
+        <v>0.1542701510779026</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.12359182951445</v>
+        <v>-1.886957986055955</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.2078306254539047</v>
+        <v>-1.251323406703834</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.298552626018501</v>
+        <v>0.2587671814966269</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.3023725514883061</v>
+        <v>1.234646210621348</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.647637281785559</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5729438397815563</v>
+        <v>-1.404723749615744</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5799475423029593</v>
+        <v>-0.6276438467633906</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.092344193979341</v>
+        <v>-0.001035646679840764</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.4385304897995905</v>
+        <v>0.234779296437687</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.2946749021016778</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2337889024897154</v>
+        <v>1.981595095076349</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3877375560776923</v>
+        <v>0.7185346318922269</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.02252654504998304</v>
+        <v>0.6884846073335283</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.3486888417061597</v>
+        <v>-2.721925770099743</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.002997864758714988</v>
+        <v>0.6987641060998647</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.4135932858032618</v>
+        <v>0.5206014688860386</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.09142810536802561</v>
+        <v>-0.06810708740699205</v>
       </c>
       <c r="Z6" t="n">
-        <v>-1.148122406345917</v>
+        <v>-0.7132575737233142</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.7245284384313951</v>
+        <v>0.1806924497077511</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.08177452209805446</v>
+        <v>-2.878307962011887</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.4234295243809658</v>
+        <v>-1.984660737691543</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hzRnqjcC</t>
+          <t>h2NyhKup</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.926098934484983</v>
+        <v>0.6116833053015214</v>
       </c>
       <c r="C7" t="n">
         <v>-0.3097959401686102</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.401280123264897</v>
+        <v>-1.789023104504522</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.79514971591096</v>
+        <v>0.7511081894611082</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.7177743806120075</v>
+        <v>-0.6384551661831334</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.03660293977161932</v>
+        <v>-1.326244988748327</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4302820552505668</v>
+        <v>0.04912275901212546</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.471069741588619</v>
+        <v>-1.13835914601475</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.411860757665362</v>
+        <v>-0.8499800293000151</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3460177214469446</v>
+        <v>0.6486025680523185</v>
       </c>
       <c r="L7" t="n">
-        <v>0.9540299073844987</v>
+        <v>-1.23040351027912</v>
       </c>
       <c r="M7" t="n">
-        <v>0.8947809093456706</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4625601788250083</v>
+        <v>0.486850804048733</v>
       </c>
       <c r="O7" t="n">
-        <v>0.8571628486135195</v>
+        <v>-0.01957356912532969</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2010585287459926</v>
+        <v>-1.078871248950952</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.57953717262625</v>
+        <v>0.261946122219274</v>
       </c>
       <c r="R7" t="n">
-        <v>-1.326465707625869</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5238585173229063</v>
+        <v>-0.07490971502892768</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6643056030701721</v>
+        <v>-1.125252348057638</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6884846073335283</v>
+        <v>0.451480889872358</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.01330542652267886</v>
+        <v>-0.7287900455807714</v>
       </c>
       <c r="W7" t="n">
-        <v>1.361539300799634</v>
+        <v>-1.094627597205394</v>
       </c>
       <c r="X7" t="n">
-        <v>0.600943602073828</v>
+        <v>-0.3737051140123193</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.4709204802661934</v>
+        <v>-0.2915349386013157</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0.4314007377642196</v>
+        <v>-0.7132575737233142</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.359357640546857</v>
+        <v>0.9499009442706992</v>
       </c>
       <c r="AB7" t="n">
-        <v>-1.640422343394405</v>
+        <v>-0.08674105908170035</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.3107628394237464</v>
+        <v>0.8354678777054844</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>4Ef51XCt</t>
+          <t>ll7vCuXF</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4239096439895982</v>
+        <v>0.4018186250117249</v>
       </c>
       <c r="C8" t="n">
         <v>-0.3097959401686102</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6374109482471113</v>
+        <v>-2.71031282951045</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4782948424569585</v>
+        <v>-1.455648661861351</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1823696832171081</v>
+        <v>-1.530796328507966</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.8349527796143428</v>
+        <v>0.7208058826432722</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1082681670491252</v>
+        <v>0.3190010653142857</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.72060268826902</v>
+        <v>0.7747267785349956</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.893472810549945</v>
+        <v>0.7553934803152608</v>
       </c>
       <c r="K8" t="n">
-        <v>0.05359894209612109</v>
+        <v>0.4932194883771746</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.557699351300999</v>
+        <v>0.6413465303676534</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3395103605384279</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2304039149577638</v>
+        <v>-0.2741274646668614</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2073633668801681</v>
+        <v>0.01038063174353976</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2010585287459926</v>
+        <v>-0.7420476232412295</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.07177834174816419</v>
+        <v>0.3162797737824484</v>
       </c>
       <c r="R8" t="n">
-        <v>-2.121085646899331</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1740589759971815</v>
+        <v>0.750694454908817</v>
       </c>
       <c r="T8" t="n">
         <v>0.02711451441102743</v>
       </c>
       <c r="U8" t="n">
-        <v>1.39949575971704</v>
+        <v>0.6884846073335283</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.01330542652267886</v>
+        <v>-1.086532355109817</v>
       </c>
       <c r="W8" t="n">
-        <v>1.020405009410047</v>
+        <v>-0.002997864758714988</v>
       </c>
       <c r="X8" t="n">
-        <v>0.1416304737984066</v>
+        <v>-0.5871627258392379</v>
       </c>
       <c r="Y8" t="n">
-        <v>-0.8026983316346978</v>
+        <v>-1.197650974482799</v>
       </c>
       <c r="Z8" t="n">
-        <v>-0.004588957597590797</v>
+        <v>-0.7132575737233142</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.003667283358006525</v>
+        <v>1.442248435922301</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0.1191665299248155</v>
+        <v>-0.4205251519600463</v>
       </c>
       <c r="AC8" t="n">
-        <v>-0.2048384609647768</v>
+        <v>0.3197067258360914</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>CQIvoCSa</t>
+          <t>YNHbsZ6C</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8767755330360011</v>
+        <v>-0.2498664348355377</v>
       </c>
       <c r="C9" t="n">
         <v>-0.3097959401686102</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.6374109482471113</v>
+        <v>1.435490933016228</v>
       </c>
       <c r="E9" t="n">
-        <v>1.933299359812426</v>
+        <v>0.5022258378081997</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1150773708911694</v>
+        <v>0.5315032466427578</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.09801446591336728</v>
+        <v>-1.71518465431273</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.501801273958083</v>
+        <v>-0.3742338458842919</v>
       </c>
       <c r="I9" t="n">
-        <v>0.525193831854594</v>
+        <v>1.024259725215397</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2737814274306781</v>
+        <v>1.237005533199844</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6804607465549539</v>
+        <v>0.5902855831130281</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.1163404560214907</v>
+        <v>0.5064573490301876</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2778136328931787</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>1.567272697653731</v>
+        <v>0.5477290655459808</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.7244189572628168</v>
+        <v>0.08886063801998015</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.4052239975315075</v>
+        <v>-0.6746828980992853</v>
       </c>
       <c r="Q9" t="n">
         <v>-0.8247269090442112</v>
       </c>
       <c r="R9" t="n">
-        <v>-0.09987253095655256</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9671315892007804</v>
+        <v>0.8306142490208803</v>
       </c>
       <c r="T9" t="n">
         <v>0.7185346318922269</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.02252654504998304</v>
+        <v>-0.7335376974334945</v>
       </c>
       <c r="V9" t="n">
-        <v>2.334378479761687</v>
+        <v>-0.4840189916924765</v>
       </c>
       <c r="W9" t="n">
-        <v>0.3381364266308723</v>
+        <v>-2.224560127281782</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.163130015000578</v>
+        <v>1.023050317790189</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0.2545051848704901</v>
+        <v>0.6483910837933486</v>
       </c>
       <c r="Z9" t="n">
-        <v>-0.2622866361887629</v>
+        <v>-0.7132575737233142</v>
       </c>
       <c r="AA9" t="n">
-        <v>-0.08131078736216305</v>
+        <v>0.129037792716401</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.622899581912565</v>
+        <v>0.8346942843785784</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.299383172538067</v>
+        <v>1.168096655482697</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>KApUeTtI</t>
+          <t>Gz9WD123</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-1.542191045041126</v>
+        <v>-1.520100026063253</v>
       </c>
       <c r="C10" t="n">
         <v>-0.3097959401686102</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.71031282951045</v>
+        <v>1.435490933016228</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.567489654392284</v>
+        <v>1.163359469378491</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2418590940387636</v>
+        <v>-0.3410081120748559</v>
       </c>
       <c r="G10" t="n">
-        <v>1.314450635346836</v>
+        <v>-1.71518465431273</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3152770951786234</v>
+        <v>-0.9059660522520135</v>
       </c>
       <c r="I10" t="n">
-        <v>0.02612793849379083</v>
+        <v>0.6083714807480611</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6894426783384875</v>
+        <v>0.7553934803152608</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.1362654728363138</v>
+        <v>-0.9018257923968866</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.09022552832562403</v>
+        <v>-1.472898518132747</v>
       </c>
       <c r="M10" t="n">
-        <v>2.005322006960156</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4441629019989174</v>
+        <v>0.1389750240644616</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.929720441679457</v>
+        <v>-0.07049571060240875</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.8094123483831741</v>
+        <v>0.3357879790298813</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.2755295351100677</v>
+        <v>-0.580225477009927</v>
       </c>
       <c r="R10" t="n">
-        <v>-1.827609550410598</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.404186066386901</v>
+        <v>0.2932587258359444</v>
       </c>
       <c r="T10" t="n">
-        <v>0.02711451441102743</v>
+        <v>-0.6643056030701721</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.7335376974334945</v>
+        <v>-0.02252654504998304</v>
       </c>
       <c r="V10" t="n">
-        <v>0.322077988660802</v>
+        <v>-0.3710477360517253</v>
       </c>
       <c r="W10" t="n">
-        <v>1.020405009410047</v>
+        <v>-0.7307510197231677</v>
       </c>
       <c r="X10" t="n">
-        <v>0.56902676096089</v>
+        <v>2.305198252626395</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0.5661540599365338</v>
+        <v>0.08412544526869645</v>
       </c>
       <c r="Z10" t="n">
-        <v>-0.7454697835472107</v>
+        <v>-0.7132575737233142</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.1018341353690165</v>
+        <v>-0.6486680276877912</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.0477435593049567</v>
+        <v>0.06108854096989604</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.3386607344840507</v>
+        <v>0.2103880982104788</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>EB22wLQj</t>
+          <t>CvbDaBsg</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.004180283410005313</v>
+        <v>1.307550403104531</v>
       </c>
       <c r="C11" t="n">
         <v>-0.3097959401686102</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.71031282951045</v>
+        <v>0.05355634550733503</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.7493652190617176</v>
+        <v>-0.6129585455596424</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3608379156820746</v>
+        <v>0.4125244249994469</v>
       </c>
       <c r="G11" t="n">
-        <v>1.621508266055576</v>
+        <v>0.3318662170788685</v>
       </c>
       <c r="H11" t="n">
-        <v>0.775296935466397</v>
+        <v>0.4532830472649555</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4729379548670124</v>
+        <v>-0.722470901547414</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.17105473122307</v>
+        <v>-0.9302487047807788</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.4129832584650066</v>
+        <v>-0.5274141898268482</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1180986399352659</v>
+        <v>0.4404262838013197</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.9561209200118049</v>
+        <v>0.09272344995743113</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.5300168605206764</v>
+        <v>0.08804403475586697</v>
       </c>
       <c r="O11" t="n">
-        <v>0.157617049860525</v>
+        <v>-0.9682823607100958</v>
       </c>
       <c r="P11" t="n">
-        <v>1.211529405875159</v>
+        <v>0.2684232538879369</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.3162797737824484</v>
+        <v>-0.17272309028612</v>
       </c>
       <c r="R11" t="n">
-        <v>-0.6353054091899147</v>
+        <v>-1.583126244040831</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4882154781904768</v>
+        <v>1.391625012703264</v>
       </c>
       <c r="T11" t="n">
         <v>0.02711451441102743</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.02252654504998304</v>
+        <v>2.110506912100552</v>
       </c>
       <c r="V11" t="n">
-        <v>1.328228234211244</v>
+        <v>-0.6840722568896406</v>
       </c>
       <c r="W11" t="n">
-        <v>-1.026400738927477</v>
+        <v>1.702673592189221</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.966135676341956</v>
+        <v>-0.1879874262999243</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.5531760860786213</v>
+        <v>0.8041601387817557</v>
       </c>
       <c r="Z11" t="n">
-        <v>-0.020695062509539</v>
+        <v>-0.9870613572264346</v>
       </c>
       <c r="AA11" t="n">
-        <v>-0.9315371250867471</v>
+        <v>-1.299643867988773</v>
       </c>
       <c r="AB11" t="n">
-        <v>-0.1079542670665366</v>
+        <v>-0.4210280012893089</v>
       </c>
       <c r="AC11" t="n">
-        <v>-0.7720286284478441</v>
+        <v>-1.789189546331395</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>40FWnYcm</t>
+          <t>YgnMckC5</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.926098934484983</v>
+        <v>0.4018186250117249</v>
       </c>
       <c r="C12" t="n">
         <v>-0.3097959401686102</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7445236392617814</v>
+        <v>-5.059601628275568</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2509503866201666</v>
+        <v>-0.7038963278943591</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8527460650796974</v>
+        <v>-0.6344892054616895</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.31909596002366</v>
+        <v>0.712617679157706</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.7887705215120336</v>
+        <v>0.5912889993512876</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.9220972588917352</v>
+        <v>-0.12359182951445</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.8820874994923205</v>
+        <v>-0.2078306254539047</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.844735562494489</v>
+        <v>-0.298552626018501</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.7891729931539919</v>
+        <v>-0.3023725514883061</v>
       </c>
       <c r="M12" t="n">
-        <v>0.709690726409923</v>
+        <v>-0.647637281785559</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.6097383934337387</v>
+        <v>-0.5729438397815563</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.9677392350899461</v>
+        <v>-0.5799475423029593</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.001035646679840764</v>
+        <v>-1.092344193979341</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.041634022150825</v>
+        <v>0.4385304897995905</v>
       </c>
       <c r="R12" t="n">
-        <v>-0.7292591595156573</v>
+        <v>-0.2946749021016778</v>
       </c>
       <c r="S12" t="n">
-        <v>0.02242156968202972</v>
+        <v>0.2337889024897154</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1111695090852124</v>
+        <v>-0.3877375560776923</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4040801463801239</v>
+        <v>-0.02252654504998304</v>
       </c>
       <c r="V12" t="n">
-        <v>0.6574614038442828</v>
+        <v>-0.3486888417061597</v>
       </c>
       <c r="W12" t="n">
-        <v>1.361539300799634</v>
+        <v>-0.002997864758714988</v>
       </c>
       <c r="X12" t="n">
-        <v>0.4049621849667915</v>
+        <v>-0.4135932858032618</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.6739276561223414</v>
+        <v>-0.09142810536802561</v>
       </c>
       <c r="Z12" t="n">
-        <v>-0.4314007377642196</v>
+        <v>-1.148122406345917</v>
       </c>
       <c r="AA12" t="n">
-        <v>-0.5335738184458958</v>
+        <v>0.7245284384313951</v>
       </c>
       <c r="AB12" t="n">
-        <v>-0.1350932666686784</v>
+        <v>-0.4205251519600463</v>
       </c>
       <c r="AC12" t="n">
-        <v>-0.09754686958519923</v>
+        <v>0.4234295243809658</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>0AJjqex0</t>
+          <t>hzRnqjcC</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.2498664348355377</v>
+        <v>1.926098934484983</v>
       </c>
       <c r="C13" t="n">
         <v>-0.3097959401686102</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.019345535756004</v>
+        <v>-3.401280123264897</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.9858034531319813</v>
+        <v>-1.79514971591096</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.2418590940387636</v>
+        <v>-0.7177743806120075</v>
       </c>
       <c r="G13" t="n">
-        <v>1.253039109205088</v>
+        <v>-0.03660293977161932</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3888802696246669</v>
+        <v>0.4302820552505668</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2234050081866108</v>
+        <v>-1.471069741588619</v>
       </c>
       <c r="J13" t="n">
         <v>-1.411860757665362</v>
       </c>
       <c r="K13" t="n">
-        <v>0.4163192727401978</v>
+        <v>0.3460177214469446</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1299480483089713</v>
+        <v>0.9540299073844987</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.573088196464297</v>
+        <v>0.8947809093456706</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.4839979019612939</v>
+        <v>-0.4625601788250083</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.1959257802911307</v>
+        <v>0.8571628486135195</v>
       </c>
       <c r="P13" t="n">
-        <v>0.4031527041718259</v>
+        <v>0.2010585287459926</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.8867831151957782</v>
+        <v>1.57953717262625</v>
       </c>
       <c r="R13" t="n">
-        <v>6.006622913511595</v>
+        <v>-1.326465707625869</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.708398228074702</v>
+        <v>-0.5238585173229063</v>
       </c>
       <c r="T13" t="n">
         <v>-0.6643056030701721</v>
@@ -1638,119 +1638,119 @@
         <v>0.6884846073335283</v>
       </c>
       <c r="V13" t="n">
-        <v>1.05992150206446</v>
+        <v>-0.01330542652267886</v>
       </c>
       <c r="W13" t="n">
         <v>1.361539300799634</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.139543333545636</v>
+        <v>0.600943602073828</v>
       </c>
       <c r="Y13" t="n">
-        <v>-0.2541491385824123</v>
+        <v>-0.4709204802661934</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.7040796585281328</v>
+        <v>-0.7132575737233142</v>
       </c>
       <c r="AA13" t="n">
-        <v>-0.1264638455008364</v>
+        <v>1.359357640546857</v>
       </c>
       <c r="AB13" t="n">
-        <v>-0.3250163372417064</v>
+        <v>-1.640422343394405</v>
       </c>
       <c r="AC13" t="n">
-        <v>-0.8273884094412809</v>
+        <v>0.3107628394237464</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>QmPfsURO</t>
+          <t>4Ef51XCt</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6116833053015214</v>
+        <v>0.4239096439895982</v>
       </c>
       <c r="C14" t="n">
         <v>-0.3097959401686102</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7445236392617814</v>
+        <v>-0.6374109482471113</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1145437131180915</v>
+        <v>0.4782948424569585</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4125244249994469</v>
+        <v>-0.1823696832171081</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4546892693623644</v>
+        <v>-0.8349527796143428</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.7427685374832562</v>
+        <v>0.1082681670491252</v>
       </c>
       <c r="I14" t="n">
-        <v>0.02612793849379083</v>
+        <v>-1.72060268826902</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.4486366518961961</v>
+        <v>-1.893472810549945</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.1598030411128303</v>
+        <v>0.05359894209612109</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.9197721169762291</v>
+        <v>-1.557699351300999</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.819875107045294</v>
+        <v>0.3395103605384279</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.7201220543902866</v>
+        <v>0.2304039149577638</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.4963061967998838</v>
+        <v>-0.2073633668801681</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.4052239975315075</v>
+        <v>0.2010585287459926</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.8052826378510168</v>
+        <v>0.07177834174816419</v>
       </c>
       <c r="R14" t="n">
-        <v>0.9553631176160025</v>
+        <v>-2.121085646899331</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7623012768489876</v>
+        <v>0.1740589759971815</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.355725720551371</v>
+        <v>0.02711451441102743</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.7335376974334945</v>
+        <v>1.39949575971704</v>
       </c>
       <c r="V14" t="n">
         <v>-0.01330542652267886</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.002997864758714988</v>
+        <v>1.020405009410047</v>
       </c>
       <c r="X14" t="n">
-        <v>0.04545428873891213</v>
+        <v>0.1416304737984066</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.8073859195193533</v>
+        <v>-0.8026983316346978</v>
       </c>
       <c r="Z14" t="n">
-        <v>-0.9870613572264346</v>
+        <v>-0.004588957597590797</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.8647354310643771</v>
+        <v>0.003667283358006525</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.08177452209805446</v>
+        <v>-0.1191665299248155</v>
       </c>
       <c r="AC14" t="n">
-        <v>-0.2655328768710732</v>
+        <v>-0.2048384609647768</v>
       </c>
     </row>
   </sheetData>

--- a/data/spain/p6_deployment/data_preparation/df_selected_nan.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_selected_nan.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC14"/>
+  <dimension ref="A1:AL21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,1311 +446,2533 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_180_matches_expected_points</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_30_matches_shots_on_goal</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_180_matches_shots_on_goal</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_shots_on_goal_against</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_30_matches_goal_attempts</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_30_matches_goal_attempts_against</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_goal_attempts</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_180_matches_goal_attempts_against</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_30_matches_goals</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_goals</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_goals_against</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_30_matches_points</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_30_matches_goal_ratio</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_points</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_180_matches_goal_ratio</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_30_matches_PPS_against</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_attacks_against</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_30_matches_dangerous_attacks</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_180_matches_dangerous_attacks</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_180_matches_dangerous_attacks_against</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_30_matches_yellow_cards_against</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_dead_balls_against</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_30_matches_total_passes_against</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_total_passes</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_30_matches_yellow_cards</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_red_cards</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_30_matches_defensive_actions</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_30_matches_KGP_against</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_30_matches_defensive_actions_against</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_defensive_actions</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_180_matches_KGP</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_30_matches_clean_sheet</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_30_matches_clean_sheet_against</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_180_matches_clean_sheet</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_180_matches_clean_sheet_against</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_180_matches_mean_rat_player_start_against</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_age_player_sub</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_value_player_start</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_value_player_sub</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_sub</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rep_player_sub</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2Xrca2mA</t>
+          <t>E595Qvn9</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.4239096439895982</v>
+        <v>-0.7641890397354772</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.3097959401686102</v>
+        <v>-0.2054762389029784</v>
       </c>
       <c r="D2" t="n">
-        <v>3.508392814279567</v>
+        <v>0.06406591879471901</v>
       </c>
       <c r="E2" t="n">
-        <v>1.998254918622938</v>
+        <v>0.6617670520036656</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1943965853200431</v>
+        <v>-0.1962257956361834</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.09801446591336728</v>
+        <v>0.5965990294627511</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.370367033875862</v>
+        <v>-0.09393704080606534</v>
       </c>
       <c r="I2" t="n">
-        <v>1.356970320789266</v>
+        <v>-0.4184587731565022</v>
       </c>
       <c r="J2" t="n">
-        <v>0.5145874538729694</v>
+        <v>0.6498504164410249</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.06339331463549755</v>
+        <v>-0.4956390672493506</v>
       </c>
       <c r="L2" t="n">
-        <v>-1.354454925720055</v>
+        <v>-0.8795056532788108</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>-0.1634663124753931</v>
       </c>
       <c r="N2" t="n">
-        <v>0.8854584686140449</v>
+        <v>-0.1183240480672929</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.436407270222881</v>
+        <v>-0.2274520748134197</v>
       </c>
       <c r="P2" t="n">
-        <v>1.07679995559127</v>
+        <v>-0.72828930975652</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.7024761930270691</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>0.02867578179418842</v>
       </c>
       <c r="S2" t="n">
-        <v>1.176270662791933</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7185346318922269</v>
+        <v>0.2895712362215844</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.02252654504998304</v>
+        <v>-0.1644862236704181</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7021791925354133</v>
+        <v>-0.1824970362529664</v>
       </c>
       <c r="W2" t="n">
-        <v>-1.458504174687621</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.06216137689557534</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0.1646117133838152</v>
+        <v>2.819814287316804</v>
       </c>
       <c r="Z2" t="n">
-        <v>-0.7132575737233142</v>
+        <v>-2.244760836728082</v>
       </c>
       <c r="AA2" t="n">
-        <v>-1.32359045641759</v>
+        <v>0.7004688999391814</v>
       </c>
       <c r="AB2" t="n">
-        <v>-0.4205251519600463</v>
+        <v>-0.231355654752598</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.543872280971335</v>
+        <v>-0.02940156208751926</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.09926644434272593</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>-0.3705908099312528</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.9264737360906898</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>-0.02423268263222032</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>-0.1821042411260427</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>-0.7567216140570332</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>-0.3709377002271878</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>-0.05595631676440389</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>-0.5169668667661257</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>f1xuAJ1S</t>
+          <t>jiAoNQdE</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-1.453826969129633</v>
+        <v>-1.643070416066077</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.3097959401686102</v>
+        <v>-0.2054762389029784</v>
       </c>
       <c r="D3" t="n">
-        <v>0.283878776758817</v>
+        <v>1.782998908285793</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7961440435697303</v>
+        <v>-0.315726358151494</v>
       </c>
       <c r="F3" t="n">
-        <v>1.304865587324279</v>
+        <v>1.655825792006121</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5570418129319442</v>
+        <v>0.08726814049164042</v>
       </c>
       <c r="H3" t="n">
-        <v>2.004864251435575</v>
+        <v>-0.1668611875395509</v>
       </c>
       <c r="I3" t="n">
-        <v>1.024259725215397</v>
+        <v>1.397892143037846</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7553934803152608</v>
+        <v>-0.1117723139137551</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.4672463016328856</v>
+        <v>-0.0009663049688479437</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.3318725279673022</v>
+        <v>-1.32275446680535</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>-1.436269975734275</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1897069086455015</v>
+        <v>0.05157814492130637</v>
       </c>
       <c r="O3" t="n">
-        <v>1.70878382100847</v>
+        <v>-0.3418125497313447</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.2031298221056741</v>
+        <v>-0.23237396070206</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.009722135596597209</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>-0.2574496990383842</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.6832340099333994</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6643056030701721</v>
+        <v>-0.009654767499176802</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.7335376974334945</v>
+        <v>-0.7445614113992082</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.31994169183329</v>
+        <v>0.0608776828987215</v>
       </c>
       <c r="W3" t="n">
-        <v>-2.914010484616526</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.3800154697293414</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.009313015429009945</v>
+        <v>-2.477456343395107</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.7132575737233142</v>
+        <v>-0.0009543883689459594</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.2213184512292846</v>
+        <v>-0.273580185534121</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.2017539966970474</v>
+        <v>-0.0428705693757219</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.544974656154859</v>
+        <v>0.3098243041358852</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>-0.3215047406227721</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.919765401904505</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.4776168060305839</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>-0.8834063186483847</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>-0.3993534485272661</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.6046778968578574</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.4258985200295491</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0.08180379259917757</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1.177162926784322</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>65kl1OIc</t>
+          <t>842EOIGL</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6116833053015214</v>
+        <v>-0.9839093838181272</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.3097959401686102</v>
+        <v>-0.2054762389029784</v>
       </c>
       <c r="D4" t="n">
-        <v>0.05355634550733503</v>
+        <v>1.782998908285793</v>
       </c>
       <c r="E4" t="n">
-        <v>1.007466128233262</v>
+        <v>0.3359359152852791</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3530350141777914</v>
+        <v>2.714140984944581</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3113957083649523</v>
+        <v>1.105929918433862</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.4012585703362851</v>
+        <v>0.4894561330618175</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3588385340676596</v>
+        <v>2.046588898821542</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5145874538729694</v>
+        <v>1.030661781618415</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2944141041964158</v>
+        <v>0.215453028528871</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6780670468337456</v>
+        <v>-0.8795056532788108</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>0.7911364349687681</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2549336173925521</v>
+        <v>0.391382530898505</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4147623434732851</v>
+        <v>-1.027975399238895</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.6746828980992853</v>
+        <v>-0.8610015636377254</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.7160596059178626</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>-0.4536113762049238</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.8797295675091525</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2033588580827057</v>
+        <v>0.6511359907175055</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.9705414148946649</v>
+        <v>-0.04292634977137068</v>
       </c>
       <c r="V4" t="n">
-        <v>2.133148430651598</v>
+        <v>0.6591738674799537</v>
       </c>
       <c r="W4" t="n">
-        <v>-1.822380752169847</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3146098042699321</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0.9124105230311773</v>
+        <v>-0.03256220614345577</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0.7132575737233142</v>
+        <v>-2.448743241124367</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.2931448593450513</v>
+        <v>0.4805223322516616</v>
       </c>
       <c r="AB4" t="n">
-        <v>-0.4205251519600463</v>
+        <v>1.213696666470117</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.005233133266385</v>
+        <v>0.7561741281140492</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.7351173206508055</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>-1.515768915849132</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.09625420207161761</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>-1.538272361598156</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>-2.133095278698381</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>-2.17756847025259</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>-0.4409192176565106</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>-1.471977983677767</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>-3.032220911464559</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>0SQqjbAd</t>
+          <t>naHJ2yf2</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-1.520100026063253</v>
+        <v>0.5194403388526357</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.3097959401686102</v>
+        <v>-0.2054762389029784</v>
       </c>
       <c r="D5" t="n">
-        <v>1.896135795519192</v>
+        <v>2.64246540303133</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.07339437037365608</v>
+        <v>1.965091598877212</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.02373125435936023</v>
+        <v>1.655825792006121</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04527909508404478</v>
+        <v>0.9785971961910845</v>
       </c>
       <c r="H5" t="n">
-        <v>0.09293417237286632</v>
+        <v>-0.8231785081409194</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6915491296415285</v>
+        <v>1.397892143037846</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5145874538729694</v>
+        <v>1.323593600985637</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.274520158852697</v>
+        <v>-1.268565258312636</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6660679736556924</v>
+        <v>-0.1407576307345782</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>-0.640767686197474</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3997492741056258</v>
+        <v>1.070991302852903</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4170089085384505</v>
+        <v>0.001268875022430359</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.2704945472476183</v>
+        <v>-0.5753407372360136</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.07177834174816419</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>-0.929810758016108</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9454951898895119</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6643056030701721</v>
+        <v>-0.8378695992262862</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.7335376974334945</v>
+        <v>-0.6880467331829847</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3444368830063673</v>
+        <v>1.328454345147095</v>
       </c>
       <c r="W5" t="n">
-        <v>-1.458504174687621</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.4284879951853053</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.9118642122551711</v>
+        <v>0.3749201500651528</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.7132575737233142</v>
+        <v>0.8149752292161943</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.9985437045781238</v>
+        <v>0.6690479616981072</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.2634027060161795</v>
+        <v>0.5854130485471977</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.02631547403007915</v>
+        <v>1.452479853519985</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.1232305518540011</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>-0.3705908099312528</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>-0.1100942369778535</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.3878044354823547</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>-0.0630233859672171</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>-0.1379036264043823</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>-0.5988864131296676</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>-0.0875485454950454</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.3587487582224743</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>8Uo5ctIM</t>
+          <t>02sgHz9e</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.307550403104531</v>
+        <v>0.2187703943184832</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.3097959401686102</v>
+        <v>-0.2054762389029784</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.789023104504522</v>
+        <v>0.06406591879471901</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.210865292298236</v>
+        <v>-0.967388631588267</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.828243382616244</v>
+        <v>0.06835300259843144</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.4869541314777712</v>
+        <v>-1.122392720814748</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1542701510779026</v>
+        <v>-0.896102654874405</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.886957986055955</v>
+        <v>0.6194560360974111</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.251323406703834</v>
+        <v>-0.492583679091145</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2587671814966269</v>
+        <v>-0.5883902101769445</v>
       </c>
       <c r="L6" t="n">
-        <v>1.234646210621348</v>
+        <v>-1.76600328033189</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>-1.277169517826915</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.404723749615744</v>
+        <v>-0.6280306270330911</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.6276438467633906</v>
+        <v>-0.5705334995671951</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.001035646679840764</v>
+        <v>-0.7620849925743708</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.234779296437687</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>0.6773621555966406</v>
       </c>
       <c r="S6" t="n">
-        <v>1.981595095076349</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.7185346318922269</v>
+        <v>-0.6909282581134121</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6884846073335283</v>
+        <v>0.4145226493750463</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.721925770099743</v>
+        <v>1.581969677596769</v>
       </c>
       <c r="W6" t="n">
-        <v>0.6987641060998647</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.5206014688860386</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.06810708740699205</v>
+        <v>-2.477456343395107</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.7132575737233142</v>
+        <v>-0.6129016015578012</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.1806924497077511</v>
+        <v>0.1663129498409187</v>
       </c>
       <c r="AB6" t="n">
-        <v>-2.878307962011887</v>
+        <v>0.1456145160011541</v>
       </c>
       <c r="AC6" t="n">
-        <v>-1.984660737691543</v>
+        <v>0.5776341985227837</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>-0.68955135701367</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.7745872959866259</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.1389048195692081</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.1860020848758931</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>-0.06535216563387881</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-0.168652226857996</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>-0.4441335400127469</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0.1926833654500472</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>-0.5909950427078076</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>h2NyhKup</t>
+          <t>4zlpJdvq</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6116833053015214</v>
+        <v>1.89558354652818</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.3097959401686102</v>
+        <v>-0.2054762389029784</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.789023104504522</v>
+        <v>0.06406591879471901</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7511081894611082</v>
+        <v>0.2544781311056827</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.6384551661831334</v>
+        <v>-2.312856181513102</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.326244988748327</v>
+        <v>-0.273507905862896</v>
       </c>
       <c r="H7" t="n">
-        <v>0.04912275901212546</v>
+        <v>-0.06476738211267129</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.13835914601475</v>
+        <v>-0.4184587731565022</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.8499800293000151</v>
+        <v>0.03078783817829368</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6486025680523185</v>
+        <v>0.8544053464745197</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.23040351027912</v>
+        <v>-0.7514559960378105</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>-0.7892614469110099</v>
       </c>
       <c r="N7" t="n">
-        <v>0.486850804048733</v>
+        <v>0.3913825308985052</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.01957356912532969</v>
+        <v>-0.5133532621082321</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.078871248950952</v>
+        <v>1.832425746338087</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.261946122219274</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.453891829345562</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.07490971502892768</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.125252348057638</v>
+        <v>1.604918877577434</v>
       </c>
       <c r="U7" t="n">
-        <v>0.451480889872358</v>
+        <v>1.796466478964223</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.7287900455807714</v>
+        <v>-0.2027782628489403</v>
       </c>
       <c r="W7" t="n">
-        <v>-1.094627597205394</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.3737051140123193</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.2915349386013157</v>
+        <v>-1.255009274769281</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0.7132575737233142</v>
+        <v>-0.0009543883689459594</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.9499009442706992</v>
+        <v>0.6690479616981072</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0.08674105908170035</v>
+        <v>0.01995779241657001</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.8354678777054844</v>
+        <v>0.07883827022718511</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>-2.270105961489987</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.9177345592263605</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>-0.357987618354051</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.443995175118813</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>2.294070165149101</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>2.462347558965596</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.112361078621093</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>2.109325989115507</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1.643735281742362</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>ll7vCuXF</t>
+          <t>8Sp1FEw8</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4018186250117249</v>
+        <v>-0.7641890397354772</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.3097959401686102</v>
+        <v>-0.2054762389029784</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.71031282951045</v>
+        <v>-1.225133823323586</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.455648661861351</v>
+        <v>-3.248206588616974</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.530796328507966</v>
+        <v>-0.8135763248502847</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7208058826432722</v>
+        <v>-0.3583963873580808</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3190010653142857</v>
+        <v>0.1977595461278752</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7747267785349956</v>
+        <v>-0.5481981243132414</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7553934803152608</v>
+        <v>-0.9026882262052566</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4932194883771746</v>
+        <v>0.06086779031621384</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6413465303676534</v>
+        <v>-2.20925209385843</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>0.7911364349687678</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2741274646668614</v>
+        <v>-1.137737205998889</v>
       </c>
       <c r="O8" t="n">
-        <v>0.01038063174353976</v>
+        <v>-1.828498723664371</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.7420476232412295</v>
+        <v>0.9698109724131596</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.3162797737824484</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.570235996492611</v>
       </c>
       <c r="S8" t="n">
-        <v>0.750694454908817</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.02711451441102743</v>
+        <v>-1.376654516640158</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6884846073335283</v>
+        <v>-0.3948101952686147</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.086532355109817</v>
+        <v>1.044517172803459</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.002997864758714988</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.5871627258392379</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>-1.197650974482799</v>
+        <v>1.054057410412834</v>
       </c>
       <c r="Z8" t="n">
-        <v>-0.7132575737233142</v>
+        <v>-0.0009543883689459594</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.442248435922301</v>
+        <v>0.2448652954436046</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0.4205251519600463</v>
+        <v>0.5382917772029787</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.3197067258360914</v>
+        <v>0.4348022548497712</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.050905289632128</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>-1.134042880543172</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.2981710498135253</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.03153181611364578</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>-0.6989677048516648</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>-0.7153707896176377</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>-1.300280517559695</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>-0.3718972642333383</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>-0.7460647807302981</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>YNHbsZ6C</t>
+          <t>dhkQFrkl</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.2498664348355377</v>
+        <v>1.89558354652818</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.3097959401686102</v>
+        <v>-0.2054762389029784</v>
       </c>
       <c r="D9" t="n">
-        <v>1.435490933016228</v>
+        <v>0.9235324135402561</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5022258378081997</v>
+        <v>0.3359359152852791</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5315032466427578</v>
+        <v>1.655825792006121</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.71518465431273</v>
+        <v>0.2782672238558071</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.3742338458842919</v>
+        <v>-1.625344122209259</v>
       </c>
       <c r="I9" t="n">
-        <v>1.024259725215397</v>
+        <v>1.527631494194585</v>
       </c>
       <c r="J9" t="n">
-        <v>1.237005533199844</v>
+        <v>0.6498504164410249</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5902855831130281</v>
+        <v>-0.3719708766792248</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5064573490301876</v>
+        <v>-0.4362568397522711</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>-1.277169517826915</v>
       </c>
       <c r="N9" t="n">
-        <v>0.5477290655459808</v>
+        <v>1.410795688830101</v>
       </c>
       <c r="O9" t="n">
-        <v>0.08886063801998015</v>
+        <v>-0.1130915998954947</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.6746828980992853</v>
+        <v>1.484944721886985</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.8247269090442112</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>0.6922433862782392</v>
       </c>
       <c r="S9" t="n">
-        <v>0.8306142490208803</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.7185346318922269</v>
+        <v>0.5531750966422561</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.7335376974334945</v>
+        <v>-0.1367620419039696</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.4840189916924765</v>
+        <v>0.273830562156448</v>
       </c>
       <c r="W9" t="n">
-        <v>-2.224560127281782</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.023050317790189</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.6483910837933486</v>
+        <v>-1.66249163097789</v>
       </c>
       <c r="Z9" t="n">
-        <v>-0.7132575737233142</v>
+        <v>1.630904846801335</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.129037792716401</v>
+        <v>-0.3364220620162695</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8346942843785784</v>
+        <v>-0.1685272929603059</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.168096655482697</v>
+        <v>0.2384083322993792</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>-0.4072302675458508</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>-0.3705908099312528</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>-0.2081119119120145</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.473513512716482</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.7318336576850462</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.3352175725633407</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>-0.1620303375485396</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>-0.09873848805820837</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1.298010419924098</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Gz9WD123</t>
+          <t>x88gL4RQ</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-1.520100026063253</v>
+        <v>-0.3594410374779641</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.3097959401686102</v>
+        <v>-0.2054762389029784</v>
       </c>
       <c r="D10" t="n">
-        <v>1.435490933016228</v>
+        <v>-2.084600318069123</v>
       </c>
       <c r="E10" t="n">
-        <v>1.163359469378491</v>
+        <v>-1.944882041743427</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3410081120748559</v>
+        <v>-0.4608045938707983</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.71518465431273</v>
+        <v>-1.440724526421692</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.9059660522520135</v>
+        <v>-0.6773302146739482</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6083714807480611</v>
+        <v>-0.5914445746988209</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7553934803152608</v>
+        <v>-1.283499591382647</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.9018257923968866</v>
+        <v>-0.09371744789644332</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.472898518132747</v>
+        <v>-2.504751302876123</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>-0.4816672282901139</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1389750240644616</v>
+        <v>-1.392590495481788</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.07049571060240875</v>
+        <v>-1.37105682399267</v>
       </c>
       <c r="P10" t="n">
-        <v>0.3357879790298813</v>
+        <v>1.087794754588288</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.580225477009927</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>-0.193189839276932</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2932587258359444</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6643056030701721</v>
+        <v>0.01439017922838413</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.02252654504998304</v>
+        <v>-1.520838500859795</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.3710477360517253</v>
+        <v>1.034376559505472</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.7307510197231677</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2.305198252626395</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.08412544526869645</v>
+        <v>1.733194670760515</v>
       </c>
       <c r="Z10" t="n">
-        <v>-0.7132575737233142</v>
+        <v>-0.8576804868333432</v>
       </c>
       <c r="AA10" t="n">
-        <v>-0.6486680276877912</v>
+        <v>-0.5092372223421778</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.06108854096989604</v>
+        <v>0.3969279631703218</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.2103880982104788</v>
+        <v>0.4883642337271512</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.3369705713874642</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.538039366598545</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>-2.183704525138614</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0.246481960026735</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>-0.80292307807476</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>-0.6781146148888081</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>-1.290098635356893</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>-0.3979679833379874</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>-1.309932450073804</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>CvbDaBsg</t>
+          <t>vymauDyP</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.307550403104531</v>
+        <v>0.1956419370466253</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.3097959401686102</v>
+        <v>-0.2054762389029784</v>
       </c>
       <c r="D11" t="n">
-        <v>0.05355634550733503</v>
+        <v>-0.5805339522644337</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.6129585455596424</v>
+        <v>1.344511900982653</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4125244249994469</v>
+        <v>-0.9899621903400281</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3318662170788685</v>
+        <v>-1.541175896190994</v>
       </c>
       <c r="H11" t="n">
-        <v>0.4532830472649555</v>
+        <v>-0.1911692364507131</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.722470901547414</v>
+        <v>-1.067155528940198</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.9302487047807788</v>
+        <v>-1.08170211581856</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.5274141898268482</v>
+        <v>0.2759130328075996</v>
       </c>
       <c r="L11" t="n">
-        <v>0.4404262838013197</v>
+        <v>-0.2458240161630914</v>
       </c>
       <c r="M11" t="n">
-        <v>0.09272344995743113</v>
+        <v>-0.969575299206018</v>
       </c>
       <c r="N11" t="n">
-        <v>0.08804403475586697</v>
+        <v>-0.6280306270330911</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.9682823607100958</v>
+        <v>0.6163326134790338</v>
       </c>
       <c r="P11" t="n">
-        <v>0.2684232538879369</v>
+        <v>0.9408541802712783</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.17272309028612</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>-1.583126244040831</v>
+        <v>-0.08728185988061413</v>
       </c>
       <c r="S11" t="n">
-        <v>1.391625012703264</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>0.02711451441102743</v>
+        <v>-0.3981905733508801</v>
       </c>
       <c r="U11" t="n">
-        <v>2.110506912100552</v>
+        <v>-0.1008120040090118</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.6840722568896406</v>
+        <v>0.02058208795145801</v>
       </c>
       <c r="W11" t="n">
-        <v>1.702673592189221</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.1879874262999243</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.8041601387817557</v>
+        <v>-0.9833543706302088</v>
       </c>
       <c r="Z11" t="n">
-        <v>-0.9870613572264346</v>
+        <v>0.4886033821821381</v>
       </c>
       <c r="AA11" t="n">
-        <v>-1.299643867988773</v>
+        <v>0.8104421837829414</v>
       </c>
       <c r="AB11" t="n">
-        <v>-0.4210280012893089</v>
+        <v>1.245110847366263</v>
       </c>
       <c r="AC11" t="n">
-        <v>-1.789189546331395</v>
+        <v>0.3858212346921676</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>-1.105425530221956</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0.9905638685939447</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>-0.2152624368171645</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0.505705186234064</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>-0.6627577955592421</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>-0.7873919552149141</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>-1.092749723554103</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>-0.2010157300432614</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>-0.6130055094780278</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>YgnMckC5</t>
+          <t>QqTA4cPk</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.4018186250117249</v>
+        <v>0.2187703943184832</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.3097959401686102</v>
+        <v>-0.2054762389029784</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.059601628275568</v>
+        <v>0.9235324135402558</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.7038963278943591</v>
+        <v>0.01010477856689252</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.6344892054616895</v>
+        <v>-0.4608045938707983</v>
       </c>
       <c r="G12" t="n">
-        <v>0.712617679157706</v>
+        <v>-1.2836808356556</v>
       </c>
       <c r="H12" t="n">
-        <v>0.5912889993512876</v>
+        <v>0.2512372537324318</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.12359182951445</v>
+        <v>-0.07248717007186425</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.2078306254539047</v>
+        <v>-0.1293482230757884</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.298552626018501</v>
+        <v>0.1412521141867959</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.3023725514883061</v>
+        <v>-0.2688072879755787</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.647637281785559</v>
+        <v>-0.1528596152815691</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.5729438397815563</v>
+        <v>0.3913825308985051</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.5799475423029593</v>
+        <v>0.2299898248582804</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.092344193979341</v>
+        <v>0.4289679133182492</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.4385304897995905</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>-0.2946749021016778</v>
+        <v>0.836997175635617</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2337889024897154</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3877375560776923</v>
+        <v>0.7188180629876781</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.02252654504998304</v>
+        <v>0.8527779842216145</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.3486888417061597</v>
+        <v>0.1927056557725524</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.002997864758714988</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.4135932858032618</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>-0.09142810536802561</v>
+        <v>-1.119181822699745</v>
       </c>
       <c r="Z12" t="n">
-        <v>-1.148122406345917</v>
+        <v>1.222940038008764</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.7245284384313951</v>
+        <v>-0.4621058149805665</v>
       </c>
       <c r="AB12" t="n">
-        <v>-0.4205251519600463</v>
+        <v>-0.6083258255063496</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.4234295243809658</v>
+        <v>-0.01154756912839323</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>-0.6927890577801395</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.156313331292585</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0.3078056570759571</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>-0.8550260097693017</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>-0.08356917940114636</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0.3942633345988409</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.03281987406622</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0.2333313396609227</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>-0.1852737039762769</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>hzRnqjcC</t>
+          <t>2Xrca2mA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.926098934484983</v>
+        <v>0.1956419370466253</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.3097959401686102</v>
+        <v>-0.2054762389029784</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.401280123264897</v>
+        <v>3.287065274090483</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.79514971591096</v>
+        <v>4.245909555905918</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.7177743806120075</v>
+        <v>1.920404590240736</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.03660293977161932</v>
+        <v>2.519323135328695</v>
       </c>
       <c r="H13" t="n">
-        <v>0.4302820552505668</v>
+        <v>-1.314201096146388</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.471069741588619</v>
+        <v>0.2302379826271937</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.411860757665362</v>
+        <v>1.48372966223972</v>
       </c>
       <c r="K13" t="n">
-        <v>0.3460177214469446</v>
+        <v>-1.503534820395874</v>
       </c>
       <c r="L13" t="n">
-        <v>0.9540299073844987</v>
+        <v>3.7302820073972</v>
       </c>
       <c r="M13" t="n">
-        <v>0.8947809093456706</v>
+        <v>-0.4498471367086415</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.4625601788250083</v>
+        <v>0.5612847238871044</v>
       </c>
       <c r="O13" t="n">
-        <v>0.8571628486135195</v>
+        <v>2.631559798134707</v>
       </c>
       <c r="P13" t="n">
-        <v>0.2010585287459926</v>
+        <v>-1.976593582956553</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.57953717262625</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>-1.326465707625869</v>
+        <v>-2.829196928649358</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5238585173229063</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6643056030701721</v>
+        <v>1.092850567638631</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6884846073335283</v>
+        <v>-1.663724668425342</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.01330542652267886</v>
+        <v>-1.176277139455691</v>
       </c>
       <c r="W13" t="n">
-        <v>1.361539300799634</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0.600943602073828</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>-0.4709204802661934</v>
+        <v>-2.477456343395107</v>
       </c>
       <c r="Z13" t="n">
-        <v>-0.7132575737233142</v>
+        <v>-0.7352910441955723</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.359357640546857</v>
+        <v>-1.279050209248497</v>
       </c>
       <c r="AB13" t="n">
-        <v>-1.640422343394405</v>
+        <v>0.4911705058587597</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.3107628394237464</v>
+        <v>-0.6721453086160757</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.147898708918259</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0.7745872959866259</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>-0.1850132256637204</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>-1.165318793319315</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>-0.5232008016252527</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>1.352541857646848</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0.5148135048711792</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.249212909418156</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1.23402853825696</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>4Ef51XCt</t>
+          <t>f1xuAJ1S</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.4239096439895982</v>
+        <v>-1.643070416066077</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.3097959401686102</v>
+        <v>-0.2054762389029784</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.6374109482471113</v>
+        <v>0.06406591879471901</v>
       </c>
       <c r="E14" t="n">
-        <v>0.4782948424569585</v>
+        <v>0.9875981887220522</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.1823696832171081</v>
+        <v>0.2006424017157389</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.8349527796143428</v>
+        <v>0.7366650239298073</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1082681670491252</v>
+        <v>1.816675603611252</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.72060268826902</v>
+        <v>1.138413440724368</v>
       </c>
       <c r="J14" t="n">
-        <v>-1.893472810549945</v>
+        <v>0.8002220837161996</v>
       </c>
       <c r="K14" t="n">
-        <v>0.05359894209612109</v>
+        <v>2.247733626897934</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.557699351300999</v>
+        <v>2.902884222147661</v>
       </c>
       <c r="M14" t="n">
-        <v>0.3395103605384279</v>
+        <v>1.480571752567329</v>
       </c>
       <c r="N14" t="n">
-        <v>0.2304039149577638</v>
+        <v>0.3064314344042054</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.2073633668801681</v>
+        <v>1.945396948627156</v>
       </c>
       <c r="P14" t="n">
-        <v>0.2010585287459926</v>
+        <v>-0.6299865370545078</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.07177834174816419</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>-2.121085646899331</v>
+        <v>0.8843465459861602</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1740589759971815</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>0.02711451441102743</v>
+        <v>0.2379191284364539</v>
       </c>
       <c r="U14" t="n">
-        <v>1.39949575971704</v>
+        <v>2.068376723212093</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.01330542652267886</v>
+        <v>-2.078791722976533</v>
       </c>
       <c r="W14" t="n">
-        <v>1.020405009410047</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0.1416304737984066</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>-0.8026983316346978</v>
+        <v>0.1711789719608485</v>
       </c>
       <c r="Z14" t="n">
-        <v>-0.004588957597590797</v>
+        <v>1.222940038008764</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.003667283358006525</v>
+        <v>-0.2892906546546581</v>
       </c>
       <c r="AB14" t="n">
-        <v>-0.1191665299248155</v>
+        <v>-0.4512549210256196</v>
       </c>
       <c r="AC14" t="n">
-        <v>-0.2048384609647768</v>
+        <v>-1.422013012899392</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>-0.713962273255933</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>-0.3705908099312529</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0.7046203997048154</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0.2340992168026741</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0.6686058607098164</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0.2405388649090753</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0.8250878602451994</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0.2770522518974885</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>1.084869341947973</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>65kl1OIc</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.5194403388526357</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-0.2054762389029784</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.06406591879471901</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2.616753872313986</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.5975105990676612</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.033774709162955</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.04704964287867258</v>
+      </c>
+      <c r="I15" t="n">
+        <v>-0.02924071968628468</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.9369235994209039</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-0.2915865528086435</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.385988282523502</v>
+      </c>
+      <c r="M15" t="n">
+        <v>-0.746834658135714</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.5612847238871044</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.487955048955456</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.9244546099262378</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.6611280857621683</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.3180689508616575</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.5328835792241192</v>
+      </c>
+      <c r="V15" t="n">
+        <v>-1.804995163930884</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.5107476021346889</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.222940038008764</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-0.4463953458600292</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>-0.9381747249158822</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>-0.4936053790248102</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>-0.9107068242038274</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>2.301491437210464</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0.1389048195692081</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0.2991908557623304</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>2.399166526024115</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>2.54729389471753</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>2.200714053774123</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1.406872968921546</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>3.556428668364208</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>0SQqjbAd</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>-1.712455787881651</v>
+      </c>
+      <c r="C16" t="n">
+        <v>-0.2054762389029784</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.782998908285793</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-0.967388631588267</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.303054061026634</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-0.09524209472300701</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.2512372537324318</v>
+      </c>
+      <c r="I16" t="n">
+        <v>-0.0508639448790747</v>
+      </c>
+      <c r="J16" t="n">
+        <v>-1.113599136149658</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.1123962030537667</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.4206908663990384</v>
+      </c>
+      <c r="M16" t="n">
+        <v>-0.5983408974221776</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.5612847238871044</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.6874317245299809</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.8628339656860612</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.3263003954261789</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>-0.4863977853320574</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.5355493659324319</v>
+      </c>
+      <c r="V16" t="n">
+        <v>-0.4968560484905624</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.5107476021346892</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-1.632813623539227</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0.04062919687662175</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.6953626816837084</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>-0.5650213508613167</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>-0.9765557828401791</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0.3928612606806661</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0.3847574525332738</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>-0.9080809724420557</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0.01537032742776497</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0.2312618970026505</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0.547550588274531</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0.2248212797790453</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>-0.6800187835386231</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>8Uo5ctIM</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>-0.3594410374779641</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-0.2054762389029784</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-1.225133823323586</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-2.596544315180201</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-1.651409185926565</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-2.412697639541562</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.9318626232449619</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-1.586112933567155</v>
+      </c>
+      <c r="J17" t="n">
+        <v>-2.261891868069172</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.1701080253198251</v>
+      </c>
+      <c r="L17" t="n">
+        <v>-1.509903965849889</v>
+      </c>
+      <c r="M17" t="n">
+        <v>2.22304055613501</v>
+      </c>
+      <c r="N17" t="n">
+        <v>-1.477541591976088</v>
+      </c>
+      <c r="O17" t="n">
+        <v>-1.37105682399267</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.297322090560393</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.8437613713999806</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>-1.721298753068535</v>
+      </c>
+      <c r="U17" t="n">
+        <v>-0.704041453432859</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.6186114142880054</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.7824025062737613</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0.6109928248199092</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0.2762862336846788</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.5382917772029787</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0.1134303815854928</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.954243624558819</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>-3.042673057072969</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0.4906124494587784</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0.2574596287721836</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>-2.386275478235936</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>-4.281692652249272</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>-2.591119128756817</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>-3.44054747843899</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>-2.688516957374928</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>h2NyhKup</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>-0.9839093838181272</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-0.2054762389029784</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-1.654867070696355</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1.965091598877212</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-1.210444522202208</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.7960869609764367</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.3873623276349383</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-0.7211839258555601</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.9095832962799631</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.3143875809849711</v>
+      </c>
+      <c r="L18" t="n">
+        <v>2.351285698647966</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.7381029489996479</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-0.3731773375501921</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.8017921994479059</v>
+      </c>
+      <c r="P18" t="n">
+        <v>-1.32233453201169</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>-0.8692712059250565</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0.6030460972623829</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0.01749814895037835</v>
+      </c>
+      <c r="V18" t="n">
+        <v>-1.348667565521469</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.1711789719608485</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-1.224848814746656</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0.3391281101668274</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.3183925109299569</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>-0.8149772522890882</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>-0.1048671277560966</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>-0.7523168452372127</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>-0.5147573096338856</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0.9305826025001082</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.062987768824252</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>-0.04075749382774697</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0.4179130669728224</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0.1486975310738488</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>-0.4582519851720804</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>ll7vCuXF</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.1956419370466253</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-0.2054762389029784</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-2.514333565441892</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-3.899868862053747</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-1.651409185926565</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-1.640212457935377</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.2512372537324318</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-1.326634231253677</v>
+      </c>
+      <c r="J19" t="n">
+        <v>-1.414342470700007</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.2855316698519419</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.6964901281488851</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.332077991853793</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1.070991302852903</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.001268875022430359</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.111547180585318</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>-0.9352221146276002</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>-0.3320351643649982</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0.05304197172787709</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0.3143930153483968</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0.1711789719608485</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1.222940038008764</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-0.4306848767394923</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>-1.629286704631094</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>-0.3150654494335448</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.7217832234229087</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>-1.134042880543172</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>-0.7824084313713265</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.277186156585806</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0.3993268381509281</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>-0.01222989455599608</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>-0.9853063107363748</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0.1394430700802125</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>-0.1754212053015475</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>YNHbsZ6C</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>-0.382569494749822</v>
+      </c>
+      <c r="C20" t="n">
+        <v>-0.2054762389029784</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.353265660913024</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-1.533305869046518</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.655825792006121</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.6397134424326745</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-0.5870066224040532</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.6843257116757807</v>
+      </c>
+      <c r="J20" t="n">
+        <v>-0.1811509027112553</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-0.3978978043513837</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.9722893898987318</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.5270854995646228</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1.070991302852903</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.3082364655915978</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.2855298213195669</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.1853796503352735</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0.6778525981925736</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0.1461667874049266</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0.4152654318388988</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>-1.458750452873586</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0.6109928248199092</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-0.2421592472930467</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>-0.7811038204351525</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>-0.4644751799862358</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.801804289539705</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>-0.4911358737120822</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0.9698667825435573</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0.1461533811068837</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1.280089224711964</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>1.50675402340325</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.171764204236275</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0.3602194852698326</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1.28990096326229</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>Gz9WD123</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>-1.712455787881651</v>
+      </c>
+      <c r="C21" t="n">
+        <v>-0.2054762389029784</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.353265660913024</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2.616753872313985</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.06835300259843144</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.271462457349473</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-0.1571379679750858</v>
+      </c>
+      <c r="I21" t="n">
+        <v>-0.3535890975781326</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.3901175366020867</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-0.9552725088683172</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.9722893898987318</v>
+      </c>
+      <c r="M21" t="n">
+        <v>-0.1528596152815691</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.5612847238871044</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.5730712496120555</v>
+      </c>
+      <c r="P21" t="n">
+        <v>-1.419273802448132</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>-0.5699555433519745</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0.1755803776612948</v>
+      </c>
+      <c r="U21" t="n">
+        <v>-0.04292634977137068</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0.5070646680101494</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>-1.255009274769281</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-0.1641403118859741</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0.08776060423823316</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>-0.6868612777467145</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0.1491383675037458</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0.2637678452926984</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>-0.3705908099312531</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.401447912791578</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>-0.5624586871000927</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>0.2704391661584956</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>0.2277443759257419</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0.6409218737489284</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0.2038264030000874</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0.0306013907387916</v>
       </c>
     </row>
   </sheetData>

--- a/data/spain/p6_deployment/data_preparation/df_selected_nan.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_selected_nan.xlsx
@@ -833,22 +833,22 @@
         <v>0.4776168060305839</v>
       </c>
       <c r="AG3" t="n">
-        <v>-0.8834063186483847</v>
+        <v>-0.9132961719330722</v>
       </c>
       <c r="AH3" t="n">
-        <v>-0.3993534485272661</v>
+        <v>-0.3777409907378055</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.6046778968578574</v>
+        <v>0.6352016887305229</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.4258985200295491</v>
+        <v>0.4739210944771274</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.08180379259917757</v>
+        <v>0.0883151312391733</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.177162926784322</v>
+        <v>1.147013396588433</v>
       </c>
     </row>
     <row r="4">
@@ -1066,7 +1066,7 @@
         <v>-0.3705908099312528</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.1100942369778535</v>
+        <v>-0.1097785050616115</v>
       </c>
       <c r="AG5" t="n">
         <v>0.3878044354823547</v>
@@ -1184,25 +1184,25 @@
         <v>0.7745872959866259</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.1389048195692081</v>
+        <v>0.1380230300720776</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.1860020848758931</v>
+        <v>0.1390240508843947</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0.06535216563387881</v>
+        <v>-0.1653707890073625</v>
       </c>
       <c r="AI6" t="n">
-        <v>-0.168652226857996</v>
+        <v>-0.2038759180406916</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-0.4441335400127469</v>
+        <v>-0.5005662944417005</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.1926833654500472</v>
+        <v>0.176028408112968</v>
       </c>
       <c r="AL6" t="n">
-        <v>-0.5909950427078076</v>
+        <v>-0.6310850539221001</v>
       </c>
     </row>
     <row r="7">
@@ -1302,7 +1302,7 @@
         <v>0.9177345592263605</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.357987618354051</v>
+        <v>-0.3708311416613675</v>
       </c>
       <c r="AG7" t="n">
         <v>1.443995175118813</v>
@@ -1423,22 +1423,22 @@
         <v>0.2981710498135253</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.03153181611364578</v>
+        <v>0.03711185671583531</v>
       </c>
       <c r="AH8" t="n">
-        <v>-0.6989677048516648</v>
+        <v>-0.7090913482393774</v>
       </c>
       <c r="AI8" t="n">
-        <v>-0.7153707896176377</v>
+        <v>-0.7106160909509259</v>
       </c>
       <c r="AJ8" t="n">
-        <v>-1.300280517559695</v>
+        <v>-1.298688762028124</v>
       </c>
       <c r="AK8" t="n">
-        <v>-0.3718972642333383</v>
+        <v>-0.3720776560230028</v>
       </c>
       <c r="AL8" t="n">
-        <v>-0.7460647807302981</v>
+        <v>-0.7316353400780231</v>
       </c>
     </row>
     <row r="9">
@@ -1541,22 +1541,22 @@
         <v>-0.2081119119120145</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.473513512716482</v>
+        <v>1.485595099754728</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.7318336576850462</v>
+        <v>0.6845353744587311</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.3352175725633407</v>
+        <v>0.3130394512167934</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-0.1620303375485396</v>
+        <v>-0.2033099607226342</v>
       </c>
       <c r="AK9" t="n">
-        <v>-0.09873848805820837</v>
+        <v>-0.1034987565194739</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.298010419924098</v>
+        <v>1.278642612410262</v>
       </c>
     </row>
     <row r="10">
@@ -1656,7 +1656,7 @@
         <v>1.538039366598545</v>
       </c>
       <c r="AF10" t="n">
-        <v>-2.183704525138614</v>
+        <v>-2.18704894469589</v>
       </c>
       <c r="AG10" t="n">
         <v>0.246481960026735</v>
@@ -1777,22 +1777,22 @@
         <v>-0.2152624368171645</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.505705186234064</v>
+        <v>0.4709982796446491</v>
       </c>
       <c r="AH11" t="n">
-        <v>-0.6627577955592421</v>
+        <v>-0.6988467680409347</v>
       </c>
       <c r="AI11" t="n">
-        <v>-0.7873919552149141</v>
+        <v>-0.7703901531283284</v>
       </c>
       <c r="AJ11" t="n">
-        <v>-1.092749723554103</v>
+        <v>-1.067549414250177</v>
       </c>
       <c r="AK11" t="n">
-        <v>-0.2010157300432614</v>
+        <v>-0.2078538302352926</v>
       </c>
       <c r="AL11" t="n">
-        <v>-0.6130055094780278</v>
+        <v>-0.6340747115973111</v>
       </c>
     </row>
     <row r="12">
@@ -1895,22 +1895,22 @@
         <v>0.3078056570759571</v>
       </c>
       <c r="AG12" t="n">
-        <v>-0.8550260097693017</v>
+        <v>-0.8606060503714912</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0.08356917940114636</v>
+        <v>-0.07344553601343379</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.3942633345988409</v>
+        <v>0.3895086359321291</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.03281987406622</v>
+        <v>1.03122811853465</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.2333313396609227</v>
+        <v>0.2335117314505872</v>
       </c>
       <c r="AL12" t="n">
-        <v>-0.1852737039762769</v>
+        <v>-0.1997031446285519</v>
       </c>
     </row>
     <row r="13">
@@ -2013,22 +2013,22 @@
         <v>-0.1850132256637204</v>
       </c>
       <c r="AG13" t="n">
-        <v>-1.165318793319315</v>
+        <v>-1.20002569990873</v>
       </c>
       <c r="AH13" t="n">
-        <v>-0.5232008016252527</v>
+        <v>-0.5592897741069454</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.352541857646848</v>
+        <v>1.369543659733434</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.5148135048711792</v>
+        <v>0.5400138141751046</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.249212909418156</v>
+        <v>1.242374809226125</v>
       </c>
       <c r="AL13" t="n">
-        <v>1.23402853825696</v>
+        <v>1.212959336137676</v>
       </c>
     </row>
     <row r="14">
@@ -2246,25 +2246,25 @@
         <v>2.301491437210464</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.1389048195692081</v>
+        <v>0.1380230300720776</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.2991908557623304</v>
+        <v>0.3167029148693964</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.399166526024115</v>
+        <v>2.445027052572944</v>
       </c>
       <c r="AI15" t="n">
-        <v>2.54729389471753</v>
+        <v>2.570469531860629</v>
       </c>
       <c r="AJ15" t="n">
-        <v>2.200714053774123</v>
+        <v>2.209366665068331</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.406872968921546</v>
+        <v>1.418769190024015</v>
       </c>
       <c r="AL15" t="n">
-        <v>3.556428668364208</v>
+        <v>3.56669540350172</v>
       </c>
     </row>
     <row r="16">
@@ -2485,22 +2485,22 @@
         <v>0.4906124494587784</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.2574596287721836</v>
+        <v>0.286925603656616</v>
       </c>
       <c r="AH17" t="n">
-        <v>-2.386275478235936</v>
+        <v>-2.332117381411281</v>
       </c>
       <c r="AI17" t="n">
-        <v>-4.281692652249272</v>
+        <v>-4.269644598209675</v>
       </c>
       <c r="AJ17" t="n">
-        <v>-2.591119128756817</v>
+        <v>-2.543338985622071</v>
       </c>
       <c r="AK17" t="n">
-        <v>-3.44054747843899</v>
+        <v>-3.435788742204379</v>
       </c>
       <c r="AL17" t="n">
-        <v>-2.688516957374928</v>
+        <v>-2.658693681298147</v>
       </c>
     </row>
     <row r="18">
@@ -2721,22 +2721,22 @@
         <v>-0.7824084313713265</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.277186156585806</v>
+        <v>1.307076009870493</v>
       </c>
       <c r="AH19" t="n">
-        <v>0.3993268381509281</v>
+        <v>0.3777143803614675</v>
       </c>
       <c r="AI19" t="n">
-        <v>-0.01222989455599608</v>
+        <v>-0.04275368642866142</v>
       </c>
       <c r="AJ19" t="n">
-        <v>-0.9853063107363748</v>
+        <v>-1.033328885183953</v>
       </c>
       <c r="AK19" t="n">
-        <v>0.1394430700802125</v>
+        <v>0.1329317314402168</v>
       </c>
       <c r="AL19" t="n">
-        <v>-0.1754212053015475</v>
+        <v>-0.1452716751056584</v>
       </c>
     </row>
     <row r="20">
@@ -2957,22 +2957,22 @@
         <v>2.401447912791578</v>
       </c>
       <c r="AG21" t="n">
-        <v>-0.5624586871000927</v>
+        <v>-0.5745402741383394</v>
       </c>
       <c r="AH21" t="n">
-        <v>0.2704391661584956</v>
+        <v>0.3177374493848105</v>
       </c>
       <c r="AI21" t="n">
-        <v>0.2277443759257419</v>
+        <v>0.2499224972722892</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0.6409218737489284</v>
+        <v>0.682201496923023</v>
       </c>
       <c r="AK21" t="n">
-        <v>0.2038264030000874</v>
+        <v>0.208586671461353</v>
       </c>
       <c r="AL21" t="n">
-        <v>0.0306013907387916</v>
+        <v>0.04996919825262754</v>
       </c>
     </row>
   </sheetData>

--- a/data/spain/p6_deployment/data_preparation/df_selected_nan.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_selected_nan.xlsx
@@ -1069,22 +1069,22 @@
         <v>-0.1097785050616115</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.3878044354823547</v>
+        <v>0.3818437329432747</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.0630233859672171</v>
+        <v>-0.1138223493575785</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0.1379036264043823</v>
+        <v>-0.1737709571459944</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.5988864131296676</v>
+        <v>-0.6328570341565101</v>
       </c>
       <c r="AK5" t="n">
-        <v>-0.0875485454950454</v>
+        <v>-0.09726832136830627</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.3587487582224743</v>
+        <v>0.3657188489842962</v>
       </c>
     </row>
     <row r="6">
@@ -1184,7 +1184,7 @@
         <v>0.7745872959866259</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.1380230300720776</v>
+        <v>0.1379293158038532</v>
       </c>
       <c r="AG6" t="n">
         <v>0.1390240508843947</v>
@@ -1305,22 +1305,22 @@
         <v>-0.3708311416613675</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.443995175118813</v>
+        <v>1.457640856791977</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.294070165149101</v>
+        <v>2.352814814074617</v>
       </c>
       <c r="AI7" t="n">
-        <v>2.462347558965596</v>
+        <v>2.580373431153953</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.112361078621093</v>
+        <v>1.117162837525694</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.109325989115507</v>
+        <v>2.143864653688333</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.643735281742362</v>
+        <v>1.706574213898514</v>
       </c>
     </row>
     <row r="8">
@@ -1420,7 +1420,7 @@
         <v>-1.134042880543172</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.2981710498135253</v>
+        <v>0.2968949666520344</v>
       </c>
       <c r="AG8" t="n">
         <v>0.03711185671583531</v>
@@ -1774,7 +1774,7 @@
         <v>0.9905638685939447</v>
       </c>
       <c r="AF11" t="n">
-        <v>-0.2152624368171645</v>
+        <v>-0.2156732104837122</v>
       </c>
       <c r="AG11" t="n">
         <v>0.4709982796446491</v>
@@ -1895,22 +1895,22 @@
         <v>0.3078056570759571</v>
       </c>
       <c r="AG12" t="n">
-        <v>-0.8606060503714912</v>
+        <v>-0.8546453478324111</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0.07344553601343379</v>
+        <v>-0.02264657262307239</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.3895086359321291</v>
+        <v>0.4253759666737412</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.03122811853465</v>
+        <v>1.065198739561492</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.2335117314505872</v>
+        <v>0.2432315073238481</v>
       </c>
       <c r="AL12" t="n">
-        <v>-0.1997031446285519</v>
+        <v>-0.2066732353903737</v>
       </c>
     </row>
     <row r="13">
@@ -2013,22 +2013,22 @@
         <v>-0.1850132256637204</v>
       </c>
       <c r="AG13" t="n">
-        <v>-1.20002569990873</v>
+        <v>-1.213671381581894</v>
       </c>
       <c r="AH13" t="n">
-        <v>-0.5592897741069454</v>
+        <v>-0.6180344230324608</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.369543659733434</v>
+        <v>1.251517787545078</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.5400138141751046</v>
+        <v>0.5352120552705044</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.242374809226125</v>
+        <v>1.207836144653299</v>
       </c>
       <c r="AL13" t="n">
-        <v>1.212959336137676</v>
+        <v>1.150120403981524</v>
       </c>
     </row>
     <row r="14">
@@ -2246,7 +2246,7 @@
         <v>2.301491437210464</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.1380230300720776</v>
+        <v>0.1379293158038532</v>
       </c>
       <c r="AG15" t="n">
         <v>0.3167029148693964</v>

--- a/data/spain/p6_deployment/data_preparation/df_selected_nan.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_selected_nan.xlsx
@@ -425,191 +425,366 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL6"/>
+  <dimension ref="A1:BU21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>id_coach_away</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>is_cup</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_30_matches_expected_points</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_180_matches_expected_points</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_30_matches_shots_on_goal</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_30_matches_shots_on_goal_against</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_180_matches_shots_on_goal</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_180_matches_shots_on_goal_against</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_30_matches_goal_attempts</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_30_matches_goal_attempts_against</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_180_matches_goal_attempts</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_180_matches_goal_attempts_against</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_30_matches_goals</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_30_matches_goals_against</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_180_matches_goals</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_180_matches_goals_against</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_30_matches_points</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_180_matches_points</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_30_matches_goal_ratio</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_30_matches_goal_ratio_against</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_180_matches_goal_ratio</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_goal_ratio_against</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_30_matches_PPS</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_30_matches_PPS_against</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_PPS</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_PPS_against</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_30_matches_attacks</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_30_matches_attacks_against</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_attacks</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_180_matches_attacks_against</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_30_matches_dangerous_attacks</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_30_matches_dangerous_attacks_against</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_180_matches_dangerous_attacks</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_180_matches_dangerous_attacks_against</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_30_matches_dead_balls</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_30_matches_dead_balls_against</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_dead_balls</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_180_matches_dead_balls_against</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_30_matches_total_passes_against</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_180_matches_total_passes</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_total_passes_against</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_30_matches_yellow_cards</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_30_matches_yellow_cards_against</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_yellow_cards</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_yellow_cards_against</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_180_matches_red_cards</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_red_cards_against</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_30_matches_defensive_actions</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_30_matches_defensive_actions_against</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_180_matches_defensive_actions</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_defensive_actions_against</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_30_matches_PPDA</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_30_matches_PPDA_against</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_PPDA</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_PPDA_against</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_30_matches_KGP</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_30_matches_KGP_against</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_180_matches_KGP</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_KGP_against</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_30_matches_clean_sheet</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_30_matches_clean_sheet_against</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_180_matches_clean_sheet</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_clean_sheet_against</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_180_matches_mean_rat_player_start_against</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_age_player_sub</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_rat_player_sub</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_value_player_sub</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_pot_player_sub</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_sub</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_rep_player_sub</t>
         </is>
@@ -618,591 +793,4461 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>QqTA4cPk</t>
+          <t>zeCiJHet</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2187703943184832</v>
+        <v>1.910080355503086</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.2054762389029784</v>
+        <v>1.805149320052122</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9235324135402558</v>
+        <v>-1.463268858082171</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01010477856689252</v>
+        <v>-0.2058317055638894</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.4608045938707983</v>
+        <v>-3.20872234484278</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.2836808356556</v>
+        <v>0.8337395356168954</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2512372537324318</v>
+        <v>0.5986077292491325</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.07248717007186425</v>
+        <v>-0.6349018439546278</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.1293482230757884</v>
+        <v>0.6505517365678246</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1412521141867959</v>
+        <v>0.6901935917619201</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.2688072879755787</v>
+        <v>-1.985613912436762</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.1528596152815691</v>
+        <v>-0.09398855380644348</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3913825308985051</v>
+        <v>-0.9426254969163388</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2299898248582804</v>
+        <v>1.142495624339516</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4289679133182492</v>
+        <v>0.03041006058334787</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>1.177233062487739</v>
       </c>
       <c r="R2" t="n">
-        <v>0.836997175635617</v>
+        <v>2.174340023149884</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.128528195521976</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7188180629876781</v>
+        <v>-0.4625197820256056</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8527779842216145</v>
+        <v>1.264883760308195</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1927056557725524</v>
+        <v>6.159742565176198</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>-2.621787745075117</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.587935098559682</v>
       </c>
       <c r="Y2" t="n">
-        <v>-1.119181822699745</v>
+        <v>-1.520004266450132</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.222940038008764</v>
+        <v>2.277459712954391</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0.4621058149805665</v>
+        <v>-5.278159620049714</v>
       </c>
       <c r="AB2" t="n">
-        <v>-0.6083258255063496</v>
+        <v>2.909894461436554</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.01154756912839323</v>
+        <v>-7.983663501120209</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0.6927890577801395</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.156313331292585</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.3078056570759571</v>
+        <v>-0.1389906885879181</v>
       </c>
       <c r="AG2" t="n">
-        <v>-0.8546453478324111</v>
+        <v>0.6345970470906692</v>
       </c>
       <c r="AH2" t="n">
-        <v>-0.02264657262307239</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.4253759666737412</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.065198739561492</v>
+        <v>0.5879821696653247</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.2432315073238481</v>
+        <v>0.5064698520208593</v>
       </c>
       <c r="AL2" t="n">
-        <v>-0.2066732353903737</v>
+        <v>-1.405494690164241</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>-0.9556242723486339</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>-1.393444359540287</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>-1.998313976220888</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>2.50750427261751</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>2.317578871811711</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>3.350093992710342</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>-0.8624868604486826</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>-2.493625751459987</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>-0.393632561168577</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>-2.0641631911956</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>1.173374464399779</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>-0.3737514212012704</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>-2.02905838291999</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>-0.354848132751914</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>-1.633373644721553</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>-0.03152798019286856</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>2.969199484962235</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>2.036689258016122</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>3.934808434988395</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>2.384109940286072</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>0.1499494701103776</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>2.087878028826297</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>0.03128825462301144</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>-0.0285540927585344</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>-0.7381206495893828</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>-1.937911943267697</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>0.4072498057655553</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>0.2938639983173975</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>-0.1412970155705537</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>-0.08573793520216166</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>-0.08505722880131719</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>-0.5006760568259889</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>0.3531669267888535</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>2Xrca2mA</t>
+          <t>U5mYDMJ0</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1956419370466253</v>
+        <v>1.942564741172752</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.2054762389029784</v>
+        <v>-0.7733584466023637</v>
       </c>
       <c r="D3" t="n">
-        <v>3.287065274090483</v>
+        <v>0.195231428532302</v>
       </c>
       <c r="E3" t="n">
-        <v>4.245909555905918</v>
+        <v>-0.2058317055638894</v>
       </c>
       <c r="F3" t="n">
-        <v>1.920404590240736</v>
+        <v>0.05060358331690091</v>
       </c>
       <c r="G3" t="n">
-        <v>2.519323135328695</v>
+        <v>-4.120853715099421</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.314201096146388</v>
+        <v>0.06295539227748714</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2302379826271937</v>
+        <v>-0.9187013930437127</v>
       </c>
       <c r="J3" t="n">
-        <v>1.48372966223972</v>
+        <v>-1.348992653672368</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.503534820395874</v>
+        <v>-0.8059555388848278</v>
       </c>
       <c r="L3" t="n">
-        <v>3.7302820073972</v>
+        <v>0.2276037638472619</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.4498471367086415</v>
+        <v>-1.945241490657405</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5612847238871044</v>
+        <v>-1.506978507826463</v>
       </c>
       <c r="O3" t="n">
-        <v>2.631559798134707</v>
+        <v>-0.2707932115787764</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.976593582956553</v>
+        <v>1.724510666616079</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>0.5710361968479852</v>
       </c>
       <c r="R3" t="n">
-        <v>-2.829196928649358</v>
+        <v>1.163898441843333</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>-0.002532351390126108</v>
       </c>
       <c r="T3" t="n">
-        <v>1.092850567638631</v>
+        <v>0.04326372136400455</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.663724668425342</v>
+        <v>0.4605662051525108</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.176277139455691</v>
+        <v>1.430018415816542</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>-0.7920037251003184</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.424519785541078</v>
       </c>
       <c r="Y3" t="n">
-        <v>-2.477456343395107</v>
+        <v>-0.4015596653415653</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.7352910441955723</v>
+        <v>2.779835193677982</v>
       </c>
       <c r="AA3" t="n">
-        <v>-1.279050209248497</v>
+        <v>-3.193556823435683</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.4911705058587597</v>
+        <v>3.637930820099494</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.6721453086160757</v>
+        <v>-4.646866373267843</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.147898708918259</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.7745872959866259</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.1850132256637204</v>
+        <v>1.811909741072753</v>
       </c>
       <c r="AG3" t="n">
-        <v>-1.213671381581894</v>
+        <v>-0.7744767500016826</v>
       </c>
       <c r="AH3" t="n">
-        <v>-0.6180344230324608</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.251517787545078</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.5352120552705044</v>
+        <v>-0.4328948320649244</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.207836144653299</v>
+        <v>-0.561901756642659</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.150120403981524</v>
+        <v>-0.263638315143467</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0.09622643772834651</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>-0.5268334756195794</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0.7748113740991492</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>-0.2766048188628574</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1.401670666080667</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>-0.3248505915856329</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>0.3862009444542097</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>-0.4056679712377373</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>0.09178236676881241</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>-0.6807969955355617</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1.566432562343917</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>-1.516873002237066</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>0.05063096359535006</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0.1524263161315845</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>-0.01405480171376642</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>-0.5903800798950433</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>-0.2305461740485769</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>0.4551872866957549</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>-0.2889427133730788</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>0.4969842776187397</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>-0.1864021514264455</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>1.009855550726795</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>0.03128825462301144</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>-0.9857932694003733</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>0.007760465128248513</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>-1.553268212095585</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>0.05628319734897231</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>1.247744097429556</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>1.10118975398456</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>1.071423495339686</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>-0.1543902901113048</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>0.2198981065613369</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>0.6707663212321756</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>f1xuAJ1S</t>
+          <t>rsizUY9b</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-1.643070416066077</v>
+        <v>1.942564741172752</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.2054762389029784</v>
+        <v>1.805149320052122</v>
       </c>
       <c r="D4" t="n">
-        <v>0.06406591879471901</v>
+        <v>-0.5555761336512771</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9875981887220522</v>
+        <v>-0.2058317055638894</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2006424017157389</v>
+        <v>-3.20872234484278</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7366650239298073</v>
+        <v>-2.056439860634289</v>
       </c>
       <c r="H4" t="n">
-        <v>1.816675603611252</v>
+        <v>-1.276175450151626</v>
       </c>
       <c r="I4" t="n">
-        <v>1.138413440724368</v>
+        <v>2.203093646936222</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8002220837161996</v>
+        <v>0.7755232609578362</v>
       </c>
       <c r="K4" t="n">
-        <v>2.247733626897934</v>
+        <v>1.046419575249241</v>
       </c>
       <c r="L4" t="n">
-        <v>2.902884222147661</v>
+        <v>-1.074288986908046</v>
       </c>
       <c r="M4" t="n">
-        <v>1.480571752567329</v>
+        <v>2.550658498837787</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3064314344042054</v>
+        <v>1.166272596484652</v>
       </c>
       <c r="O4" t="n">
-        <v>1.945396948627156</v>
+        <v>0.7891734153599432</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.6299865370545078</v>
+        <v>0.03041006058334787</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.389626793767247</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8843465459861602</v>
+        <v>0.2978056578662902</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.774848508043178</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2379191284364539</v>
+        <v>-0.2939252808957357</v>
       </c>
       <c r="U4" t="n">
-        <v>2.068376723212093</v>
+        <v>-0.6884588736413244</v>
       </c>
       <c r="V4" t="n">
-        <v>-2.078791722976533</v>
+        <v>1.355997853286435</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>-1.565610070120093</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.4188010984402339</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.1711789719608485</v>
+        <v>-0.6532707721531763</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.222940038008764</v>
+        <v>1.876900007614107</v>
       </c>
       <c r="AA4" t="n">
-        <v>-0.2892906546546581</v>
+        <v>-0.377698646175701</v>
       </c>
       <c r="AB4" t="n">
-        <v>-0.4512549210256196</v>
+        <v>2.329408270344971</v>
       </c>
       <c r="AC4" t="n">
-        <v>-1.422013012899392</v>
+        <v>-0.139558077614441</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0.713962273255933</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0.3705908099312529</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.7046203997048154</v>
+        <v>-0.661407540045168</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.331972129375343</v>
+        <v>0.4860038103063856</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.6890445866454669</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.2158317258279149</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.7854575424848882</v>
+        <v>-0.05355843036936852</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.2960956516099905</v>
+        <v>0.1673239808986021</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.176538013797588</v>
+        <v>-0.6442571068170581</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0.4117816507514407</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>-0.4425796396828436</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>-0.2114465956799439</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.929670310234793</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>-1.76878081529602</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>2.587369645026272</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>2.883576554259994</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0.01192358480671266</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>1.539936901782024</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>-0.7424757431127607</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0.7017047468668141</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>-0.6785838428108157</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1.311048749362223</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0.5328821527942085</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0.09707492280637536</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>-0.1592656029819367</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>-0.3122312906252522</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>-2.15594455410557</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>-0.3967692851423593</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>-2.618746208173866</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>0.2684194334315433</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>-0.03830856365060071</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>0.03128825462301144</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>-0.0285540927585344</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>-1.484001764307014</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>-0.7839807497513599</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>-0.1832812121274911</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>0.2421875348541276</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>0.5133215694726395</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>-0.2602621452128921</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>0.2998129721653025</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>-0.08558817824439115</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>-0.9252988622001921</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>65kl1OIc</t>
+          <t>UaS8aGMt</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5194403388526357</v>
+        <v>1.910080355503086</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.2054762389029784</v>
+        <v>1.805149320052122</v>
       </c>
       <c r="D5" t="n">
-        <v>0.06406591879471901</v>
+        <v>0.2960861756912902</v>
       </c>
       <c r="E5" t="n">
-        <v>2.616753872313986</v>
+        <v>-0.2058317055638894</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5975105990676612</v>
+        <v>2.223487535423355</v>
       </c>
       <c r="G5" t="n">
-        <v>1.033774709162955</v>
+        <v>5.136412621765275</v>
       </c>
       <c r="H5" t="n">
-        <v>0.04704964287867258</v>
+        <v>3.544695582593182</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.02924071968628468</v>
+        <v>-2.053899589400053</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9369235994209039</v>
+        <v>3.781782708784236</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.2915865528086435</v>
+        <v>-1.850885090447635</v>
       </c>
       <c r="L5" t="n">
-        <v>1.385988282523502</v>
+        <v>3.091767815508939</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.746834658135714</v>
+        <v>-0.4906856117030781</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5612847238871044</v>
+        <v>2.694316128948906</v>
       </c>
       <c r="O5" t="n">
-        <v>1.487955048955456</v>
+        <v>-1.788770109416943</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9244546099262378</v>
+        <v>2.853911070637899</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-2.459948131350784</v>
       </c>
       <c r="R5" t="n">
-        <v>0.6611280857621683</v>
+        <v>4.050874388433479</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-0.6129459798823721</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3180689508616575</v>
+        <v>1.054830728143225</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5328835792241192</v>
+        <v>2.238531327075603</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.804995163930884</v>
+        <v>-0.9633131059902501</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.2744817320668533</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-2.299567369038825</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.5107476021346889</v>
+        <v>1.29084544909255</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.222940038008764</v>
+        <v>3.038988086560607</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.4463953458600292</v>
+        <v>-2.741872424249195</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.9381747249158822</v>
+        <v>4.013492000353515</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.4936053790248102</v>
+        <v>-3.923860912299802</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.9107068242038274</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.301491437210464</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.3030425709125815</v>
+        <v>1.87093279880951</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.3188405064763489</v>
+        <v>-2.784623985014549</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.420970853257167</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>2.531411578909091</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2.182635491700993</v>
+        <v>1.415429844751947</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.420347779659757</v>
+        <v>-1.570069956231222</v>
       </c>
       <c r="AL5" t="n">
-        <v>3.503877023966795</v>
+        <v>-0.2092642020472399</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>-1.849697375914068</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0.7838521375616656</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>-1.4230477176872</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>-1.9575763457944</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>2.343999300823183</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>-2.543685057575655</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>-0.4462575921477186</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>-1.240851083326637</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>-1.310527425050312</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0.4773928200807334</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>-0.005799829432633994</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0.007289105810661419</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>-1.209786822171522</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0.2792449283524594</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>-1.038453615711468</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>-0.3744026518898419</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0.496091635604766</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>0.5459739704041541</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0.6702389248059334</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>0.6053153981367531</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>0.9140404747734812</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>0.8034329501013033</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>0.9801808485475174</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>-0.0285540927585344</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>0.1844165186140035</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>-2.444022115862582</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>0.1882604685828206</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>-1.839624826324192</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>0.1350316347400943</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>2.180093341407037</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>1.609958549651608</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>0.06052978064136308</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>1.910735417454908</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>0SQqjbAd</t>
+          <t>QXtsC0lD</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-1.712455787881651</v>
+        <v>2.007533512512086</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.2054762389029784</v>
+        <v>-0.9975765132679711</v>
       </c>
       <c r="D6" t="n">
-        <v>1.782998908285793</v>
+        <v>1.472724892546153</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.967388631588267</v>
+        <v>-0.2058317055638894</v>
       </c>
       <c r="F6" t="n">
-        <v>1.303054061026634</v>
+        <v>2.223487535423355</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.09524209472300701</v>
+        <v>7.02698109901229</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2512372537324318</v>
+        <v>-0.2048707762083355</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0508639448790747</v>
+        <v>0.2164968033126271</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.113599136149658</v>
+        <v>0.02569411461776414</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1123962030537667</v>
+        <v>-1.304671915767077</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4206908663990384</v>
+        <v>0.7483608641493851</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5983408974221776</v>
+        <v>0.1704761514579796</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5612847238871044</v>
+        <v>0.8692446960056391</v>
       </c>
       <c r="O6" t="n">
-        <v>0.6874317245299809</v>
+        <v>-1.065768181782816</v>
       </c>
       <c r="P6" t="n">
-        <v>0.8628339656860612</v>
+        <v>0.5951102625942581</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.6413575344315225</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3263003954261789</v>
+        <v>1.163898441843333</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-2.10307336708403</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4863977853320574</v>
+        <v>0.3804527236237448</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5355493659324319</v>
+        <v>2.299006331222647</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.4968560484905624</v>
+        <v>1.059001769060697</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>-0.3179750376473644</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>0.8099570301099928</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.5107476021346892</v>
+        <v>0.8815119747769353</v>
       </c>
       <c r="Z6" t="n">
-        <v>-1.632813623539227</v>
+        <v>4.09880853617539</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.04062919687662175</v>
+        <v>-3.135961978992276</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.6953626816837084</v>
+        <v>5.54937074161437</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.5650213508613167</v>
+        <v>-4.554675039825317</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0.9765557828401791</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.3928612606806661</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.3847574525332738</v>
+        <v>-0.9797553089019299</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.9705157796220211</v>
+        <v>1.10428831278812</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0.02445241492040967</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.2112314101394219</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.5652168043518545</v>
+        <v>0.3838067693192739</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.2116441066079947</v>
+        <v>1.077924433399021</v>
       </c>
       <c r="AL6" t="n">
-        <v>-0.7987244579294914</v>
+        <v>-0.4811347675283761</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>-0.4296989173101437</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>-1.17679163856011</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>-0.6755679932230459</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>-0.7388719887690317</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0.6971258924414039</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>-0.935030069732889</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>-2.111174665351575</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>-4.581583531682237</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>-0.4098130587664899</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>-1.147793227191498</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>2.352548758232193</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>-2.850514846778827</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0.4917771886137555</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0.08901701002114742</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0.1288262726692734</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>-0.3668392400141736</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>-1.296560855769593</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>-0.1611495904759581</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>-1.69611103733333</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>-0.2384590913123325</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>-2.050236145613386</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>1.415695343114976</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>0.03128825462301144</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>-0.9857932694003733</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>2.618344366639958</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>-1.168624480923472</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>0.158002600811192</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>0.2587053385081953</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>1.834568780482931</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>2.361989559970304</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>1.848056426234504</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>-0.02412710876876343</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>3.252090711916944</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>zHmSVfun</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1.910080355503086</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.5202073226222947</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.21498498313985</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-0.2058317055638894</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.05060358331690091</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-6.185267569564552</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.8664338977349552</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-0.06730274577645783</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-2.973622470742523</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.476458001669527</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-0.03277478630379965</v>
+      </c>
+      <c r="M7" t="n">
+        <v>-0.8873826695997128</v>
+      </c>
+      <c r="N7" t="n">
+        <v>-2.3683594192156</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-0.4180107986535989</v>
+      </c>
+      <c r="P7" t="n">
+        <v>-1.098990343438473</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.177233062487739</v>
+      </c>
+      <c r="R7" t="n">
+        <v>-3.455263072700897</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.774848508043178</v>
+      </c>
+      <c r="T7" t="n">
+        <v>-1.642681289934696</v>
+      </c>
+      <c r="U7" t="n">
+        <v>-2.756704015470228</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.5766635131125479</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.3356954969129662</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.744312579423651</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.05904865764602932</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>5.03290569354019</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>-4.301394871161423</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>6.903052836341126</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>-6.420168616640616</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>-1.763380586087806</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.599599102069068</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>-1.550486497116986</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>-0.9221666014245438</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>2.23757088728299</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0.306596579743743</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1.254533341328541</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1.43618436559807</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>-0.4447019715560118</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>-1.733553576614056</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>-0.5467340381846351</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>2.051118017658066</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>3.352656033162313</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0.9682259866557655</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>1.743765200891957</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>-0.005799829432633994</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0.007289105810661419</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0.1766727421720375</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0.2792449283524594</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0.2399559971894152</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>-0.07942958873876911</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0.01091643778157313</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>-1.120530422628249</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0.02979449035806034</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>-1.383239320143915</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>2.253978190073735</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>-1.524372726106824</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>0.03128825462301144</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>0.9286850838833044</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>-1.111061206948198</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>2.29316909962554</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>1.082890406033068</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>-0.4829442034359446</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>-2.009255793103132</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>-4.108695750774997</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>-1.676583144934904</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>-0.5134135087171809</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>-3.491203692062761</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>YFePBifU</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1.910080355503086</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-0.368041172245304</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-1.653772269382483</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-0.2058317055638894</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.05060358331690091</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.8337395356168954</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.06295539227748714</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-1.202500942132798</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.71303749876283</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1.901361935618811</v>
+      </c>
+      <c r="L8" t="n">
+        <v>-0.423342611530392</v>
+      </c>
+      <c r="M8" t="n">
+        <v>-0.09398855380644348</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.9583530661493435</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.7891734153599432</v>
+      </c>
+      <c r="P8" t="n">
+        <v>-0.5342901414275624</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.5710361968479852</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.029991225820377</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.613268429912878</v>
+      </c>
+      <c r="T8" t="n">
+        <v>-0.6311142831554755</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.035078744549428</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.998057695677215</v>
+      </c>
+      <c r="W8" t="n">
+        <v>-3.360127216581838</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.2789166249114317</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>-0.8295193232879278</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.172392883914694</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>-2.397401428879516</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>4.206820589467669</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-3.372470580364633</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.2446591867010009</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>-0.005891042496763281</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.09366277935383543</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1.239422467266761</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.06260636343389694</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>-0.7452541303332374</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>-0.8999576061965504</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>-1.627016858186406</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>-1.064560222112018</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>-0.02503250053884159</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>-1.364929247518456</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0.8024302127551737</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>-0.8232595272821873</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>1.094973217839417</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>1.143131682818755</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>-0.7919160253209098</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0.7693701598345251</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>-0.01238992569299367</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>1.166975213898582</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>-0.3791953251370911</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>0.03234083120166593</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>-1.456101331412326</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>-1.186582002544335</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>-1.906708796973529</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>-1.46205530253267</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>0.1650478282490899</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>1.835502965667389</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>0.03128825462301144</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>-0.0285540927585344</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>-0.7381206495893828</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>-1.937911943267697</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>0.4177116239714078</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>-1.253124495523265</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>-0.2633077158007873</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>0.09138095579948366</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>0.7804178371092445</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>0.7201595435055085</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>-0.1136745234005542</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>dA00HeQh</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.910080355503086</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-1.704725800444118</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.1073328129446628</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-0.2058317055638894</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.05060358331690091</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.072387848295974</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.937738571678246</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-0.6349018439546278</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.33789512071289</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.1914772148796705</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.269117964451508</v>
+      </c>
+      <c r="M9" t="n">
+        <v>-0.4906856117030781</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1.700922817346875</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.05308547998583196</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.5951102625942581</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>-0.6413575344315225</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.596944833831855</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.1590477267401742</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.7176417258834847</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.4605662051525105</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.7720578599933691</v>
+      </c>
+      <c r="W9" t="n">
+        <v>-3.228165201717776</v>
+      </c>
+      <c r="X9" t="n">
+        <v>-0.8100170556584335</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>-0.6358916721140084</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.983921563665069</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>-4.342578629984416</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>3.933690273654288</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-6.486090934493178</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.469073682303933</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>-3.396207996712908</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>2.189147151326451</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>-1.096087560974419</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.6607216074923972</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>-1.849697375914068</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>-0.08149177138254902</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>-2.5088475135183</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>-0.7598841328556759</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0.7675803698053303</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>-0.9627655005577643</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>1.218659481056138</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>-1.240851083326637</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>-0.3370008195758814</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0.7730591973555607</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>-2.364148417097461</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>2.293532267882252</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>-0.8946823757298042</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>-0.7987132755249751</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>-0.6967088237660689</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>-0.6542488912895777</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>1.80497340020747</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>1.849524003283614</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>2.397998392419102</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>2.160775185242738</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>0.9682226432930051</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>0.02876158400843228</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>-0.9176043393014947</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>-0.0285540927585344</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>0.3807010224870641</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>-0.3993370185792475</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>-0.05052648706912563</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>0.1891119420369848</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>1.279154511306741</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>0.7992586524991334</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>1.447622176538413</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>0.04677616041084656</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>0.9816596612687066</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>4z48FZf5</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1.910080355503086</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-1.583992995316483</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.2642179751919778</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-0.2058317055638894</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-2.122280368789553</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.007973993830842931</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0.2048707762083355</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.784095901490797</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.02546630973786</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-0.8059555388848274</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.09741448877173114</v>
+      </c>
+      <c r="M10" t="n">
+        <v>-0.6229179643352897</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-0.1703529556709055</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-0.9774376295379226</v>
+      </c>
+      <c r="P10" t="n">
+        <v>-1.098990343438473</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-0.6413575344315225</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.308247239172841</v>
+      </c>
+      <c r="S10" t="n">
+        <v>-0.8104327420416282</v>
+      </c>
+      <c r="T10" t="n">
+        <v>-0.6311142831554755</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.9201762366700444</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.8852252997230091</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.482298945686944</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.043592319098541</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>-0.2270893138225617</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.1834727153291</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>-2.922473282256285</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.773689662161274</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>-4.212946403916988</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.003796173974819</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>-0.5524408789447062</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>-0.1964812106116037</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0.717659588617136</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0.60634749439617</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>-0.008958633279351194</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0.3999587196845099</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0.1946596271702698</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>-1.033042005982052</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1.119852756624962</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>-1.323326101281143</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>-0.03002832384675448</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>-2.076034195415537</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>-0.7010620155289232</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>-1.940805696041202</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>-0.9491392644985649</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0.9217863706392978</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>-0.2644734828463679</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>-0.2914388266414766</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>-0.347443975274193</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>-0.7181177026841119</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>-0.7757537199782432</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>1.15913764872621</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>-1.008631477300545</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>1.336972350679779</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>-0.5972435077159699</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>1.315760576680705</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>0.03128825462301144</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>-0.0285540927585344</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>-0.7381206495893827</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>-1.168624480923472</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>0.9419745937157892</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>0.05982513781915626</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>0.4163522238908682</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>0.4256518267186482</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>0.5038338719452831</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>-0.5279679195975019</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>0.2791552404924548</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>02cHDDPH</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1.910080355503086</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1.1324951200553</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-1.653772269382483</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-0.2058317055638894</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-3.20872234484278</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-0.4049087770621833</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-0.740523113179981</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.203093646936222</v>
+      </c>
+      <c r="J11" t="n">
+        <v>-0.2867346963572663</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1.260155165341633</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-1.074288986908046</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.09610261988346</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-0.1406501656230044</v>
+      </c>
+      <c r="O11" t="n">
+        <v>-0.06468858967402537</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.03041006058334787</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.389626793767247</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.1534568605367828</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.259588742434079</v>
+      </c>
+      <c r="T11" t="n">
+        <v>-0.9683032854152156</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-1.148068905158859</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.704158153620762</v>
+      </c>
+      <c r="W11" t="n">
+        <v>-1.9738224540167</v>
+      </c>
+      <c r="X11" t="n">
+        <v>-0.8057569660024158</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.1067154738895052</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.3459198237461631</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.6563704366501388</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.1107306457066826</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.515663123843563</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>-0.117767503997466</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>-1.000782541655909</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>-0.08902047358736738</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>-0.8998053351967024</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>-0.9161276722981941</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0.9377070057899315</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0.36384993285448</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0.705193164467683</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>-1.327212023195072</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0.4593420313381523</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>-1.711622132829397</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0.8024302127551737</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0.8471066968956126</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0.7228217730874188</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>2.182859141977255</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0.3872582685115039</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>-0.3737514212012703</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>-0.3905152614230551</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0.08901701002114742</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0.4463397712982508</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>0.5273241195093067</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>-0.8787376437213287</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>-0.187300800552988</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>-1.144573052827864</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>-0.269663996864847</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>1.844419865445105</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>0.3343846226742828</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>-0.9176043393014947</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>0.9286850838833044</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>-0.7381206495893825</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>0.7545941749370902</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>0.4382927326825876</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>-0.5376224293894303</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>-0.6265537405305722</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>-0.5056905348638414</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>-0.320866878935276</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>-0.3869746351922934</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>-0.5130776189015736</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>E595Qvn9</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1.910080355503086</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-0.3852887158349662</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.2960861756912902</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-0.2058317055638894</v>
+      </c>
+      <c r="F12" t="n">
+        <v>3.309929511476581</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.659505077402948</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-0.2048707762083355</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-0.7295016936509894</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.4922544723404759</v>
+      </c>
+      <c r="K12" t="n">
+        <v>-0.08875389213035469</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.8785501392249159</v>
+      </c>
+      <c r="M12" t="n">
+        <v>-0.5347630625804818</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.8692446960056391</v>
+      </c>
+      <c r="O12" t="n">
+        <v>-0.3100512347987289</v>
+      </c>
+      <c r="P12" t="n">
+        <v>-1.098990343438473</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>-0.4392919125516045</v>
+      </c>
+      <c r="R12" t="n">
+        <v>-1.203421834360585</v>
+      </c>
+      <c r="S12" t="n">
+        <v>-0.3041484972333534</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.2118582224938746</v>
+      </c>
+      <c r="U12" t="n">
+        <v>-0.2288488421237904</v>
+      </c>
+      <c r="V12" t="n">
+        <v>-0.02804644613753196</v>
+      </c>
+      <c r="W12" t="n">
+        <v>-0.2125680840590385</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-0.66195750681459</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>-1.241591155269555</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0.3463889375450271</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-0.517353793450501</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.1114104796456949</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>-0.3631022919238845</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>-1.33750696243537</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0.03797268727498227</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0.2804490786177808</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>-0.1684338195830713</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1.911326208705626</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>-0.9556242723486339</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>-0.09352803365922482</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>-0.4319042595129174</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0.2066744951299611</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>-0.9849747546223385</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0.3130643173864986</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>1.079916391622483</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>-1.936837010067387</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0.3792558740917333</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>-1.276437472138229</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>-2.167619368125392</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>1.531451213858389</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>1.657663640448112</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>-0.3231434796966951</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0.03357222308058006</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>-0.2231344143764716</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>-0.2337826753444321</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>0.5049402448404956</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>-0.2932149829600521</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>0.5563519457033813</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>0.1092342528961072</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>-1.645217608153971</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>1.454627145509771</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>-0.0285540927585344</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>0.007760465128248513</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>0.7545941749370905</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>0.7552509843713513</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>-0.02023210189878434</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>-0.1673013831074609</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>-0.7325109894787699</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>-0.3270156992143647</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>-0.3975636601827129</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>-0.5530863017608216</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>jiAoNQdE</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1.942564741172752</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-1.704725800444118</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.195231428532302</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-0.2058317055638894</v>
+      </c>
+      <c r="F13" t="n">
+        <v>4.396371487529809</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.4208567647238691</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.7771585082396812</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-1.580900340918244</v>
+      </c>
+      <c r="J13" t="n">
+        <v>-0.03262593009757497</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-0.4212314767185214</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.5313787390235003</v>
+      </c>
+      <c r="M13" t="n">
+        <v>-1.240002276618944</v>
+      </c>
+      <c r="N13" t="n">
+        <v>-0.239659465782675</v>
+      </c>
+      <c r="O13" t="n">
+        <v>-0.09020630476699447</v>
+      </c>
+      <c r="P13" t="n">
+        <v>-0.3460567407572589</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>-1.651685643831112</v>
+      </c>
+      <c r="R13" t="n">
+        <v>-1.203421834360585</v>
+      </c>
+      <c r="S13" t="n">
+        <v>-1.661421153527877</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.054830728143225</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.0009561736349765304</v>
+      </c>
+      <c r="V13" t="n">
+        <v>-0.5474923536022943</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.441564820482067</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-0.7320247773345041</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.5084198486566553</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-3.445852089525309</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.166789593681649</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>-5.384258505918402</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>3.933371817903754</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0.1731979043212665</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>-0.2575834529746366</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>-0.01497025661975652</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>-0.7213669481260511</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>-0.7530053330095128</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>-0.3245138463024454</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0.002762064554185427</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0.1598505223545378</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.089184546769021</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.111045946954471</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>1.477952412031261</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>-1.833688486484265</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0.2903179555030126</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>-0.3289105707769246</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0.69375795047059</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0.3872582685115039</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>-0.3737514212012703</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>-0.7056197078647735</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>-0.354848132751914</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0.1764532974636199</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>0.6390945394497413</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>1.693709677881079</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>2.172769750376071</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>2.251127257951385</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>2.5464878531675</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>-0.3421755746124052</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>-0.8093179631351023</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>1.929073442472024</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>-0.0285540927585344</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>2.245403809281142</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>1.139237906109203</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>0.4165569740332744</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>-0.9409900481995425</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>-0.3664984169123259</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>0.644813475817937</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>0.4383780515902679</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>0.953340906264492</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>1.203473405963594</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>842EOIGL</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1.910080355503086</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-1.583992995316483</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-0.1073328129446628</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-0.2058317055638894</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.05060358331690091</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-0.4049087770621833</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.491361624201875</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-0.2565024451691809</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.9004947853478482</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.7091923108812433</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.2710001888724387</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.611250660232018</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.6197412596032685</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.5693284853282088</v>
+      </c>
+      <c r="P14" t="n">
+        <v>-0.7225235420978658</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>-0.4392919125516046</v>
+      </c>
+      <c r="R14" t="n">
+        <v>-0.9339707460121718</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.7515080132179423</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.3804527236237445</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-1.033166397279475</v>
+      </c>
+      <c r="V14" t="n">
+        <v>-1.382884804874898</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0.3535529944237157</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-1.120298128117189</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>-0.07543278924143212</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-2.08771873135754</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.38046150375648</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>-3.416068372046884</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>4.275393721068474</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0.3475100043316476</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>-0.4602105940441156</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0.637414108696473</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>-0.052561803675168</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0.6063474943961705</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0.9377070057899315</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1.122134456285099</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0.8908417234849244</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0.3012291435198604</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>-2.156280440797615</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0.4378737560984374</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>-1.139973039315992</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>2.795867291769713</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>-0.3148874728587341</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>1.297034843439957</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>-1.774561270181254</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>1.721971477364355</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>-0.3274943721347117</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>1.230384520009019</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0.4780911211611484</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>0.8147337707847103</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>1.372727722784365</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>-1.42019933344944</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>1.827422362024694</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>-1.740818951513012</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>0.7913848959324219</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>-1.508716320367424</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>0.9801808485475174</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>0.9286850838833044</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>-1.484001764307014</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>1.523881637281315</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>0.2800973356712006</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>-1.555972622958719</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>-2.046015969922268</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>-2.120449420260839</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>-0.4020625210200002</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>0.9985347240740724</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>-2.91333986093756</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>naHJ2yf2</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2.007533512512086</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-0.368041172245304</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.472724892546153</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-0.2058317055638894</v>
+      </c>
+      <c r="F15" t="n">
+        <v>5.482813463583036</v>
+      </c>
+      <c r="G15" t="n">
+        <v>3.311036160975053</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.5986077292491325</v>
+      </c>
+      <c r="I15" t="n">
+        <v>-1.013301242740074</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.7255346512018311</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-0.8867000951419531</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.572892939627747</v>
+      </c>
+      <c r="M15" t="n">
+        <v>-0.5347630625804818</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1.451419380944504</v>
+      </c>
+      <c r="O15" t="n">
+        <v>-1.161950338671701</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.7833436632645615</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>-1.651685643831112</v>
+      </c>
+      <c r="R15" t="n">
+        <v>-0.2603430251411378</v>
+      </c>
+      <c r="S15" t="n">
+        <v>-0.9073807889198086</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.392019730402965</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.11585868151436</v>
+      </c>
+      <c r="V15" t="n">
+        <v>-0.3169000902250848</v>
+      </c>
+      <c r="W15" t="n">
+        <v>-0.8711960289349856</v>
+      </c>
+      <c r="X15" t="n">
+        <v>-1.348858224580942</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>2.027803220291297</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-1.585257472032716</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>3.545783784487493</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>-2.687907704091616</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>6.140710243564516</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0.5679046135401753</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>-0.9521054468472634</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>-0.8326487737950856</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>-0.6674966249407981</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0.6063474943961694</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1.989557715866913</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0.7008652766014216</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>1.598626854738155</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>-1.31670595115175</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>-1.240372235066572</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>-1.697754417416959</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>-0.307514502714064</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>-0.684062341934037</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0.5604774471883585</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0.8370876115071291</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>-0.3988579273767718</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>1.150410686846457</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>2.256362088687377</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0.8499286833463957</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>1.700518090882713</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>0.2718488739311696</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>-2.644963620441896</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>-1.164532953864081</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>-3.476039298099878</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>-1.43574529700851</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>0.1349433176433692</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>0.2192395497064556</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>0.03128825462301144</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>-1.943032446042212</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>-0.365180092230567</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>-0.01469328740713478</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>-0.2647927418295623</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>0.3807676207942143</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>-0.3182780019221074</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>-0.2935735549855171</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>-0.7320216085991254</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>0.8440637114692113</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>0.2256153619136884</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>02sgHz9e</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1.910080355503086</v>
+      </c>
+      <c r="C16" t="n">
+        <v>-0.9975765132679711</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.21498498313985</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-0.2058317055638894</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-1.035838392736326</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-1.643557089741262</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-0.4726969446941581</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.6894960517944352</v>
+      </c>
+      <c r="J16" t="n">
+        <v>-1.199026824404353</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-0.421231476718521</v>
+      </c>
+      <c r="L16" t="n">
+        <v>-0.2497569114296844</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.140180070760864</v>
+      </c>
+      <c r="N16" t="n">
+        <v>-0.6832211304980006</v>
+      </c>
+      <c r="O16" t="n">
+        <v>-0.1451675372749279</v>
+      </c>
+      <c r="P16" t="n">
+        <v>-0.346056740757259</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.3689705749680672</v>
+      </c>
+      <c r="R16" t="n">
+        <v>-1.607598466883206</v>
+      </c>
+      <c r="S16" t="n">
+        <v>-1.058188861841422</v>
+      </c>
+      <c r="T16" t="n">
+        <v>-0.6311142831554755</v>
+      </c>
+      <c r="U16" t="n">
+        <v>-0.5735563657619414</v>
+      </c>
+      <c r="V16" t="n">
+        <v>-0.8672667983578004</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.6855630435156713</v>
+      </c>
+      <c r="X16" t="n">
+        <v>-0.8127961982970057</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.7411314403747327</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-2.291681774289124</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>4.522634581928831</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>-3.711649101551922</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>7.704342864866263</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>-0.3504062581620234</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0.708039681363362</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>-0.687576778812366</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0.3834828877677331</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0.06260636343389694</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.516224896332271</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0.07497963821424408</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>1.946717902895482</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>-0.4447019715560118</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>-1.645485479909149</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>-0.5467340381846351</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>-1.97243157591792</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>1.403895438288213</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>-0.4551184520406461</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0.6708487013704878</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>-0.5953869763488407</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0.007289105810661419</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0.3027145207487243</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0.786519377235958</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0.5574694958183929</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>0.2718488739311696</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>-0.6184276686107751</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>-1.885966678888772</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>-0.8009568178290335</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>-2.296595375665791</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>-0.7370216704393564</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>-0.7058959575717524</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>0.03128825462301144</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>0.9286850838833044</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>0.7536415798458798</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>1.523881637281316</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>-0.9236440753012113</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>0.1437288353070549</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>-0.1224530787678412</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>-0.1993561810270117</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>-0.41992888653672</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>0.3850732401426941</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>-0.5981544335413412</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>4zlpJdvq</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1.942564741172752</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1.805149320052122</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.3184983417266209</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-0.2058317055638894</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-2.122280368789553</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-0.4565191234238114</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-2.61530629258074</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.311096653008989</v>
+      </c>
+      <c r="J17" t="n">
+        <v>-0.5903113576880034</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.1938520547695864</v>
+      </c>
+      <c r="L17" t="n">
+        <v>-1.204478261983577</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.6112506602320185</v>
+      </c>
+      <c r="N17" t="n">
+        <v>-0.2639167443217952</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.9128361885027941</v>
+      </c>
+      <c r="P17" t="n">
+        <v>-1.851923946119686</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>-1.247554400071276</v>
+      </c>
+      <c r="R17" t="n">
+        <v>-1.068696290186378</v>
+      </c>
+      <c r="S17" t="n">
+        <v>-0.7471472114405938</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.3804527236237448</v>
+      </c>
+      <c r="U17" t="n">
+        <v>-0.5017422983373261</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.5843064892660498</v>
+      </c>
+      <c r="W17" t="n">
+        <v>-0.9716835446215749</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.341388708777531</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>-1.639838155104477</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-4.340617690721013</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.986260851423359</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>-6.680941793910697</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>3.644401761046542</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0.196573090146414</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.510163674286678</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.579063239766125</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.700764752826008</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>-2.873595743762378</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>-0.1141437042870489</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>-1.191084700013663</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>-0.1135459883856952</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>2.433961768314255</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>-0.04264611987982319</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>3.253019984823279</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>-0.8624868604486826</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0.01192358480671266</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>-0.6207662961992807</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>-1.249710014854775</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>-0.005799829432633994</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>0.007289105810661419</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>1.121986081497191</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>-0.354848132751914</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0.2101891066929485</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>0.2728468241092091</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>0.8232840322056911</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>0.757985719854534</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>1.102141772142098</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>0.8582982084210667</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>-2.43266506729635</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>-1.101918741649671</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>0.03128825462301144</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>-0.0285540927585344</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>0.8934942888554355</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>0.3699504437649777</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>-0.241197630974217</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>1.553392787833908</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>2.327837612488691</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>2.646822826629002</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>1.085640447421712</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>-0.3601102758811309</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>1.771923311168684</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>8Sp1FEw8</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1.942564741172752</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.5202073226222947</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-0.5555761336512771</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-0.2058317055638894</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-0.4926174047097124</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-3.707970944206394</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-0.1155953867130612</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.8786957511871586</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-0.1492660195282528</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.3767147262930771</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-0.1195676363541537</v>
+      </c>
+      <c r="M18" t="n">
+        <v>-0.02787237749033771</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-0.7663889426321245</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.04719677650283909</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.312760161588803</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.8741346296678622</v>
+      </c>
+      <c r="R18" t="n">
+        <v>-1.607598466883206</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.9023160861395562</v>
+      </c>
+      <c r="T18" t="n">
+        <v>-0.2939252808957354</v>
+      </c>
+      <c r="U18" t="n">
+        <v>-1.492776428797009</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0.06475026248345796</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0.9729087872976648</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0.5578835082163714</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>-0.2327128473768448</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-3.406346016627455</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>3.586877368652223</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>-5.327006791690232</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>6.20648821999089</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>-0.100625701059026</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.630342530369264</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>-1.364579422065057</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>-0.3879807970927844</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0.8918115881513641</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0.6615961943947241</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1.459149800032041</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>1.331757051150871</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>-0.9489934296354745</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0.5562169377135511</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>-1.212384377981642</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>2.259232651808548</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>1.543092623636362</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0.8910989481057137</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>-0.1767935153333063</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>-0.005799829432633994</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0.5788498963285592</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>0.381490632359154</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0.3268019079352871</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0.5257181459554953</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>0.6390945394497413</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>-2.568378943421152</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>0.1759247785065109</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>-3.374945445029925</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>0.1637545660017617</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>1.130167107501427</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>-1.55605214054661</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>0.03128825462301144</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>-0.267863886918994</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>-1.111061206948198</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>-0.01469328740713478</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>0.3266306258192789</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>-0.08808455799140411</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>-0.6362147374432513</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>-0.6125793253215052</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>-1.145900486525255</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>-0.7687898761521132</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>-0.7593304601066735</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>dhkQFrkl</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1.910080355503086</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-0.3852887158349662</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-0.2642179751919778</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-0.2058317055638894</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.137045559370128</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.4208567647238691</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.7771585082396808</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-1.580900340918244</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.1423342040484424</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-1.418664230483019</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.052135839325623</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.2586310532127875</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.6197412596032678</v>
+      </c>
+      <c r="O19" t="n">
+        <v>-0.1451675372749279</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.4068768619239547</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>-2.055816887590948</v>
+      </c>
+      <c r="R19" t="n">
+        <v>-0.664519657663758</v>
+      </c>
+      <c r="S19" t="n">
+        <v>-1.510613080606263</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.392019730402965</v>
+      </c>
+      <c r="U19" t="n">
+        <v>-0.113946334244407</v>
+      </c>
+      <c r="V19" t="n">
+        <v>-1.180667163341096</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0.5597968099063279</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0.9221009929671575</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0.3572328200601073</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-2.480082098569506</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.543266800455535</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>-3.98467653088117</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.935306829711856</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0.09038296025503199</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0.7234113955134596</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0.54069944537466</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>-0.1420068685865329</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>-1.079250011586877</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>-1.271179485371728</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0.2073785232576856</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0.3106899765560462</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>1.236269555375531</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>-0.4037253163699459</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>1.672100427805387</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>-2.527403933652539</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>-0.2664707858895874</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>-0.3569567666133077</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>-1.054981397503904</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>1.173374464399779</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>-1.135832475225134</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>-0.4535361507113985</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>-0.2914388266414769</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0.1923289723950683</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>0.2399144682339025</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>1.197642107925223</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>-0.06249324838853759</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>1.596304596542204</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>-0.1207375087191584</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>-0.4341432442250389</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>-0.5768550809722222</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>0.03128825462301144</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>-0.9857932694003733</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>-0.365180092230567</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>1.139237906109203</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>-0.4305630082407516</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>1.613223830675933</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>0.7146773253168378</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>0.3431123433887726</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>-0.1745537783745968</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>-0.5238346015819227</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>1.373933081870994</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>x88gL4RQ</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1.910080355503086</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1.1324951200553</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-1.463268858082171</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-0.2058317055638894</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.3222140773302074</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-1.230674318848236</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-0.2941461657036097</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.8313958263389777</v>
+      </c>
+      <c r="J20" t="n">
+        <v>-1.315666913835031</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-0.6207180274714212</v>
+      </c>
+      <c r="L20" t="n">
+        <v>-0.3148515489674498</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.3908634058449991</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-1.154505399258034</v>
+      </c>
+      <c r="O20" t="n">
+        <v>-0.392493083560629</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.2186434612536514</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.8741346296678622</v>
+      </c>
+      <c r="R20" t="n">
+        <v>-2.011775099405826</v>
+      </c>
+      <c r="S20" t="n">
+        <v>-0.3041484972333534</v>
+      </c>
+      <c r="T20" t="n">
+        <v>-0.7154115337204106</v>
+      </c>
+      <c r="U20" t="n">
+        <v>-1.148068905158859</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.226106879456301</v>
+      </c>
+      <c r="W20" t="n">
+        <v>-1.27390285955326</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0.6160669904670291</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>-0.05608405590762777</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-1.491005010796101</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.641529842886616</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>-2.551318198220647</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>3.092595229348776</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>-0.4459105888190529</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>-0.1912055964173939</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0.008768797104688213</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>-1.461321576029156</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>2.210383830734876</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>-0.1141437042870489</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1.206388292221835</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>1.006872072870701</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>1.551451716675195</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>-1.046622422315774</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>2.088131890178517</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0.8024302127551737</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>0.4991137335252377</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>-0.111552553044961</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>0.4341197940027614</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>-0.9884450742929786</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>0.9598904233404909</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>-0.1856973712359385</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>-0.3707004592795231</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>0.4145884214353531</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>0.01637362835303242</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>1.155672227129922</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>0.5049216783662173</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>1.540903214339674</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>0.5563297912763169</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>0.364246912558449</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>-1.936434198563993</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>0.03128825462301144</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>-0.7464834752399137</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>1.499522694563511</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>1.523881637281315</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>-2.095541809489502</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>0.3069034905480136</v>
+      </c>
+      <c r="BQ20" t="n">
+        <v>-0.6504577483980113</v>
+      </c>
+      <c r="BR20" t="n">
+        <v>-0.6233632377050287</v>
+      </c>
+      <c r="BS20" t="n">
+        <v>-1.143508306836416</v>
+      </c>
+      <c r="BT20" t="n">
+        <v>-0.1617623194733395</v>
+      </c>
+      <c r="BU20" t="n">
+        <v>-1.298778769472439</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>vymauDyP</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1.942564741172752</v>
+      </c>
+      <c r="C21" t="n">
+        <v>-0.7733584466023637</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.3184983417266209</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-0.2058317055638894</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.3222140773302078</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2.08596951839114</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-0.4726969446941582</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.4056965027053503</v>
+      </c>
+      <c r="J21" t="n">
+        <v>-1.352692468539177</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-0.3798905138980193</v>
+      </c>
+      <c r="L21" t="n">
+        <v>-0.7705140117318076</v>
+      </c>
+      <c r="M21" t="n">
+        <v>-0.3584532590708666</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-1.052643067949026</v>
+      </c>
+      <c r="O21" t="n">
+        <v>-0.02846531495956247</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.03041006058334787</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>-0.03516066879176864</v>
+      </c>
+      <c r="R21" t="n">
+        <v>-0.2235594061725223</v>
+      </c>
+      <c r="S21" t="n">
+        <v>-1.133592898302229</v>
+      </c>
+      <c r="T21" t="n">
+        <v>-0.5468170325905405</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0.6359437171789382</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.176678679076294</v>
+      </c>
+      <c r="W21" t="n">
+        <v>-0.9195907535894603</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0.9273628543521361</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>-0.4735959640807607</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-0.08561149059576098</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-0.3779261396527595</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>-0.5146392196577948</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>-0.1399222235237179</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0.1859826998337952</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>-0.08180690350500623</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>-0.3985632199766616</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>-0.1077389541075025</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1.272430379824955</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>0.5169667217591396</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>0.01365013075841643</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0.03637743674171403</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>-1.432272743628293</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0.4769556506791339</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>-1.850299286953774</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>-0.3768860474308911</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>1.403895438288213</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>-0.8610041052714515</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>0.3124395279491468</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>0.4658698881003313</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>-0.4499595266036568</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>0.4287562993254118</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>1.182827540426191</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>0.3073753930331667</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>0.708740957138189</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>-0.976934625385923</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>-0.09033112400500001</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>-1.274195734838059</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>-0.1539550262579497</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>-1.183177908083317</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>0.6161075484263532</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>-0.9176043393014947</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>0.6893752897228448</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>0.96464742150942</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>1.275887652709822</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>-0.1539904367951914</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>0.6453718367963285</v>
+      </c>
+      <c r="BQ21" t="n">
+        <v>-0.5209867650714514</v>
+      </c>
+      <c r="BR21" t="n">
+        <v>-0.7269478742749185</v>
+      </c>
+      <c r="BS21" t="n">
+        <v>-1.010873744715364</v>
+      </c>
+      <c r="BT21" t="n">
+        <v>-0.1462720751577322</v>
+      </c>
+      <c r="BU21" t="n">
+        <v>-0.6488878809662317</v>
       </c>
     </row>
   </sheetData>

--- a/data/spain/p6_deployment/data_preparation/df_selected_nan.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_selected_nan.xlsx
@@ -3909,7 +3909,7 @@
         <v>0.8440637114692113</v>
       </c>
       <c r="BU15" t="n">
-        <v>0.2256153619136884</v>
+        <v>0.2256153619136878</v>
       </c>
     </row>
     <row r="16">

--- a/data/spain/p6_deployment/data_preparation/df_selected_nan.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_selected_nan.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BU11"/>
+  <dimension ref="A1:BU21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -793,92 +793,92 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>E595Qvn9</t>
+          <t>QP8QvjOG</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.975049126842419</v>
+        <v>1.910080355503086</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.3852887158349662</v>
+        <v>-0.5577641517315873</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2960861756912902</v>
+        <v>1.84252563212911</v>
       </c>
       <c r="E2" t="n">
         <v>-0.2058317055638894</v>
       </c>
       <c r="F2" t="n">
-        <v>3.309929511476581</v>
+        <v>0.05060358331690091</v>
       </c>
       <c r="G2" t="n">
-        <v>1.659505077402948</v>
+        <v>-4.120853715099421</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.2048707762083355</v>
+        <v>-0.740523113179981</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.7295016936509894</v>
+        <v>0.5002963524017121</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4922544723404759</v>
+        <v>-2.7236794219625</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.08875389213035469</v>
+        <v>0.8326839851568478</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8785501392249159</v>
+        <v>-0.2931533364548612</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.5347630625804818</v>
+        <v>0.1704761514579796</v>
       </c>
       <c r="N2" t="n">
-        <v>0.8692446960056391</v>
+        <v>-2.190142678928193</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.3100512347987289</v>
+        <v>0.7008428631150495</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.098990343438473</v>
+        <v>-4.487191555503934</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.4392919125516045</v>
+        <v>0.5710361968479852</v>
       </c>
       <c r="R2" t="n">
-        <v>-1.203421834360585</v>
+        <v>-4.754402248666463</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3041484972333534</v>
+        <v>0.1590477267401742</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2118582224938746</v>
+        <v>-0.9683032854152158</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2288488421237904</v>
+        <v>-2.411996491832077</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.02804644613753196</v>
+        <v>-0.06424463596082228</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.2125680840590385</v>
+        <v>-0.6233357880426353</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.66195750681459</v>
+        <v>3.207325738502238</v>
       </c>
       <c r="Y2" t="n">
-        <v>-1.241591155269555</v>
+        <v>-1.438483776174849</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.3463889375450271</v>
+        <v>0.1616589713349502</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0.517353793450501</v>
+        <v>0.02842335127478235</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.1114104796456949</v>
+        <v>-0.1562979119776401</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.3631022919238845</v>
+        <v>0.5105162275968775</v>
       </c>
       <c r="AD2" t="n">
         <v>0</v>
@@ -887,10 +887,10 @@
         <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>-1.33750696243537</v>
+        <v>-1.209333026827481</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.03797268727498227</v>
+        <v>2.287056318226246</v>
       </c>
       <c r="AH2" t="n">
         <v>0</v>
@@ -899,73 +899,73 @@
         <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.2804490786177808</v>
+        <v>-0.6679651943054423</v>
       </c>
       <c r="AK2" t="n">
-        <v>-0.1684338195830713</v>
+        <v>1.272032647182363</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.911326208705626</v>
+        <v>0.6607216074923972</v>
       </c>
       <c r="AM2" t="n">
-        <v>-0.9556242723486339</v>
+        <v>-0.0615511687832006</v>
       </c>
       <c r="AN2" t="n">
-        <v>-0.09352803365922482</v>
+        <v>0.09905216276759826</v>
       </c>
       <c r="AO2" t="n">
-        <v>-0.4319042595129174</v>
+        <v>1.494199540290957</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.2066744951299611</v>
+        <v>0.08585466663175645</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-0.9849747546223385</v>
+        <v>0.07624581067180258</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.3130643173864986</v>
+        <v>0.1535855901434658</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.079916391622483</v>
+        <v>-0.8624868604486826</v>
       </c>
       <c r="AT2" t="n">
-        <v>-1.936837010067387</v>
+        <v>0.8471066968956126</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.3792558740917333</v>
+        <v>0.3263995819385508</v>
       </c>
       <c r="AV2" t="n">
-        <v>-1.276437472138229</v>
+        <v>0.3148742153535101</v>
       </c>
       <c r="AW2" t="n">
-        <v>-2.167619368125392</v>
+        <v>-1.184974123265047</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.531451213858389</v>
+        <v>1.150410686846457</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.657663640448112</v>
+        <v>-0.7056197078647735</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-0.3231434796966951</v>
+        <v>-1.432806336629349</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.03357222308058006</v>
+        <v>0.5892208456812906</v>
       </c>
       <c r="BB2" t="n">
-        <v>-0.2231344143764716</v>
+        <v>-0.07942958873876911</v>
       </c>
       <c r="BC2" t="n">
-        <v>-0.2337826753444321</v>
+        <v>0.8045475806951334</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.5049402448404956</v>
+        <v>1.855081813655487</v>
       </c>
       <c r="BE2" t="n">
-        <v>-0.2932149829600521</v>
+        <v>1.077409147422043</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.5563519457033813</v>
+        <v>2.167407036970525</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -974,134 +974,134 @@
         <v>0</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.1092342528961072</v>
+        <v>0.155048822874438</v>
       </c>
       <c r="BJ2" t="n">
-        <v>-1.645217608153971</v>
+        <v>-1.844536117088589</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.454627145509771</v>
+        <v>0.03128825462301144</v>
       </c>
       <c r="BL2" t="n">
-        <v>-0.0285540927585344</v>
+        <v>0.9286850838833044</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.007760465128248513</v>
+        <v>0.3807010224870641</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.7545941749370905</v>
+        <v>2.29316909962554</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.7552509843713513</v>
+        <v>0.4723741925635851</v>
       </c>
       <c r="BP2" t="n">
-        <v>-0.04221577359256398</v>
+        <v>0.9927280756432079</v>
       </c>
       <c r="BQ2" t="n">
-        <v>-0.1815927944402194</v>
+        <v>-0.3096826750749664</v>
       </c>
       <c r="BR2" t="n">
-        <v>-0.7471804557946606</v>
+        <v>-1.701430345767716</v>
       </c>
       <c r="BS2" t="n">
-        <v>-0.2983661240841705</v>
+        <v>-1.070211387729257</v>
       </c>
       <c r="BT2" t="n">
-        <v>-0.3746359569126559</v>
+        <v>0.2926008227894071</v>
       </c>
       <c r="BU2" t="n">
-        <v>-0.4947925302325759</v>
+        <v>-0.8200469076949382</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>jiAoNQdE</t>
+          <t>MXB9rYOi</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.910080355503086</v>
+        <v>1.975049126842419</v>
       </c>
       <c r="C3" t="n">
-        <v>-1.704725800444118</v>
+        <v>1.813773091846953</v>
       </c>
       <c r="D3" t="n">
-        <v>0.195231428532302</v>
+        <v>-0.7348734619339229</v>
       </c>
       <c r="E3" t="n">
         <v>-0.2058317055638894</v>
       </c>
       <c r="F3" t="n">
-        <v>4.396371487529809</v>
+        <v>1.137045559370128</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4208567647238691</v>
+        <v>-1.643557089741262</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7771585082396812</v>
+        <v>0.06295539227748714</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.580900340918244</v>
+        <v>2.770692745114392</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.03262593009757497</v>
+        <v>-0.724135031722308</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.4212314767185214</v>
+        <v>2.257587919106131</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5313787390235003</v>
+        <v>-1.334667537059107</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.240002276618944</v>
+        <v>2.815123204102211</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.239659465782675</v>
+        <v>0.1266749448081069</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.09020630476699447</v>
+        <v>1.996357629373485</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.3460567407572589</v>
+        <v>0.03041006058334787</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.651685643831112</v>
+        <v>1.783429928127493</v>
       </c>
       <c r="R3" t="n">
-        <v>-1.203421834360585</v>
+        <v>-1.001333518099275</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.661421153527877</v>
+        <v>2.421168820564379</v>
       </c>
       <c r="T3" t="n">
-        <v>1.054830728143225</v>
+        <v>-0.2939252808957357</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0009561736349765304</v>
+        <v>-1.377873920917626</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.5474923536022943</v>
+        <v>1.934454841947641</v>
       </c>
       <c r="W3" t="n">
-        <v>0.441564820482067</v>
+        <v>-2.71032958608931</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.7320247773345041</v>
+        <v>0.3188927665364289</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.5084198486566553</v>
+        <v>-1.832063572059012</v>
       </c>
       <c r="Z3" t="n">
-        <v>-3.445852089525309</v>
+        <v>1.445133743603033</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.166789593681649</v>
+        <v>-0.9769609424606372</v>
       </c>
       <c r="AB3" t="n">
-        <v>-5.384258505918402</v>
+        <v>1.703697918813951</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.933371817903754</v>
+        <v>-1.098789597557577</v>
       </c>
       <c r="AD3" t="n">
         <v>0</v>
@@ -1110,10 +1110,10 @@
         <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.1731979043212665</v>
+        <v>-3.033710625275849</v>
       </c>
       <c r="AG3" t="n">
-        <v>-0.2575834529746366</v>
+        <v>0.504364468874558</v>
       </c>
       <c r="AH3" t="n">
         <v>0</v>
@@ -1122,73 +1122,73 @@
         <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-0.01497025661975652</v>
+        <v>0.5745495775372946</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0.7213669481260511</v>
+        <v>-0.02461022089036663</v>
       </c>
       <c r="AL3" t="n">
-        <v>-0.7530053330095128</v>
+        <v>-0.5898829937208309</v>
       </c>
       <c r="AM3" t="n">
-        <v>-0.3245138463024454</v>
+        <v>0.3591891152475924</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.002762064554185427</v>
+        <v>0.135160949597627</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.1598505223545378</v>
+        <v>-0.3274769450657191</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.089184546769021</v>
+        <v>1.582969932805162</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.111045946954471</v>
+        <v>-1.557417383204241</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.477952412031261</v>
+        <v>2.12973503641583</v>
       </c>
       <c r="AS3" t="n">
-        <v>-1.833688486484265</v>
+        <v>1.218659481056138</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.2903179555030126</v>
+        <v>0.4295151408511626</v>
       </c>
       <c r="AU3" t="n">
-        <v>-0.3289105707769246</v>
+        <v>1.564207648178893</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.69375795047059</v>
+        <v>0.6937579504705906</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.3872582685115039</v>
+        <v>-0.5953869763488407</v>
       </c>
       <c r="AX3" t="n">
-        <v>-0.3737514212012703</v>
+        <v>0.5788498963285592</v>
       </c>
       <c r="AY3" t="n">
-        <v>-0.7056197078647735</v>
+        <v>0.1766727421720372</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-0.354848132751914</v>
+        <v>-0.6084853571936631</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.1764532974636199</v>
+        <v>0.2875830219837617</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.6390945394497413</v>
+        <v>0.5113569166606727</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.693709677881079</v>
+        <v>1.039146713155204</v>
       </c>
       <c r="BD3" t="n">
-        <v>2.172769750376071</v>
+        <v>-0.7147703580368526</v>
       </c>
       <c r="BE3" t="n">
-        <v>2.251127257951385</v>
+        <v>1.387086372029688</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.5464878531675</v>
+        <v>-0.8990665244965642</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1197,59 +1197,59 @@
         <v>0</v>
       </c>
       <c r="BI3" t="n">
-        <v>-0.3421755746124052</v>
+        <v>1.546814883609058</v>
       </c>
       <c r="BJ3" t="n">
-        <v>-0.8093179631351023</v>
+        <v>-1.211707743831091</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.929073442472024</v>
+        <v>-0.9176043393014947</v>
       </c>
       <c r="BL3" t="n">
-        <v>-0.0285540927585344</v>
+        <v>-0.9857932694003733</v>
       </c>
       <c r="BM3" t="n">
-        <v>2.245403809281142</v>
+        <v>-0.7381206495893825</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.139237906109203</v>
+        <v>0.7545941749370902</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.4165569740332744</v>
+        <v>-0.7334805938466565</v>
       </c>
       <c r="BP3" t="n">
-        <v>-0.9547668054377251</v>
+        <v>0.07681425041331949</v>
       </c>
       <c r="BQ3" t="n">
-        <v>-0.4135950578391409</v>
+        <v>-1.170940662710138</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.5903452720656543</v>
+        <v>-1.480964230982633</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.3863572294532712</v>
+        <v>-1.352127683921888</v>
       </c>
       <c r="BT3" t="n">
-        <v>1.064524385190061</v>
+        <v>-0.4858375170721904</v>
       </c>
       <c r="BU3" t="n">
-        <v>1.168014399197667</v>
+        <v>-1.225696730023886</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>842EOIGL</t>
+          <t>UwPNKUWp</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.007533512512086</v>
+        <v>1.975049126842419</v>
       </c>
       <c r="C4" t="n">
-        <v>-1.583992995316483</v>
+        <v>-0.1007042466055413</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1073328129446628</v>
+        <v>0.3184983417266209</v>
       </c>
       <c r="E4" t="n">
         <v>-0.2058317055638894</v>
@@ -1258,73 +1258,73 @@
         <v>0.05060358331690091</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.4049087770621833</v>
+        <v>0.8337395356168954</v>
       </c>
       <c r="H4" t="n">
-        <v>1.491361624201875</v>
+        <v>0.5986077292491325</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2565024451691809</v>
+        <v>1.067895450579882</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9004947853478482</v>
+        <v>-1.348992653672368</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7091923108812433</v>
+        <v>-0.734710342187364</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2710001888724387</v>
+        <v>-0.03277478630379965</v>
       </c>
       <c r="M4" t="n">
-        <v>0.611250660232018</v>
+        <v>0.5671732093546142</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6197412596032685</v>
+        <v>-2.071331518736587</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5693284853282088</v>
+        <v>-0.3002367289937408</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.7225235420978658</v>
+        <v>0.5951102625942581</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.4392919125516046</v>
+        <v>-1.247554400071276</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.9339707460121718</v>
+        <v>0.29780565786629</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7515080132179423</v>
+        <v>-0.8104327420416282</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3804527236237445</v>
+        <v>0.04326372136400455</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.033166397279475</v>
+        <v>0.345663697273127</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.382884804874898</v>
+        <v>1.133936165696114</v>
       </c>
       <c r="W4" t="n">
-        <v>0.3535529944237157</v>
+        <v>-3.069575648818976</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.120298128117189</v>
+        <v>1.384200753922026</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0.07543278924143212</v>
+        <v>0.1118301983996613</v>
       </c>
       <c r="Z4" t="n">
-        <v>-2.08771873135754</v>
+        <v>2.010437053734057</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.38046150375648</v>
+        <v>-2.713146838537069</v>
       </c>
       <c r="AB4" t="n">
-        <v>-3.416068372046884</v>
+        <v>2.522928512741643</v>
       </c>
       <c r="AC4" t="n">
-        <v>4.275393721068474</v>
+        <v>-3.877880233363849</v>
       </c>
       <c r="AD4" t="n">
         <v>0</v>
@@ -1333,10 +1333,10 @@
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.3475100043316476</v>
+        <v>-0.471623293226714</v>
       </c>
       <c r="AG4" t="n">
-        <v>-0.4602105940441156</v>
+        <v>1.407452675192838</v>
       </c>
       <c r="AH4" t="n">
         <v>0</v>
@@ -1345,73 +1345,73 @@
         <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.637414108696473</v>
+        <v>-1.396011687644646</v>
       </c>
       <c r="AK4" t="n">
-        <v>-0.052561803675168</v>
+        <v>0.9676709679700819</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.6063474943961705</v>
+        <v>0.769469833684852</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9377070057899315</v>
+        <v>-0.1667362397908983</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.122134456285099</v>
+        <v>-0.4546159019595207</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8908417234849244</v>
+        <v>1.064887247563588</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.3012291435198604</v>
+        <v>1.18373919515892</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-2.156280440797615</v>
+        <v>-0.2936401954888109</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.4378737560984374</v>
+        <v>1.602761850743199</v>
       </c>
       <c r="AS4" t="n">
-        <v>-1.139973039315992</v>
+        <v>0.3862009444542097</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.795867291769713</v>
+        <v>1.682289808984513</v>
       </c>
       <c r="AU4" t="n">
-        <v>-0.3148874728587341</v>
+        <v>-1.275469680254834</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.297034843439957</v>
+        <v>0.4646654594695647</v>
       </c>
       <c r="AW4" t="n">
-        <v>-1.774561270181254</v>
+        <v>0.4658698881003313</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.721971477364355</v>
+        <v>-0.4499595266036568</v>
       </c>
       <c r="AY4" t="n">
-        <v>-0.3274943721347117</v>
+        <v>-0.1384317042696811</v>
       </c>
       <c r="AZ4" t="n">
         <v>1.230384520009019</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.4780911211611484</v>
+        <v>0.03357222308057964</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.8147337707847103</v>
+        <v>0.7189305536929097</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.372727722784365</v>
+        <v>1.264286705190872</v>
       </c>
       <c r="BD4" t="n">
-        <v>-1.42019933344944</v>
+        <v>-1.005273685085284</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.827422362024694</v>
+        <v>1.684277274445577</v>
       </c>
       <c r="BF4" t="n">
-        <v>-1.740818951513012</v>
+        <v>-1.245709332096506</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1420,134 +1420,134 @@
         <v>0</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.7913848959324219</v>
+        <v>-1.108401036690552</v>
       </c>
       <c r="BJ4" t="n">
-        <v>-1.508716320367424</v>
+        <v>1.998979930495965</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.9801808485475174</v>
+        <v>0.03128825462301144</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.9286850838833044</v>
+        <v>-0.0285540927585344</v>
       </c>
       <c r="BM4" t="n">
-        <v>-1.484001764307014</v>
+        <v>0.007760465128248513</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.523881637281315</v>
+        <v>0.3699504437649776</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.2800973356712006</v>
+        <v>-0.136924473813237</v>
       </c>
       <c r="BP4" t="n">
-        <v>-1.513724024410418</v>
+        <v>0.7040101496628376</v>
       </c>
       <c r="BQ4" t="n">
-        <v>-2.029198174564697</v>
+        <v>-0.746961097634274</v>
       </c>
       <c r="BR4" t="n">
-        <v>-2.121890938500002</v>
+        <v>-0.6652436619106641</v>
       </c>
       <c r="BS4" t="n">
-        <v>-0.4184782569682083</v>
+        <v>-1.372336508122919</v>
       </c>
       <c r="BT4" t="n">
-        <v>1.049632632957424</v>
+        <v>-0.08014443681095196</v>
       </c>
       <c r="BU4" t="n">
-        <v>-2.918579995785531</v>
+        <v>-0.5119901859838873</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>naHJ2yf2</t>
+          <t>Ia5ItCg4</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.910080355503086</v>
+        <v>2.007533512512086</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.368041172245304</v>
+        <v>-0.3852887158349662</v>
       </c>
       <c r="D5" t="n">
-        <v>1.472724892546153</v>
+        <v>-0.9477890392695648</v>
       </c>
       <c r="E5" t="n">
         <v>-0.2058317055638894</v>
       </c>
       <c r="F5" t="n">
-        <v>5.482813463583036</v>
+        <v>1.137045559370128</v>
       </c>
       <c r="G5" t="n">
-        <v>3.311036160975053</v>
+        <v>-2.05643986063429</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5986077292491325</v>
+        <v>-1.544001618637449</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.013301242740074</v>
+        <v>-0.6349018439546278</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7255346512018311</v>
+        <v>0.2131514012027815</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.8867000951419531</v>
+        <v>0.3339676082745991</v>
       </c>
       <c r="L5" t="n">
-        <v>1.572892939627747</v>
+        <v>-1.334667537059107</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5347630625804818</v>
+        <v>0.03824379882576807</v>
       </c>
       <c r="N5" t="n">
-        <v>1.451419380944504</v>
+        <v>0.2157833149518111</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.161950338671701</v>
+        <v>0.5241817586252635</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7833436632645615</v>
+        <v>-1.098990343438473</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.651685643831112</v>
+        <v>-1.247554400071276</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.2603430251411378</v>
+        <v>-1.001333518099275</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9073807889198086</v>
+        <v>0.1590477267401742</v>
       </c>
       <c r="T5" t="n">
-        <v>1.392019730402965</v>
+        <v>0.3804527236237448</v>
       </c>
       <c r="U5" t="n">
-        <v>0.11585868151436</v>
+        <v>-0.343751350003174</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.3169000902250848</v>
+        <v>1.689258722533421</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.8711960289349856</v>
+        <v>-4.341645929623544</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.348858224580942</v>
+        <v>-0.498272438686195</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.027803220291297</v>
+        <v>-2.067473822395283</v>
       </c>
       <c r="Z5" t="n">
-        <v>-1.585257472032716</v>
+        <v>2.383340740076607</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.545783784487493</v>
+        <v>-2.586006378186927</v>
       </c>
       <c r="AB5" t="n">
-        <v>-2.687907704091616</v>
+        <v>3.063335941754266</v>
       </c>
       <c r="AC5" t="n">
-        <v>6.140710243564516</v>
+        <v>-3.67436811891247</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
@@ -1556,10 +1556,10 @@
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.5679046135401753</v>
+        <v>0.5272948661026781</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.9521054468472634</v>
+        <v>-0.8161084758248661</v>
       </c>
       <c r="AH5" t="n">
         <v>0</v>
@@ -1568,73 +1568,73 @@
         <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.8326487737950856</v>
+        <v>0.2884353652102642</v>
       </c>
       <c r="AK5" t="n">
-        <v>-0.6674966249407981</v>
+        <v>-0.08051338645996936</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.6063474943961694</v>
+        <v>-1.02487589849065</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.989557715866913</v>
+        <v>0.4117816507514407</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.7008652766014216</v>
+        <v>0.07497963821424536</v>
       </c>
       <c r="AO5" t="n">
-        <v>1.598626854738155</v>
+        <v>1.09969635237932</v>
       </c>
       <c r="AP5" t="n">
-        <v>-1.31670595115175</v>
+        <v>0.9526056102058332</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-1.240372235066572</v>
+        <v>-2.002161271564026</v>
       </c>
       <c r="AR5" t="n">
-        <v>-1.697754417416959</v>
+        <v>1.297672111669571</v>
       </c>
       <c r="AS5" t="n">
-        <v>-0.307514502714064</v>
+        <v>-0.4462575921477186</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0.684062341934037</v>
+        <v>-0.8232595272821873</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.5604774471883585</v>
+        <v>-0.2560983315863165</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.8370876115071291</v>
+        <v>-1.033246981690986</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0.3988579273767718</v>
+        <v>-1.184974123265047</v>
       </c>
       <c r="AX5" t="n">
         <v>1.150410686846457</v>
       </c>
       <c r="AY5" t="n">
-        <v>2.256362088687377</v>
+        <v>0.1766727421720375</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.8499286833463957</v>
+        <v>-0.7987132755249754</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.700518090882713</v>
+        <v>0.3193343718466597</v>
       </c>
       <c r="BB5" t="n">
-        <v>0.2718488739311696</v>
+        <v>-0.1592656029819371</v>
       </c>
       <c r="BC5" t="n">
-        <v>-2.644963620441896</v>
+        <v>-0.755845334193592</v>
       </c>
       <c r="BD5" t="n">
-        <v>-1.164532953864081</v>
+        <v>-0.6960745372318523</v>
       </c>
       <c r="BE5" t="n">
-        <v>-3.476039298099878</v>
+        <v>-0.9823518675187045</v>
       </c>
       <c r="BF5" t="n">
-        <v>-1.43574529700851</v>
+        <v>-0.8767577548171372</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1643,134 +1643,134 @@
         <v>0</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.1349433176433692</v>
+        <v>0.226191024646511</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.2192395497064556</v>
+        <v>-1.875794331158212</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.03128825462301144</v>
+        <v>1.929073442472024</v>
       </c>
       <c r="BL5" t="n">
-        <v>-1.943032446042212</v>
+        <v>-0.0285540927585344</v>
       </c>
       <c r="BM5" t="n">
-        <v>-0.365180092230567</v>
+        <v>-0.7381206495893828</v>
       </c>
       <c r="BN5" t="n">
-        <v>-0.01469328740713478</v>
+        <v>0.3699504437649778</v>
       </c>
       <c r="BO5" t="n">
-        <v>-0.2647927418295623</v>
+        <v>0.1326046891399987</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.4302916963961286</v>
+        <v>-0.3475013709343893</v>
       </c>
       <c r="BQ5" t="n">
-        <v>-0.3800153272325547</v>
+        <v>-1.068715993535585</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0.3209010199923868</v>
+        <v>-1.698638995124383</v>
       </c>
       <c r="BS5" t="n">
-        <v>-0.8150655123339969</v>
+        <v>-0.8123431731545082</v>
       </c>
       <c r="BT5" t="n">
-        <v>0.9761439587760445</v>
+        <v>0.8448733587270704</v>
       </c>
       <c r="BU5" t="n">
-        <v>0.2684115348681911</v>
+        <v>-2.647983082447586</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>02sgHz9e</t>
+          <t>4duqSCvB</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1.910080355503086</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.9975765132679711</v>
+        <v>0.1925039944187146</v>
       </c>
       <c r="D6" t="n">
-        <v>1.21498498313985</v>
+        <v>0.2176435945676327</v>
       </c>
       <c r="E6" t="n">
         <v>-0.2058317055638894</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.035838392736326</v>
+        <v>2.223487535423355</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.643557089741262</v>
+        <v>3.72391893186808</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4726969446941581</v>
+        <v>0.06295539227748714</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6894960517944352</v>
+        <v>0.5002963524017121</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.199026824404353</v>
+        <v>0.8380090231528423</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.421231476718521</v>
+        <v>0.1914772148796705</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.2497569114296844</v>
+        <v>0.6181715890738543</v>
       </c>
       <c r="M6" t="n">
-        <v>1.140180070760864</v>
+        <v>1.492799677780095</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6832211304980006</v>
+        <v>1.611814447203171</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1451675372749279</v>
+        <v>0.2297465844756194</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.346056740757259</v>
+        <v>1.159810464605168</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.3689705749680672</v>
+        <v>-2.459948131350784</v>
       </c>
       <c r="R6" t="n">
-        <v>-1.607598466883206</v>
+        <v>-1.434379910087797</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.058188861841422</v>
+        <v>-1.77991321082343</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6311142831554755</v>
+        <v>2.066397734922445</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5735563657619414</v>
+        <v>0.0009561736349765304</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.8672667983578004</v>
+        <v>1.649479190953288</v>
       </c>
       <c r="W6" t="n">
-        <v>0.6855630435156713</v>
+        <v>-0.7006174093577126</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.8127961982970057</v>
+        <v>-0.3344127285813329</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.7411314403747327</v>
+        <v>0.2646504872087984</v>
       </c>
       <c r="Z6" t="n">
-        <v>-2.291681774289124</v>
+        <v>1.362877906698403</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.522634581928831</v>
+        <v>-0.05758368187910669</v>
       </c>
       <c r="AB6" t="n">
-        <v>-3.711649101551922</v>
+        <v>1.584493773156674</v>
       </c>
       <c r="AC6" t="n">
-        <v>7.704342864866263</v>
+        <v>0.3728458658046226</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
@@ -1779,10 +1779,10 @@
         <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.3504062581620234</v>
+        <v>-0.2420455753011644</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.708039681363362</v>
+        <v>0.5427937542498039</v>
       </c>
       <c r="AH6" t="n">
         <v>0</v>
@@ -1791,73 +1791,73 @@
         <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-0.687576778812366</v>
+        <v>0.5020135800459349</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.3834828877677331</v>
+        <v>0.869840428223277</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.06260636343389694</v>
+        <v>-0.80737944610574</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.516224896332271</v>
+        <v>1.411039825324573</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.07497963821424408</v>
+        <v>0.5082850801745985</v>
       </c>
       <c r="AO6" t="n">
-        <v>1.946717902895482</v>
+        <v>0.4847355006347095</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.4447019715560118</v>
+        <v>-0.38691857531774</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-1.645485479909149</v>
+        <v>-1.830428482989455</v>
       </c>
       <c r="AR6" t="n">
-        <v>-0.5467340381846351</v>
+        <v>-0.4704616034162281</v>
       </c>
       <c r="AS6" t="n">
-        <v>-1.97243157591792</v>
+        <v>-0.03002832384675448</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.403895438288213</v>
+        <v>0.4295151408511626</v>
       </c>
       <c r="AU6" t="n">
-        <v>-0.4551184520406461</v>
+        <v>-0.5877985323435327</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.6708487013704878</v>
+        <v>1.266489177973154</v>
       </c>
       <c r="AW6" t="n">
-        <v>-0.5953869763488407</v>
+        <v>-1.578032221209186</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.007289105810661419</v>
+        <v>0.7693701598345251</v>
       </c>
       <c r="AY6" t="n">
-        <v>0.3027145207487243</v>
+        <v>0.1136518528836941</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.786519377235958</v>
+        <v>-0.4182574388623511</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.5574694958183929</v>
+        <v>0.5415938208869436</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.2718488739311696</v>
+        <v>0.09620964259619999</v>
       </c>
       <c r="BC6" t="n">
-        <v>-0.6184276686107751</v>
+        <v>-0.3385098637573808</v>
       </c>
       <c r="BD6" t="n">
-        <v>-1.885966678888772</v>
+        <v>-0.1040778722208225</v>
       </c>
       <c r="BE6" t="n">
-        <v>-0.8009568178290335</v>
+        <v>-0.4314577151841529</v>
       </c>
       <c r="BF6" t="n">
-        <v>-2.296595375665791</v>
+        <v>-0.1703583199665542</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1866,134 +1866,134 @@
         <v>0</v>
       </c>
       <c r="BI6" t="n">
-        <v>-0.7370216704393564</v>
+        <v>-0.8688579097777013</v>
       </c>
       <c r="BJ6" t="n">
-        <v>-0.7058959575717524</v>
+        <v>-2.255335927734422</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.03128825462301144</v>
+        <v>0.9801808485475174</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.9286850838833044</v>
+        <v>-0.9857932694003733</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.7536415798458798</v>
+        <v>1.499522694563511</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.523881637281316</v>
+        <v>1.139237906109203</v>
       </c>
       <c r="BO6" t="n">
-        <v>-0.9236440753012113</v>
+        <v>0.182880957571713</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.1863176717961902</v>
+        <v>-0.9185062902621178</v>
       </c>
       <c r="BQ6" t="n">
-        <v>-0.1172907337656789</v>
+        <v>0.3689003650553145</v>
       </c>
       <c r="BR6" t="n">
-        <v>-0.2157094016534944</v>
+        <v>0.2090339552852626</v>
       </c>
       <c r="BS6" t="n">
-        <v>-0.4474004569108809</v>
+        <v>1.285673415170064</v>
       </c>
       <c r="BT6" t="n">
-        <v>0.4094560392915655</v>
+        <v>0.6154781898473372</v>
       </c>
       <c r="BU6" t="n">
-        <v>-0.5664190358004755</v>
+        <v>0.0651510664763366</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>4zlpJdvq</t>
+          <t>CMriQj9N</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.910080355503086</v>
+        <v>1.975049126842419</v>
       </c>
       <c r="C7" t="n">
-        <v>1.805149320052122</v>
+        <v>-1.454636418394017</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3184983417266209</v>
+        <v>-1.676184435417813</v>
       </c>
       <c r="E7" t="n">
         <v>-0.2058317055638894</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.122280368789553</v>
+        <v>5.482813463583036</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.4565191234238114</v>
+        <v>0.007973993830842931</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.61530629258074</v>
+        <v>0.5986077292491325</v>
       </c>
       <c r="I7" t="n">
-        <v>0.311096653008989</v>
+        <v>-0.6349018439546278</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.5903113576880034</v>
+        <v>-0.5991635073322964</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1938520547695864</v>
+        <v>-0.6634651454898995</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.204478261983577</v>
+        <v>2.701199990282347</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6112506602320185</v>
+        <v>-1.945241490657405</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2639167443217952</v>
+        <v>0.3642972651913177</v>
       </c>
       <c r="O7" t="n">
-        <v>0.9128361885027941</v>
+        <v>-1.68408204749707</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.851923946119686</v>
+        <v>1.159810464605168</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.247554400071276</v>
+        <v>-0.03516066879176864</v>
       </c>
       <c r="R7" t="n">
-        <v>-1.068696290186378</v>
+        <v>-1.723077504746811</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7471472114405938</v>
+        <v>-0.1641124295204264</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3804527236237448</v>
+        <v>0.7176417258834848</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5017422983373261</v>
+        <v>-0.9182638894000916</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5843064892660498</v>
+        <v>-1.562422745431462</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.9716835446215749</v>
+        <v>1.633586795788856</v>
       </c>
       <c r="X7" t="n">
-        <v>1.341388708777531</v>
+        <v>-0.008424735431978249</v>
       </c>
       <c r="Y7" t="n">
-        <v>-1.639838155104477</v>
+        <v>1.270696519292619</v>
       </c>
       <c r="Z7" t="n">
-        <v>-4.340617690721013</v>
+        <v>1.205799980230591</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.986260851423359</v>
+        <v>0.6727645833200175</v>
       </c>
       <c r="AB7" t="n">
-        <v>-6.680941793910697</v>
+        <v>1.356858376924285</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.644401761046542</v>
+        <v>1.541905025471295</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
@@ -2002,10 +2002,10 @@
         <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.196573090146414</v>
+        <v>-0.9583280552288793</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.510163674286678</v>
+        <v>1.618813744756691</v>
       </c>
       <c r="AH7" t="n">
         <v>0</v>
@@ -2014,73 +2014,73 @@
         <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.579063239766125</v>
+        <v>-1.480637018051233</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.700764752826008</v>
+        <v>-0.1643681348143735</v>
       </c>
       <c r="AL7" t="n">
-        <v>-2.873595743762378</v>
+        <v>1.585081530128262</v>
       </c>
       <c r="AM7" t="n">
-        <v>-0.1141437042870489</v>
+        <v>0.727336863774535</v>
       </c>
       <c r="AN7" t="n">
-        <v>-1.191084700013663</v>
+        <v>1.952636553375777</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.1135459883856952</v>
+        <v>2.747327313657334</v>
       </c>
       <c r="AP7" t="n">
-        <v>2.433961768314255</v>
+        <v>-1.442778815671615</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-0.04264611987982319</v>
+        <v>-1.068639446492001</v>
       </c>
       <c r="AR7" t="n">
-        <v>3.253019984823279</v>
+        <v>-1.864167002366211</v>
       </c>
       <c r="AS7" t="n">
-        <v>-0.8624868604486826</v>
+        <v>-0.4462575921477186</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.01192358480671266</v>
+        <v>2.517472921073413</v>
       </c>
       <c r="AU7" t="n">
-        <v>-0.6207662961992807</v>
+        <v>0.8118145098759406</v>
       </c>
       <c r="AV7" t="n">
-        <v>-1.249710014854775</v>
+        <v>0.9492841904332725</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0.005799829432633994</v>
+        <v>0.7017047468668139</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.007289105810661419</v>
+        <v>-0.6785838428108159</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.121986081497191</v>
+        <v>2.31938297797572</v>
       </c>
       <c r="AZ7" t="n">
-        <v>-0.354848132751914</v>
+        <v>0.596291458904646</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.2101891066929485</v>
+        <v>2.097409964168935</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.2728468241092091</v>
+        <v>0.6550617422983757</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.8232840322056911</v>
+        <v>-2.810985149263953</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.757985719854534</v>
+        <v>-1.169039296358654</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.102141772142098</v>
+        <v>-3.69519222390826</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.8582982084210667</v>
+        <v>-1.441122485731947</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -2089,134 +2089,134 @@
         <v>0</v>
       </c>
       <c r="BI7" t="n">
-        <v>-2.43266506729635</v>
+        <v>0.2978519936437202</v>
       </c>
       <c r="BJ7" t="n">
-        <v>-1.101918741649671</v>
+        <v>-1.650643791443825</v>
       </c>
       <c r="BK7" t="n">
         <v>0.03128825462301144</v>
       </c>
       <c r="BL7" t="n">
-        <v>-0.0285540927585344</v>
+        <v>-1.943032446042212</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.8934942888554355</v>
+        <v>-0.365180092230567</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.3699504437649777</v>
+        <v>-0.01469328740713478</v>
       </c>
       <c r="BO7" t="n">
-        <v>-0.241197630974217</v>
+        <v>0.3139598343172839</v>
       </c>
       <c r="BP7" t="n">
-        <v>1.479258623820844</v>
+        <v>-0.5838429042913515</v>
       </c>
       <c r="BQ7" t="n">
-        <v>2.198226132164874</v>
+        <v>-1.044701085902224</v>
       </c>
       <c r="BR7" t="n">
-        <v>2.600575761522295</v>
+        <v>-0.5054074713876417</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.9774501200737241</v>
+        <v>-0.9260349614324764</v>
       </c>
       <c r="BT7" t="n">
-        <v>-0.2245543196424023</v>
+        <v>-0.03317151130028029</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.496805767430762</v>
+        <v>-0.8919657632544458</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>8Sp1FEw8</t>
+          <t>jFGHcfig</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.975049126842419</v>
+        <v>1.910080355503086</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5202073226222947</v>
+        <v>0.2701179405721941</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5555761336512771</v>
+        <v>0.5090017530269321</v>
       </c>
       <c r="E8" t="n">
         <v>-0.2058317055638894</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.4926174047097124</v>
+        <v>1.137045559370128</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.707970944206394</v>
+        <v>3.463150866040906</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1155953867130612</v>
+        <v>-1.276175450151626</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8786957511871586</v>
+        <v>-0.3511022948655427</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.1492660195282528</v>
+        <v>-0.04373451004335378</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3767147262930771</v>
+        <v>0.5793677302325317</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.1195676363541537</v>
+        <v>0.7483608641493851</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.02787237749033771</v>
+        <v>-1.416312080128559</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.7663889426321245</v>
+        <v>0.5095109054255019</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04719677650283909</v>
+        <v>0.864417959864852</v>
       </c>
       <c r="P8" t="n">
-        <v>0.312760161588803</v>
+        <v>-1.098990343438473</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.8741346296678622</v>
+        <v>1.177233062487739</v>
       </c>
       <c r="R8" t="n">
-        <v>-1.607598466883206</v>
+        <v>0.4421544551957974</v>
       </c>
       <c r="S8" t="n">
-        <v>0.9023160861395562</v>
+        <v>-1.079732872258795</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2939252808957354</v>
+        <v>-0.2939252808957355</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.492776428797009</v>
+        <v>1.234646258234673</v>
       </c>
       <c r="V8" t="n">
-        <v>0.06475026248345796</v>
+        <v>-0.2052877156356361</v>
       </c>
       <c r="W8" t="n">
-        <v>0.9729087872976648</v>
+        <v>0.3993671937728233</v>
       </c>
       <c r="X8" t="n">
-        <v>0.5578835082163714</v>
+        <v>-0.02221150941343877</v>
       </c>
       <c r="Y8" t="n">
-        <v>-0.2327128473768448</v>
+        <v>-1.057280653928698</v>
       </c>
       <c r="Z8" t="n">
-        <v>-3.406346016627455</v>
+        <v>-0.1090913635440902</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.586877368652223</v>
+        <v>-0.3532713092688632</v>
       </c>
       <c r="AB8" t="n">
-        <v>-5.327006791690232</v>
+        <v>-0.5486659623215661</v>
       </c>
       <c r="AC8" t="n">
-        <v>6.20648821999089</v>
+        <v>-0.1004575507590558</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
@@ -2225,10 +2225,10 @@
         <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>-0.100625701059026</v>
+        <v>-0.1930689954770468</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.630342530369264</v>
+        <v>-0.5716555216323291</v>
       </c>
       <c r="AH8" t="n">
         <v>0</v>
@@ -2237,73 +2237,73 @@
         <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>-1.364579422065057</v>
+        <v>-1.258999247938745</v>
       </c>
       <c r="AK8" t="n">
-        <v>-0.3879807970927844</v>
+        <v>0.6229347802908647</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.8918115881513641</v>
+        <v>0.4432251551074886</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.6615961943947241</v>
+        <v>-0.745254130333238</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.459149800032041</v>
+        <v>-0.5914491994206847</v>
       </c>
       <c r="AO8" t="n">
-        <v>1.331757051150871</v>
+        <v>-0.04839342049045889</v>
       </c>
       <c r="AP8" t="n">
-        <v>-0.9489934296354745</v>
+        <v>0.3957837919097597</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.5562169377135511</v>
+        <v>0.102666239683275</v>
       </c>
       <c r="AR8" t="n">
-        <v>-1.212384377981642</v>
+        <v>0.5626831948103762</v>
       </c>
       <c r="AS8" t="n">
-        <v>2.259232651808548</v>
+        <v>-2.527403933652539</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.543092623636362</v>
+        <v>-4.163991975637787</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.8910989481057137</v>
+        <v>-0.5041992947543154</v>
       </c>
       <c r="AV8" t="n">
-        <v>-0.1767935153333063</v>
+        <v>-0.973526289592428</v>
       </c>
       <c r="AW8" t="n">
-        <v>-0.005799829432633994</v>
+        <v>1.173374464399779</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.5788498963285592</v>
+        <v>-1.135832475225134</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.381490632359154</v>
+        <v>0.3657354100370677</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.3268019079352871</v>
+        <v>-0.7987132755249754</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.5257181459554953</v>
+        <v>0.5649895523648688</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.6390945394497413</v>
+        <v>0.5441317014552368</v>
       </c>
       <c r="BC8" t="n">
-        <v>-2.568378943421152</v>
+        <v>-0.1245134561691722</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.1759247785065109</v>
+        <v>0.6779412667126552</v>
       </c>
       <c r="BE8" t="n">
-        <v>-3.374945445029925</v>
+        <v>-0.1489766468059389</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.1637545660017617</v>
+        <v>0.762785243899056</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2312,134 +2312,134 @@
         <v>0</v>
       </c>
       <c r="BI8" t="n">
-        <v>1.130167107501427</v>
+        <v>-2.551632837775278</v>
       </c>
       <c r="BJ8" t="n">
-        <v>-1.55605214054661</v>
+        <v>1.868291012051589</v>
       </c>
       <c r="BK8" t="n">
         <v>0.03128825462301144</v>
       </c>
       <c r="BL8" t="n">
-        <v>-0.267863886918994</v>
+        <v>0.9286850838833044</v>
       </c>
       <c r="BM8" t="n">
-        <v>-1.111061206948198</v>
+        <v>0.6554993279093492</v>
       </c>
       <c r="BN8" t="n">
-        <v>-0.01469328740713478</v>
+        <v>0.1067731540156373</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.3266306258192789</v>
+        <v>-0.7554648687409651</v>
       </c>
       <c r="BP8" t="n">
-        <v>-0.1590157948502563</v>
+        <v>0.6812101874639427</v>
       </c>
       <c r="BQ8" t="n">
-        <v>-0.736630348415892</v>
+        <v>-0.3683395133570731</v>
       </c>
       <c r="BR8" t="n">
-        <v>-0.6528596021662291</v>
+        <v>-0.5874580482439136</v>
       </c>
       <c r="BS8" t="n">
-        <v>-1.167389502671402</v>
+        <v>-0.877415614758403</v>
       </c>
       <c r="BT8" t="n">
-        <v>-0.8039317652463828</v>
+        <v>0.9008843034424165</v>
       </c>
       <c r="BU8" t="n">
-        <v>-0.7938453067844194</v>
+        <v>-0.1723770601541214</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>dhkQFrkl</t>
+          <t>bXuieB8c</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>1.910080355503086</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.3852887158349662</v>
+        <v>1.813773091846953</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2642179751919778</v>
+        <v>1.181366734086854</v>
       </c>
       <c r="E9" t="n">
         <v>-0.2058317055638894</v>
       </c>
       <c r="F9" t="n">
-        <v>1.137045559370128</v>
+        <v>2.223487535423355</v>
       </c>
       <c r="G9" t="n">
         <v>0.4208567647238691</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7771585082396808</v>
+        <v>0.5986077292491325</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.580900340918244</v>
+        <v>-0.3511022948655427</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1423342040484424</v>
+        <v>0.6505517365678242</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.418664230483019</v>
+        <v>0.3339676082745987</v>
       </c>
       <c r="L9" t="n">
-        <v>1.052135839325623</v>
+        <v>0.8785501392249159</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2586310532127875</v>
+        <v>-0.09398855380644348</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6197412596032678</v>
+        <v>1.047461436293047</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1451675372749279</v>
+        <v>0.7891734153599432</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4068768619239547</v>
+        <v>0.5951102625942581</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.055816887590948</v>
+        <v>-1.247554400071276</v>
       </c>
       <c r="R9" t="n">
-        <v>-0.664519657663758</v>
+        <v>1.596944833831855</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.510613080606263</v>
+        <v>-0.1641124295204269</v>
       </c>
       <c r="T9" t="n">
         <v>1.392019730402965</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.113946334244407</v>
+        <v>1.379786268187579</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.180667163341096</v>
+        <v>-0.3508614886115133</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5597968099063279</v>
+        <v>-2.048565566561149</v>
       </c>
       <c r="X9" t="n">
-        <v>0.9221009929671575</v>
+        <v>0.3959069049089576</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.3572328200601073</v>
+        <v>-0.3999063373904598</v>
       </c>
       <c r="Z9" t="n">
-        <v>-2.480082098569506</v>
+        <v>-0.1719476428548113</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.543266800455535</v>
+        <v>-0.4271756769747242</v>
       </c>
       <c r="AB9" t="n">
-        <v>-3.98467653088117</v>
+        <v>-0.6397565080674806</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.935306829711856</v>
+        <v>-0.2187553302195912</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
@@ -2448,10 +2448,10 @@
         <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.09038296025503199</v>
+        <v>-0.489989510660758</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.7234113955134596</v>
+        <v>1.10001839219087</v>
       </c>
       <c r="AH9" t="n">
         <v>0</v>
@@ -2460,73 +2460,73 @@
         <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.54069944537466</v>
+        <v>-0.1991677290372097</v>
       </c>
       <c r="AK9" t="n">
-        <v>-0.1420068685865329</v>
+        <v>2.309346941640547</v>
       </c>
       <c r="AL9" t="n">
-        <v>-1.079250011586877</v>
+        <v>1.258836851550898</v>
       </c>
       <c r="AM9" t="n">
-        <v>-1.271179485371728</v>
+        <v>0.04363390222449766</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.2073785232576856</v>
+        <v>-0.9842114421332855</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.3106899765560462</v>
+        <v>-1.383353124476278</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.236269555375531</v>
+        <v>0.3012291435198604</v>
       </c>
       <c r="AQ9" t="n">
-        <v>-0.4037253163699459</v>
+        <v>0.3932909588094713</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.672100427805387</v>
+        <v>0.4378737560984374</v>
       </c>
       <c r="AS9" t="n">
-        <v>-2.527403933652539</v>
+        <v>-1.278716128749647</v>
       </c>
       <c r="AT9" t="n">
-        <v>-0.2664707858895874</v>
+        <v>1.264698252940063</v>
       </c>
       <c r="AU9" t="n">
-        <v>-0.3569567666133077</v>
+        <v>0.6176485387009848</v>
       </c>
       <c r="AV9" t="n">
-        <v>-1.054981397503904</v>
+        <v>-0.2226120135335112</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.173374464399779</v>
+        <v>0.6230931272779863</v>
       </c>
       <c r="AX9" t="n">
-        <v>-1.135832475225134</v>
+        <v>-0.6023757374084294</v>
       </c>
       <c r="AY9" t="n">
-        <v>-0.4535361507113985</v>
+        <v>-0.01238992569299334</v>
       </c>
       <c r="AZ9" t="n">
-        <v>-0.2914388266414769</v>
+        <v>1.547431050561206</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.1923289723950683</v>
+        <v>-0.4268223499314376</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.2399144682339025</v>
+        <v>0.144111251142101</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.197642107925223</v>
+        <v>0.3671319960843878</v>
       </c>
       <c r="BD9" t="n">
-        <v>-0.06249324838853759</v>
+        <v>-0.3371144260581935</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.596304596542204</v>
+        <v>0.5000086991682905</v>
       </c>
       <c r="BF9" t="n">
-        <v>-0.1207375087191584</v>
+        <v>-0.4484289572853967</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2535,10 +2535,10 @@
         <v>0</v>
       </c>
       <c r="BI9" t="n">
-        <v>-0.4341432442250389</v>
+        <v>-1.603901659360164</v>
       </c>
       <c r="BJ9" t="n">
-        <v>-0.5768550809722222</v>
+        <v>1.654358487731495</v>
       </c>
       <c r="BK9" t="n">
         <v>0.03128825462301144</v>
@@ -2547,122 +2547,122 @@
         <v>-0.9857932694003733</v>
       </c>
       <c r="BM9" t="n">
-        <v>-0.365180092230567</v>
+        <v>-0.7381206495893828</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.139237906109203</v>
+        <v>-1.553268212095585</v>
       </c>
       <c r="BO9" t="n">
-        <v>-0.4305630082407516</v>
+        <v>0.2457731930236593</v>
       </c>
       <c r="BP9" t="n">
-        <v>1.672566089146305</v>
+        <v>0.1738772503366769</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.6982714739256393</v>
+        <v>0.3334671740690803</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.3160017178677484</v>
+        <v>0.3398234132447389</v>
       </c>
       <c r="BS9" t="n">
-        <v>-0.2211472358958367</v>
+        <v>0.5072815225971719</v>
       </c>
       <c r="BT9" t="n">
-        <v>-0.5310894735901972</v>
+        <v>-0.1236183389614137</v>
       </c>
       <c r="BU9" t="n">
-        <v>1.378762212832217</v>
+        <v>0.902264581682573</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>x88gL4RQ</t>
+          <t>nucZxUhT</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.975049126842419</v>
+        <v>1.910080355503086</v>
       </c>
       <c r="C10" t="n">
-        <v>1.1324951200553</v>
+        <v>1.149742663644962</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.463268858082171</v>
+        <v>-1.58653577127649</v>
       </c>
       <c r="E10" t="n">
         <v>-0.2058317055638894</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3222140773302074</v>
+        <v>0.05060358331690091</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.230674318848236</v>
+        <v>3.311036160975054</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2941461657036097</v>
+        <v>-0.740523113179981</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8313958263389777</v>
+        <v>-1.202500942132798</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.315666913835031</v>
+        <v>2.150210029247968</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6207180274714212</v>
+        <v>-0.449729555397507</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.3148515489674498</v>
+        <v>-1.204478261983577</v>
       </c>
       <c r="M10" t="n">
-        <v>0.3908634058449991</v>
+        <v>-0.3584532590708666</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.154505399258034</v>
+        <v>2.146464668065394</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.392493083560629</v>
+        <v>0.08252899740079703</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2186434612536514</v>
+        <v>-0.5342901414275624</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.8741346296678622</v>
+        <v>1.783429928127493</v>
       </c>
       <c r="R10" t="n">
-        <v>-2.011775099405826</v>
+        <v>1.163898441843333</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3041484972333534</v>
+        <v>-0.6488526639113279</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7154115337204106</v>
+        <v>0.04326372136400455</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.148068905158859</v>
+        <v>0.6903712209112775</v>
       </c>
       <c r="V10" t="n">
-        <v>1.226106879456301</v>
+        <v>0.2794852450540128</v>
       </c>
       <c r="W10" t="n">
-        <v>-1.27390285955326</v>
+        <v>-0.609277648029647</v>
       </c>
       <c r="X10" t="n">
-        <v>0.6160669904670291</v>
+        <v>-1.721254619363161</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0.05608405590762777</v>
+        <v>-0.6855914083689442</v>
       </c>
       <c r="Z10" t="n">
-        <v>-1.491005010796101</v>
+        <v>-1.255352593998753</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.641529842886616</v>
+        <v>-0.8949478148321682</v>
       </c>
       <c r="AB10" t="n">
-        <v>-2.551318198220647</v>
+        <v>-2.209813618442685</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.092595229348776</v>
+        <v>-0.9675122294367212</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -2671,10 +2671,10 @@
         <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.4459105888190529</v>
+        <v>2.310858648030948</v>
       </c>
       <c r="AG10" t="n">
-        <v>-0.1912055964173939</v>
+        <v>-1.042414267479092</v>
       </c>
       <c r="AH10" t="n">
         <v>0</v>
@@ -2683,73 +2683,73 @@
         <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.008768797104688213</v>
+        <v>2.472574845227876</v>
       </c>
       <c r="AK10" t="n">
-        <v>-1.461321576029156</v>
+        <v>0.3667119380968525</v>
       </c>
       <c r="AL10" t="n">
-        <v>2.210383830734876</v>
+        <v>0.1713545896263518</v>
       </c>
       <c r="AM10" t="n">
-        <v>-0.1141437042870489</v>
+        <v>-0.8504392013409362</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.206388292221835</v>
+        <v>-0.8157037702598152</v>
       </c>
       <c r="AO10" t="n">
-        <v>1.006872072870701</v>
+        <v>-1.905489696712267</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.551451716675195</v>
+        <v>0.3800246838447764</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-1.046622422315774</v>
+        <v>1.53377281113803</v>
       </c>
       <c r="AR10" t="n">
-        <v>2.088131890178517</v>
+        <v>0.5418816216917198</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.8024302127551737</v>
+        <v>-1.278716128749647</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.4991137335252377</v>
+        <v>1.264698252940063</v>
       </c>
       <c r="AU10" t="n">
-        <v>-0.111552553044961</v>
+        <v>-1.218837938662139</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.4341197940027614</v>
+        <v>-0.5750619996889355</v>
       </c>
       <c r="AW10" t="n">
-        <v>-0.9884450742929786</v>
+        <v>1.173374464399779</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.9598904233404909</v>
+        <v>-1.135832475225134</v>
       </c>
       <c r="AY10" t="n">
-        <v>-0.1856973712359385</v>
+        <v>0.3657354100370684</v>
       </c>
       <c r="AZ10" t="n">
-        <v>-0.3707004592795231</v>
+        <v>1.230384520009019</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.4145884214353531</v>
+        <v>-0.06168182650811332</v>
       </c>
       <c r="BB10" t="n">
-        <v>0.01637362835303242</v>
+        <v>0.9424713935737794</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.155672227129922</v>
+        <v>-0.1390370966687367</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.5049216783662173</v>
+        <v>0.1491058578224922</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.540903214339674</v>
+        <v>-0.1681482466065897</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.5563297912763169</v>
+        <v>0.1317529154280368</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2758,134 +2758,134 @@
         <v>0</v>
       </c>
       <c r="BI10" t="n">
-        <v>0.364246912558449</v>
+        <v>-1.517176855193095</v>
       </c>
       <c r="BJ10" t="n">
-        <v>-1.936434198563993</v>
+        <v>-0.7430802976783423</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.03128825462301144</v>
+        <v>-0.9176043393014947</v>
       </c>
       <c r="BL10" t="n">
-        <v>-0.7464834752399137</v>
+        <v>0.9286850838833044</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.499522694563511</v>
+        <v>1.126582137204695</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.523881637281315</v>
+        <v>-0.01469328740713478</v>
       </c>
       <c r="BO10" t="n">
-        <v>-2.095541809489502</v>
+        <v>0.1426202683507487</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.5025807683222069</v>
+        <v>-0.4216394854370737</v>
       </c>
       <c r="BQ10" t="n">
-        <v>-0.5784373379476486</v>
+        <v>1.995840865173142</v>
       </c>
       <c r="BR10" t="n">
-        <v>-0.621179855989677</v>
+        <v>4.501060173798745</v>
       </c>
       <c r="BS10" t="n">
-        <v>-1.1220118343787</v>
+        <v>2.359872003598779</v>
       </c>
       <c r="BT10" t="n">
-        <v>0.00905824414105634</v>
+        <v>0.5634366075280607</v>
       </c>
       <c r="BU10" t="n">
-        <v>-1.079570822065418</v>
+        <v>3.53529795001021</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>vymauDyP</t>
+          <t>rPc4X7Gj</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>1.975049126842419</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.7733584466023637</v>
+        <v>-1.687478256854456</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3184983417266209</v>
+        <v>-1.676184435417813</v>
       </c>
       <c r="E11" t="n">
         <v>-0.2058317055638894</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3222140773302078</v>
+        <v>-1.035838392736326</v>
       </c>
       <c r="G11" t="n">
-        <v>2.08596951839114</v>
+        <v>2.898153390082027</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.4726969446941582</v>
+        <v>-0.740523113179981</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4056965027053503</v>
+        <v>0.5002963524017121</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.352692468539177</v>
+        <v>-0.5366777451372903</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.3798905138980193</v>
+        <v>-1.090936325674684</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.7705140117318076</v>
+        <v>0.4879823139983235</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.3584532590708666</v>
+        <v>1.492799677780095</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.052643067949026</v>
+        <v>0.839541905957738</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.02846531495956247</v>
+        <v>-0.3002367289937408</v>
       </c>
       <c r="P11" t="n">
-        <v>0.03041006058334787</v>
+        <v>-1.663690545449383</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.03516066879176864</v>
+        <v>-0.6413575344315225</v>
       </c>
       <c r="R11" t="n">
-        <v>-0.2235594061725223</v>
+        <v>-0.2795895314517387</v>
       </c>
       <c r="S11" t="n">
         <v>-1.133592898302229</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5468170325905405</v>
+        <v>-0.9683032854152158</v>
       </c>
       <c r="U11" t="n">
-        <v>0.6359437171789382</v>
+        <v>0.8052737287906609</v>
       </c>
       <c r="V11" t="n">
-        <v>1.176678679076294</v>
+        <v>-0.0348576549953281</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.9195907535894603</v>
+        <v>-1.448048534802204</v>
       </c>
       <c r="X11" t="n">
-        <v>0.9273628543521361</v>
+        <v>-0.611807390577257</v>
       </c>
       <c r="Y11" t="n">
-        <v>-0.4735959640807607</v>
+        <v>0.437382712138558</v>
       </c>
       <c r="Z11" t="n">
-        <v>-0.08561149059576098</v>
+        <v>0.8093353254507413</v>
       </c>
       <c r="AA11" t="n">
-        <v>-0.3779261396527595</v>
+        <v>0.06547789437195976</v>
       </c>
       <c r="AB11" t="n">
-        <v>-0.5146392196577948</v>
+        <v>0.7823066826641667</v>
       </c>
       <c r="AC11" t="n">
-        <v>-0.1399222235237179</v>
+        <v>0.569828962464822</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
@@ -2894,10 +2894,10 @@
         <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.1859826998337952</v>
+        <v>-1.298103077758693</v>
       </c>
       <c r="AG11" t="n">
-        <v>-0.08180690350500623</v>
+        <v>0.1681082218411557</v>
       </c>
       <c r="AH11" t="n">
         <v>0</v>
@@ -2906,73 +2906,73 @@
         <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>-0.3985632199766616</v>
+        <v>0.1876909242500425</v>
       </c>
       <c r="AK11" t="n">
-        <v>-0.1077389541075025</v>
+        <v>0.3806877294892532</v>
       </c>
       <c r="AL11" t="n">
-        <v>1.272430379824955</v>
+        <v>-0.04614186275855788</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.5169667217591396</v>
+        <v>-0.9556242723486339</v>
       </c>
       <c r="AN11" t="n">
-        <v>0.01365013075841643</v>
+        <v>-0.3823983282994621</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.03637743674171403</v>
+        <v>1.192520631887941</v>
       </c>
       <c r="AP11" t="n">
-        <v>-1.432272743628293</v>
+        <v>-0.7808962769423202</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.4769556506791339</v>
+        <v>-0.50500362758059</v>
       </c>
       <c r="AR11" t="n">
-        <v>-1.850299286953774</v>
+        <v>-0.9905009313826396</v>
       </c>
       <c r="AS11" t="n">
-        <v>-0.3768860474308911</v>
+        <v>-4.192321006856396</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.403895438288213</v>
+        <v>-1.658442639371087</v>
       </c>
       <c r="AU11" t="n">
-        <v>-0.8610041052714515</v>
+        <v>-0.2803690779831858</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.3124395279491468</v>
+        <v>-0.4164595059189949</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.4658698881003313</v>
+        <v>2.352548758232193</v>
       </c>
       <c r="AX11" t="n">
-        <v>-0.4499595266036568</v>
+        <v>-2.736202688675248</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.4287562993254118</v>
+        <v>-0.8316614864414605</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.182827540426191</v>
+        <v>0.4060635405733336</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.3073753930331667</v>
+        <v>0.4304640963668016</v>
       </c>
       <c r="BB11" t="n">
-        <v>0.708740957138189</v>
+        <v>0.2399144682339021</v>
       </c>
       <c r="BC11" t="n">
-        <v>-0.976934625385923</v>
+        <v>0.3594169095337443</v>
       </c>
       <c r="BD11" t="n">
-        <v>-0.09033112400500001</v>
+        <v>-0.6781727961732771</v>
       </c>
       <c r="BE11" t="n">
-        <v>-1.274195734838059</v>
+        <v>0.489824575443887</v>
       </c>
       <c r="BF11" t="n">
-        <v>-0.1539550262579497</v>
+        <v>-0.8553965200095334</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2981,43 +2981,2273 @@
         <v>0</v>
       </c>
       <c r="BI11" t="n">
-        <v>-1.183177908083317</v>
+        <v>-1.08959669120433</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.6161075484263532</v>
+        <v>-0.08273237107793407</v>
       </c>
       <c r="BK11" t="n">
+        <v>0.03128825462301144</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>0.9286850838833044</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>0.3807010224870642</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>0.7545941749370901</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>0.177992039168424</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>1.048037043332169</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>0.7258364180831179</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>0.3693451412412282</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>0.3632980571599288</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>-0.07620691672068809</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>1.356827207900689</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>zeCiJHet</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1.910080355503086</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-0.1007042466055413</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.5090017530269321</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-0.2058317055638894</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-6.468048273002461</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.007973993830842931</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.5986077292491325</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.5002963524017121</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.6672146064864924</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.8421833447165101</v>
+      </c>
+      <c r="L12" t="n">
+        <v>-0.5535318866059228</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.5671732093546142</v>
+      </c>
+      <c r="N12" t="n">
+        <v>-0.7941115466768324</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.201382659169445</v>
+      </c>
+      <c r="P12" t="n">
+        <v>-0.5342901414275624</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.783429928127493</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.89526568164617</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.354740304904397</v>
+      </c>
+      <c r="T12" t="n">
+        <v>-0.9683032854152156</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.149981252428812</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.588784915426897</v>
+      </c>
+      <c r="W12" t="n">
+        <v>-1.370703030484952</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.7401288584605914</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>-1.401817393196672</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-0.921699149514986</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-1.896307377094578</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>-1.726287156467602</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>-2.570375718218352</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>-0.1389906885879181</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0.6345970470906692</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0.5879821696653247</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0.5064698520208593</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>-2.710473404473697</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>-1.665623501650596</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>-1.58602455596711</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>-2.102741290668086</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1.945429418299776</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>2.040164367191251</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>2.608171218144928</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>-0.8624868604486826</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>-3.328808863548887</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>-0.4691415499588373</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>-2.460082008976859</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1.173374464399779</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>-0.3737514212012704</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>-2.21812105078502</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>-1.40110168357413</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>-1.66512499458445</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>-0.2071672115278377</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>1.975887506234532</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>2.383585538630343</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>2.623609652979777</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>2.798043583937746</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>0.1499494701103776</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>2.087878028826297</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>0.03128825462301144</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>1.407304672204224</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>-0.7381206495893828</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>-1.553268212095585</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>0.3449809141344286</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>0.09286235253306596</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>-0.250221180180991</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>-0.1023700253247302</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>-0.1011061661204176</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>-0.6484169438327477</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>0.2014352846217424</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>U5mYDMJ0</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2.007533512512086</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-0.3852887158349662</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.9477890392695648</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-0.2058317055638894</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-2.122280368789553</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-4.946619256885473</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-0.2941461657036097</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-1.013301242740074</v>
+      </c>
+      <c r="J13" t="n">
+        <v>-1.373986958550371</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-0.886700095141954</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-0.1629640613793304</v>
+      </c>
+      <c r="M13" t="n">
+        <v>-1.857086588902598</v>
+      </c>
+      <c r="N13" t="n">
+        <v>-1.514899251839237</v>
+      </c>
+      <c r="O13" t="n">
+        <v>-0.4199736998145965</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.7833436632645616</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.3689705749680673</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.9521868724267232</v>
+      </c>
+      <c r="S13" t="n">
+        <v>-0.002532351390126108</v>
+      </c>
+      <c r="T13" t="n">
+        <v>-0.6311142831554756</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.2307611893937435</v>
+      </c>
+      <c r="V13" t="n">
+        <v>-0.9069600028294693</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.3635389163426095</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.5023020200791934</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.0200202403345747</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-0.4547332952835654</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.3443265295265225</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>-1.049565992359627</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.016178418774015</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.811909741072753</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>-0.7744767500016826</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>-0.4328948320649244</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>-0.561901756642659</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0.5519733812999428</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>-1.008216807852483</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>-0.346289541469432</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0.5311476403890208</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>-1.495309175888226</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.397267261245422</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>-1.933505579428399</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>-0.307514502714064</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0.5687123261993124</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>-0.1115525530449607</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>-0.3142490099339218</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0.9768454154277105</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>-0.9453122117191679</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>-0.3905152614230551</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0.9133379894568322</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>-0.125184526233909</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>-0.3987736457114407</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>-0.634688090861987</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>-0.8318802156286331</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>-0.8224210166983994</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>-1.038807746208894</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>-0.1864021514264455</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>1.009855550726795</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>0.03128825462301144</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>-0.0285540927585344</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>0.007760465128248513</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>-1.168624480923472</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>0.182880957571713</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>1.294945429647204</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>1.226180342810239</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>1.078963575486843</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>-0.06578373405521808</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>0.2014326151857617</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>0.7558699652654427</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>rsizUY9b</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1.910080355503086</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.2701179405721941</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-1.58653577127649</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-0.2058317055638894</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-3.20872234484278</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-2.056439860634289</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-1.901103176618546</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.8786957511871586</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.375614382909798</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.7756878277988768</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-1.812028212336053</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2.198038891818557</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.7306316757821003</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.8990958803758108</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.7833436632645615</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.7731018187279033</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.5480102399041028</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.354740304904397</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.7176417258834848</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-0.343751350003174</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.6844259789473295</v>
+      </c>
+      <c r="W14" t="n">
+        <v>-0.3869686799960866</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-0.516842028976898</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>-0.3101768147352018</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-0.7412249801572538</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.3981071519474786</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>-1.464746213221978</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.102264375638241</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>-0.661407540045168</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0.4860038103063856</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>-0.05355843036936852</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0.1673239808986021</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>-1.40549469016424</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1.674002502843818</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>-0.6110873115563151</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0.0670262428459177</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.540945644631873</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>-1.337247141441971</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>2.074264174766079</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>1.079916391622483</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>-0.5448651565858872</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>1.136503161674061</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>-0.9175259029032879</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0.7017047468668141</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>-0.6785838428108157</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>1.752194974380628</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0.7231100711255205</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0.2082046473265176</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>-0.1113639944360361</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>-0.1900787348691188</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>-1.646497479091975</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>-0.2355245948972731</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>-2.010848989919805</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>0.2684194334315433</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>-0.03830856365060071</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>0.9801808485475174</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>-0.9857932694003733</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>-1.111061206948198</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>-1.168624480923472</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>-0.1896655664396968</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>0.06447489767980011</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>0.2384145522770629</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>-0.4566612864512171</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>0.2279338188127427</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>-0.1461197066850931</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>-1.132492192966289</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>UaS8aGMt</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1.975049126842419</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1.149742663644962</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.3184983417266209</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-0.2058317055638894</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.223487535423355</v>
+      </c>
+      <c r="G15" t="n">
+        <v>5.136412621765275</v>
+      </c>
+      <c r="H15" t="n">
+        <v>3.455420193097908</v>
+      </c>
+      <c r="I15" t="n">
+        <v>-1.202500942132797</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.859469685641887</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-1.688146062201848</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2.006857189879516</v>
+      </c>
+      <c r="M15" t="n">
+        <v>-0.09398855380644348</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.523846432147676</v>
+      </c>
+      <c r="O15" t="n">
+        <v>-1.636352556108601</v>
+      </c>
+      <c r="P15" t="n">
+        <v>3.41861127264881</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>-2.459948131350784</v>
+      </c>
+      <c r="R15" t="n">
+        <v>4.291962204324165</v>
+      </c>
+      <c r="S15" t="n">
+        <v>-0.8438826529528133</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.066397734922445</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.559048849054935</v>
+      </c>
+      <c r="V15" t="n">
+        <v>-1.579237292969165</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0.4156825253585427</v>
+      </c>
+      <c r="X15" t="n">
+        <v>-2.546719900832653</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.352892250091921</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-0.01895932708599358</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0.377341047961883</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>-0.4180477252863634</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.069024337656728</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.87093279880951</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>-2.784623985014549</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.415429844751947</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>-1.570069956231222</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>-1.187998237779331</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>-1.21858694986788</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0.6938969142307142</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>-1.203200739903625</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>-1.873527769447823</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>1.793573696417508</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>-2.432743334276154</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0.5249440338878641</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>-0.2664707858895874</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>-0.9433436769292525</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0.6085516204842437</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>-0.005799829432633994</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0.007289105810661419</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>-1.083745043594835</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0.9767472955672699</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>-0.92314608199884</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>-0.1348946091603383</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>-0.4561458398324107</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>0.1829242000691406</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>-0.5867403976174603</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>0.1721066188567055</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>0.9140404747734812</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>0.8034329501013033</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>1.929073442472024</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>-0.9857932694003733</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>0.557357075972819</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>-2.747688219419513</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>0.1424102203300835</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>-1.666809358036875</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>0.5482916107256394</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>2.834041307925753</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>1.839814459745406</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>-0.2057480611813637</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>2.581283261372423</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>QXtsC0lD</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1.975049126842419</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.1925039944187146</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-1.676184435417813</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-0.2058317055638894</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.137045559370128</v>
+      </c>
+      <c r="G16" t="n">
+        <v>6.614098328119265</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-0.1155953867130616</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.1218969536162656</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.02569411461776414</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-1.21917767973012</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.3577930389227927</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.492799677780095</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.7583542798268073</v>
+      </c>
+      <c r="O16" t="n">
+        <v>-0.55737678108443</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.03041006058334787</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>-0.03516066879176864</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.9521868724267232</v>
+      </c>
+      <c r="S16" t="n">
+        <v>-1.812229226449491</v>
+      </c>
+      <c r="T16" t="n">
+        <v>-0.6311142831554756</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.954298807584496</v>
+      </c>
+      <c r="V16" t="n">
+        <v>-0.1393393543691005</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.4470239133951817</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.3625306136477928</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.123194384196828</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0.1852495725080938</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0.1517082192765279</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>-0.1221107033343607</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0.7078567445164901</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>-0.9797553089019299</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.10428831278812</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0.3838067693192739</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1.077924433399021</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>-0.04614186275855846</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>-1.16599441436403</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>-1.080501540346698</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>-0.8380104823631311</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>-0.8859569973755417</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.062608493766772</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>-1.129178085507016</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>-1.97243157591792</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>-3.607203234245187</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>-0.5813263333043676</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>-1.276437472138228</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>2.352548758232193</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>-2.736202688675248</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>-0.7686405971531168</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0.596291458904646</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>-0.1886872259597043</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>-0.2391016172251051</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>1.333699324804937</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>0.03254907602601448</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>1.775903817005313</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>-0.007328349138716355</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>-2.050236145613386</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>1.415695343114976</v>
+      </c>
+      <c r="BK16" t="n">
         <v>-0.9176043393014947</v>
       </c>
-      <c r="BL11" t="n">
-        <v>0.6893752897228448</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>0.96464742150942</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>1.275887652709822</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>-0.1539904367951914</v>
-      </c>
-      <c r="BP11" t="n">
-        <v>0.7295019043648998</v>
-      </c>
-      <c r="BQ11" t="n">
-        <v>-0.3872570284256149</v>
-      </c>
-      <c r="BR11" t="n">
-        <v>-0.6394697638958361</v>
-      </c>
-      <c r="BS11" t="n">
-        <v>-0.9732707592455118</v>
-      </c>
-      <c r="BT11" t="n">
-        <v>-0.009800946505869386</v>
-      </c>
-      <c r="BU11" t="n">
-        <v>-0.5405893497289537</v>
+      <c r="BL16" t="n">
+        <v>-0.0285540927585344</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>2.245403809281142</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>-0.7839807497513597</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>0.2812926291791707</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>0.1707346964363057</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>1.733589796758104</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>2.275403062218514</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>1.790334721959052</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>-0.1539522912243915</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>3.084558098593004</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>zHmSVfun</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1.910080355503086</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-1.454636418394017</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.84252563212911</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-0.2058317055638894</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-1.035838392736326</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-6.59815034045758</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.06295539227748714</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-0.6349018439546276</v>
+      </c>
+      <c r="J17" t="n">
+        <v>-2.948628165864521</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.2437236924578111</v>
+      </c>
+      <c r="L17" t="n">
+        <v>-0.5969283116310998</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-0.6229179643352897</v>
+      </c>
+      <c r="N17" t="n">
+        <v>-2.402022581269887</v>
+      </c>
+      <c r="O17" t="n">
+        <v>-0.3924930835606297</v>
+      </c>
+      <c r="P17" t="n">
+        <v>-0.3460567407572589</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>-0.4392919125516048</v>
+      </c>
+      <c r="R17" t="n">
+        <v>-3.089579452799479</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.203932231982784</v>
+      </c>
+      <c r="T17" t="n">
+        <v>-1.305492287674956</v>
+      </c>
+      <c r="U17" t="n">
+        <v>-2.641801507590844</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.46593266536206</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.210140772912118</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.630745604088053</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.488390937993476</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.798416939560804</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-0.5501248469541896</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.21567157483602</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>-0.4155584995934795</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>-1.763380586087806</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.599599102069068</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>-1.550486497116986</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>-0.9221666014245438</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>2.128822661090535</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1.779187573851516</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>1.230460816775188</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>1.761069343878241</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>-0.5655218000542164</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>-1.218355210890345</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>-0.706212765427668</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>2.744833464826339</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>1.682289808984513</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>1.466585312671485</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>1.420979755237948</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>-0.005799829432633994</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>0.007289105810661419</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>0.2396936314603809</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0.406063540573334</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0.2558316721208644</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>-0.0474951830415025</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>-0.2344584492220415</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>-0.8288315708344436</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>-0.2941070228268919</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>-1.035169953824311</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>2.253978190073735</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>-1.524372726106824</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>0.03128825462301144</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>-0.0285540927585344</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>-1.111061206948198</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>1.908525368453428</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>1.103343985588834</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>-0.4698333069848775</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>-2.039140799882752</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>-4.225799973871165</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>-1.693860318231402</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>-0.5938281897528791</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>-3.683460810619636</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>YFePBifU</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1.910080355503086</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1.813773091846953</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.181366734086854</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-0.2058317055638894</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2.223487535423355</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.659505077402948</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.9557092872302295</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-1.580900340918244</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.9588148300631869</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1.507138513892843</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.1842073388220852</v>
+      </c>
+      <c r="M18" t="n">
+        <v>-0.7992277678449049</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1.035580320273886</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.5143672528202746</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.03041006058334787</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.7731018187279031</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2.029991225820377</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.656356450747624</v>
+      </c>
+      <c r="T18" t="n">
+        <v>-0.6311142831554756</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.035078744549428</v>
+      </c>
+      <c r="V18" t="n">
+        <v>-0.4301822889524177</v>
+      </c>
+      <c r="W18" t="n">
+        <v>-0.8080932129134126</v>
+      </c>
+      <c r="X18" t="n">
+        <v>-0.5250037668082033</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>-0.1601009678967687</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-0.1602491365924647</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0.07757222386781995</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>-0.6228031768882456</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0.5891882015441497</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0.2446591867010009</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>-0.005891042496763281</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0.09366277935383543</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1.239422467266761</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0.1169804765301247</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>-0.3245138463024454</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>-0.8879213439198739</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>-1.534192578677785</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>-0.3396412511227903</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0.6090577957364959</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>-0.4080568840602588</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0.8024302127551735</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>-0.5448651565858872</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>1.12248006375587</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>1.05266951970553</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>-0.7919160253209098</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0.7693701598345251</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>0.1766727421720369</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0.786519377235958</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>-0.3315683003427446</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>-0.06346238589013517</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>-0.8217057823523964</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>0.2224468171147866</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>-1.069289447310077</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>0.219266942545928</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>0.1650478282490899</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>1.835502965667389</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>-0.9176043393014947</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>-0.0285540927585344</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>-1.111061206948198</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>-1.937911943267697</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>0.5364974647083683</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>-1.539241558860609</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>-0.4113893836010407</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>0.005890889312127125</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>0.709253004771779</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>0.455859143290966</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>-0.4708305165865023</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>dA00HeQh</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1.910080355503086</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1.425703361079556</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.2176435945676327</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-0.2058317055638894</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.05060358331690091</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2.072387848295974</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.134260066220778</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-0.8241015433473512</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.192095008924543</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.04423714170491172</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.9653429892752696</v>
+      </c>
+      <c r="M19" t="n">
+        <v>-0.8873826695997128</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1.617755005212752</v>
+      </c>
+      <c r="O19" t="n">
+        <v>-0.1176869210209619</v>
+      </c>
+      <c r="P19" t="n">
+        <v>-0.7225235420978657</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>-0.03516066879176864</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.08691241660093</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.2990837944531012</v>
+      </c>
+      <c r="T19" t="n">
+        <v>-0.2939252808957354</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0.11585868151436</v>
+      </c>
+      <c r="V19" t="n">
+        <v>-0.1673636002652727</v>
+      </c>
+      <c r="W19" t="n">
+        <v>-0.4109248058116152</v>
+      </c>
+      <c r="X19" t="n">
+        <v>-1.079658949054871</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0.146085050305666</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-0.160190656239117</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-0.02491813634295266</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>-0.6227184278805049</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0.4251331882153057</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.469073682303933</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>-3.396207996712908</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>2.189147151326451</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>-1.096087560974419</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>1.041340399165989</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>-2.27043765994486</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0.002762064554186709</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>-2.60167179302692</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>-1.542586500083176</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0.8732620858512198</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>-1.995910298784369</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>1.634888749357102</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>-0.2664707858895874</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0.0006322303005692695</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0.9457596905717176</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>-1.892478699564496</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>1.836283635467934</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>-0.64259881857643</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>-0.6084853571936631</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>-0.6332061240402728</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>-0.6063472827436772</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>-0.3801924043354417</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>1.128294283933287</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>-0.4864798004981573</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>1.300168536154566</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>0.9682226432930051</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>0.02876158400843228</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>-1.866496933226001</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>0.9286850838833044</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>0.007760465128248513</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>-0.01469328740713478</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>-0.2080023901381274</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>0.2659593718207326</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>1.417414378884451</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>0.8737882440834143</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>1.506480522900335</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>0.2395829475328093</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>1.213050890673743</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>4z48FZf5</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1.975049126842419</v>
+      </c>
+      <c r="C20" t="n">
+        <v>-0.5577641517315873</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-0.3426605563156353</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-0.2058317055638894</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-1.035838392736326</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.4208567647238691</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.06295539227748714</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.5002963524017121</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.017134874778526</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-0.7537090613066872</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.3577930389227927</v>
+      </c>
+      <c r="M20" t="n">
+        <v>-0.6229179643352897</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-0.07332384151442839</v>
+      </c>
+      <c r="O20" t="n">
+        <v>-0.9695860248939321</v>
+      </c>
+      <c r="P20" t="n">
+        <v>-0.3460567407572591</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>-1.247554400071276</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.356363504949343</v>
+      </c>
+      <c r="S20" t="n">
+        <v>-1.058188861841422</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0.3804527236237445</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.264883760308195</v>
+      </c>
+      <c r="V20" t="n">
+        <v>-0.06267594907559375</v>
+      </c>
+      <c r="W20" t="n">
+        <v>2.157802764467061</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0.6628754973577242</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0.5662181207909743</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0.5229013168076597</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0.3568162712832804</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.367210045484785</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.036170589219752</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.003796173974819</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>-0.5524408789447062</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>-0.1964812106116037</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0.717659588617136</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0.1169804765301247</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0.2540040442398936</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>0.2916323591944213</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0.2526748018631592</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>-0.1505319543429917</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>-0.3684980776879827</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>-0.1584380066363812</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>-0.03002832384675448</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>-1.380048268674787</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>-0.644430273936228</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>-1.803350201440586</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>-0.9491392644985649</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>0.9217863706392978</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>-0.2644734828463676</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>-0.92553188774585</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>-0.3474439752741935</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>-0.8777897311704479</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>-0.1030006958895223</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>0.4330540575499863</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>-0.1205792191292383</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>0.4705738238373859</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>-0.5972435077159699</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>1.315760576680705</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>0.9801808485475174</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>-0.0285540927585344</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>-0.365180092230567</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>-1.168624480923472</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>0.9996661921178854</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>0.03898844578789743</v>
+      </c>
+      <c r="BQ20" t="n">
+        <v>0.4524040314100904</v>
+      </c>
+      <c r="BR20" t="n">
+        <v>0.4352134572834266</v>
+      </c>
+      <c r="BS20" t="n">
+        <v>0.533772584780837</v>
+      </c>
+      <c r="BT20" t="n">
+        <v>-0.7382419495841687</v>
+      </c>
+      <c r="BU20" t="n">
+        <v>0.2313221579819047</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>02cHDDPH</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1.975049126842419</v>
+      </c>
+      <c r="C21" t="n">
+        <v>-1.687478256854456</v>
+      </c>
+      <c r="D21" t="n">
+        <v>-0.7348734619339229</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-0.2058317055638894</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-3.20872234484278</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-0.4049087770621833</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.5986077292491322</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.013893947543499</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.08401415933310287</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1.374147480057576</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.2710001888724387</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.3467859549675953</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.1761795948879429</v>
+      </c>
+      <c r="O21" t="n">
+        <v>-0.1726481535288946</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.03041006058334787</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.985495550007411</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.1438336073814824</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.259588742434079</v>
+      </c>
+      <c r="T21" t="n">
+        <v>-1.305492287674956</v>
+      </c>
+      <c r="U21" t="n">
+        <v>-1.262971413038242</v>
+      </c>
+      <c r="V21" t="n">
+        <v>-0.2295113152855294</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0.6354787698106731</v>
+      </c>
+      <c r="X21" t="n">
+        <v>-1.367847690989007</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0.9244714221846945</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-1.055274402850793</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.248883666688389</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>-1.919862768290876</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>4.064778754259944</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>-0.117767503997466</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>-1.000782541655909</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>-0.08902047358736738</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>-0.8998053351967024</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>-0.6986312199132862</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>0.8851144702860833</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>0.4119949819611857</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0.693590129529106</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>-1.537333464061514</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0.6707054634299314</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>-1.98897644107815</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>0.2474578550205551</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>0.8471066968956126</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>0.5755792449464106</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>2.144677060143751</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>-0.2416346881991166</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>0.2359134220178204</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>-0.01238992569299334</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>-0.2914388266414769</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>0.5415938208869441</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>0.4315209024175051</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>-1.454095041742103</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>0.6177162712222163</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>-1.904060440134701</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>0.6909218276118505</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>1.844419865445105</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>0.3343846226742828</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>-1.866496933226001</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>0.9286850838833044</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>-1.111061206948198</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>0.7545941749370901</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>0.4218795066470472</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>-0.4666919748470745</v>
+      </c>
+      <c r="BQ21" t="n">
+        <v>-0.6385426382961619</v>
+      </c>
+      <c r="BR21" t="n">
+        <v>-0.5118134969392623</v>
+      </c>
+      <c r="BS21" t="n">
+        <v>-0.3706262336648388</v>
+      </c>
+      <c r="BT21" t="n">
+        <v>-0.2045209062415419</v>
+      </c>
+      <c r="BU21" t="n">
+        <v>-0.4320742028417193</v>
       </c>
     </row>
   </sheetData>

--- a/data/spain/p6_deployment/data_preparation/df_selected_nan.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_selected_nan.xlsx
@@ -425,1374 +425,1705 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL11"/>
+  <dimension ref="A1:AI15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>id_coach_away</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>is_cup</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_30_matches_expected_points</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_180_matches_expected_points</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_30_matches_shots_on_goal</t>
+          <t>dif_mean_last_60_matches_shots_on_goal</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_180_matches_shots_on_goal</t>
+          <t>dif_mean_last_360_matches_shots_on_goal</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_180_matches_shots_on_goal_against</t>
+          <t>dif_mean_last_60_matches_goal_attempts</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_30_matches_goal_attempts</t>
+          <t>dif_mean_last_360_matches_goal_attempts</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_180_matches_goal_attempts</t>
+          <t>dif_mean_last_360_matches_goals</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_180_matches_goal_attempts_against</t>
+          <t>dif_mean_last_360_matches_points</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_180_matches_goals</t>
+          <t>dif_mean_last_60_matches_goal_ratio</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_180_matches_goals_against</t>
+          <t>dif_mean_last_360_matches_goal_ratio</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_30_matches_points</t>
+          <t>dif_mean_last_360_matches_PPS</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_180_matches_points</t>
+          <t>dif_mean_last_60_matches_attacks</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_180_matches_goal_ratio</t>
+          <t>dif_mean_last_360_matches_attacks</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_30_matches_PPS_against</t>
+          <t>dif_mean_last_60_matches_dangerous_attacks</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_180_matches_attacks_against</t>
+          <t>dif_mean_last_360_matches_dangerous_attacks</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_30_matches_dangerous_attacks</t>
+          <t>dif_mean_last_60_matches_dead_balls</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_180_matches_dangerous_attacks</t>
+          <t>dif_mean_last_360_matches_dead_balls</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_180_matches_dangerous_attacks_against</t>
+          <t>dif_mean_last_60_matches_ball_possession</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_180_matches_dead_balls_against</t>
+          <t>dif_mean_last_360_matches_ball_possession</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_30_matches_total_passes_against</t>
+          <t>dif_mean_last_360_matches_yellow_cards</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_180_matches_total_passes</t>
+          <t>dif_mean_last_60_matches_defensive_actions</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_30_matches_yellow_cards</t>
+          <t>dif_mean_last_360_matches_PPDA</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_180_matches_red_cards</t>
+          <t>dif_mean_last_60_matches_KGP</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_30_matches_defensive_actions</t>
+          <t>dif_mean_last_360_matches_KGP</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_30_matches_defensive_actions_against</t>
+          <t>dif_mean_last_360_matches_clean_sheet</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_180_matches_defensive_actions</t>
+          <t>dif_mean_hei_player_sub</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_180_matches_KGP</t>
+          <t>dif_mean_rat_player_sub</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_180_matches_clean_sheet</t>
+          <t>dif_mean_value_player_sub</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_180_matches_mean_rat_player_start_against</t>
+          <t>dif_mean_rep_player_sub</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_wage_player_sub</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_value_player_sub</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_sub</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_sub</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>QP8QvjOG</t>
+          <t>IsCnpo0d</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2997199947699858</v>
+        <v>0.8291903891555538</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.2054762389029784</v>
+        <v>-1.0471119207546</v>
       </c>
       <c r="D2" t="n">
-        <v>0.06406591879471901</v>
+        <v>-0.4241230630803175</v>
       </c>
       <c r="E2" t="n">
-        <v>-3.248206588616974</v>
+        <v>-0.4155225963195664</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.519119786809259</v>
+        <v>-1.061682926186582</v>
       </c>
       <c r="G2" t="n">
-        <v>-2.947495072961228</v>
+        <v>-0.7324677246361208</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5915499384886966</v>
+        <v>-0.5731369679032363</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5914445746988215</v>
+        <v>-0.547006859199812</v>
       </c>
       <c r="J2" t="n">
-        <v>-2.152530655505408</v>
+        <v>-0.9136044704323139</v>
       </c>
       <c r="K2" t="n">
-        <v>0.6318026034482938</v>
+        <v>-1.227327020599096</v>
       </c>
       <c r="L2" t="n">
-        <v>-4.681595475973127</v>
+        <v>-0.02993462232117578</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.004365854568032956</v>
+        <v>0.1438644661335698</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.9678350130102897</v>
+        <v>-0.3591305534922936</v>
       </c>
       <c r="O2" t="n">
-        <v>-2.400301098253995</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>2.8564211831959</v>
+        <v>0.8505634514651847</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.4313458867454203</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.205995240612058</v>
+        <v>-0.1156101866182074</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>-0.6392398903014666</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6710639657037082</v>
+        <v>1.314070651996652</v>
       </c>
       <c r="U2" t="n">
-        <v>1.346689021567283</v>
+        <v>-0.247952790924923</v>
       </c>
       <c r="V2" t="n">
-        <v>1.429860478126965</v>
+        <v>1.272431265342826</v>
       </c>
       <c r="W2" t="n">
-        <v>0.9941927727146774</v>
+        <v>-0.9812833261279628</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.9305455070642712</v>
+        <v>0.6143829776777732</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0.3042171102825281</v>
+        <v>-0.1177888548710433</v>
       </c>
       <c r="Z2" t="n">
-        <v>-1.224848814746656</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0.3364220620162695</v>
+        <v>0.5675830974870011</v>
       </c>
       <c r="AB2" t="n">
-        <v>-2.116206508521357</v>
+        <v>-0.6605052932068455</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.7561741281140487</v>
+        <v>-1.074547828625946</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.1419714315266913</v>
+        <v>-0.5853879400187174</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.7745872959866256</v>
+        <v>-0.5410823373239064</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.4660396791732371</v>
+        <v>-0.453251471603821</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.9367289768175286</v>
+        <v>-0.1936910313729533</v>
       </c>
       <c r="AH2" t="n">
-        <v>-0.5322065827972393</v>
+        <v>-1.03492896959581</v>
       </c>
       <c r="AI2" t="n">
-        <v>-2.21231221941525</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>-1.262241144776661</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>-1.521793601042682</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>-1.15969584103598</v>
+        <v>0.287995495398468</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>CMriQj9N</t>
+          <t>buKPeYL5</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.1165922361234562</v>
+        <v>0.7838864189088033</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.2054762389029784</v>
+        <v>-1.765247010304935</v>
       </c>
       <c r="D3" t="n">
-        <v>1.997865531972177</v>
+        <v>0.2499731415308259</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.8452019553188725</v>
+        <v>-0.4155225963195664</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.284418728381055</v>
+        <v>1.86617877526076</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.8083053392825625</v>
+        <v>1.793881307048784</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.7697008005363636</v>
+        <v>0.686966840730948</v>
       </c>
       <c r="I3" t="n">
-        <v>1.397892143037846</v>
+        <v>0.4464795544860428</v>
       </c>
       <c r="J3" t="n">
-        <v>0.198735414615501</v>
+        <v>1.914463286211645</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.590102553794962</v>
+        <v>1.271194396270169</v>
       </c>
       <c r="L3" t="n">
-        <v>-2.501057562763401</v>
+        <v>-1.06094491714966</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.2735107958613173</v>
+        <v>-0.6225340695408692</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.7979328200216904</v>
+        <v>-0.8794926807038973</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.428237061451633</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.4244729225248912</v>
+        <v>0.5470393518137588</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.375041694137222</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.559075073481412</v>
+        <v>0.4846644320826911</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.442771985970319</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.494207589530457</v>
+        <v>0.7284484441788532</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1602209649371187</v>
+        <v>1.778120703756835</v>
       </c>
       <c r="V3" t="n">
-        <v>2.618213598984815</v>
+        <v>1.019597059515015</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.3860997126397309</v>
+        <v>-1.750345870155601</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.8913716837058379</v>
+        <v>-1.498617258866374</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.2390926979956167</v>
+        <v>-0.6246714632143675</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.14134707625025</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.229854428345659</v>
+        <v>-0.9744038416317505</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.574959746775796</v>
+        <v>0.2405786309482036</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.550500420506269</v>
+        <v>0.3609825026572786</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.2750820900009757</v>
+        <v>1.168024434878308</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0.6330274592041</v>
+        <v>0.7874205300319551</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.4154099644229413</v>
+        <v>1.430245552985236</v>
       </c>
       <c r="AG3" t="n">
-        <v>-0.6766958967761431</v>
+        <v>0.4438686410415142</v>
       </c>
       <c r="AH3" t="n">
-        <v>-1.129387139785423</v>
+        <v>1.096336569617447</v>
       </c>
       <c r="AI3" t="n">
-        <v>-0.5356240493555842</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>-1.024915536619733</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>-0.3568199713331477</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>-1.078017607781065</v>
+        <v>0.4845363297986006</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>MXB9rYOi</t>
+          <t>vVwOqx6D</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1956419370466253</v>
+        <v>0.8291903891555538</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.2054762389029784</v>
+        <v>-1.0471119207546</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.654867070696355</v>
+        <v>-0.4241230630803175</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.189255394282217</v>
+        <v>-0.4155225963195664</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.6371904593605416</v>
+        <v>0.9270533238531219</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.9271492133758217</v>
+        <v>0.2331478521926095</v>
       </c>
       <c r="H4" t="n">
-        <v>2.156988288367517</v>
+        <v>1.073731376054312</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.715852284723894</v>
+        <v>-0.02911879302836013</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.1566885262167291</v>
+        <v>1.499721180706727</v>
       </c>
       <c r="K4" t="n">
-        <v>2.334301360297022</v>
+        <v>1.252717935372312</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.699743634459714</v>
+        <v>-0.6375902839769987</v>
       </c>
       <c r="M4" t="n">
-        <v>2.093108515510666</v>
+        <v>0.8889810454516309</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.118324048067293</v>
+        <v>-0.7179205005374437</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.249548819392375</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0.04250851113220764</v>
+        <v>-0.359788981128766</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.5569798171659135</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.4801858490654464</v>
+        <v>0.01140720895607278</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.186910285512822</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5874614095685935</v>
+        <v>0.05443861438574025</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.01360269597993368</v>
+        <v>0.8366367378266494</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.579882319867831</v>
+        <v>0.7197282647510689</v>
       </c>
       <c r="W4" t="n">
-        <v>0.497684684457696</v>
+        <v>0.5058845785140136</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.325081870888491</v>
+        <v>-0.4058585566536028</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.733194670760515</v>
+        <v>0.1754318974943095</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0.6129016015578012</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>-1.106235048922589</v>
+        <v>-1.529453425096228</v>
       </c>
       <c r="AB4" t="n">
-        <v>-0.9695889058120283</v>
+        <v>1.010530181628086</v>
       </c>
       <c r="AC4" t="n">
-        <v>-0.04167618224691903</v>
+        <v>-0.7586023703262179</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.439273835867958</v>
+        <v>1.83828250782615</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0.8238904768570798</v>
+        <v>2.17420450346322</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.780267804726381</v>
+        <v>3.084003553452368</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.06916502612262868</v>
+        <v>1.420991047488874</v>
       </c>
       <c r="AH4" t="n">
-        <v>-1.254925235487221</v>
+        <v>1.425435855274262</v>
       </c>
       <c r="AI4" t="n">
-        <v>-1.521442296314119</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>-1.484085681934656</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>-0.3212397933342881</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>-1.331599804175216</v>
+        <v>0.7934933484963721</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Ia5ItCg4</t>
+          <t>C2KEmK6l</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.513964001542525</v>
+        <v>0.7838864189088033</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.2054762389029784</v>
+        <v>-1.511272405463963</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.150800704891665</v>
+        <v>0.147144906929126</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.046704271967923</v>
+        <v>-0.4155225963195664</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.166348055829772</v>
+        <v>-0.2882854956155859</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1424456534635114</v>
+        <v>-0.5147399519296741</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4554248645861906</v>
+        <v>0.08810562474638517</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.542866483181575</v>
+        <v>-0.3943945262812207</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.01998701051202479</v>
+        <v>-0.9686877891830561</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8626498925125281</v>
+        <v>-0.8465066320932709</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.285817065678139</v>
+        <v>-0.2497293663278394</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3947111273495956</v>
+        <v>0.5936254151914515</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.8828839165159901</v>
+        <v>0.8474171713724731</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.7992544494030448</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.7595219542447956</v>
+        <v>-0.5073437028125565</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.690166020333</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.7981532032358465</v>
+        <v>-0.05097073330404141</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>0.4143082880529309</v>
       </c>
       <c r="T5" t="n">
-        <v>0.297660431262647</v>
+        <v>0.3181269076192577</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.07225000356280768</v>
+        <v>-0.03706038255656199</v>
       </c>
       <c r="V5" t="n">
-        <v>1.370918163332415</v>
+        <v>-0.7055626271631482</v>
       </c>
       <c r="W5" t="n">
-        <v>0.30570155699833</v>
+        <v>-1.04415646664966</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.935074263184094</v>
+        <v>0.1592752344221104</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.03256220614345577</v>
+        <v>0.4216206329016086</v>
       </c>
       <c r="Z5" t="n">
-        <v>-1.224848814746656</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.423150479483889</v>
+        <v>0.3095291501264595</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.9309690384048033</v>
+        <v>-0.07649169513038655</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.6535136685990711</v>
+        <v>-1.210476444408428</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.2082849823545699</v>
+        <v>0.3051377338843169</v>
       </c>
       <c r="AE5" t="n">
-        <v>-1.301048020989529</v>
+        <v>0.2642857562302454</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.02011026808263245</v>
+        <v>-0.5732892639746386</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.4209713938729296</v>
+        <v>0.151237002599305</v>
       </c>
       <c r="AH5" t="n">
-        <v>-1.163327246814735</v>
+        <v>-0.2324762210065059</v>
       </c>
       <c r="AI5" t="n">
-        <v>-1.753712962120515</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>-0.8646717886831302</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>-1.330569700875512</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>-2.690531488454759</v>
+        <v>0.2704778022056666</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>4duqSCvB</t>
+          <t>SCX7iT7M</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-1.515863901070859</v>
+        <v>0.7838864189088033</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.2054762389029784</v>
+        <v>1.79915520246319</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.5805339522644337</v>
+        <v>-0.3212948284786177</v>
       </c>
       <c r="E6" t="n">
-        <v>1.842904922607817</v>
+        <v>-0.4155225963195664</v>
       </c>
       <c r="F6" t="n">
-        <v>0.244738868088175</v>
+        <v>0.9270533238531219</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8555088980230665</v>
+        <v>0.3140785424299803</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5915499384886972</v>
+        <v>1.622687490706828</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1869915322416141</v>
+        <v>0.9173759603225083</v>
       </c>
       <c r="J6" t="n">
-        <v>1.401708752816897</v>
+        <v>-0.2598086025909912</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4298112255170886</v>
+        <v>-0.1365999455956196</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.156536161732898</v>
+        <v>-1.711029291034129</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.396494861257435</v>
+        <v>-1.11606270235341</v>
       </c>
       <c r="N6" t="n">
-        <v>1.070991302852903</v>
+        <v>-2.891700704916469</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2131570154486791</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.5536662263141001</v>
+        <v>0.9007986461881624</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.912497445470088</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.5173889257694453</v>
+        <v>-0.1621177886682386</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-0.2128037228723057</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5139907390121564</v>
+        <v>0.3543840479388678</v>
       </c>
       <c r="U6" t="n">
-        <v>0.9247542253460505</v>
+        <v>0.2642144865410967</v>
       </c>
       <c r="V6" t="n">
-        <v>0.4969240547121619</v>
+        <v>-0.3081623825298872</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.05509432046841019</v>
+        <v>-0.5382971417665228</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.378246345446365</v>
+        <v>0.339317858127647</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.2390926979956165</v>
+        <v>-1.546214983071868</v>
       </c>
       <c r="Z6" t="n">
-        <v>-1.020866410350371</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.1348920115998446</v>
+        <v>0.4795699618723664</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.3570123783371817</v>
+        <v>-0.3083727637005933</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.5787500730827291</v>
+        <v>0.4614344863140294</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0.8124394451041853</v>
+        <v>-0.05769693212096507</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.084739699672718</v>
+        <v>0.3469991862731468</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.01310954113289054</v>
+        <v>0.3008251786007478</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.7309808261048071</v>
+        <v>0.09452527798729449</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.4281273398997139</v>
+        <v>0.3722921299093562</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.2117022551216242</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.304316429181927</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>0.1236314230263143</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0.2036893991126418</v>
+        <v>-0.4976669233491389</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>UwPNKUWp</t>
+          <t>QP8QvjOG</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.579161381560614</v>
+        <v>0.7838864189088033</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.2054762389029784</v>
+        <v>0.2577920834283252</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5805339522644337</v>
+        <v>0.2499731415308259</v>
       </c>
       <c r="E7" t="n">
-        <v>0.31557146924038</v>
+        <v>-0.4155225963195664</v>
       </c>
       <c r="F7" t="n">
-        <v>1.303054061026634</v>
+        <v>-1.415236037304751</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.9865711504224519</v>
+        <v>-1.002256810594094</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4974506527313516</v>
+        <v>-0.8775580860287227</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01400573069929512</v>
+        <v>-0.6707559494622853</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.906467927236942</v>
+        <v>-2.325624820353418</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.1184510860104683</v>
+        <v>-2.509432742032982</v>
       </c>
       <c r="L7" t="n">
-        <v>0.524115589555231</v>
+        <v>0.4107228205253211</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2827916559059134</v>
+        <v>0.2574773634130141</v>
       </c>
       <c r="N7" t="n">
-        <v>0.05157814492130637</v>
+        <v>-1.784184731930369</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3229077107290946</v>
+        <v>-0.9633490247189468</v>
       </c>
       <c r="P7" t="n">
-        <v>1.174407469486118</v>
+        <v>-0.9201911133894347</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.7764057526673295</v>
+        <v>-2.054642297196725</v>
       </c>
       <c r="R7" t="n">
-        <v>1.354458151609419</v>
+        <v>-0.317066480744918</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-0.6643243707384761</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.408491807214614</v>
+        <v>-0.7402994975460764</v>
       </c>
       <c r="U7" t="n">
-        <v>1.02738701361608</v>
+        <v>-0.4211858406560775</v>
       </c>
       <c r="V7" t="n">
-        <v>0.9247311782209878</v>
+        <v>-0.6735187548213853</v>
       </c>
       <c r="W7" t="n">
-        <v>0.9743324491843981</v>
+        <v>-0.04073606068391965</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.4352764546040799</v>
+        <v>0.0317450426306885</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.7824025062737615</v>
+        <v>-0.8194820347309221</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.4886033821821381</v>
+        <v>1.043221880326451</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0.05363361784660105</v>
+        <v>1.268363238562182</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.9623832193009494</v>
+        <v>-1.585754816303071</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.0431302843089321</v>
+        <v>0.2970383777288947</v>
       </c>
       <c r="AD7" t="n">
-        <v>-1.035724006536469</v>
+        <v>-0.5336023429316848</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.3467329327246304</v>
+        <v>-2.038618546838299</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.2525232528159044</v>
+        <v>-1.086976088437986</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.5652946835489203</v>
+        <v>-1.500641373705581</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0.9647492234166632</v>
+        <v>-1.272465518644387</v>
       </c>
       <c r="AI7" t="n">
-        <v>-0.7301736869943863</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>-1.502205356720271</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>-0.04020729960343378</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>-0.5312453588660044</v>
+        <v>0.9460762655122389</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>jFGHcfig</t>
+          <t>CMriQj9N</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5194403388526357</v>
+        <v>0.8291903891555538</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.2054762389029784</v>
+        <v>1.79915520246319</v>
       </c>
       <c r="D8" t="n">
-        <v>1.353265660913024</v>
+        <v>-0.1613397968759735</v>
       </c>
       <c r="E8" t="n">
-        <v>2.837853572230033</v>
+        <v>-0.4155225963195664</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.9899621903400281</v>
+        <v>-0.03969346436062292</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.03671372063948528</v>
+        <v>-0.1923745191183454</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8156957368695158</v>
+        <v>0.6121091887328777</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7059489368685707</v>
+        <v>0.7592502723352776</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4833418033270246</v>
+        <v>-1.091130557776231</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9216634852056407</v>
+        <v>-0.7211559759109933</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7605149567693853</v>
+        <v>-1.603905234474341</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.9907886935936662</v>
+        <v>-0.7072802195939326</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3064314344042054</v>
+        <v>-1.08721905841306</v>
       </c>
       <c r="O8" t="n">
-        <v>1.336835849956769</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.1914381396951894</v>
+        <v>0.04279688709290465</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.2979604496035086</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.5615002986465205</v>
+        <v>-0.2782650201211757</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>0.2638014054308741</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.269713873941344</v>
+        <v>-0.4555922265420329</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6657286168550233</v>
+        <v>-0.8505025291202418</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.453758441974118</v>
+        <v>-1.198271574534725</v>
       </c>
       <c r="W8" t="n">
-        <v>1.297062706551437</v>
+        <v>0.3101181489345187</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2533979890113542</v>
+        <v>0.1517734584343795</v>
       </c>
       <c r="Y8" t="n">
-        <v>-2.341628891325571</v>
+        <v>-0.4513977057580634</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.222940038008764</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>-0.7606047282707721</v>
+        <v>0.8363140620447198</v>
       </c>
       <c r="AB8" t="n">
-        <v>-2.147620689417503</v>
+        <v>-0.6512418136127281</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.5361874291533831</v>
+        <v>-0.2591654082774553</v>
       </c>
       <c r="AD8" t="n">
-        <v>-2.380999005253369</v>
+        <v>-1.133520033597017</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.7882203686761242</v>
+        <v>-0.4916139427161348</v>
       </c>
       <c r="AF8" t="n">
-        <v>-0.5355511949491106</v>
+        <v>-1.010421986289763</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.6925807896608424</v>
+        <v>-0.3562955823546253</v>
       </c>
       <c r="AH8" t="n">
-        <v>-0.4188909887067181</v>
+        <v>-1.03224076969753</v>
       </c>
       <c r="AI8" t="n">
-        <v>-0.6337981914683791</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>-0.9768572619557848</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>-0.2369775566884024</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>-0.1246423744427934</v>
+        <v>-0.696442607085148</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>bXuieB8c</t>
+          <t>MXB9rYOi</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.382569494749822</v>
+        <v>0.7838864189088033</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.2054762389029784</v>
+        <v>1.816670692452222</v>
       </c>
       <c r="D9" t="n">
-        <v>1.568132284599408</v>
+        <v>0.147144906929126</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3970292534199764</v>
+        <v>-0.4155225963195664</v>
       </c>
       <c r="F9" t="n">
-        <v>1.038475262792019</v>
+        <v>-1.282653620635438</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7196873276307703</v>
+        <v>-0.5998638165938392</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5429338406663733</v>
+        <v>-1.708478023207304</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8356882880253099</v>
+        <v>0.1197862041359041</v>
       </c>
       <c r="J9" t="n">
-        <v>1.009180114864818</v>
+        <v>-0.4021235115341891</v>
       </c>
       <c r="K9" t="n">
-        <v>0.9801346735541477</v>
+        <v>-0.297345155406973</v>
       </c>
       <c r="L9" t="n">
-        <v>2.222004794702725</v>
+        <v>2.068622702716488</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2276556465468675</v>
+        <v>-0.1683504928848889</v>
       </c>
       <c r="N9" t="n">
-        <v>0.9010891098643032</v>
+        <v>2.147069442160786</v>
       </c>
       <c r="O9" t="n">
-        <v>1.173463742931162</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1040925222693921</v>
+        <v>0.3855534370673273</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.08099922250361552</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.056833537977428</v>
+        <v>0.5335727150977928</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>0.01295660106077945</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.196225743033402</v>
+        <v>0.1759607521555286</v>
       </c>
       <c r="U9" t="n">
-        <v>2.434922395605056</v>
+        <v>-0.6923332228439707</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.261838564157456</v>
+        <v>0.6931130328707882</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2891512873897638</v>
+        <v>-0.09284735679688547</v>
       </c>
       <c r="X9" t="n">
-        <v>0.5692523015157431</v>
+        <v>-0.260824220890809</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0.7116994664911364</v>
+        <v>3.426818010959438</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.651789305699166</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>-0.7763151973913091</v>
+        <v>0.4231279821762348</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.9623832193009494</v>
+        <v>-0.8999121034963715</v>
       </c>
       <c r="AC9" t="n">
-        <v>-0.7580676497318727</v>
+        <v>-0.6359868149433441</v>
       </c>
       <c r="AD9" t="n">
-        <v>-1.497593402031416</v>
+        <v>-1.259633524035783</v>
       </c>
       <c r="AE9" t="n">
-        <v>-1.396479529816019</v>
+        <v>-1.40118400714751</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.3214060485591281</v>
+        <v>-1.248095557229304</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.1409634292766007</v>
+        <v>-0.3213454118871061</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.4404935594784479</v>
+        <v>-1.497020081710214</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.4260384259090284</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>0.6406491116455646</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>0.281977083342038</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>0.9292645816705203</v>
+        <v>0.06286801359805984</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>nucZxUhT</t>
+          <t>Ia5ItCg4</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.2784914370264615</v>
+        <v>0.7838864189088033</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.2054762389029784</v>
+        <v>1.11605109289092</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.654867070696355</v>
+        <v>1.449635878550657</v>
       </c>
       <c r="E10" t="n">
-        <v>2.151280819859148</v>
+        <v>-0.4155225963195664</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5489975266156701</v>
+        <v>0.2088985668943401</v>
       </c>
       <c r="G10" t="n">
-        <v>2.184013633422714</v>
+        <v>-1.40262645830145</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.4293881157800988</v>
+        <v>-0.2861826352439666</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.672605834338314</v>
+        <v>-1.004599601245044</v>
       </c>
       <c r="J10" t="n">
-        <v>1.86454102741711</v>
+        <v>-0.4751922199482068</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2381255301333947</v>
+        <v>-0.3748903019025236</v>
       </c>
       <c r="L10" t="n">
-        <v>1.267788598916425</v>
+        <v>0.9337526363694273</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.4392404395148175</v>
+        <v>0.9787482726017029</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4581284340444916</v>
+        <v>1.658899906567989</v>
       </c>
       <c r="O10" t="n">
-        <v>0.5812398549633362</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.901664717552774</v>
+        <v>-0.5015002851128422</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.3293515062149316</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>-1.017237988270506</v>
+        <v>-0.4833020618832661</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>-1.211166044265282</v>
       </c>
       <c r="T10" t="n">
-        <v>2.509943955795364</v>
+        <v>-1.823516448986733</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3969284571001843</v>
+        <v>-0.2404209191974819</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.85280091233568</v>
+        <v>-0.9694598329774816</v>
       </c>
       <c r="W10" t="n">
-        <v>0.6664974344650696</v>
+        <v>2.249497908965507</v>
       </c>
       <c r="X10" t="n">
-        <v>1.270183926607709</v>
+        <v>-0.02826916527115715</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0.7116994664911368</v>
+        <v>-2.452013424505211</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.222940038008764</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>-0.08505455608767554</v>
+        <v>-0.0999387089939389</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.527838475431577</v>
+        <v>-0.1552245880731731</v>
       </c>
       <c r="AC10" t="n">
-        <v>-0.4221894071883042</v>
+        <v>1.043538078227876</v>
       </c>
       <c r="AD10" t="n">
-        <v>-1.416754890347506</v>
+        <v>-1.167615702639976</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.9381841682606082</v>
+        <v>-1.615489681763337</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.05954906531917537</v>
+        <v>-2.521773877940672</v>
       </c>
       <c r="AG10" t="n">
-        <v>-0.4647001203941162</v>
+        <v>-1.312803417736932</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.027577022646355</v>
+        <v>-0.8700395036086229</v>
       </c>
       <c r="AI10" t="n">
-        <v>4.750276359497913</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>2.513381416151073</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>3.603172618384886</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>3.497499407968039</v>
+        <v>-0.4361067655603104</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
+          <t>4duqSCvB</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.8291903891555538</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-0.8194105508971767</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-1.543808284298827</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-0.4155225963195664</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.302703504416177</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.184537925027971</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.4449270992705202</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.315422802239775</v>
+      </c>
+      <c r="J11" t="n">
+        <v>-0.1355770963337579</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.1600872250036015</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-0.09275367776188109</v>
+      </c>
+      <c r="M11" t="n">
+        <v>-0.6507708072241029</v>
+      </c>
+      <c r="N11" t="n">
+        <v>3.031673695137615</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>-0.06920195215162046</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.336865986580957</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.6952544689474366</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.197948052468238</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-0.1696213249595316</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.1163534526451783</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.4124473929468719</v>
+      </c>
+      <c r="X11" t="n">
+        <v>-0.1933082370012328</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>-0.6495475417245792</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.6437206083020884</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.4258482228305502</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.5315839648195317</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.4311332004985</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0.197910355512022</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0.1908763917444903</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0.115648603387186</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.32544481075491</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>-0.7517064265410524</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>UwPNKUWp</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.7838864189088033</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-1.765247010304935</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.6183541728835283</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-0.4155225963195664</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-0.1225574747789439</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-0.01990901256428396</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-0.04913340391674401</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-0.2874609738784509</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.1374871848754358</v>
+      </c>
+      <c r="K12" t="n">
+        <v>-0.06560927694585435</v>
+      </c>
+      <c r="L12" t="n">
+        <v>-0.2993131573341187</v>
+      </c>
+      <c r="M12" t="n">
+        <v>-0.2463609381070614</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.585725448272593</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>-0.1687692066820477</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.1371174014375723</v>
+      </c>
+      <c r="S12" t="n">
+        <v>-0.866672512930352</v>
+      </c>
+      <c r="T12" t="n">
+        <v>-0.5861261719517883</v>
+      </c>
+      <c r="U12" t="n">
+        <v>-0.7751838118458269</v>
+      </c>
+      <c r="V12" t="n">
+        <v>-0.2115739162919043</v>
+      </c>
+      <c r="W12" t="n">
+        <v>-0.793861488191858</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-0.7359367001137533</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>3.115946882236961</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-0.03689695891332823</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>-0.3849214538069025</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>-0.275763159962014</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>-0.9681275113052159</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>-0.6711161247747197</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>-0.4979518099990946</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>-0.04528907616219199</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>-1.515361104241144</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0.5679441029252824</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>bXuieB8c</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.8291903891555538</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1.807912947457706</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.4241230630803175</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-0.4155225963195664</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-0.592120200482763</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-0.4836411689996404</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-1.097140531889729</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-0.2352283526005532</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.6791273274018984</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.5978574892715371</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.68563688678214</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.726127722381367</v>
+      </c>
+      <c r="N13" t="n">
+        <v>-2.012908220465649</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.196399627936484</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.2523415671541613</v>
+      </c>
+      <c r="S13" t="n">
+        <v>-0.4920776050710108</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.8865109014531278</v>
+      </c>
+      <c r="U13" t="n">
+        <v>-0.6245463772969975</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.5671245331521892</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.6265625145561681</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-1.166038523410314</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.718389323736504</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-1.072512755493732</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.2423242318903089</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>-0.0546335668337009</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.44355609974584</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0.3956686799035093</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0.8709321964335354</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0.2711904846280223</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0.6536702139150038</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0.1359611176730467</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>nucZxUhT</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.7838864189088033</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1.133566582879953</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-0.3212948284786177</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-0.4155225963195664</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.120402681495871</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2.132728581537685</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.686966840730948</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.389921098955134</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.065746386730809</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1.618047957670844</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-0.5616530037724464</v>
+      </c>
+      <c r="M14" t="n">
+        <v>-0.7602523460887415</v>
+      </c>
+      <c r="N14" t="n">
+        <v>-1.784184731930369</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.255477925010098</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.587576036197024</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.6651530924230256</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.9096907759918249</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.409058989112202</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.750505596617739</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0.8058856932012646</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-0.185806461013502</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>-0.8194820347309221</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-0.7333927034021123</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.217454660873304</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0.6641327968422193</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>2.037913844610712</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>4.385448122519641</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>3.278047328556826</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>3.533578607290919</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>2.549279588681794</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>-0.4806240280379357</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
           <t>rPc4X7Gj</t>
         </is>
       </c>
-      <c r="B11" t="n">
-        <v>1.513964001542525</v>
-      </c>
-      <c r="C11" t="n">
-        <v>-0.2054762389029784</v>
-      </c>
-      <c r="D11" t="n">
-        <v>-0.1508007048916653</v>
-      </c>
-      <c r="E11" t="n">
-        <v>2.49456719604459</v>
-      </c>
-      <c r="F11" t="n">
-        <v>-0.1080328628913119</v>
-      </c>
-      <c r="G11" t="n">
-        <v>-0.3329298429095262</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-1.003058070083517</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1.397892143037846</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1.100965418266548</v>
-      </c>
-      <c r="K11" t="n">
-        <v>-0.3699097401697227</v>
-      </c>
-      <c r="L11" t="n">
-        <v>-0.3463758303427231</v>
-      </c>
-      <c r="M11" t="n">
-        <v>-1.118069059919555</v>
-      </c>
-      <c r="N11" t="n">
-        <v>-0.2032751445615927</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0.9090051446834602</v>
-      </c>
-      <c r="P11" t="n">
-        <v>-0.7890140633092589</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>-0.5266867526115541</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0.1546589279054567</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0.1956178332675957</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0.4115902839959029</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0.9386745215057203</v>
-      </c>
-      <c r="W11" t="n">
-        <v>-1.071280874434365</v>
-      </c>
-      <c r="X11" t="n">
-        <v>-0.4268820638844157</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>-2.613283795464643</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.446834464386475</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>-1.26333974012796</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>-0.0114563884795762</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>0.2674210708579592</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>-1.018195972695449</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>0.4644348923005336</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>0.3271600235418826</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>0.870590578349553</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>0.585919834097746</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>0.3429695009246306</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>0.3763271980342827</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>0.04448670404812114</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>1.290355803777208</v>
+      <c r="B15" t="n">
+        <v>0.8291903891555538</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-1.747731520315902</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.449635878550657</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-0.4155225963195664</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-0.03969346436062292</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.6909067667846969</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.210970404717441</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.5680074453437061</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.08627538052087606</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.08963405339813772</v>
+      </c>
+      <c r="L15" t="n">
+        <v>-0.7628888941055885</v>
+      </c>
+      <c r="M15" t="n">
+        <v>-0.09426754374869407</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.02050729460846057</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>-1.016408503593555</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>-0.4365260607191279</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.3290210545670986</v>
+      </c>
+      <c r="T15" t="n">
+        <v>-0.2967337636341088</v>
+      </c>
+      <c r="U15" t="n">
+        <v>-0.03706038255656199</v>
+      </c>
+      <c r="V15" t="n">
+        <v>-1.030622556078423</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.23941713092711</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.06175214658161093</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.5971994627102</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-0.9180187697068363</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>-0.02061673884840901</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0.0747684779432196</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.5896489251246105</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0.319024726838719</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.209370152304947</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0.03790527619021657</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0.386119375926899</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0.8787452298594599</v>
       </c>
     </row>
   </sheetData>
